--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -28330,7 +28330,7 @@
     <t>95635740.jpg</t>
   </si>
   <si>
-    <t>9701.png</t>
+    <t>9701.jpg</t>
   </si>
   <si>
     <t>9006-15.jpg</t>
@@ -28483,10 +28483,10 @@
     <t>816314.jpeg</t>
   </si>
   <si>
-    <t>816413.jpeg</t>
-  </si>
-  <si>
-    <t>816412.jpeg</t>
+    <t>816413.jpg</t>
+  </si>
+  <si>
+    <t>816412.jpg</t>
   </si>
   <si>
     <t>817208.jpg</t>
@@ -28510,13 +28510,13 @@
     <t>816118.jpg</t>
   </si>
   <si>
-    <t>817206.jpeg</t>
+    <t>817206.jpg</t>
   </si>
   <si>
     <t>817205.jpg</t>
   </si>
   <si>
-    <t>817204.jpeg</t>
+    <t>817204.jpg</t>
   </si>
   <si>
     <t>816507.jpg</t>
@@ -28966,7 +28966,7 @@
     <t>4489101.jpg</t>
   </si>
   <si>
-    <t>44076.jpeg</t>
+    <t>44076.jpg</t>
   </si>
   <si>
     <t>817207.jpeg</t>
@@ -29188,7 +29188,7 @@
     <t>9611.jpeg</t>
   </si>
   <si>
-    <t>9609.jpeg</t>
+    <t>9609.jpg</t>
   </si>
   <si>
     <t>71133802.jpeg</t>
@@ -29266,7 +29266,7 @@
     <t>714834.jpeg</t>
   </si>
   <si>
-    <t>9610.jpeg</t>
+    <t>9610.jpg</t>
   </si>
   <si>
     <t>715720.jpeg</t>
@@ -29545,7 +29545,7 @@
     <t>916831.jpeg</t>
   </si>
   <si>
-    <t>9607.jpeg</t>
+    <t>9607.jpg</t>
   </si>
   <si>
     <t>926250.jpeg</t>
@@ -29806,7 +29806,7 @@
     <t>22558.jpg</t>
   </si>
   <si>
-    <t>44160.jpeg</t>
+    <t>44160.jpg</t>
   </si>
   <si>
     <t>2268205.jpg</t>
@@ -29917,7 +29917,7 @@
     <t>926230.jpg</t>
   </si>
   <si>
-    <t>926231.jpeg</t>
+    <t>926231.jpg</t>
   </si>
   <si>
     <t>926232.jpg</t>
@@ -31510,7 +31510,7 @@
     <t>40487.jpg</t>
   </si>
   <si>
-    <t>40095.jpeg</t>
+    <t>40095.jpg</t>
   </si>
   <si>
     <t>4052301.jpg</t>
@@ -31591,7 +31591,7 @@
     <t>5486.jpg</t>
   </si>
   <si>
-    <t>5485.jpeg</t>
+    <t>5485.jpg</t>
   </si>
   <si>
     <t>542502.jpg</t>
@@ -33559,7 +33559,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\95635740.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9701.png</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9701.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9006-15.jpg</t>
@@ -33712,10 +33712,10 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816314.jpeg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816413.jpeg</t>
-  </si>
-  <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816412.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816413.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816412.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817208.jpg</t>
@@ -33739,13 +33739,13 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816118.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817206.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817206.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817205.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817204.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817204.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\816507.jpg</t>
@@ -34195,7 +34195,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\4489101.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\44076.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\44076.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\817207.jpeg</t>
@@ -34417,7 +34417,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9611.jpeg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9609.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9609.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\71133802.jpeg</t>
@@ -34495,7 +34495,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\714834.jpeg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9610.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9610.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\715720.jpeg</t>
@@ -34774,7 +34774,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\916831.jpeg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9607.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9607.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\926250.jpeg</t>
@@ -35035,7 +35035,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\22558.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\44160.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\44160.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\2268205.jpg</t>
@@ -35146,7 +35146,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\926230.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\926231.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\926231.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\926232.jpg</t>
@@ -36739,7 +36739,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\40487.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\40095.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\40095.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\4052301.jpg</t>
@@ -36820,7 +36820,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\5486.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\5485.jpeg</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\5485.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\542502.jpg</t>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -22678,7 +22678,7 @@
     <t>95634440.jpg</t>
   </si>
   <si>
-    <t>9701.png</t>
+    <t>9701.jpg</t>
   </si>
   <si>
     <t>9006-15.jpg</t>
@@ -28006,7 +28006,7 @@
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\95634440.jpg</t>
   </si>
   <si>
-    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9701.png</t>
+    <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9701.jpg</t>
   </si>
   <si>
     <t>C:\Users\ALAA-ORANGE\Desktop\catalog\images\9006-15.jpg</t>
@@ -32205,7 +32205,7 @@
         <v>6998</v>
       </c>
       <c r="F2">
-        <v>1872</v>
+        <v>1863</v>
       </c>
       <c r="G2" t="s">
         <v>7042</v>
@@ -32231,7 +32231,7 @@
         <v>6998</v>
       </c>
       <c r="F3">
-        <v>1403</v>
+        <v>1388</v>
       </c>
       <c r="G3" t="s">
         <v>7042</v>
@@ -32257,7 +32257,7 @@
         <v>6999</v>
       </c>
       <c r="F4">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
         <v>7043</v>
@@ -32691,7 +32691,7 @@
         <v>7000</v>
       </c>
       <c r="F23">
-        <v>1340</v>
+        <v>1326</v>
       </c>
       <c r="G23" t="s">
         <v>7042</v>
@@ -32717,7 +32717,7 @@
         <v>7001</v>
       </c>
       <c r="F24">
-        <v>1752</v>
+        <v>1730</v>
       </c>
       <c r="G24" t="s">
         <v>7042</v>
@@ -32743,7 +32743,7 @@
         <v>7001</v>
       </c>
       <c r="F25">
-        <v>1743</v>
+        <v>1717</v>
       </c>
       <c r="G25" t="s">
         <v>7042</v>
@@ -32769,7 +32769,7 @@
         <v>7001</v>
       </c>
       <c r="F26">
-        <v>1676</v>
+        <v>1654</v>
       </c>
       <c r="G26" t="s">
         <v>7042</v>
@@ -32795,7 +32795,7 @@
         <v>7001</v>
       </c>
       <c r="F27">
-        <v>1772</v>
+        <v>1754</v>
       </c>
       <c r="G27" t="s">
         <v>7042</v>
@@ -32821,7 +32821,7 @@
         <v>7001</v>
       </c>
       <c r="F28">
-        <v>1684</v>
+        <v>1666</v>
       </c>
       <c r="G28" t="s">
         <v>7042</v>
@@ -32847,7 +32847,7 @@
         <v>7001</v>
       </c>
       <c r="F29">
-        <v>1748</v>
+        <v>1722</v>
       </c>
       <c r="G29" t="s">
         <v>7042</v>
@@ -32873,7 +32873,7 @@
         <v>7001</v>
       </c>
       <c r="F30">
-        <v>1747</v>
+        <v>1729</v>
       </c>
       <c r="G30" t="s">
         <v>7042</v>
@@ -32899,7 +32899,7 @@
         <v>7000</v>
       </c>
       <c r="F31">
-        <v>1396</v>
+        <v>1382</v>
       </c>
       <c r="G31" t="s">
         <v>7042</v>
@@ -32925,7 +32925,7 @@
         <v>7000</v>
       </c>
       <c r="F32">
-        <v>1384</v>
+        <v>1370</v>
       </c>
       <c r="G32" t="s">
         <v>7042</v>
@@ -32951,7 +32951,7 @@
         <v>7000</v>
       </c>
       <c r="F33">
-        <v>1375</v>
+        <v>1357</v>
       </c>
       <c r="G33" t="s">
         <v>7042</v>
@@ -32977,7 +32977,7 @@
         <v>7000</v>
       </c>
       <c r="F34">
-        <v>1388</v>
+        <v>1370</v>
       </c>
       <c r="G34" t="s">
         <v>7042</v>
@@ -33003,7 +33003,7 @@
         <v>7000</v>
       </c>
       <c r="F35">
-        <v>1376</v>
+        <v>1358</v>
       </c>
       <c r="G35" t="s">
         <v>7042</v>
@@ -33029,7 +33029,7 @@
         <v>7002</v>
       </c>
       <c r="F36">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
         <v>7043</v>
@@ -33049,7 +33049,7 @@
         <v>7002</v>
       </c>
       <c r="F37">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
         <v>7043</v>
@@ -33069,7 +33069,7 @@
         <v>7002</v>
       </c>
       <c r="F38">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s">
         <v>7043</v>
@@ -33089,7 +33089,7 @@
         <v>7000</v>
       </c>
       <c r="F39">
-        <v>1387</v>
+        <v>1372</v>
       </c>
       <c r="G39" t="s">
         <v>7042</v>
@@ -33135,7 +33135,7 @@
         <v>7003</v>
       </c>
       <c r="F41">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G41" t="s">
         <v>7042</v>
@@ -33161,7 +33161,7 @@
         <v>7003</v>
       </c>
       <c r="F42">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G42" t="s">
         <v>7042</v>
@@ -33187,7 +33187,7 @@
         <v>7003</v>
       </c>
       <c r="F43">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G43" t="s">
         <v>7042</v>
@@ -33313,7 +33313,7 @@
         <v>7004</v>
       </c>
       <c r="F49">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G49" t="s">
         <v>7042</v>
@@ -33339,7 +33339,7 @@
         <v>7003</v>
       </c>
       <c r="F50">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G50" t="s">
         <v>7042</v>
@@ -33385,7 +33385,7 @@
         <v>7004</v>
       </c>
       <c r="F52">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G52" t="s">
         <v>7042</v>
@@ -33411,7 +33411,7 @@
         <v>7000</v>
       </c>
       <c r="F53">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G53" t="s">
         <v>7042</v>
@@ -33437,7 +33437,7 @@
         <v>7002</v>
       </c>
       <c r="F54">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G54" t="s">
         <v>7042</v>
@@ -33463,7 +33463,7 @@
         <v>7002</v>
       </c>
       <c r="F55">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="G55" t="s">
         <v>7042</v>
@@ -33489,7 +33489,7 @@
         <v>7002</v>
       </c>
       <c r="F56">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="G56" t="s">
         <v>7042</v>
@@ -33515,7 +33515,7 @@
         <v>6999</v>
       </c>
       <c r="F57">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="G57" t="s">
         <v>7042</v>
@@ -33541,7 +33541,7 @@
         <v>6999</v>
       </c>
       <c r="F58">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="G58" t="s">
         <v>7042</v>
@@ -33567,7 +33567,7 @@
         <v>6999</v>
       </c>
       <c r="F59">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="G59" t="s">
         <v>7042</v>
@@ -33593,7 +33593,7 @@
         <v>7000</v>
       </c>
       <c r="F60">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s">
         <v>7042</v>
@@ -33619,7 +33619,7 @@
         <v>7004</v>
       </c>
       <c r="F61">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="G61" t="s">
         <v>7042</v>
@@ -33645,7 +33645,7 @@
         <v>7000</v>
       </c>
       <c r="F62">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="G62" t="s">
         <v>7042</v>
@@ -33671,7 +33671,7 @@
         <v>7000</v>
       </c>
       <c r="F63">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s">
         <v>7042</v>
@@ -33697,7 +33697,7 @@
         <v>6999</v>
       </c>
       <c r="F64">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G64" t="s">
         <v>7042</v>
@@ -33749,7 +33749,7 @@
         <v>7006</v>
       </c>
       <c r="F66">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="G66" t="s">
         <v>7042</v>
@@ -33775,7 +33775,7 @@
         <v>7006</v>
       </c>
       <c r="F67">
-        <v>3237</v>
+        <v>3221</v>
       </c>
       <c r="G67" t="s">
         <v>7042</v>
@@ -33801,7 +33801,7 @@
         <v>7006</v>
       </c>
       <c r="F68">
-        <v>1767</v>
+        <v>1747</v>
       </c>
       <c r="G68" t="s">
         <v>7042</v>
@@ -33827,7 +33827,7 @@
         <v>7006</v>
       </c>
       <c r="F69">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="G69" t="s">
         <v>7042</v>
@@ -33853,7 +33853,7 @@
         <v>7006</v>
       </c>
       <c r="F70">
-        <v>1045</v>
+        <v>1025</v>
       </c>
       <c r="G70" t="s">
         <v>7042</v>
@@ -33879,7 +33879,7 @@
         <v>7006</v>
       </c>
       <c r="F71">
-        <v>1360</v>
+        <v>1336</v>
       </c>
       <c r="G71" t="s">
         <v>7042</v>
@@ -33905,7 +33905,7 @@
         <v>7007</v>
       </c>
       <c r="F72">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="G72" t="s">
         <v>7042</v>
@@ -33931,7 +33931,7 @@
         <v>7007</v>
       </c>
       <c r="F73">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="G73" t="s">
         <v>7042</v>
@@ -33957,7 +33957,7 @@
         <v>7007</v>
       </c>
       <c r="F74">
-        <v>1467</v>
+        <v>1427</v>
       </c>
       <c r="G74" t="s">
         <v>7042</v>
@@ -33983,7 +33983,7 @@
         <v>7007</v>
       </c>
       <c r="F75">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="G75" t="s">
         <v>7042</v>
@@ -34009,7 +34009,7 @@
         <v>7006</v>
       </c>
       <c r="F76">
-        <v>2581</v>
+        <v>2573</v>
       </c>
       <c r="G76" t="s">
         <v>7042</v>
@@ -34061,7 +34061,7 @@
         <v>7007</v>
       </c>
       <c r="F78">
-        <v>1758</v>
+        <v>1730</v>
       </c>
       <c r="G78" t="s">
         <v>7042</v>
@@ -34087,7 +34087,7 @@
         <v>7007</v>
       </c>
       <c r="F79">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="G79" t="s">
         <v>7042</v>
@@ -34113,7 +34113,7 @@
         <v>7007</v>
       </c>
       <c r="F80">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="G80" t="s">
         <v>7042</v>
@@ -34139,7 +34139,7 @@
         <v>7007</v>
       </c>
       <c r="F81">
-        <v>2401</v>
+        <v>2361</v>
       </c>
       <c r="G81" t="s">
         <v>7042</v>
@@ -34165,7 +34165,7 @@
         <v>7007</v>
       </c>
       <c r="F82">
-        <v>1402</v>
+        <v>1378</v>
       </c>
       <c r="G82" t="s">
         <v>7042</v>
@@ -34191,7 +34191,7 @@
         <v>7007</v>
       </c>
       <c r="F83">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="G83" t="s">
         <v>7042</v>
@@ -34243,7 +34243,7 @@
         <v>7006</v>
       </c>
       <c r="F85">
-        <v>1798</v>
+        <v>1782</v>
       </c>
       <c r="G85" t="s">
         <v>7042</v>
@@ -34269,7 +34269,7 @@
         <v>7006</v>
       </c>
       <c r="F86">
-        <v>1407</v>
+        <v>1395</v>
       </c>
       <c r="G86" t="s">
         <v>7042</v>
@@ -34295,7 +34295,7 @@
         <v>7006</v>
       </c>
       <c r="F87">
-        <v>1413</v>
+        <v>1405</v>
       </c>
       <c r="G87" t="s">
         <v>7042</v>
@@ -34321,7 +34321,7 @@
         <v>6999</v>
       </c>
       <c r="F88">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="G88" t="s">
         <v>7042</v>
@@ -34347,7 +34347,7 @@
         <v>6999</v>
       </c>
       <c r="F89">
-        <v>1804</v>
+        <v>1788</v>
       </c>
       <c r="G89" t="s">
         <v>7042</v>
@@ -34373,7 +34373,7 @@
         <v>6999</v>
       </c>
       <c r="F90">
-        <v>1860</v>
+        <v>1852</v>
       </c>
       <c r="G90" t="s">
         <v>7042</v>
@@ -34399,7 +34399,7 @@
         <v>6999</v>
       </c>
       <c r="F91">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="G91" t="s">
         <v>7042</v>
@@ -34425,7 +34425,7 @@
         <v>6999</v>
       </c>
       <c r="F92">
-        <v>1840</v>
+        <v>1833</v>
       </c>
       <c r="G92" t="s">
         <v>7042</v>
@@ -34451,7 +34451,7 @@
         <v>6999</v>
       </c>
       <c r="F93">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="G93" t="s">
         <v>7042</v>
@@ -34477,7 +34477,7 @@
         <v>6999</v>
       </c>
       <c r="F94">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="G94" t="s">
         <v>7042</v>
@@ -34503,7 +34503,7 @@
         <v>6999</v>
       </c>
       <c r="F95">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="G95" t="s">
         <v>7042</v>
@@ -34529,7 +34529,7 @@
         <v>6999</v>
       </c>
       <c r="F96">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="G96" t="s">
         <v>7042</v>
@@ -34555,7 +34555,7 @@
         <v>6999</v>
       </c>
       <c r="F97">
-        <v>1306</v>
+        <v>1292</v>
       </c>
       <c r="G97" t="s">
         <v>7042</v>
@@ -34581,7 +34581,7 @@
         <v>6999</v>
       </c>
       <c r="F98">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="G98" t="s">
         <v>7042</v>
@@ -34607,7 +34607,7 @@
         <v>6999</v>
       </c>
       <c r="F99">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="G99" t="s">
         <v>7042</v>
@@ -34917,7 +34917,7 @@
         <v>6999</v>
       </c>
       <c r="F113">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G113" t="s">
         <v>7043</v>
@@ -34957,7 +34957,7 @@
         <v>6999</v>
       </c>
       <c r="F115">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G115" t="s">
         <v>7043</v>
@@ -34997,7 +34997,7 @@
         <v>6999</v>
       </c>
       <c r="F117">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G117" t="s">
         <v>7043</v>
@@ -35057,7 +35057,7 @@
         <v>6999</v>
       </c>
       <c r="F120">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G120" t="s">
         <v>7043</v>
@@ -35097,7 +35097,7 @@
         <v>7000</v>
       </c>
       <c r="F122">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G122" t="s">
         <v>7043</v>
@@ -35137,7 +35137,7 @@
         <v>7000</v>
       </c>
       <c r="F124">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G124" t="s">
         <v>7043</v>
@@ -35157,7 +35157,7 @@
         <v>7000</v>
       </c>
       <c r="F125">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G125" t="s">
         <v>7043</v>
@@ -35217,7 +35217,7 @@
         <v>7000</v>
       </c>
       <c r="F128">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G128" t="s">
         <v>7043</v>
@@ -35533,7 +35533,7 @@
         <v>7009</v>
       </c>
       <c r="F142">
-        <v>836</v>
+        <v>812</v>
       </c>
       <c r="G142" t="s">
         <v>7042</v>
@@ -35559,7 +35559,7 @@
         <v>7000</v>
       </c>
       <c r="F143">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G143" t="s">
         <v>7042</v>
@@ -35585,7 +35585,7 @@
         <v>7010</v>
       </c>
       <c r="F144">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="G144" t="s">
         <v>7042</v>
@@ -35689,7 +35689,7 @@
         <v>7010</v>
       </c>
       <c r="F148">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="G148" t="s">
         <v>7042</v>
@@ -35715,7 +35715,7 @@
         <v>7010</v>
       </c>
       <c r="F149">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="G149" t="s">
         <v>7042</v>
@@ -35767,7 +35767,7 @@
         <v>7010</v>
       </c>
       <c r="F151">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="G151" t="s">
         <v>7042</v>
@@ -35819,7 +35819,7 @@
         <v>7010</v>
       </c>
       <c r="F153">
-        <v>1722</v>
+        <v>1708</v>
       </c>
       <c r="G153" t="s">
         <v>7042</v>
@@ -36391,7 +36391,7 @@
         <v>7001</v>
       </c>
       <c r="F175">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G175" t="s">
         <v>7042</v>
@@ -36417,7 +36417,7 @@
         <v>7000</v>
       </c>
       <c r="F176">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G176" t="s">
         <v>7042</v>
@@ -36443,7 +36443,7 @@
         <v>7001</v>
       </c>
       <c r="F177">
-        <v>1003</v>
+        <v>983</v>
       </c>
       <c r="G177" t="s">
         <v>7042</v>
@@ -36469,7 +36469,7 @@
         <v>7001</v>
       </c>
       <c r="F178">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="G178" t="s">
         <v>7042</v>
@@ -36495,7 +36495,7 @@
         <v>7000</v>
       </c>
       <c r="F179">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G179" t="s">
         <v>7042</v>
@@ -36521,7 +36521,7 @@
         <v>7001</v>
       </c>
       <c r="F180">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="G180" t="s">
         <v>7042</v>
@@ -36547,7 +36547,7 @@
         <v>7001</v>
       </c>
       <c r="F181">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="G181" t="s">
         <v>7042</v>
@@ -36625,7 +36625,7 @@
         <v>7000</v>
       </c>
       <c r="F184">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="G184" t="s">
         <v>7042</v>
@@ -36651,7 +36651,7 @@
         <v>7009</v>
       </c>
       <c r="F185">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G185" t="s">
         <v>7042</v>
@@ -36755,7 +36755,7 @@
         <v>7009</v>
       </c>
       <c r="F189">
-        <v>1338</v>
+        <v>1320</v>
       </c>
       <c r="G189" t="s">
         <v>7042</v>
@@ -36833,7 +36833,7 @@
         <v>7009</v>
       </c>
       <c r="F192">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="G192" t="s">
         <v>7042</v>
@@ -36885,7 +36885,7 @@
         <v>7009</v>
       </c>
       <c r="F194">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="G194" t="s">
         <v>7043</v>
@@ -36905,7 +36905,7 @@
         <v>7008</v>
       </c>
       <c r="F195">
-        <v>1397</v>
+        <v>1347</v>
       </c>
       <c r="G195" t="s">
         <v>7042</v>
@@ -36931,7 +36931,7 @@
         <v>7008</v>
       </c>
       <c r="F196">
-        <v>1268</v>
+        <v>1238</v>
       </c>
       <c r="G196" t="s">
         <v>7042</v>
@@ -37017,7 +37017,7 @@
         <v>7008</v>
       </c>
       <c r="F200">
-        <v>1223</v>
+        <v>1183</v>
       </c>
       <c r="G200" t="s">
         <v>7042</v>
@@ -37063,7 +37063,7 @@
         <v>7008</v>
       </c>
       <c r="F202">
-        <v>2466</v>
+        <v>2456</v>
       </c>
       <c r="G202" t="s">
         <v>7042</v>
@@ -37089,7 +37089,7 @@
         <v>7008</v>
       </c>
       <c r="F203">
-        <v>3592</v>
+        <v>3552</v>
       </c>
       <c r="G203" t="s">
         <v>7042</v>
@@ -37115,7 +37115,7 @@
         <v>7008</v>
       </c>
       <c r="F204">
-        <v>1708</v>
+        <v>1628</v>
       </c>
       <c r="G204" t="s">
         <v>7042</v>
@@ -37141,7 +37141,7 @@
         <v>7008</v>
       </c>
       <c r="F205">
-        <v>1517</v>
+        <v>1457</v>
       </c>
       <c r="G205" t="s">
         <v>7042</v>
@@ -37193,7 +37193,7 @@
         <v>7000</v>
       </c>
       <c r="F207">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="G207" t="s">
         <v>7042</v>
@@ -37375,7 +37375,7 @@
         <v>7013</v>
       </c>
       <c r="F214">
-        <v>2328</v>
+        <v>2324</v>
       </c>
       <c r="G214" t="s">
         <v>7042</v>
@@ -37453,7 +37453,7 @@
         <v>7012</v>
       </c>
       <c r="F217">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="G217" t="s">
         <v>7042</v>
@@ -37505,7 +37505,7 @@
         <v>7012</v>
       </c>
       <c r="F219">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="G219" t="s">
         <v>7042</v>
@@ -37531,7 +37531,7 @@
         <v>7012</v>
       </c>
       <c r="F220">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="G220" t="s">
         <v>7042</v>
@@ -37609,7 +37609,7 @@
         <v>7014</v>
       </c>
       <c r="F223">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G223" t="s">
         <v>7043</v>
@@ -37629,7 +37629,7 @@
         <v>7000</v>
       </c>
       <c r="F224">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G224" t="s">
         <v>7042</v>
@@ -37655,7 +37655,7 @@
         <v>7000</v>
       </c>
       <c r="F225">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G225" t="s">
         <v>7042</v>
@@ -37681,7 +37681,7 @@
         <v>7000</v>
       </c>
       <c r="F226">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G226" t="s">
         <v>7042</v>
@@ -37707,7 +37707,7 @@
         <v>7000</v>
       </c>
       <c r="F227">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G227" t="s">
         <v>7042</v>
@@ -37733,7 +37733,7 @@
         <v>7000</v>
       </c>
       <c r="F228">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="G228" t="s">
         <v>7042</v>
@@ -37759,7 +37759,7 @@
         <v>7000</v>
       </c>
       <c r="F229">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G229" t="s">
         <v>7042</v>
@@ -37785,7 +37785,7 @@
         <v>7000</v>
       </c>
       <c r="F230">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="G230" t="s">
         <v>7042</v>
@@ -37831,7 +37831,7 @@
         <v>7008</v>
       </c>
       <c r="F232">
-        <v>3672</v>
+        <v>3632</v>
       </c>
       <c r="G232" t="s">
         <v>7042</v>
@@ -37877,7 +37877,7 @@
         <v>7008</v>
       </c>
       <c r="F234">
-        <v>3250</v>
+        <v>3240</v>
       </c>
       <c r="G234" t="s">
         <v>7042</v>
@@ -37903,7 +37903,7 @@
         <v>7008</v>
       </c>
       <c r="F235">
-        <v>1646</v>
+        <v>1636</v>
       </c>
       <c r="G235" t="s">
         <v>7042</v>
@@ -37929,7 +37929,7 @@
         <v>7008</v>
       </c>
       <c r="F236">
-        <v>3835</v>
+        <v>3815</v>
       </c>
       <c r="G236" t="s">
         <v>7042</v>
@@ -37955,7 +37955,7 @@
         <v>7008</v>
       </c>
       <c r="F237">
-        <v>4044</v>
+        <v>4014</v>
       </c>
       <c r="G237" t="s">
         <v>7042</v>
@@ -37981,7 +37981,7 @@
         <v>7008</v>
       </c>
       <c r="F238">
-        <v>2860</v>
+        <v>2830</v>
       </c>
       <c r="G238" t="s">
         <v>7042</v>
@@ -38007,7 +38007,7 @@
         <v>7008</v>
       </c>
       <c r="F239">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="G239" t="s">
         <v>7043</v>
@@ -38127,7 +38127,7 @@
         <v>7009</v>
       </c>
       <c r="F245">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="G245" t="s">
         <v>7043</v>
@@ -38167,7 +38167,7 @@
         <v>6999</v>
       </c>
       <c r="F247">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G247" t="s">
         <v>7043</v>
@@ -38207,7 +38207,7 @@
         <v>7009</v>
       </c>
       <c r="F249">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="G249" t="s">
         <v>7043</v>
@@ -38227,7 +38227,7 @@
         <v>6999</v>
       </c>
       <c r="F250">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G250" t="s">
         <v>7043</v>
@@ -38247,7 +38247,7 @@
         <v>7009</v>
       </c>
       <c r="F251">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G251" t="s">
         <v>7043</v>
@@ -38267,7 +38267,7 @@
         <v>7009</v>
       </c>
       <c r="F252">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G252" t="s">
         <v>7043</v>
@@ -38287,7 +38287,7 @@
         <v>7009</v>
       </c>
       <c r="F253">
-        <v>1842</v>
+        <v>1830</v>
       </c>
       <c r="G253" t="s">
         <v>7043</v>
@@ -38307,7 +38307,7 @@
         <v>7009</v>
       </c>
       <c r="F254">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="G254" t="s">
         <v>7043</v>
@@ -38327,7 +38327,7 @@
         <v>6999</v>
       </c>
       <c r="F255">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G255" t="s">
         <v>7042</v>
@@ -38353,7 +38353,7 @@
         <v>6999</v>
       </c>
       <c r="F256">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G256" t="s">
         <v>7042</v>
@@ -38425,7 +38425,7 @@
         <v>6999</v>
       </c>
       <c r="F259">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G259" t="s">
         <v>7042</v>
@@ -38555,7 +38555,7 @@
         <v>7008</v>
       </c>
       <c r="F264">
-        <v>1734</v>
+        <v>1704</v>
       </c>
       <c r="G264" t="s">
         <v>7042</v>
@@ -38607,7 +38607,7 @@
         <v>7008</v>
       </c>
       <c r="F266">
-        <v>3039</v>
+        <v>2999</v>
       </c>
       <c r="G266" t="s">
         <v>7042</v>
@@ -38737,7 +38737,7 @@
         <v>7008</v>
       </c>
       <c r="F271">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="G271" t="s">
         <v>7042</v>
@@ -38893,7 +38893,7 @@
         <v>7012</v>
       </c>
       <c r="F277">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="G277" t="s">
         <v>7042</v>
@@ -38919,7 +38919,7 @@
         <v>7012</v>
       </c>
       <c r="F278">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="G278" t="s">
         <v>7042</v>
@@ -38945,7 +38945,7 @@
         <v>7012</v>
       </c>
       <c r="F279">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="G279" t="s">
         <v>7042</v>
@@ -38997,7 +38997,7 @@
         <v>6999</v>
       </c>
       <c r="F281">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G281" t="s">
         <v>7042</v>
@@ -39023,7 +39023,7 @@
         <v>7008</v>
       </c>
       <c r="F282">
-        <v>2519</v>
+        <v>2488</v>
       </c>
       <c r="G282" t="s">
         <v>7042</v>
@@ -39049,7 +39049,7 @@
         <v>7008</v>
       </c>
       <c r="F283">
-        <v>726</v>
+        <v>686</v>
       </c>
       <c r="G283" t="s">
         <v>7042</v>
@@ -39101,7 +39101,7 @@
         <v>6999</v>
       </c>
       <c r="F285">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="G285" t="s">
         <v>7042</v>
@@ -39127,7 +39127,7 @@
         <v>6999</v>
       </c>
       <c r="F286">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="G286" t="s">
         <v>7042</v>
@@ -39153,7 +39153,7 @@
         <v>6999</v>
       </c>
       <c r="F287">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="G287" t="s">
         <v>7043</v>
@@ -39173,7 +39173,7 @@
         <v>6999</v>
       </c>
       <c r="F288">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="G288" t="s">
         <v>7042</v>
@@ -39225,7 +39225,7 @@
         <v>7000</v>
       </c>
       <c r="F290">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G290" t="s">
         <v>7042</v>
@@ -39277,7 +39277,7 @@
         <v>7000</v>
       </c>
       <c r="F292">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G292" t="s">
         <v>7042</v>
@@ -39303,7 +39303,7 @@
         <v>7008</v>
       </c>
       <c r="F293">
-        <v>1053</v>
+        <v>1023</v>
       </c>
       <c r="G293" t="s">
         <v>7042</v>
@@ -39329,7 +39329,7 @@
         <v>7000</v>
       </c>
       <c r="F294">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G294" t="s">
         <v>7042</v>
@@ -39355,7 +39355,7 @@
         <v>7008</v>
       </c>
       <c r="F295">
-        <v>1540</v>
+        <v>1529</v>
       </c>
       <c r="G295" t="s">
         <v>7042</v>
@@ -39381,7 +39381,7 @@
         <v>7008</v>
       </c>
       <c r="F296">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="G296" t="s">
         <v>7042</v>
@@ -39407,7 +39407,7 @@
         <v>7008</v>
       </c>
       <c r="F297">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G297" t="s">
         <v>7042</v>
@@ -39433,7 +39433,7 @@
         <v>7008</v>
       </c>
       <c r="F298">
-        <v>668</v>
+        <v>628</v>
       </c>
       <c r="G298" t="s">
         <v>7042</v>
@@ -39459,7 +39459,7 @@
         <v>7008</v>
       </c>
       <c r="F299">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G299" t="s">
         <v>7042</v>
@@ -39485,7 +39485,7 @@
         <v>7008</v>
       </c>
       <c r="F300">
-        <v>689</v>
+        <v>649</v>
       </c>
       <c r="G300" t="s">
         <v>7042</v>
@@ -39511,7 +39511,7 @@
         <v>7008</v>
       </c>
       <c r="F301">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="G301" t="s">
         <v>7043</v>
@@ -39531,7 +39531,7 @@
         <v>7015</v>
       </c>
       <c r="F302">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="G302" t="s">
         <v>7042</v>
@@ -39635,7 +39635,7 @@
         <v>7000</v>
       </c>
       <c r="F306">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G306" t="s">
         <v>7042</v>
@@ -39661,7 +39661,7 @@
         <v>7000</v>
       </c>
       <c r="F307">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G307" t="s">
         <v>7042</v>
@@ -39765,7 +39765,7 @@
         <v>6999</v>
       </c>
       <c r="F311">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G311" t="s">
         <v>7042</v>
@@ -39791,7 +39791,7 @@
         <v>7010</v>
       </c>
       <c r="F312">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="G312" t="s">
         <v>7042</v>
@@ -39817,7 +39817,7 @@
         <v>7010</v>
       </c>
       <c r="F313">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="G313" t="s">
         <v>7042</v>
@@ -40211,7 +40211,7 @@
         <v>7010</v>
       </c>
       <c r="F330">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="G330" t="s">
         <v>7042</v>
@@ -40237,7 +40237,7 @@
         <v>7010</v>
       </c>
       <c r="F331">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="G331" t="s">
         <v>7042</v>
@@ -40263,7 +40263,7 @@
         <v>7010</v>
       </c>
       <c r="F332">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="G332" t="s">
         <v>7042</v>
@@ -40289,7 +40289,7 @@
         <v>7010</v>
       </c>
       <c r="F333">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="G333" t="s">
         <v>7042</v>
@@ -40315,7 +40315,7 @@
         <v>7010</v>
       </c>
       <c r="F334">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="G334" t="s">
         <v>7042</v>
@@ -40367,7 +40367,7 @@
         <v>7019</v>
       </c>
       <c r="F336">
-        <v>4005</v>
+        <v>3999</v>
       </c>
       <c r="G336" t="s">
         <v>7042</v>
@@ -40393,7 +40393,7 @@
         <v>7019</v>
       </c>
       <c r="F337">
-        <v>4244</v>
+        <v>4226</v>
       </c>
       <c r="G337" t="s">
         <v>7042</v>
@@ -40419,7 +40419,7 @@
         <v>7020</v>
       </c>
       <c r="F338">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="G338" t="s">
         <v>7042</v>
@@ -40445,7 +40445,7 @@
         <v>7021</v>
       </c>
       <c r="F339">
-        <v>3225</v>
+        <v>3219</v>
       </c>
       <c r="G339" t="s">
         <v>7042</v>
@@ -40577,7 +40577,7 @@
         <v>7022</v>
       </c>
       <c r="F345">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="G345" t="s">
         <v>7043</v>
@@ -41067,7 +41067,7 @@
         <v>7023</v>
       </c>
       <c r="F368">
-        <v>1692</v>
+        <v>1680</v>
       </c>
       <c r="G368" t="s">
         <v>7043</v>
@@ -41283,7 +41283,7 @@
         <v>7023</v>
       </c>
       <c r="F377">
-        <v>1741</v>
+        <v>1729</v>
       </c>
       <c r="G377" t="s">
         <v>7043</v>
@@ -41381,7 +41381,7 @@
         <v>7007</v>
       </c>
       <c r="F381">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="G381" t="s">
         <v>7042</v>
@@ -41493,7 +41493,7 @@
         <v>7023</v>
       </c>
       <c r="F386">
-        <v>1512</v>
+        <v>1500</v>
       </c>
       <c r="G386" t="s">
         <v>7042</v>
@@ -41519,7 +41519,7 @@
         <v>6999</v>
       </c>
       <c r="F387">
-        <v>444</v>
+        <v>592</v>
       </c>
       <c r="G387" t="s">
         <v>7042</v>
@@ -41565,7 +41565,7 @@
         <v>7023</v>
       </c>
       <c r="F389">
-        <v>1368</v>
+        <v>1356</v>
       </c>
       <c r="G389" t="s">
         <v>7042</v>
@@ -41617,7 +41617,7 @@
         <v>6999</v>
       </c>
       <c r="F391">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G391" t="s">
         <v>7042</v>
@@ -41643,7 +41643,7 @@
         <v>6999</v>
       </c>
       <c r="F392">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G392" t="s">
         <v>7042</v>
@@ -41669,7 +41669,7 @@
         <v>6999</v>
       </c>
       <c r="F393">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G393" t="s">
         <v>7042</v>
@@ -45233,7 +45233,7 @@
         <v>7004</v>
       </c>
       <c r="F531">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G531" t="s">
         <v>7042</v>
@@ -45463,7 +45463,7 @@
         <v>7022</v>
       </c>
       <c r="F541">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="G541" t="s">
         <v>7042</v>
@@ -45489,7 +45489,7 @@
         <v>7022</v>
       </c>
       <c r="F542">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="G542" t="s">
         <v>7042</v>
@@ -45593,7 +45593,7 @@
         <v>7022</v>
       </c>
       <c r="F546">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G546" t="s">
         <v>7042</v>
@@ -45671,7 +45671,7 @@
         <v>7022</v>
       </c>
       <c r="F549">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="G549" t="s">
         <v>7042</v>
@@ -45775,7 +45775,7 @@
         <v>7022</v>
       </c>
       <c r="F553">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G553" t="s">
         <v>7042</v>
@@ -45801,7 +45801,7 @@
         <v>7022</v>
       </c>
       <c r="F554">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G554" t="s">
         <v>7042</v>
@@ -46081,7 +46081,7 @@
         <v>7024</v>
       </c>
       <c r="F565">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G565" t="s">
         <v>7042</v>
@@ -48551,7 +48551,7 @@
         <v>7022</v>
       </c>
       <c r="F663">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="G663" t="s">
         <v>7042</v>
@@ -48881,7 +48881,7 @@
         <v>7026</v>
       </c>
       <c r="F678">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="G678" t="s">
         <v>7042</v>
@@ -48933,7 +48933,7 @@
         <v>7026</v>
       </c>
       <c r="F680">
-        <v>1066</v>
+        <v>1050</v>
       </c>
       <c r="G680" t="s">
         <v>7042</v>
@@ -49037,7 +49037,7 @@
         <v>7026</v>
       </c>
       <c r="F684">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="G684" t="s">
         <v>7042</v>
@@ -49687,7 +49687,7 @@
         <v>7013</v>
       </c>
       <c r="F709">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="G709" t="s">
         <v>7042</v>
@@ -49843,7 +49843,7 @@
         <v>7013</v>
       </c>
       <c r="F715">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G715" t="s">
         <v>7042</v>
@@ -49941,7 +49941,7 @@
         <v>7013</v>
       </c>
       <c r="F719">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="G719" t="s">
         <v>7042</v>
@@ -49967,7 +49967,7 @@
         <v>7013</v>
       </c>
       <c r="F720">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="G720" t="s">
         <v>7042</v>
@@ -50097,7 +50097,7 @@
         <v>7013</v>
       </c>
       <c r="F725">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="G725" t="s">
         <v>7042</v>
@@ -50253,7 +50253,7 @@
         <v>7013</v>
       </c>
       <c r="F731">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="G731" t="s">
         <v>7042</v>
@@ -50279,7 +50279,7 @@
         <v>7013</v>
       </c>
       <c r="F732">
-        <v>1843</v>
+        <v>1837</v>
       </c>
       <c r="G732" t="s">
         <v>7042</v>
@@ -50305,7 +50305,7 @@
         <v>7013</v>
       </c>
       <c r="F733">
-        <v>2941</v>
+        <v>2935</v>
       </c>
       <c r="G733" t="s">
         <v>7042</v>
@@ -50865,7 +50865,7 @@
         <v>7013</v>
       </c>
       <c r="F755">
-        <v>3752</v>
+        <v>3746</v>
       </c>
       <c r="G755" t="s">
         <v>7042</v>
@@ -50891,7 +50891,7 @@
         <v>7013</v>
       </c>
       <c r="F756">
-        <v>1686</v>
+        <v>1680</v>
       </c>
       <c r="G756" t="s">
         <v>7042</v>
@@ -50943,7 +50943,7 @@
         <v>7013</v>
       </c>
       <c r="F758">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G758" t="s">
         <v>7042</v>
@@ -51087,7 +51087,7 @@
         <v>7030</v>
       </c>
       <c r="F764">
-        <v>1347</v>
+        <v>1335</v>
       </c>
       <c r="G764" t="s">
         <v>7042</v>
@@ -51113,7 +51113,7 @@
         <v>7030</v>
       </c>
       <c r="F765">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="G765" t="s">
         <v>7042</v>
@@ -51139,7 +51139,7 @@
         <v>7030</v>
       </c>
       <c r="F766">
-        <v>2636</v>
+        <v>2624</v>
       </c>
       <c r="G766" t="s">
         <v>7042</v>
@@ -51165,7 +51165,7 @@
         <v>7030</v>
       </c>
       <c r="F767">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="G767" t="s">
         <v>7042</v>
@@ -51269,7 +51269,7 @@
         <v>7030</v>
       </c>
       <c r="F771">
-        <v>1689</v>
+        <v>1677</v>
       </c>
       <c r="G771" t="s">
         <v>7042</v>
@@ -52623,7 +52623,7 @@
         <v>6998</v>
       </c>
       <c r="F824">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G824" t="s">
         <v>7042</v>
@@ -53801,7 +53801,7 @@
         <v>7005</v>
       </c>
       <c r="F879">
-        <v>7440</v>
+        <v>7439</v>
       </c>
       <c r="G879" t="s">
         <v>7042</v>
@@ -54259,7 +54259,7 @@
         <v>7030</v>
       </c>
       <c r="F901">
-        <v>958</v>
+        <v>928</v>
       </c>
       <c r="G901" t="s">
         <v>7042</v>
@@ -54285,7 +54285,7 @@
         <v>7005</v>
       </c>
       <c r="F902">
-        <v>7440</v>
+        <v>7430</v>
       </c>
       <c r="G902" t="s">
         <v>7042</v>
@@ -54371,7 +54371,7 @@
         <v>7030</v>
       </c>
       <c r="F906">
-        <v>1960</v>
+        <v>1948</v>
       </c>
       <c r="G906" t="s">
         <v>7042</v>
@@ -54397,7 +54397,7 @@
         <v>7030</v>
       </c>
       <c r="F907">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="G907" t="s">
         <v>7042</v>
@@ -54423,7 +54423,7 @@
         <v>7030</v>
       </c>
       <c r="F908">
-        <v>1445</v>
+        <v>1421</v>
       </c>
       <c r="G908" t="s">
         <v>7042</v>
@@ -54449,7 +54449,7 @@
         <v>7030</v>
       </c>
       <c r="F909">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="G909" t="s">
         <v>7042</v>
@@ -54495,7 +54495,7 @@
         <v>7030</v>
       </c>
       <c r="F911">
-        <v>1005</v>
+        <v>981</v>
       </c>
       <c r="G911" t="s">
         <v>7042</v>
@@ -54521,7 +54521,7 @@
         <v>7030</v>
       </c>
       <c r="F912">
-        <v>1884</v>
+        <v>1872</v>
       </c>
       <c r="G912" t="s">
         <v>7042</v>
@@ -54547,7 +54547,7 @@
         <v>7030</v>
       </c>
       <c r="F913">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="G913" t="s">
         <v>7042</v>
@@ -54653,7 +54653,7 @@
         <v>7030</v>
       </c>
       <c r="F918">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="G918" t="s">
         <v>7042</v>
@@ -54731,7 +54731,7 @@
         <v>6998</v>
       </c>
       <c r="F921">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G921" t="s">
         <v>7042</v>
@@ -54783,7 +54783,7 @@
         <v>6998</v>
       </c>
       <c r="F923">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G923" t="s">
         <v>7042</v>
@@ -54881,7 +54881,7 @@
         <v>7008</v>
       </c>
       <c r="F927">
-        <v>963</v>
+        <v>953</v>
       </c>
       <c r="G927" t="s">
         <v>7042</v>
@@ -55083,7 +55083,7 @@
         <v>7030</v>
       </c>
       <c r="F935">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="G935" t="s">
         <v>7042</v>
@@ -55109,7 +55109,7 @@
         <v>7030</v>
       </c>
       <c r="F936">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G936" t="s">
         <v>7042</v>
@@ -55187,7 +55187,7 @@
         <v>7030</v>
       </c>
       <c r="F939">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G939" t="s">
         <v>7042</v>
@@ -55265,7 +55265,7 @@
         <v>7030</v>
       </c>
       <c r="F942">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="G942" t="s">
         <v>7042</v>
@@ -55853,7 +55853,7 @@
         <v>6999</v>
       </c>
       <c r="F966">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G966" t="s">
         <v>7042</v>
@@ -55905,7 +55905,7 @@
         <v>6999</v>
       </c>
       <c r="F968">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G968" t="s">
         <v>7042</v>
@@ -55957,7 +55957,7 @@
         <v>6999</v>
       </c>
       <c r="F970">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G970" t="s">
         <v>7042</v>
@@ -55983,7 +55983,7 @@
         <v>6999</v>
       </c>
       <c r="F971">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G971" t="s">
         <v>7042</v>
@@ -56113,7 +56113,7 @@
         <v>6999</v>
       </c>
       <c r="F976">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="G976" t="s">
         <v>7042</v>
@@ -56285,7 +56285,7 @@
         <v>7013</v>
       </c>
       <c r="F984">
-        <v>2213</v>
+        <v>2207</v>
       </c>
       <c r="G984" t="s">
         <v>7042</v>
@@ -56715,7 +56715,7 @@
         <v>6999</v>
       </c>
       <c r="F1001">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1001" t="s">
         <v>7042</v>
@@ -56741,7 +56741,7 @@
         <v>6999</v>
       </c>
       <c r="F1002">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="G1002" t="s">
         <v>7042</v>
@@ -56865,7 +56865,7 @@
         <v>6999</v>
       </c>
       <c r="F1007">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G1007" t="s">
         <v>7042</v>
@@ -56917,7 +56917,7 @@
         <v>6999</v>
       </c>
       <c r="F1009">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G1009" t="s">
         <v>7042</v>
@@ -56969,7 +56969,7 @@
         <v>6999</v>
       </c>
       <c r="F1011">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G1011" t="s">
         <v>7042</v>
@@ -56995,7 +56995,7 @@
         <v>6999</v>
       </c>
       <c r="F1012">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G1012" t="s">
         <v>7042</v>
@@ -57047,7 +57047,7 @@
         <v>7005</v>
       </c>
       <c r="F1014">
-        <v>7440</v>
+        <v>7430</v>
       </c>
       <c r="G1014" t="s">
         <v>7042</v>
@@ -57073,7 +57073,7 @@
         <v>7005</v>
       </c>
       <c r="F1015">
-        <v>4464</v>
+        <v>4458</v>
       </c>
       <c r="G1015" t="s">
         <v>7042</v>
@@ -57272,7 +57272,7 @@
         <v>7004</v>
       </c>
       <c r="F1023">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G1023" t="s">
         <v>7043</v>
@@ -57390,7 +57390,7 @@
         <v>7004</v>
       </c>
       <c r="F1028">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G1028" t="s">
         <v>7042</v>
@@ -57482,7 +57482,7 @@
         <v>7004</v>
       </c>
       <c r="F1032">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G1032" t="s">
         <v>7042</v>
@@ -57629,7 +57629,7 @@
         <v>7034</v>
       </c>
       <c r="F1038">
-        <v>5845</v>
+        <v>5826</v>
       </c>
       <c r="G1038" t="s">
         <v>7042</v>
@@ -57727,7 +57727,7 @@
         <v>6999</v>
       </c>
       <c r="F1042">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G1042" t="s">
         <v>7042</v>
@@ -57753,7 +57753,7 @@
         <v>6999</v>
       </c>
       <c r="F1043">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G1043" t="s">
         <v>7042</v>
@@ -57779,7 +57779,7 @@
         <v>6999</v>
       </c>
       <c r="F1044">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1044" t="s">
         <v>7042</v>
@@ -57805,7 +57805,7 @@
         <v>6999</v>
       </c>
       <c r="F1045">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G1045" t="s">
         <v>7042</v>
@@ -57831,7 +57831,7 @@
         <v>6999</v>
       </c>
       <c r="F1046">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G1046" t="s">
         <v>7042</v>
@@ -57857,7 +57857,7 @@
         <v>6999</v>
       </c>
       <c r="F1047">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G1047" t="s">
         <v>7042</v>
@@ -57909,7 +57909,7 @@
         <v>6999</v>
       </c>
       <c r="F1049">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G1049" t="s">
         <v>7042</v>
@@ -57978,7 +57978,7 @@
         <v>6999</v>
       </c>
       <c r="F1052">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G1052" t="s">
         <v>7043</v>
@@ -58396,7 +58396,7 @@
         <v>7026</v>
       </c>
       <c r="F1072">
-        <v>1984</v>
+        <v>1972</v>
       </c>
       <c r="G1072" t="s">
         <v>7043</v>
@@ -58644,7 +58644,7 @@
         <v>7026</v>
       </c>
       <c r="F1082">
-        <v>1529</v>
+        <v>1505</v>
       </c>
       <c r="G1082" t="s">
         <v>7043</v>
@@ -58664,7 +58664,7 @@
         <v>7026</v>
       </c>
       <c r="F1083">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="G1083" t="s">
         <v>7042</v>
@@ -58690,7 +58690,7 @@
         <v>7026</v>
       </c>
       <c r="F1084">
-        <v>1431</v>
+        <v>1419</v>
       </c>
       <c r="G1084" t="s">
         <v>7043</v>
@@ -58822,7 +58822,7 @@
         <v>7026</v>
       </c>
       <c r="F1090">
-        <v>1809</v>
+        <v>1797</v>
       </c>
       <c r="G1090" t="s">
         <v>7042</v>
@@ -58848,7 +58848,7 @@
         <v>7033</v>
       </c>
       <c r="F1091">
-        <v>950</v>
+        <v>884</v>
       </c>
       <c r="G1091" t="s">
         <v>7042</v>
@@ -58874,7 +58874,7 @@
         <v>7033</v>
       </c>
       <c r="F1092">
-        <v>1182</v>
+        <v>1146</v>
       </c>
       <c r="G1092" t="s">
         <v>7042</v>
@@ -58900,7 +58900,7 @@
         <v>7005</v>
       </c>
       <c r="F1093">
-        <v>4464</v>
+        <v>4458</v>
       </c>
       <c r="G1093" t="s">
         <v>7042</v>
@@ -59050,7 +59050,7 @@
         <v>7013</v>
       </c>
       <c r="F1099">
-        <v>2057</v>
+        <v>2053</v>
       </c>
       <c r="G1099" t="s">
         <v>7042</v>
@@ -59102,7 +59102,7 @@
         <v>7013</v>
       </c>
       <c r="F1101">
-        <v>2269</v>
+        <v>2265</v>
       </c>
       <c r="G1101" t="s">
         <v>7042</v>
@@ -59288,7 +59288,7 @@
         <v>7011</v>
       </c>
       <c r="F1110">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G1110" t="s">
         <v>7043</v>
@@ -59654,7 +59654,7 @@
         <v>6999</v>
       </c>
       <c r="F1125">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G1125" t="s">
         <v>7042</v>
@@ -59706,7 +59706,7 @@
         <v>6999</v>
       </c>
       <c r="F1127">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G1127" t="s">
         <v>7042</v>
@@ -59922,7 +59922,7 @@
         <v>7035</v>
       </c>
       <c r="F1136">
-        <v>1797</v>
+        <v>1769</v>
       </c>
       <c r="G1136" t="s">
         <v>7042</v>
@@ -59948,7 +59948,7 @@
         <v>7035</v>
       </c>
       <c r="F1137">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="G1137" t="s">
         <v>7042</v>
@@ -60078,7 +60078,7 @@
         <v>7035</v>
       </c>
       <c r="F1142">
-        <v>1232</v>
+        <v>1220</v>
       </c>
       <c r="G1142" t="s">
         <v>7042</v>
@@ -60130,7 +60130,7 @@
         <v>7035</v>
       </c>
       <c r="F1144">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G1144" t="s">
         <v>7042</v>
@@ -60208,7 +60208,7 @@
         <v>7035</v>
       </c>
       <c r="F1147">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="G1147" t="s">
         <v>7042</v>
@@ -60234,7 +60234,7 @@
         <v>7035</v>
       </c>
       <c r="F1148">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G1148" t="s">
         <v>7042</v>
@@ -60260,7 +60260,7 @@
         <v>7035</v>
       </c>
       <c r="F1149">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="G1149" t="s">
         <v>7042</v>
@@ -60286,7 +60286,7 @@
         <v>7035</v>
       </c>
       <c r="F1150">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="G1150" t="s">
         <v>7042</v>
@@ -60312,7 +60312,7 @@
         <v>7035</v>
       </c>
       <c r="F1151">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="G1151" t="s">
         <v>7042</v>
@@ -60338,7 +60338,7 @@
         <v>7035</v>
       </c>
       <c r="F1152">
-        <v>1901</v>
+        <v>1889</v>
       </c>
       <c r="G1152" t="s">
         <v>7042</v>
@@ -60410,7 +60410,7 @@
         <v>7035</v>
       </c>
       <c r="F1155">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="G1155" t="s">
         <v>7042</v>
@@ -60482,7 +60482,7 @@
         <v>7035</v>
       </c>
       <c r="F1158">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="G1158" t="s">
         <v>7042</v>
@@ -60508,7 +60508,7 @@
         <v>7035</v>
       </c>
       <c r="F1159">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G1159" t="s">
         <v>7042</v>
@@ -60534,7 +60534,7 @@
         <v>7035</v>
       </c>
       <c r="F1160">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="G1160" t="s">
         <v>7042</v>
@@ -60560,7 +60560,7 @@
         <v>7035</v>
       </c>
       <c r="F1161">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G1161" t="s">
         <v>7042</v>
@@ -60586,7 +60586,7 @@
         <v>7035</v>
       </c>
       <c r="F1162">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G1162" t="s">
         <v>7042</v>
@@ -60612,7 +60612,7 @@
         <v>7035</v>
       </c>
       <c r="F1163">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="G1163" t="s">
         <v>7042</v>
@@ -60638,7 +60638,7 @@
         <v>7035</v>
       </c>
       <c r="F1164">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G1164" t="s">
         <v>7042</v>
@@ -60664,7 +60664,7 @@
         <v>7035</v>
       </c>
       <c r="F1165">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="G1165" t="s">
         <v>7042</v>
@@ -60690,7 +60690,7 @@
         <v>7035</v>
       </c>
       <c r="F1166">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="G1166" t="s">
         <v>7042</v>
@@ -60742,7 +60742,7 @@
         <v>7035</v>
       </c>
       <c r="F1168">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G1168" t="s">
         <v>7042</v>
@@ -60768,7 +60768,7 @@
         <v>7035</v>
       </c>
       <c r="F1169">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G1169" t="s">
         <v>7042</v>
@@ -60820,7 +60820,7 @@
         <v>7035</v>
       </c>
       <c r="F1171">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G1171" t="s">
         <v>7042</v>
@@ -60978,7 +60978,7 @@
         <v>7022</v>
       </c>
       <c r="F1178">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G1178" t="s">
         <v>7042</v>
@@ -61082,7 +61082,7 @@
         <v>7022</v>
       </c>
       <c r="F1182">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G1182" t="s">
         <v>7042</v>
@@ -61108,7 +61108,7 @@
         <v>7022</v>
       </c>
       <c r="F1183">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G1183" t="s">
         <v>7042</v>
@@ -61316,7 +61316,7 @@
         <v>7022</v>
       </c>
       <c r="F1191">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="G1191" t="s">
         <v>7042</v>
@@ -61570,7 +61570,7 @@
         <v>6999</v>
       </c>
       <c r="F1201">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G1201" t="s">
         <v>7043</v>
@@ -61766,7 +61766,7 @@
         <v>7022</v>
       </c>
       <c r="F1209">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="G1209" t="s">
         <v>7042</v>
@@ -61884,7 +61884,7 @@
         <v>7005</v>
       </c>
       <c r="F1214">
-        <v>7062</v>
+        <v>7044</v>
       </c>
       <c r="G1214" t="s">
         <v>7042</v>
@@ -61910,7 +61910,7 @@
         <v>7005</v>
       </c>
       <c r="F1215">
-        <v>4092</v>
+        <v>4076</v>
       </c>
       <c r="G1215" t="s">
         <v>7042</v>
@@ -61936,7 +61936,7 @@
         <v>7005</v>
       </c>
       <c r="F1216">
-        <v>3348</v>
+        <v>3336</v>
       </c>
       <c r="G1216" t="s">
         <v>7042</v>
@@ -61962,7 +61962,7 @@
         <v>7005</v>
       </c>
       <c r="F1217">
-        <v>8928</v>
+        <v>8896</v>
       </c>
       <c r="G1217" t="s">
         <v>7042</v>
@@ -61988,7 +61988,7 @@
         <v>7005</v>
       </c>
       <c r="F1218">
-        <v>5572</v>
+        <v>5554</v>
       </c>
       <c r="G1218" t="s">
         <v>7042</v>
@@ -62014,7 +62014,7 @@
         <v>7005</v>
       </c>
       <c r="F1219">
-        <v>5574</v>
+        <v>5556</v>
       </c>
       <c r="G1219" t="s">
         <v>7042</v>
@@ -62040,7 +62040,7 @@
         <v>7005</v>
       </c>
       <c r="F1220">
-        <v>6681</v>
+        <v>6657</v>
       </c>
       <c r="G1220" t="s">
         <v>7042</v>
@@ -62066,7 +62066,7 @@
         <v>7005</v>
       </c>
       <c r="F1221">
-        <v>7062</v>
+        <v>7044</v>
       </c>
       <c r="G1221" t="s">
         <v>7042</v>
@@ -62092,7 +62092,7 @@
         <v>7005</v>
       </c>
       <c r="F1222">
-        <v>12632</v>
+        <v>12584</v>
       </c>
       <c r="G1222" t="s">
         <v>7042</v>
@@ -62118,7 +62118,7 @@
         <v>7005</v>
       </c>
       <c r="F1223">
-        <v>3348</v>
+        <v>3336</v>
       </c>
       <c r="G1223" t="s">
         <v>7042</v>
@@ -62300,7 +62300,7 @@
         <v>7005</v>
       </c>
       <c r="F1230">
-        <v>4464</v>
+        <v>4458</v>
       </c>
       <c r="G1230" t="s">
         <v>7042</v>
@@ -62326,7 +62326,7 @@
         <v>7005</v>
       </c>
       <c r="F1231">
-        <v>3720</v>
+        <v>3708</v>
       </c>
       <c r="G1231" t="s">
         <v>7042</v>
@@ -62352,7 +62352,7 @@
         <v>7005</v>
       </c>
       <c r="F1232">
-        <v>3348</v>
+        <v>3336</v>
       </c>
       <c r="G1232" t="s">
         <v>7042</v>
@@ -62508,7 +62508,7 @@
         <v>7036</v>
       </c>
       <c r="F1238">
-        <v>8414</v>
+        <v>8366</v>
       </c>
       <c r="G1238" t="s">
         <v>7042</v>
@@ -62716,7 +62716,7 @@
         <v>7031</v>
       </c>
       <c r="F1246">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G1246" t="s">
         <v>7042</v>
@@ -63168,7 +63168,7 @@
         <v>7011</v>
       </c>
       <c r="F1268">
-        <v>5940</v>
+        <v>5916</v>
       </c>
       <c r="G1268" t="s">
         <v>7043</v>
@@ -63268,7 +63268,7 @@
         <v>7011</v>
       </c>
       <c r="F1273">
-        <v>4512</v>
+        <v>4511</v>
       </c>
       <c r="G1273" t="s">
         <v>7043</v>
@@ -63488,7 +63488,7 @@
         <v>7008</v>
       </c>
       <c r="F1284">
-        <v>1435</v>
+        <v>1423</v>
       </c>
       <c r="G1284" t="s">
         <v>7042</v>
@@ -63690,7 +63690,7 @@
         <v>7013</v>
       </c>
       <c r="F1292">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="G1292" t="s">
         <v>7042</v>
@@ -63716,7 +63716,7 @@
         <v>7011</v>
       </c>
       <c r="F1293">
-        <v>6231</v>
+        <v>6219</v>
       </c>
       <c r="G1293" t="s">
         <v>7042</v>
@@ -63814,7 +63814,7 @@
         <v>7011</v>
       </c>
       <c r="F1297">
-        <v>3714</v>
+        <v>3702</v>
       </c>
       <c r="G1297" t="s">
         <v>7042</v>
@@ -63840,7 +63840,7 @@
         <v>7031</v>
       </c>
       <c r="F1298">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="G1298" t="s">
         <v>7042</v>
@@ -63866,7 +63866,7 @@
         <v>7031</v>
       </c>
       <c r="F1299">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="G1299" t="s">
         <v>7042</v>
@@ -63912,7 +63912,7 @@
         <v>7008</v>
       </c>
       <c r="F1301">
-        <v>2139</v>
+        <v>2121</v>
       </c>
       <c r="G1301" t="s">
         <v>7042</v>
@@ -63964,7 +63964,7 @@
         <v>7008</v>
       </c>
       <c r="F1303">
-        <v>2057</v>
+        <v>2039</v>
       </c>
       <c r="G1303" t="s">
         <v>7042</v>
@@ -63990,7 +63990,7 @@
         <v>7008</v>
       </c>
       <c r="F1304">
-        <v>1868</v>
+        <v>1844</v>
       </c>
       <c r="G1304" t="s">
         <v>7042</v>
@@ -64016,7 +64016,7 @@
         <v>7008</v>
       </c>
       <c r="F1305">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="G1305" t="s">
         <v>7042</v>
@@ -64042,7 +64042,7 @@
         <v>7008</v>
       </c>
       <c r="F1306">
-        <v>1560</v>
+        <v>1548</v>
       </c>
       <c r="G1306" t="s">
         <v>7042</v>
@@ -65686,7 +65686,7 @@
         <v>6999</v>
       </c>
       <c r="F1372">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1372" t="s">
         <v>7042</v>
@@ -65712,7 +65712,7 @@
         <v>6999</v>
       </c>
       <c r="F1373">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G1373" t="s">
         <v>7042</v>
@@ -65816,7 +65816,7 @@
         <v>6999</v>
       </c>
       <c r="F1377">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G1377" t="s">
         <v>7042</v>
@@ -66740,7 +66740,7 @@
         <v>7037</v>
       </c>
       <c r="F1419">
-        <v>3705</v>
+        <v>3669</v>
       </c>
       <c r="G1419" t="s">
         <v>7042</v>
@@ -66766,7 +66766,7 @@
         <v>7037</v>
       </c>
       <c r="F1420">
-        <v>7959</v>
+        <v>7887</v>
       </c>
       <c r="G1420" t="s">
         <v>7042</v>
@@ -66818,7 +66818,7 @@
         <v>7037</v>
       </c>
       <c r="F1422">
-        <v>6300</v>
+        <v>6228</v>
       </c>
       <c r="G1422" t="s">
         <v>7042</v>
@@ -66896,7 +66896,7 @@
         <v>7008</v>
       </c>
       <c r="F1425">
-        <v>2923</v>
+        <v>2893</v>
       </c>
       <c r="G1425" t="s">
         <v>7042</v>
@@ -66922,7 +66922,7 @@
         <v>7008</v>
       </c>
       <c r="F1426">
-        <v>3471</v>
+        <v>3461</v>
       </c>
       <c r="G1426" t="s">
         <v>7042</v>
@@ -66948,7 +66948,7 @@
         <v>7008</v>
       </c>
       <c r="F1427">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="G1427" t="s">
         <v>7042</v>
@@ -67078,7 +67078,7 @@
         <v>7008</v>
       </c>
       <c r="F1432">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="G1432" t="s">
         <v>7042</v>
@@ -67208,7 +67208,7 @@
         <v>7008</v>
       </c>
       <c r="F1437">
-        <v>2570</v>
+        <v>2550</v>
       </c>
       <c r="G1437" t="s">
         <v>7042</v>
@@ -67234,7 +67234,7 @@
         <v>7008</v>
       </c>
       <c r="F1438">
-        <v>4917</v>
+        <v>4916</v>
       </c>
       <c r="G1438" t="s">
         <v>7042</v>
@@ -67286,7 +67286,7 @@
         <v>7037</v>
       </c>
       <c r="F1440">
-        <v>6900</v>
+        <v>6882</v>
       </c>
       <c r="G1440" t="s">
         <v>7042</v>
@@ -67312,7 +67312,7 @@
         <v>7037</v>
       </c>
       <c r="F1441">
-        <v>5166</v>
+        <v>5148</v>
       </c>
       <c r="G1441" t="s">
         <v>7042</v>
@@ -67390,7 +67390,7 @@
         <v>7037</v>
       </c>
       <c r="F1444">
-        <v>3081</v>
+        <v>3063</v>
       </c>
       <c r="G1444" t="s">
         <v>7042</v>
@@ -67598,7 +67598,7 @@
         <v>7038</v>
       </c>
       <c r="F1452">
-        <v>1724</v>
+        <v>1708</v>
       </c>
       <c r="G1452" t="s">
         <v>7042</v>
@@ -67736,7 +67736,7 @@
         <v>7008</v>
       </c>
       <c r="F1458">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G1458" t="s">
         <v>7042</v>
@@ -67762,7 +67762,7 @@
         <v>7008</v>
       </c>
       <c r="F1459">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G1459" t="s">
         <v>7042</v>
@@ -68048,7 +68048,7 @@
         <v>7035</v>
       </c>
       <c r="F1470">
-        <v>8183</v>
+        <v>8159</v>
       </c>
       <c r="G1470" t="s">
         <v>7042</v>
@@ -68074,7 +68074,7 @@
         <v>7035</v>
       </c>
       <c r="F1471">
-        <v>2520</v>
+        <v>2496</v>
       </c>
       <c r="G1471" t="s">
         <v>7042</v>
@@ -68244,7 +68244,7 @@
         <v>7035</v>
       </c>
       <c r="F1478">
-        <v>2731</v>
+        <v>2683</v>
       </c>
       <c r="G1478" t="s">
         <v>7042</v>
@@ -68270,7 +68270,7 @@
         <v>7035</v>
       </c>
       <c r="F1479">
-        <v>616</v>
+        <v>580</v>
       </c>
       <c r="G1479" t="s">
         <v>7042</v>
@@ -68374,7 +68374,7 @@
         <v>7035</v>
       </c>
       <c r="F1483">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="G1483" t="s">
         <v>7042</v>
@@ -68426,7 +68426,7 @@
         <v>7035</v>
       </c>
       <c r="F1485">
-        <v>1372</v>
+        <v>1360</v>
       </c>
       <c r="G1485" t="s">
         <v>7042</v>
@@ -68452,7 +68452,7 @@
         <v>7035</v>
       </c>
       <c r="F1486">
-        <v>8270</v>
+        <v>8198</v>
       </c>
       <c r="G1486" t="s">
         <v>7042</v>
@@ -68478,7 +68478,7 @@
         <v>7035</v>
       </c>
       <c r="F1487">
-        <v>1274</v>
+        <v>1226</v>
       </c>
       <c r="G1487" t="s">
         <v>7042</v>
@@ -68504,7 +68504,7 @@
         <v>7035</v>
       </c>
       <c r="F1488">
-        <v>7994</v>
+        <v>7946</v>
       </c>
       <c r="G1488" t="s">
         <v>7042</v>
@@ -68582,7 +68582,7 @@
         <v>7035</v>
       </c>
       <c r="F1491">
-        <v>3142</v>
+        <v>3106</v>
       </c>
       <c r="G1491" t="s">
         <v>7042</v>
@@ -68608,7 +68608,7 @@
         <v>7035</v>
       </c>
       <c r="F1492">
-        <v>6084</v>
+        <v>6048</v>
       </c>
       <c r="G1492" t="s">
         <v>7042</v>
@@ -68634,7 +68634,7 @@
         <v>7035</v>
       </c>
       <c r="F1493">
-        <v>1884</v>
+        <v>1872</v>
       </c>
       <c r="G1493" t="s">
         <v>7042</v>
@@ -68738,7 +68738,7 @@
         <v>7035</v>
       </c>
       <c r="F1497">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G1497" t="s">
         <v>7042</v>
@@ -68764,7 +68764,7 @@
         <v>7035</v>
       </c>
       <c r="F1498">
-        <v>2364</v>
+        <v>2352</v>
       </c>
       <c r="G1498" t="s">
         <v>7042</v>
@@ -68894,7 +68894,7 @@
         <v>7035</v>
       </c>
       <c r="F1503">
-        <v>924</v>
+        <v>900</v>
       </c>
       <c r="G1503" t="s">
         <v>7042</v>
@@ -68998,7 +68998,7 @@
         <v>7038</v>
       </c>
       <c r="F1507">
-        <v>2487</v>
+        <v>2479</v>
       </c>
       <c r="G1507" t="s">
         <v>7042</v>
@@ -69050,7 +69050,7 @@
         <v>7038</v>
       </c>
       <c r="F1509">
-        <v>3702</v>
+        <v>3694</v>
       </c>
       <c r="G1509" t="s">
         <v>7042</v>
@@ -69102,7 +69102,7 @@
         <v>7038</v>
       </c>
       <c r="F1511">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G1511" t="s">
         <v>7042</v>
@@ -69180,7 +69180,7 @@
         <v>7038</v>
       </c>
       <c r="F1514">
-        <v>4436</v>
+        <v>4421</v>
       </c>
       <c r="G1514" t="s">
         <v>7042</v>
@@ -69206,7 +69206,7 @@
         <v>7038</v>
       </c>
       <c r="F1515">
-        <v>2824</v>
+        <v>2809</v>
       </c>
       <c r="G1515" t="s">
         <v>7042</v>
@@ -69232,7 +69232,7 @@
         <v>7038</v>
       </c>
       <c r="F1516">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G1516" t="s">
         <v>7042</v>
@@ -69336,7 +69336,7 @@
         <v>7038</v>
       </c>
       <c r="F1520">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="G1520" t="s">
         <v>7042</v>
@@ -69440,7 +69440,7 @@
         <v>7038</v>
       </c>
       <c r="F1524">
-        <v>2121</v>
+        <v>2113</v>
       </c>
       <c r="G1524" t="s">
         <v>7042</v>
@@ -69544,7 +69544,7 @@
         <v>7038</v>
       </c>
       <c r="F1528">
-        <v>855</v>
+        <v>795</v>
       </c>
       <c r="G1528" t="s">
         <v>7042</v>
@@ -69674,7 +69674,7 @@
         <v>7035</v>
       </c>
       <c r="F1533">
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="G1533" t="s">
         <v>7042</v>
@@ -69830,7 +69830,7 @@
         <v>7035</v>
       </c>
       <c r="F1539">
-        <v>4501</v>
+        <v>4465</v>
       </c>
       <c r="G1539" t="s">
         <v>7042</v>
@@ -69856,7 +69856,7 @@
         <v>7035</v>
       </c>
       <c r="F1540">
-        <v>4676</v>
+        <v>4628</v>
       </c>
       <c r="G1540" t="s">
         <v>7042</v>
@@ -69882,7 +69882,7 @@
         <v>7035</v>
       </c>
       <c r="F1541">
-        <v>3205</v>
+        <v>3145</v>
       </c>
       <c r="G1541" t="s">
         <v>7042</v>
@@ -69986,7 +69986,7 @@
         <v>7035</v>
       </c>
       <c r="F1545">
-        <v>10955</v>
+        <v>10907</v>
       </c>
       <c r="G1545" t="s">
         <v>7042</v>
@@ -70012,7 +70012,7 @@
         <v>7035</v>
       </c>
       <c r="F1546">
-        <v>10622</v>
+        <v>10586</v>
       </c>
       <c r="G1546" t="s">
         <v>7042</v>
@@ -70038,7 +70038,7 @@
         <v>7035</v>
       </c>
       <c r="F1547">
-        <v>2446</v>
+        <v>2422</v>
       </c>
       <c r="G1547" t="s">
         <v>7042</v>
@@ -70064,7 +70064,7 @@
         <v>7035</v>
       </c>
       <c r="F1548">
-        <v>8668</v>
+        <v>8644</v>
       </c>
       <c r="G1548" t="s">
         <v>7042</v>
@@ -70228,7 +70228,7 @@
         <v>7034</v>
       </c>
       <c r="F1555">
-        <v>9991</v>
+        <v>9973</v>
       </c>
       <c r="G1555" t="s">
         <v>7042</v>
@@ -70794,7 +70794,7 @@
         <v>7033</v>
       </c>
       <c r="F1577">
-        <v>3409</v>
+        <v>3391</v>
       </c>
       <c r="G1577" t="s">
         <v>7042</v>
@@ -70846,7 +70846,7 @@
         <v>7033</v>
       </c>
       <c r="F1579">
-        <v>2728</v>
+        <v>2696</v>
       </c>
       <c r="G1579" t="s">
         <v>7042</v>
@@ -70872,7 +70872,7 @@
         <v>7033</v>
       </c>
       <c r="F1580">
-        <v>2236</v>
+        <v>2216</v>
       </c>
       <c r="G1580" t="s">
         <v>7042</v>
@@ -70898,7 +70898,7 @@
         <v>7033</v>
       </c>
       <c r="F1581">
-        <v>2425</v>
+        <v>2401</v>
       </c>
       <c r="G1581" t="s">
         <v>7042</v>
@@ -70924,7 +70924,7 @@
         <v>7021</v>
       </c>
       <c r="F1582">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="G1582" t="s">
         <v>7042</v>
@@ -70950,7 +70950,7 @@
         <v>6998</v>
       </c>
       <c r="F1583">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G1583" t="s">
         <v>7042</v>
@@ -71002,7 +71002,7 @@
         <v>6998</v>
       </c>
       <c r="F1585">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G1585" t="s">
         <v>7042</v>
@@ -71158,7 +71158,7 @@
         <v>7016</v>
       </c>
       <c r="F1591">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="G1591" t="s">
         <v>7042</v>
@@ -71504,7 +71504,7 @@
         <v>7017</v>
       </c>
       <c r="F1605">
-        <v>2246</v>
+        <v>2222</v>
       </c>
       <c r="G1605" t="s">
         <v>7042</v>
@@ -71556,7 +71556,7 @@
         <v>7017</v>
       </c>
       <c r="F1607">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G1607" t="s">
         <v>7042</v>
@@ -71712,7 +71712,7 @@
         <v>7017</v>
       </c>
       <c r="F1613">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="G1613" t="s">
         <v>7042</v>
@@ -71764,7 +71764,7 @@
         <v>7017</v>
       </c>
       <c r="F1615">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="G1615" t="s">
         <v>7042</v>
@@ -71790,7 +71790,7 @@
         <v>7017</v>
       </c>
       <c r="F1616">
-        <v>2100</v>
+        <v>2088</v>
       </c>
       <c r="G1616" t="s">
         <v>7042</v>
@@ -71914,7 +71914,7 @@
         <v>7016</v>
       </c>
       <c r="F1621">
-        <v>4548</v>
+        <v>4542</v>
       </c>
       <c r="G1621" t="s">
         <v>7042</v>
@@ -72220,7 +72220,7 @@
         <v>7036</v>
       </c>
       <c r="F1633">
-        <v>2781</v>
+        <v>2769</v>
       </c>
       <c r="G1633" t="s">
         <v>7042</v>
@@ -72246,7 +72246,7 @@
         <v>7036</v>
       </c>
       <c r="F1634">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="G1634" t="s">
         <v>7042</v>
@@ -72272,7 +72272,7 @@
         <v>7036</v>
       </c>
       <c r="F1635">
-        <v>2953</v>
+        <v>2937</v>
       </c>
       <c r="G1635" t="s">
         <v>7042</v>
@@ -72480,7 +72480,7 @@
         <v>7036</v>
       </c>
       <c r="F1643">
-        <v>46242</v>
+        <v>45720</v>
       </c>
       <c r="G1643" t="s">
         <v>7042</v>
@@ -72506,7 +72506,7 @@
         <v>7036</v>
       </c>
       <c r="F1644">
-        <v>11091</v>
+        <v>10983</v>
       </c>
       <c r="G1644" t="s">
         <v>7042</v>
@@ -72584,7 +72584,7 @@
         <v>7036</v>
       </c>
       <c r="F1647">
-        <v>2810</v>
+        <v>2774</v>
       </c>
       <c r="G1647" t="s">
         <v>7042</v>
@@ -72610,7 +72610,7 @@
         <v>7036</v>
       </c>
       <c r="F1648">
-        <v>4145</v>
+        <v>4097</v>
       </c>
       <c r="G1648" t="s">
         <v>7042</v>
@@ -72662,7 +72662,7 @@
         <v>7033</v>
       </c>
       <c r="F1650">
-        <v>26820</v>
+        <v>26640</v>
       </c>
       <c r="G1650" t="s">
         <v>7042</v>
@@ -72688,7 +72688,7 @@
         <v>7033</v>
       </c>
       <c r="F1651">
-        <v>19106</v>
+        <v>19040</v>
       </c>
       <c r="G1651" t="s">
         <v>7042</v>
@@ -72792,7 +72792,7 @@
         <v>7031</v>
       </c>
       <c r="F1655">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="G1655" t="s">
         <v>7042</v>
@@ -72922,7 +72922,7 @@
         <v>7031</v>
       </c>
       <c r="F1660">
-        <v>830</v>
+        <v>794</v>
       </c>
       <c r="G1660" t="s">
         <v>7042</v>
@@ -73156,7 +73156,7 @@
         <v>7039</v>
       </c>
       <c r="F1669">
-        <v>2747</v>
+        <v>2735</v>
       </c>
       <c r="G1669" t="s">
         <v>7042</v>
@@ -73182,7 +73182,7 @@
         <v>7039</v>
       </c>
       <c r="F1670">
-        <v>1892</v>
+        <v>1880</v>
       </c>
       <c r="G1670" t="s">
         <v>7042</v>
@@ -73416,7 +73416,7 @@
         <v>7009</v>
       </c>
       <c r="F1679">
-        <v>3155</v>
+        <v>3119</v>
       </c>
       <c r="G1679" t="s">
         <v>7042</v>
@@ -73442,7 +73442,7 @@
         <v>7009</v>
       </c>
       <c r="F1680">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="G1680" t="s">
         <v>7042</v>
@@ -73468,7 +73468,7 @@
         <v>7009</v>
       </c>
       <c r="F1681">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="G1681" t="s">
         <v>7042</v>
@@ -73572,7 +73572,7 @@
         <v>7009</v>
       </c>
       <c r="F1685">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="G1685" t="s">
         <v>7042</v>
@@ -73598,7 +73598,7 @@
         <v>7009</v>
       </c>
       <c r="F1686">
-        <v>5690</v>
+        <v>5666</v>
       </c>
       <c r="G1686" t="s">
         <v>7042</v>
@@ -73624,7 +73624,7 @@
         <v>7009</v>
       </c>
       <c r="F1687">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="G1687" t="s">
         <v>7042</v>
@@ -73754,7 +73754,7 @@
         <v>7009</v>
       </c>
       <c r="F1692">
-        <v>1739</v>
+        <v>1721</v>
       </c>
       <c r="G1692" t="s">
         <v>7042</v>
@@ -73884,7 +73884,7 @@
         <v>7009</v>
       </c>
       <c r="F1697">
-        <v>3935</v>
+        <v>3923</v>
       </c>
       <c r="G1697" t="s">
         <v>7042</v>
@@ -74014,7 +74014,7 @@
         <v>7009</v>
       </c>
       <c r="F1702">
-        <v>3173</v>
+        <v>3149</v>
       </c>
       <c r="G1702" t="s">
         <v>7042</v>
@@ -74040,7 +74040,7 @@
         <v>7023</v>
       </c>
       <c r="F1703">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="G1703" t="s">
         <v>7042</v>
@@ -74092,7 +74092,7 @@
         <v>7023</v>
       </c>
       <c r="F1705">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="G1705" t="s">
         <v>7042</v>
@@ -74170,7 +74170,7 @@
         <v>7023</v>
       </c>
       <c r="F1708">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="G1708" t="s">
         <v>7042</v>
@@ -74196,7 +74196,7 @@
         <v>7023</v>
       </c>
       <c r="F1709">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="G1709" t="s">
         <v>7042</v>
@@ -74222,7 +74222,7 @@
         <v>7023</v>
       </c>
       <c r="F1710">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="G1710" t="s">
         <v>7042</v>
@@ -74326,7 +74326,7 @@
         <v>7023</v>
       </c>
       <c r="F1714">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="G1714" t="s">
         <v>7042</v>
@@ -74430,7 +74430,7 @@
         <v>7009</v>
       </c>
       <c r="F1718">
-        <v>1847</v>
+        <v>1829</v>
       </c>
       <c r="G1718" t="s">
         <v>7042</v>
@@ -74542,7 +74542,7 @@
         <v>7011</v>
       </c>
       <c r="F1723">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G1723" t="s">
         <v>7042</v>
@@ -74928,7 +74928,7 @@
         <v>7030</v>
       </c>
       <c r="F1739">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="G1739" t="s">
         <v>7042</v>
@@ -75214,7 +75214,7 @@
         <v>7030</v>
       </c>
       <c r="F1750">
-        <v>1032</v>
+        <v>1008</v>
       </c>
       <c r="G1750" t="s">
         <v>7042</v>
@@ -76450,7 +76450,7 @@
         <v>7005</v>
       </c>
       <c r="F1798">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="G1798" t="s">
         <v>7042</v>
@@ -76476,7 +76476,7 @@
         <v>7005</v>
       </c>
       <c r="F1799">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="G1799" t="s">
         <v>7042</v>
@@ -76502,7 +76502,7 @@
         <v>7005</v>
       </c>
       <c r="F1800">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G1800" t="s">
         <v>7042</v>
@@ -76528,7 +76528,7 @@
         <v>7005</v>
       </c>
       <c r="F1801">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G1801" t="s">
         <v>7042</v>
@@ -76554,7 +76554,7 @@
         <v>7005</v>
       </c>
       <c r="F1802">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="G1802" t="s">
         <v>7042</v>
@@ -76580,7 +76580,7 @@
         <v>7005</v>
       </c>
       <c r="F1803">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="G1803" t="s">
         <v>7042</v>
@@ -76606,7 +76606,7 @@
         <v>7005</v>
       </c>
       <c r="F1804">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="G1804" t="s">
         <v>7042</v>
@@ -76632,7 +76632,7 @@
         <v>7005</v>
       </c>
       <c r="F1805">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G1805" t="s">
         <v>7042</v>
@@ -76658,7 +76658,7 @@
         <v>7005</v>
       </c>
       <c r="F1806">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="G1806" t="s">
         <v>7042</v>
@@ -76684,7 +76684,7 @@
         <v>7005</v>
       </c>
       <c r="F1807">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="G1807" t="s">
         <v>7042</v>
@@ -76944,7 +76944,7 @@
         <v>7005</v>
       </c>
       <c r="F1817">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="G1817" t="s">
         <v>7042</v>
@@ -77100,7 +77100,7 @@
         <v>7005</v>
       </c>
       <c r="F1823">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="G1823" t="s">
         <v>7042</v>
@@ -77726,7 +77726,7 @@
         <v>7005</v>
       </c>
       <c r="F1848">
-        <v>2490</v>
+        <v>2460</v>
       </c>
       <c r="G1848" t="s">
         <v>7042</v>
@@ -79612,7 +79612,7 @@
         <v>7010</v>
       </c>
       <c r="F1924">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G1924" t="s">
         <v>7042</v>
@@ -79684,7 +79684,7 @@
         <v>7010</v>
       </c>
       <c r="F1927">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G1927" t="s">
         <v>7042</v>
@@ -79736,7 +79736,7 @@
         <v>7010</v>
       </c>
       <c r="F1929">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="G1929" t="s">
         <v>7042</v>
@@ -80252,7 +80252,7 @@
         <v>6999</v>
       </c>
       <c r="F1950">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G1950" t="s">
         <v>7042</v>
@@ -80324,7 +80324,7 @@
         <v>6999</v>
       </c>
       <c r="F1953">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G1953" t="s">
         <v>7042</v>
@@ -80454,7 +80454,7 @@
         <v>6999</v>
       </c>
       <c r="F1958">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="G1958" t="s">
         <v>7043</v>
@@ -80526,7 +80526,7 @@
         <v>6999</v>
       </c>
       <c r="F1961">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G1961" t="s">
         <v>7042</v>
@@ -80630,7 +80630,7 @@
         <v>6999</v>
       </c>
       <c r="F1965">
-        <v>1226</v>
+        <v>1216</v>
       </c>
       <c r="G1965" t="s">
         <v>7042</v>
@@ -80656,7 +80656,7 @@
         <v>6999</v>
       </c>
       <c r="F1966">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G1966" t="s">
         <v>7042</v>
@@ -81444,7 +81444,7 @@
         <v>6999</v>
       </c>
       <c r="F2000">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="G2000" t="s">
         <v>7042</v>
@@ -81600,7 +81600,7 @@
         <v>7000</v>
       </c>
       <c r="F2006">
-        <v>1101</v>
+        <v>1091</v>
       </c>
       <c r="G2006" t="s">
         <v>7042</v>
@@ -81626,7 +81626,7 @@
         <v>7000</v>
       </c>
       <c r="F2007">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="G2007" t="s">
         <v>7042</v>
@@ -81698,7 +81698,7 @@
         <v>7000</v>
       </c>
       <c r="F2010">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G2010" t="s">
         <v>7042</v>
@@ -82658,7 +82658,7 @@
         <v>6999</v>
       </c>
       <c r="F2052">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="G2052" t="s">
         <v>7042</v>
@@ -82762,7 +82762,7 @@
         <v>6999</v>
       </c>
       <c r="F2056">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G2056" t="s">
         <v>7042</v>
@@ -82880,7 +82880,7 @@
         <v>6999</v>
       </c>
       <c r="F2061">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="G2061" t="s">
         <v>7043</v>
@@ -82966,7 +82966,7 @@
         <v>6999</v>
       </c>
       <c r="F2065">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G2065" t="s">
         <v>7043</v>
@@ -83006,7 +83006,7 @@
         <v>6999</v>
       </c>
       <c r="F2067">
-        <v>746</v>
+        <v>546</v>
       </c>
       <c r="G2067" t="s">
         <v>7043</v>
@@ -83652,7 +83652,7 @@
         <v>6999</v>
       </c>
       <c r="F2093">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G2093" t="s">
         <v>7042</v>
@@ -83678,7 +83678,7 @@
         <v>6999</v>
       </c>
       <c r="F2094">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G2094" t="s">
         <v>7042</v>
@@ -85784,7 +85784,7 @@
         <v>7015</v>
       </c>
       <c r="F2178">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="G2178" t="s">
         <v>7043</v>
@@ -85804,7 +85804,7 @@
         <v>7015</v>
       </c>
       <c r="F2179">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G2179" t="s">
         <v>7043</v>
@@ -85824,7 +85824,7 @@
         <v>7015</v>
       </c>
       <c r="F2180">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="G2180" t="s">
         <v>7043</v>
@@ -86346,7 +86346,7 @@
         <v>7015</v>
       </c>
       <c r="F2204">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G2204" t="s">
         <v>7042</v>
@@ -86666,7 +86666,7 @@
         <v>7015</v>
       </c>
       <c r="F2217">
-        <v>3197</v>
+        <v>3193</v>
       </c>
       <c r="G2217" t="s">
         <v>7042</v>
@@ -86718,7 +86718,7 @@
         <v>7015</v>
       </c>
       <c r="F2219">
-        <v>19046</v>
+        <v>18850</v>
       </c>
       <c r="G2219" t="s">
         <v>7042</v>
@@ -86770,7 +86770,7 @@
         <v>7015</v>
       </c>
       <c r="F2221">
-        <v>1891</v>
+        <v>1871</v>
       </c>
       <c r="G2221" t="s">
         <v>7042</v>
@@ -86868,7 +86868,7 @@
         <v>7015</v>
       </c>
       <c r="F2225">
-        <v>7511</v>
+        <v>7501</v>
       </c>
       <c r="G2225" t="s">
         <v>7042</v>
@@ -86894,7 +86894,7 @@
         <v>7015</v>
       </c>
       <c r="F2226">
-        <v>1134</v>
+        <v>1104</v>
       </c>
       <c r="G2226" t="s">
         <v>7042</v>
@@ -86946,7 +86946,7 @@
         <v>7015</v>
       </c>
       <c r="F2228">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="G2228" t="s">
         <v>7042</v>
@@ -87018,7 +87018,7 @@
         <v>7015</v>
       </c>
       <c r="F2231">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G2231" t="s">
         <v>7042</v>
@@ -87044,7 +87044,7 @@
         <v>7010</v>
       </c>
       <c r="F2232">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G2232" t="s">
         <v>7042</v>
@@ -87156,7 +87156,7 @@
         <v>7015</v>
       </c>
       <c r="F2237">
-        <v>6309</v>
+        <v>6301</v>
       </c>
       <c r="G2237" t="s">
         <v>7042</v>
@@ -87866,7 +87866,7 @@
         <v>7000</v>
       </c>
       <c r="F2268">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G2268" t="s">
         <v>7042</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -31538,7 +31538,7 @@
         <v>6815</v>
       </c>
       <c r="F6">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
         <v>6857</v>
@@ -31978,7 +31978,7 @@
         <v>6817</v>
       </c>
       <c r="F25">
-        <v>1602</v>
+        <v>1598</v>
       </c>
       <c r="G25" t="s">
         <v>6857</v>
@@ -32004,7 +32004,7 @@
         <v>6817</v>
       </c>
       <c r="F26">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="G26" t="s">
         <v>6857</v>
@@ -32030,7 +32030,7 @@
         <v>6817</v>
       </c>
       <c r="F27">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="G27" t="s">
         <v>6857</v>
@@ -32056,7 +32056,7 @@
         <v>6817</v>
       </c>
       <c r="F28">
-        <v>1665</v>
+        <v>1657</v>
       </c>
       <c r="G28" t="s">
         <v>6857</v>
@@ -32082,7 +32082,7 @@
         <v>6817</v>
       </c>
       <c r="F29">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="G29" t="s">
         <v>6857</v>
@@ -32108,7 +32108,7 @@
         <v>6817</v>
       </c>
       <c r="F30">
-        <v>1709</v>
+        <v>1697</v>
       </c>
       <c r="G30" t="s">
         <v>6857</v>
@@ -32134,7 +32134,7 @@
         <v>6817</v>
       </c>
       <c r="F31">
-        <v>1686</v>
+        <v>1678</v>
       </c>
       <c r="G31" t="s">
         <v>6857</v>
@@ -32160,7 +32160,7 @@
         <v>6816</v>
       </c>
       <c r="F32">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="G32" t="s">
         <v>6857</v>
@@ -32186,7 +32186,7 @@
         <v>6816</v>
       </c>
       <c r="F33">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="G33" t="s">
         <v>6857</v>
@@ -32238,7 +32238,7 @@
         <v>6816</v>
       </c>
       <c r="F35">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="G35" t="s">
         <v>6857</v>
@@ -32264,7 +32264,7 @@
         <v>6816</v>
       </c>
       <c r="F36">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="G36" t="s">
         <v>6857</v>
@@ -32290,7 +32290,7 @@
         <v>6816</v>
       </c>
       <c r="F37">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="G37" t="s">
         <v>6857</v>
@@ -32316,7 +32316,7 @@
         <v>6813</v>
       </c>
       <c r="F38">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G38" t="s">
         <v>6858</v>
@@ -32336,7 +32336,7 @@
         <v>6813</v>
       </c>
       <c r="F39">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G39" t="s">
         <v>6858</v>
@@ -32356,7 +32356,7 @@
         <v>6813</v>
       </c>
       <c r="F40">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G40" t="s">
         <v>6858</v>
@@ -32376,7 +32376,7 @@
         <v>6816</v>
       </c>
       <c r="F41">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="G41" t="s">
         <v>6857</v>
@@ -32422,7 +32422,7 @@
         <v>6818</v>
       </c>
       <c r="F43">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G43" t="s">
         <v>6857</v>
@@ -32448,7 +32448,7 @@
         <v>6818</v>
       </c>
       <c r="F44">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G44" t="s">
         <v>6857</v>
@@ -32594,7 +32594,7 @@
         <v>6818</v>
       </c>
       <c r="F51">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G51" t="s">
         <v>6857</v>
@@ -32620,7 +32620,7 @@
         <v>6818</v>
       </c>
       <c r="F52">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G52" t="s">
         <v>6857</v>
@@ -32672,7 +32672,7 @@
         <v>6819</v>
       </c>
       <c r="F54">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G54" t="s">
         <v>6857</v>
@@ -32698,7 +32698,7 @@
         <v>6816</v>
       </c>
       <c r="F55">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="G55" t="s">
         <v>6857</v>
@@ -32724,7 +32724,7 @@
         <v>6819</v>
       </c>
       <c r="F56">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G56" t="s">
         <v>6857</v>
@@ -32828,7 +32828,7 @@
         <v>6819</v>
       </c>
       <c r="F60">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G60" t="s">
         <v>6857</v>
@@ -32906,7 +32906,7 @@
         <v>6816</v>
       </c>
       <c r="F63">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G63" t="s">
         <v>6857</v>
@@ -32958,7 +32958,7 @@
         <v>6816</v>
       </c>
       <c r="F65">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s">
         <v>6857</v>
@@ -32984,7 +32984,7 @@
         <v>6815</v>
       </c>
       <c r="F66">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G66" t="s">
         <v>6857</v>
@@ -33036,7 +33036,7 @@
         <v>6821</v>
       </c>
       <c r="F68">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="G68" t="s">
         <v>6857</v>
@@ -33062,7 +33062,7 @@
         <v>6821</v>
       </c>
       <c r="F69">
-        <v>3173</v>
+        <v>3157</v>
       </c>
       <c r="G69" t="s">
         <v>6857</v>
@@ -33088,7 +33088,7 @@
         <v>6821</v>
       </c>
       <c r="F70">
-        <v>1393</v>
+        <v>1381</v>
       </c>
       <c r="G70" t="s">
         <v>6857</v>
@@ -33114,7 +33114,7 @@
         <v>6821</v>
       </c>
       <c r="F71">
-        <v>2561</v>
+        <v>2549</v>
       </c>
       <c r="G71" t="s">
         <v>6857</v>
@@ -33140,7 +33140,7 @@
         <v>6822</v>
       </c>
       <c r="F72">
-        <v>1113</v>
+        <v>1093</v>
       </c>
       <c r="G72" t="s">
         <v>6857</v>
@@ -33166,7 +33166,7 @@
         <v>6821</v>
       </c>
       <c r="F73">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="G73" t="s">
         <v>6857</v>
@@ -33192,7 +33192,7 @@
         <v>6821</v>
       </c>
       <c r="F74">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="G74" t="s">
         <v>6857</v>
@@ -33270,7 +33270,7 @@
         <v>6822</v>
       </c>
       <c r="F77">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="G77" t="s">
         <v>6857</v>
@@ -33296,7 +33296,7 @@
         <v>6822</v>
       </c>
       <c r="F78">
-        <v>2305</v>
+        <v>2277</v>
       </c>
       <c r="G78" t="s">
         <v>6857</v>
@@ -33322,7 +33322,7 @@
         <v>6822</v>
       </c>
       <c r="F79">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="G79" t="s">
         <v>6857</v>
@@ -33348,7 +33348,7 @@
         <v>6822</v>
       </c>
       <c r="F80">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s">
         <v>6857</v>
@@ -33374,7 +33374,7 @@
         <v>6822</v>
       </c>
       <c r="F81">
-        <v>1646</v>
+        <v>1634</v>
       </c>
       <c r="G81" t="s">
         <v>6857</v>
@@ -33400,7 +33400,7 @@
         <v>6822</v>
       </c>
       <c r="F82">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="G82" t="s">
         <v>6857</v>
@@ -33426,7 +33426,7 @@
         <v>6822</v>
       </c>
       <c r="F83">
-        <v>1363</v>
+        <v>1335</v>
       </c>
       <c r="G83" t="s">
         <v>6857</v>
@@ -33452,7 +33452,7 @@
         <v>6822</v>
       </c>
       <c r="F84">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="G84" t="s">
         <v>6857</v>
@@ -33478,7 +33478,7 @@
         <v>6822</v>
       </c>
       <c r="F85">
-        <v>673</v>
+        <v>653</v>
       </c>
       <c r="G85" t="s">
         <v>6857</v>
@@ -33504,7 +33504,7 @@
         <v>6821</v>
       </c>
       <c r="F86">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="G86" t="s">
         <v>6857</v>
@@ -33530,7 +33530,7 @@
         <v>6821</v>
       </c>
       <c r="F87">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="G87" t="s">
         <v>6857</v>
@@ -33556,7 +33556,7 @@
         <v>6821</v>
       </c>
       <c r="F88">
-        <v>1707</v>
+        <v>1699</v>
       </c>
       <c r="G88" t="s">
         <v>6857</v>
@@ -33582,7 +33582,7 @@
         <v>6821</v>
       </c>
       <c r="F89">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="G89" t="s">
         <v>6857</v>
@@ -33608,7 +33608,7 @@
         <v>6815</v>
       </c>
       <c r="F90">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="G90" t="s">
         <v>6857</v>
@@ -33634,7 +33634,7 @@
         <v>6815</v>
       </c>
       <c r="F91">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G91" t="s">
         <v>6857</v>
@@ -33660,7 +33660,7 @@
         <v>6815</v>
       </c>
       <c r="F92">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="G92" t="s">
         <v>6857</v>
@@ -33686,7 +33686,7 @@
         <v>6815</v>
       </c>
       <c r="F93">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="G93" t="s">
         <v>6857</v>
@@ -33712,7 +33712,7 @@
         <v>6815</v>
       </c>
       <c r="F94">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="G94" t="s">
         <v>6857</v>
@@ -33738,7 +33738,7 @@
         <v>6815</v>
       </c>
       <c r="F95">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="G95" t="s">
         <v>6857</v>
@@ -33764,7 +33764,7 @@
         <v>6815</v>
       </c>
       <c r="F96">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="G96" t="s">
         <v>6857</v>
@@ -33816,7 +33816,7 @@
         <v>6815</v>
       </c>
       <c r="F98">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="G98" t="s">
         <v>6857</v>
@@ -33842,7 +33842,7 @@
         <v>6815</v>
       </c>
       <c r="F99">
-        <v>1762</v>
+        <v>1750</v>
       </c>
       <c r="G99" t="s">
         <v>6857</v>
@@ -33868,7 +33868,7 @@
         <v>6815</v>
       </c>
       <c r="F100">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="G100" t="s">
         <v>6857</v>
@@ -33894,7 +33894,7 @@
         <v>6815</v>
       </c>
       <c r="F101">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="G101" t="s">
         <v>6857</v>
@@ -33966,7 +33966,7 @@
         <v>6815</v>
       </c>
       <c r="F104">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G104" t="s">
         <v>6857</v>
@@ -34012,7 +34012,7 @@
         <v>6819</v>
       </c>
       <c r="F106">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G106" t="s">
         <v>6858</v>
@@ -34112,7 +34112,7 @@
         <v>6816</v>
       </c>
       <c r="F111">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G111" t="s">
         <v>6857</v>
@@ -34138,7 +34138,7 @@
         <v>6816</v>
       </c>
       <c r="F112">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G112" t="s">
         <v>6857</v>
@@ -34164,7 +34164,7 @@
         <v>6816</v>
       </c>
       <c r="F113">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G113" t="s">
         <v>6857</v>
@@ -34190,7 +34190,7 @@
         <v>6816</v>
       </c>
       <c r="F114">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G114" t="s">
         <v>6857</v>
@@ -34216,7 +34216,7 @@
         <v>6816</v>
       </c>
       <c r="F115">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G115" t="s">
         <v>6858</v>
@@ -34236,7 +34236,7 @@
         <v>6816</v>
       </c>
       <c r="F116">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G116" t="s">
         <v>6857</v>
@@ -34288,7 +34288,7 @@
         <v>6815</v>
       </c>
       <c r="F118">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G118" t="s">
         <v>6857</v>
@@ -34334,7 +34334,7 @@
         <v>6815</v>
       </c>
       <c r="F120">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G120" t="s">
         <v>6857</v>
@@ -34590,7 +34590,7 @@
         <v>6815</v>
       </c>
       <c r="F131">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="G131" t="s">
         <v>6857</v>
@@ -34682,7 +34682,7 @@
         <v>6824</v>
       </c>
       <c r="F135">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="G135" t="s">
         <v>6857</v>
@@ -34898,7 +34898,7 @@
         <v>6816</v>
       </c>
       <c r="F144">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="G144" t="s">
         <v>6857</v>
@@ -34924,7 +34924,7 @@
         <v>6825</v>
       </c>
       <c r="F145">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="G145" t="s">
         <v>6857</v>
@@ -35288,7 +35288,7 @@
         <v>6825</v>
       </c>
       <c r="F159">
-        <v>1950</v>
+        <v>1944</v>
       </c>
       <c r="G159" t="s">
         <v>6857</v>
@@ -35314,7 +35314,7 @@
         <v>6825</v>
       </c>
       <c r="F160">
-        <v>1960</v>
+        <v>1950</v>
       </c>
       <c r="G160" t="s">
         <v>6857</v>
@@ -35340,7 +35340,7 @@
         <v>6825</v>
       </c>
       <c r="F161">
-        <v>1692</v>
+        <v>1686</v>
       </c>
       <c r="G161" t="s">
         <v>6857</v>
@@ -35366,7 +35366,7 @@
         <v>6825</v>
       </c>
       <c r="F162">
-        <v>1878</v>
+        <v>1866</v>
       </c>
       <c r="G162" t="s">
         <v>6857</v>
@@ -35418,7 +35418,7 @@
         <v>6813</v>
       </c>
       <c r="F164">
-        <v>1866</v>
+        <v>1860</v>
       </c>
       <c r="G164" t="s">
         <v>6857</v>
@@ -35444,7 +35444,7 @@
         <v>6813</v>
       </c>
       <c r="F165">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="G165" t="s">
         <v>6857</v>
@@ -35470,7 +35470,7 @@
         <v>6813</v>
       </c>
       <c r="F166">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="G166" t="s">
         <v>6857</v>
@@ -35496,7 +35496,7 @@
         <v>6813</v>
       </c>
       <c r="F167">
-        <v>1746</v>
+        <v>1734</v>
       </c>
       <c r="G167" t="s">
         <v>6857</v>
@@ -35548,7 +35548,7 @@
         <v>6825</v>
       </c>
       <c r="F169">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="G169" t="s">
         <v>6857</v>
@@ -35652,7 +35652,7 @@
         <v>6817</v>
       </c>
       <c r="F173">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G173" t="s">
         <v>6857</v>
@@ -35678,7 +35678,7 @@
         <v>6817</v>
       </c>
       <c r="F174">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="G174" t="s">
         <v>6857</v>
@@ -35886,7 +35886,7 @@
         <v>6817</v>
       </c>
       <c r="F182">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="G182" t="s">
         <v>6857</v>
@@ -35912,7 +35912,7 @@
         <v>6816</v>
       </c>
       <c r="F183">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="G183" t="s">
         <v>6857</v>
@@ -36166,7 +36166,7 @@
         <v>6824</v>
       </c>
       <c r="F193">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="G193" t="s">
         <v>6857</v>
@@ -36350,7 +36350,7 @@
         <v>6823</v>
       </c>
       <c r="F201">
-        <v>1397</v>
+        <v>1387</v>
       </c>
       <c r="G201" t="s">
         <v>6857</v>
@@ -36376,7 +36376,7 @@
         <v>6823</v>
       </c>
       <c r="F202">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="G202" t="s">
         <v>6857</v>
@@ -36402,7 +36402,7 @@
         <v>6823</v>
       </c>
       <c r="F203">
-        <v>1277</v>
+        <v>1247</v>
       </c>
       <c r="G203" t="s">
         <v>6857</v>
@@ -36428,7 +36428,7 @@
         <v>6823</v>
       </c>
       <c r="F204">
-        <v>1093</v>
+        <v>1073</v>
       </c>
       <c r="G204" t="s">
         <v>6857</v>
@@ -36454,7 +36454,7 @@
         <v>6823</v>
       </c>
       <c r="F205">
-        <v>2426</v>
+        <v>2416</v>
       </c>
       <c r="G205" t="s">
         <v>6857</v>
@@ -36480,7 +36480,7 @@
         <v>6823</v>
       </c>
       <c r="F206">
-        <v>3522</v>
+        <v>3502</v>
       </c>
       <c r="G206" t="s">
         <v>6857</v>
@@ -36506,7 +36506,7 @@
         <v>6823</v>
       </c>
       <c r="F207">
-        <v>1528</v>
+        <v>1518</v>
       </c>
       <c r="G207" t="s">
         <v>6857</v>
@@ -36688,7 +36688,7 @@
         <v>6827</v>
       </c>
       <c r="F214">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G214" t="s">
         <v>6857</v>
@@ -36766,7 +36766,7 @@
         <v>6827</v>
       </c>
       <c r="F217">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="G217" t="s">
         <v>6857</v>
@@ -36792,7 +36792,7 @@
         <v>6827</v>
       </c>
       <c r="F218">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="G218" t="s">
         <v>6857</v>
@@ -36818,7 +36818,7 @@
         <v>6828</v>
       </c>
       <c r="F219">
-        <v>2324</v>
+        <v>2316</v>
       </c>
       <c r="G219" t="s">
         <v>6857</v>
@@ -36916,7 +36916,7 @@
         <v>6816</v>
       </c>
       <c r="F223">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G223" t="s">
         <v>6857</v>
@@ -36994,7 +36994,7 @@
         <v>6816</v>
       </c>
       <c r="F226">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G226" t="s">
         <v>6857</v>
@@ -37046,7 +37046,7 @@
         <v>6816</v>
       </c>
       <c r="F228">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G228" t="s">
         <v>6857</v>
@@ -37072,7 +37072,7 @@
         <v>6816</v>
       </c>
       <c r="F229">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G229" t="s">
         <v>6857</v>
@@ -37098,7 +37098,7 @@
         <v>6816</v>
       </c>
       <c r="F230">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G230" t="s">
         <v>6857</v>
@@ -37176,7 +37176,7 @@
         <v>6824</v>
       </c>
       <c r="F233">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G233" t="s">
         <v>6858</v>
@@ -37216,7 +37216,7 @@
         <v>6824</v>
       </c>
       <c r="F235">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G235" t="s">
         <v>6858</v>
@@ -37236,7 +37236,7 @@
         <v>6824</v>
       </c>
       <c r="F236">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="G236" t="s">
         <v>6858</v>
@@ -37256,7 +37256,7 @@
         <v>6824</v>
       </c>
       <c r="F237">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G237" t="s">
         <v>6858</v>
@@ -37276,7 +37276,7 @@
         <v>6824</v>
       </c>
       <c r="F238">
-        <v>1800</v>
+        <v>1794</v>
       </c>
       <c r="G238" t="s">
         <v>6858</v>
@@ -37296,7 +37296,7 @@
         <v>6824</v>
       </c>
       <c r="F239">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="G239" t="s">
         <v>6858</v>
@@ -37316,7 +37316,7 @@
         <v>6815</v>
       </c>
       <c r="F240">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G240" t="s">
         <v>6857</v>
@@ -37342,7 +37342,7 @@
         <v>6815</v>
       </c>
       <c r="F241">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G241" t="s">
         <v>6857</v>
@@ -37394,7 +37394,7 @@
         <v>6815</v>
       </c>
       <c r="F243">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G243" t="s">
         <v>6857</v>
@@ -37440,7 +37440,7 @@
         <v>6824</v>
       </c>
       <c r="F245">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="G245" t="s">
         <v>6858</v>
@@ -37460,7 +37460,7 @@
         <v>6824</v>
       </c>
       <c r="F246">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G246" t="s">
         <v>6858</v>
@@ -37606,7 +37606,7 @@
         <v>6823</v>
       </c>
       <c r="F253">
-        <v>3230</v>
+        <v>3220</v>
       </c>
       <c r="G253" t="s">
         <v>6857</v>
@@ -37632,7 +37632,7 @@
         <v>6823</v>
       </c>
       <c r="F254">
-        <v>1611</v>
+        <v>1596</v>
       </c>
       <c r="G254" t="s">
         <v>6857</v>
@@ -37658,7 +37658,7 @@
         <v>6823</v>
       </c>
       <c r="F255">
-        <v>3735</v>
+        <v>3725</v>
       </c>
       <c r="G255" t="s">
         <v>6857</v>
@@ -37736,7 +37736,7 @@
         <v>6823</v>
       </c>
       <c r="F258">
-        <v>2190</v>
+        <v>2170</v>
       </c>
       <c r="G258" t="s">
         <v>6858</v>
@@ -37796,7 +37796,7 @@
         <v>6815</v>
       </c>
       <c r="F261">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G261" t="s">
         <v>6858</v>
@@ -37842,7 +37842,7 @@
         <v>6827</v>
       </c>
       <c r="F263">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="G263" t="s">
         <v>6857</v>
@@ -37868,7 +37868,7 @@
         <v>6827</v>
       </c>
       <c r="F264">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G264" t="s">
         <v>6857</v>
@@ -37894,7 +37894,7 @@
         <v>6827</v>
       </c>
       <c r="F265">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G265" t="s">
         <v>6857</v>
@@ -37920,7 +37920,7 @@
         <v>6823</v>
       </c>
       <c r="F266">
-        <v>3756</v>
+        <v>3741</v>
       </c>
       <c r="G266" t="s">
         <v>6857</v>
@@ -37946,7 +37946,7 @@
         <v>6827</v>
       </c>
       <c r="F267">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G267" t="s">
         <v>6857</v>
@@ -37998,7 +37998,7 @@
         <v>6827</v>
       </c>
       <c r="F269">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="G269" t="s">
         <v>6857</v>
@@ -38050,7 +38050,7 @@
         <v>6823</v>
       </c>
       <c r="F271">
-        <v>2894</v>
+        <v>2879</v>
       </c>
       <c r="G271" t="s">
         <v>6857</v>
@@ -38128,7 +38128,7 @@
         <v>6823</v>
       </c>
       <c r="F274">
-        <v>982</v>
+        <v>972</v>
       </c>
       <c r="G274" t="s">
         <v>6857</v>
@@ -38154,7 +38154,7 @@
         <v>6827</v>
       </c>
       <c r="F275">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="G275" t="s">
         <v>6857</v>
@@ -38180,7 +38180,7 @@
         <v>6827</v>
       </c>
       <c r="F276">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G276" t="s">
         <v>6857</v>
@@ -38206,7 +38206,7 @@
         <v>6827</v>
       </c>
       <c r="F277">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="G277" t="s">
         <v>6857</v>
@@ -38232,7 +38232,7 @@
         <v>6827</v>
       </c>
       <c r="F278">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G278" t="s">
         <v>6857</v>
@@ -38258,7 +38258,7 @@
         <v>6827</v>
       </c>
       <c r="F279">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="G279" t="s">
         <v>6857</v>
@@ -38284,7 +38284,7 @@
         <v>6827</v>
       </c>
       <c r="F280">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G280" t="s">
         <v>6857</v>
@@ -38310,7 +38310,7 @@
         <v>6827</v>
       </c>
       <c r="F281">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="G281" t="s">
         <v>6857</v>
@@ -38414,7 +38414,7 @@
         <v>6815</v>
       </c>
       <c r="F285">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G285" t="s">
         <v>6857</v>
@@ -38440,7 +38440,7 @@
         <v>6815</v>
       </c>
       <c r="F286">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G286" t="s">
         <v>6857</v>
@@ -38492,7 +38492,7 @@
         <v>6815</v>
       </c>
       <c r="F288">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G288" t="s">
         <v>6858</v>
@@ -38512,7 +38512,7 @@
         <v>6815</v>
       </c>
       <c r="F289">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="G289" t="s">
         <v>6857</v>
@@ -38590,7 +38590,7 @@
         <v>6816</v>
       </c>
       <c r="F292">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G292" t="s">
         <v>6857</v>
@@ -38642,7 +38642,7 @@
         <v>6815</v>
       </c>
       <c r="F294">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G294" t="s">
         <v>6857</v>
@@ -38668,7 +38668,7 @@
         <v>6823</v>
       </c>
       <c r="F295">
-        <v>2250</v>
+        <v>2230</v>
       </c>
       <c r="G295" t="s">
         <v>6858</v>
@@ -38740,7 +38740,7 @@
         <v>6823</v>
       </c>
       <c r="F298">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="G298" t="s">
         <v>6857</v>
@@ -38766,7 +38766,7 @@
         <v>6823</v>
       </c>
       <c r="F299">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="G299" t="s">
         <v>6857</v>
@@ -38792,7 +38792,7 @@
         <v>6823</v>
       </c>
       <c r="F300">
-        <v>609</v>
+        <v>569</v>
       </c>
       <c r="G300" t="s">
         <v>6857</v>
@@ -38844,7 +38844,7 @@
         <v>6823</v>
       </c>
       <c r="F302">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="G302" t="s">
         <v>6857</v>
@@ -38870,7 +38870,7 @@
         <v>6815</v>
       </c>
       <c r="F303">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G303" t="s">
         <v>6857</v>
@@ -38896,7 +38896,7 @@
         <v>6830</v>
       </c>
       <c r="F304">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="G304" t="s">
         <v>6857</v>
@@ -38922,7 +38922,7 @@
         <v>6831</v>
       </c>
       <c r="F305">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="G305" t="s">
         <v>6857</v>
@@ -38948,7 +38948,7 @@
         <v>6832</v>
       </c>
       <c r="F306">
-        <v>1269</v>
+        <v>1251</v>
       </c>
       <c r="G306" t="s">
         <v>6857</v>
@@ -38974,7 +38974,7 @@
         <v>6833</v>
       </c>
       <c r="F307">
-        <v>4278</v>
+        <v>4266</v>
       </c>
       <c r="G307" t="s">
         <v>6857</v>
@@ -39000,7 +39000,7 @@
         <v>6825</v>
       </c>
       <c r="F308">
-        <v>1852</v>
+        <v>1846</v>
       </c>
       <c r="G308" t="s">
         <v>6857</v>
@@ -39026,7 +39026,7 @@
         <v>6825</v>
       </c>
       <c r="F309">
-        <v>1762</v>
+        <v>1752</v>
       </c>
       <c r="G309" t="s">
         <v>6857</v>
@@ -39078,7 +39078,7 @@
         <v>6825</v>
       </c>
       <c r="F311">
-        <v>1786</v>
+        <v>1774</v>
       </c>
       <c r="G311" t="s">
         <v>6857</v>
@@ -39130,7 +39130,7 @@
         <v>6825</v>
       </c>
       <c r="F313">
-        <v>1864</v>
+        <v>1854</v>
       </c>
       <c r="G313" t="s">
         <v>6857</v>
@@ -39182,7 +39182,7 @@
         <v>6815</v>
       </c>
       <c r="F315">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G315" t="s">
         <v>6857</v>
@@ -39260,7 +39260,7 @@
         <v>6825</v>
       </c>
       <c r="F318">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="G318" t="s">
         <v>6857</v>
@@ -39312,7 +39312,7 @@
         <v>6816</v>
       </c>
       <c r="F320">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G320" t="s">
         <v>6857</v>
@@ -39378,7 +39378,7 @@
         <v>6815</v>
       </c>
       <c r="F323">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G323" t="s">
         <v>6857</v>
@@ -39576,7 +39576,7 @@
         <v>6813</v>
       </c>
       <c r="F332">
-        <v>1836</v>
+        <v>1830</v>
       </c>
       <c r="G332" t="s">
         <v>6857</v>
@@ -39602,7 +39602,7 @@
         <v>6815</v>
       </c>
       <c r="F333">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G333" t="s">
         <v>6857</v>
@@ -39628,7 +39628,7 @@
         <v>6813</v>
       </c>
       <c r="F334">
-        <v>1763</v>
+        <v>1757</v>
       </c>
       <c r="G334" t="s">
         <v>6857</v>
@@ -39732,7 +39732,7 @@
         <v>6834</v>
       </c>
       <c r="F338">
-        <v>3989</v>
+        <v>3981</v>
       </c>
       <c r="G338" t="s">
         <v>6857</v>
@@ -39758,7 +39758,7 @@
         <v>6834</v>
       </c>
       <c r="F339">
-        <v>4204</v>
+        <v>4200</v>
       </c>
       <c r="G339" t="s">
         <v>6857</v>
@@ -39784,7 +39784,7 @@
         <v>6835</v>
       </c>
       <c r="F340">
-        <v>3205</v>
+        <v>3195</v>
       </c>
       <c r="G340" t="s">
         <v>6857</v>
@@ -39968,7 +39968,7 @@
         <v>6837</v>
       </c>
       <c r="F348">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="G348" t="s">
         <v>6858</v>
@@ -39988,7 +39988,7 @@
         <v>6815</v>
       </c>
       <c r="F349">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="G349" t="s">
         <v>6857</v>
@@ -40080,7 +40080,7 @@
         <v>6837</v>
       </c>
       <c r="F353">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G353" t="s">
         <v>6858</v>
@@ -40300,7 +40300,7 @@
         <v>6838</v>
       </c>
       <c r="F364">
-        <v>1320</v>
+        <v>1284</v>
       </c>
       <c r="G364" t="s">
         <v>6857</v>
@@ -40372,7 +40372,7 @@
         <v>6837</v>
       </c>
       <c r="F367">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G367" t="s">
         <v>6858</v>
@@ -40392,7 +40392,7 @@
         <v>6837</v>
       </c>
       <c r="F368">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G368" t="s">
         <v>6858</v>
@@ -40536,7 +40536,7 @@
         <v>6838</v>
       </c>
       <c r="F374">
-        <v>1644</v>
+        <v>1632</v>
       </c>
       <c r="G374" t="s">
         <v>6857</v>
@@ -40634,7 +40634,7 @@
         <v>6838</v>
       </c>
       <c r="F378">
-        <v>1585</v>
+        <v>1573</v>
       </c>
       <c r="G378" t="s">
         <v>6857</v>
@@ -40706,7 +40706,7 @@
         <v>6837</v>
       </c>
       <c r="F381">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G381" t="s">
         <v>6858</v>
@@ -40896,7 +40896,7 @@
         <v>6838</v>
       </c>
       <c r="F389">
-        <v>1729</v>
+        <v>1717</v>
       </c>
       <c r="G389" t="s">
         <v>6858</v>
@@ -41008,7 +41008,7 @@
         <v>6838</v>
       </c>
       <c r="F394">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="G394" t="s">
         <v>6857</v>
@@ -41034,7 +41034,7 @@
         <v>6815</v>
       </c>
       <c r="F395">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G395" t="s">
         <v>6857</v>
@@ -44364,7 +44364,7 @@
         <v>6819</v>
       </c>
       <c r="F524">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="G524" t="s">
         <v>6857</v>
@@ -44410,7 +44410,7 @@
         <v>6837</v>
       </c>
       <c r="F526">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G526" t="s">
         <v>6857</v>
@@ -44724,7 +44724,7 @@
         <v>6837</v>
       </c>
       <c r="F539">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="G539" t="s">
         <v>6857</v>
@@ -44750,7 +44750,7 @@
         <v>6837</v>
       </c>
       <c r="F540">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G540" t="s">
         <v>6857</v>
@@ -44932,7 +44932,7 @@
         <v>6837</v>
       </c>
       <c r="F547">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G547" t="s">
         <v>6857</v>
@@ -45186,7 +45186,7 @@
         <v>6839</v>
       </c>
       <c r="F557">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G557" t="s">
         <v>6857</v>
@@ -48610,7 +48610,7 @@
         <v>6828</v>
       </c>
       <c r="F694">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G694" t="s">
         <v>6857</v>
@@ -48714,7 +48714,7 @@
         <v>6828</v>
       </c>
       <c r="F698">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G698" t="s">
         <v>6857</v>
@@ -48766,7 +48766,7 @@
         <v>6828</v>
       </c>
       <c r="F700">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="G700" t="s">
         <v>6857</v>
@@ -48968,7 +48968,7 @@
         <v>6828</v>
       </c>
       <c r="F708">
-        <v>2132</v>
+        <v>2126</v>
       </c>
       <c r="G708" t="s">
         <v>6857</v>
@@ -49228,7 +49228,7 @@
         <v>6828</v>
       </c>
       <c r="F718">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G718" t="s">
         <v>6857</v>
@@ -49280,7 +49280,7 @@
         <v>6828</v>
       </c>
       <c r="F720">
-        <v>2929</v>
+        <v>2923</v>
       </c>
       <c r="G720" t="s">
         <v>6857</v>
@@ -49462,7 +49462,7 @@
         <v>6828</v>
       </c>
       <c r="F727">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="G727" t="s">
         <v>6857</v>
@@ -49488,7 +49488,7 @@
         <v>6828</v>
       </c>
       <c r="F728">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="G728" t="s">
         <v>6857</v>
@@ -49644,7 +49644,7 @@
         <v>6828</v>
       </c>
       <c r="F734">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G734" t="s">
         <v>6857</v>
@@ -49722,7 +49722,7 @@
         <v>6828</v>
       </c>
       <c r="F737">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G737" t="s">
         <v>6858</v>
@@ -50048,7 +50048,7 @@
         <v>6845</v>
       </c>
       <c r="F750">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="G750" t="s">
         <v>6857</v>
@@ -50178,7 +50178,7 @@
         <v>6845</v>
       </c>
       <c r="F755">
-        <v>1641</v>
+        <v>1617</v>
       </c>
       <c r="G755" t="s">
         <v>6857</v>
@@ -51192,7 +51192,7 @@
         <v>6823</v>
       </c>
       <c r="F794">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G794" t="s">
         <v>6857</v>
@@ -51218,7 +51218,7 @@
         <v>6814</v>
       </c>
       <c r="F795">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G795" t="s">
         <v>6858</v>
@@ -51238,7 +51238,7 @@
         <v>6814</v>
       </c>
       <c r="F796">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="G796" t="s">
         <v>6858</v>
@@ -51258,7 +51258,7 @@
         <v>6814</v>
       </c>
       <c r="F797">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="G797" t="s">
         <v>6858</v>
@@ -51650,7 +51650,7 @@
         <v>6814</v>
       </c>
       <c r="F813">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G813" t="s">
         <v>6858</v>
@@ -52410,7 +52410,7 @@
         <v>6823</v>
       </c>
       <c r="F851">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="G851" t="s">
         <v>6857</v>
@@ -52488,7 +52488,7 @@
         <v>6845</v>
       </c>
       <c r="F854">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="G854" t="s">
         <v>6858</v>
@@ -52508,7 +52508,7 @@
         <v>6845</v>
       </c>
       <c r="F855">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="G855" t="s">
         <v>6858</v>
@@ -52528,7 +52528,7 @@
         <v>6845</v>
       </c>
       <c r="F856">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="G856" t="s">
         <v>6858</v>
@@ -52548,7 +52548,7 @@
         <v>6845</v>
       </c>
       <c r="F857">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="G857" t="s">
         <v>6858</v>
@@ -52568,7 +52568,7 @@
         <v>6845</v>
       </c>
       <c r="F858">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="G858" t="s">
         <v>6858</v>
@@ -52628,7 +52628,7 @@
         <v>6845</v>
       </c>
       <c r="F861">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G861" t="s">
         <v>6858</v>
@@ -52688,7 +52688,7 @@
         <v>6845</v>
       </c>
       <c r="F864">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="G864" t="s">
         <v>6858</v>
@@ -52708,7 +52708,7 @@
         <v>6845</v>
       </c>
       <c r="F865">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G865" t="s">
         <v>6858</v>
@@ -52748,7 +52748,7 @@
         <v>6845</v>
       </c>
       <c r="F867">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="G867" t="s">
         <v>6858</v>
@@ -52768,7 +52768,7 @@
         <v>6845</v>
       </c>
       <c r="F868">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="G868" t="s">
         <v>6858</v>
@@ -52808,7 +52808,7 @@
         <v>6845</v>
       </c>
       <c r="F870">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="G870" t="s">
         <v>6858</v>
@@ -52828,7 +52828,7 @@
         <v>6845</v>
       </c>
       <c r="F871">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="G871" t="s">
         <v>6858</v>
@@ -52848,7 +52848,7 @@
         <v>6845</v>
       </c>
       <c r="F872">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="G872" t="s">
         <v>6858</v>
@@ -52868,7 +52868,7 @@
         <v>6845</v>
       </c>
       <c r="F873">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="G873" t="s">
         <v>6858</v>
@@ -52888,7 +52888,7 @@
         <v>6845</v>
       </c>
       <c r="F874">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="G874" t="s">
         <v>6857</v>
@@ -53026,7 +53026,7 @@
         <v>6845</v>
       </c>
       <c r="F880">
-        <v>1904</v>
+        <v>1886</v>
       </c>
       <c r="G880" t="s">
         <v>6857</v>
@@ -53052,7 +53052,7 @@
         <v>6845</v>
       </c>
       <c r="F881">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G881" t="s">
         <v>6857</v>
@@ -53078,7 +53078,7 @@
         <v>6845</v>
       </c>
       <c r="F882">
-        <v>860</v>
+        <v>842</v>
       </c>
       <c r="G882" t="s">
         <v>6857</v>
@@ -53104,7 +53104,7 @@
         <v>6845</v>
       </c>
       <c r="F883">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="G883" t="s">
         <v>6858</v>
@@ -53124,7 +53124,7 @@
         <v>6845</v>
       </c>
       <c r="F884">
-        <v>821</v>
+        <v>803</v>
       </c>
       <c r="G884" t="s">
         <v>6857</v>
@@ -53150,7 +53150,7 @@
         <v>6845</v>
       </c>
       <c r="F885">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="G885" t="s">
         <v>6857</v>
@@ -53176,7 +53176,7 @@
         <v>6845</v>
       </c>
       <c r="F886">
-        <v>1852</v>
+        <v>1840</v>
       </c>
       <c r="G886" t="s">
         <v>6857</v>
@@ -53202,7 +53202,7 @@
         <v>6845</v>
       </c>
       <c r="F887">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="G887" t="s">
         <v>6857</v>
@@ -53228,7 +53228,7 @@
         <v>6845</v>
       </c>
       <c r="F888">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G888" t="s">
         <v>6858</v>
@@ -53248,7 +53248,7 @@
         <v>6845</v>
       </c>
       <c r="F889">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="G889" t="s">
         <v>6858</v>
@@ -53268,7 +53268,7 @@
         <v>6845</v>
       </c>
       <c r="F890">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G890" t="s">
         <v>6858</v>
@@ -53314,7 +53314,7 @@
         <v>6845</v>
       </c>
       <c r="F892">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G892" t="s">
         <v>6857</v>
@@ -53366,7 +53366,7 @@
         <v>6814</v>
       </c>
       <c r="F894">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G894" t="s">
         <v>6857</v>
@@ -53392,7 +53392,7 @@
         <v>6814</v>
       </c>
       <c r="F895">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G895" t="s">
         <v>6857</v>
@@ -53470,7 +53470,7 @@
         <v>6814</v>
       </c>
       <c r="F898">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G898" t="s">
         <v>6857</v>
@@ -53548,7 +53548,7 @@
         <v>6845</v>
       </c>
       <c r="F901">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="G901" t="s">
         <v>6858</v>
@@ -53568,7 +53568,7 @@
         <v>6823</v>
       </c>
       <c r="F902">
-        <v>923</v>
+        <v>913</v>
       </c>
       <c r="G902" t="s">
         <v>6857</v>
@@ -53764,7 +53764,7 @@
         <v>6845</v>
       </c>
       <c r="F910">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="G910" t="s">
         <v>6857</v>
@@ -53842,7 +53842,7 @@
         <v>6845</v>
       </c>
       <c r="F913">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="G913" t="s">
         <v>6857</v>
@@ -53920,7 +53920,7 @@
         <v>6845</v>
       </c>
       <c r="F916">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="G916" t="s">
         <v>6857</v>
@@ -53998,7 +53998,7 @@
         <v>6845</v>
       </c>
       <c r="F919">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="G919" t="s">
         <v>6857</v>
@@ -54070,7 +54070,7 @@
         <v>6845</v>
       </c>
       <c r="F922">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="G922" t="s">
         <v>6857</v>
@@ -54122,7 +54122,7 @@
         <v>6845</v>
       </c>
       <c r="F924">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G924" t="s">
         <v>6857</v>
@@ -54148,7 +54148,7 @@
         <v>6845</v>
       </c>
       <c r="F925">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="G925" t="s">
         <v>6857</v>
@@ -54488,7 +54488,7 @@
         <v>6815</v>
       </c>
       <c r="F939">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G939" t="s">
         <v>6857</v>
@@ -54514,7 +54514,7 @@
         <v>6815</v>
       </c>
       <c r="F940">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G940" t="s">
         <v>6857</v>
@@ -54540,7 +54540,7 @@
         <v>6815</v>
       </c>
       <c r="F941">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G941" t="s">
         <v>6857</v>
@@ -54618,7 +54618,7 @@
         <v>6815</v>
       </c>
       <c r="F944">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G944" t="s">
         <v>6857</v>
@@ -54644,7 +54644,7 @@
         <v>6815</v>
       </c>
       <c r="F945">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G945" t="s">
         <v>6857</v>
@@ -54748,7 +54748,7 @@
         <v>6828</v>
       </c>
       <c r="F949">
-        <v>2195</v>
+        <v>2189</v>
       </c>
       <c r="G949" t="s">
         <v>6857</v>
@@ -55090,7 +55090,7 @@
         <v>6815</v>
       </c>
       <c r="F964">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G964" t="s">
         <v>6857</v>
@@ -55298,7 +55298,7 @@
         <v>6815</v>
       </c>
       <c r="F972">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G972" t="s">
         <v>6857</v>
@@ -55428,7 +55428,7 @@
         <v>6815</v>
       </c>
       <c r="F977">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G977" t="s">
         <v>6857</v>
@@ -55578,7 +55578,7 @@
         <v>6815</v>
       </c>
       <c r="F983">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G983" t="s">
         <v>6857</v>
@@ -55858,7 +55858,7 @@
         <v>6815</v>
       </c>
       <c r="F994">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G994" t="s">
         <v>6857</v>
@@ -55953,7 +55953,7 @@
         <v>6819</v>
       </c>
       <c r="F998">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G998" t="s">
         <v>6858</v>
@@ -56071,7 +56071,7 @@
         <v>6819</v>
       </c>
       <c r="F1003">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G1003" t="s">
         <v>6857</v>
@@ -56163,7 +56163,7 @@
         <v>6819</v>
       </c>
       <c r="F1007">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1007" t="s">
         <v>6857</v>
@@ -56232,7 +56232,7 @@
         <v>6815</v>
       </c>
       <c r="F1010">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G1010" t="s">
         <v>6857</v>
@@ -56284,7 +56284,7 @@
         <v>6848</v>
       </c>
       <c r="F1012">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="G1012" t="s">
         <v>6857</v>
@@ -56310,7 +56310,7 @@
         <v>6849</v>
       </c>
       <c r="F1013">
-        <v>5792</v>
+        <v>5786</v>
       </c>
       <c r="G1013" t="s">
         <v>6857</v>
@@ -56434,7 +56434,7 @@
         <v>6815</v>
       </c>
       <c r="F1018">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G1018" t="s">
         <v>6857</v>
@@ -56503,7 +56503,7 @@
         <v>6815</v>
       </c>
       <c r="F1021">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1021" t="s">
         <v>6857</v>
@@ -56529,7 +56529,7 @@
         <v>6815</v>
       </c>
       <c r="F1022">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G1022" t="s">
         <v>6857</v>
@@ -56581,7 +56581,7 @@
         <v>6815</v>
       </c>
       <c r="F1024">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G1024" t="s">
         <v>6857</v>
@@ -56627,7 +56627,7 @@
         <v>6815</v>
       </c>
       <c r="F1026">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G1026" t="s">
         <v>6857</v>
@@ -56731,7 +56731,7 @@
         <v>6826</v>
       </c>
       <c r="F1030">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="G1030" t="s">
         <v>6858</v>
@@ -56771,7 +56771,7 @@
         <v>6841</v>
       </c>
       <c r="F1032">
-        <v>1468</v>
+        <v>1456</v>
       </c>
       <c r="G1032" t="s">
         <v>6858</v>
@@ -56791,7 +56791,7 @@
         <v>6826</v>
       </c>
       <c r="F1033">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="G1033" t="s">
         <v>6858</v>
@@ -56911,7 +56911,7 @@
         <v>6826</v>
       </c>
       <c r="F1039">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="G1039" t="s">
         <v>6858</v>
@@ -57051,7 +57051,7 @@
         <v>6841</v>
       </c>
       <c r="F1046">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G1046" t="s">
         <v>6857</v>
@@ -57207,7 +57207,7 @@
         <v>6837</v>
       </c>
       <c r="F1052">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G1052" t="s">
         <v>6857</v>
@@ -57535,7 +57535,7 @@
         <v>6848</v>
       </c>
       <c r="F1066">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="G1066" t="s">
         <v>6857</v>
@@ -57653,7 +57653,7 @@
         <v>6828</v>
       </c>
       <c r="F1071">
-        <v>2133</v>
+        <v>2129</v>
       </c>
       <c r="G1071" t="s">
         <v>6857</v>
@@ -58133,7 +58133,7 @@
         <v>6815</v>
       </c>
       <c r="F1092">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G1092" t="s">
         <v>6857</v>
@@ -58211,7 +58211,7 @@
         <v>6815</v>
       </c>
       <c r="F1095">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1095" t="s">
         <v>6857</v>
@@ -58927,7 +58927,7 @@
         <v>6850</v>
       </c>
       <c r="F1123">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="G1123" t="s">
         <v>6857</v>
@@ -59273,7 +59273,7 @@
         <v>6850</v>
       </c>
       <c r="F1137">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G1137" t="s">
         <v>6857</v>
@@ -59645,7 +59645,7 @@
         <v>6837</v>
       </c>
       <c r="F1152">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="G1152" t="s">
         <v>6857</v>
@@ -59723,7 +59723,7 @@
         <v>6837</v>
       </c>
       <c r="F1155">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G1155" t="s">
         <v>6857</v>
@@ -59749,7 +59749,7 @@
         <v>6837</v>
       </c>
       <c r="F1156">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G1156" t="s">
         <v>6857</v>
@@ -59879,7 +59879,7 @@
         <v>6837</v>
       </c>
       <c r="F1161">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="G1161" t="s">
         <v>6857</v>
@@ -60263,7 +60263,7 @@
         <v>6837</v>
       </c>
       <c r="F1176">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="G1176" t="s">
         <v>6857</v>
@@ -60341,7 +60341,7 @@
         <v>6837</v>
       </c>
       <c r="F1179">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G1179" t="s">
         <v>6857</v>
@@ -60367,7 +60367,7 @@
         <v>6837</v>
       </c>
       <c r="F1180">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G1180" t="s">
         <v>6857</v>
@@ -60419,7 +60419,7 @@
         <v>6837</v>
       </c>
       <c r="F1182">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="G1182" t="s">
         <v>6857</v>
@@ -61025,7 +61025,7 @@
         <v>6851</v>
       </c>
       <c r="F1206">
-        <v>8216</v>
+        <v>8168</v>
       </c>
       <c r="G1206" t="s">
         <v>6857</v>
@@ -61103,7 +61103,7 @@
         <v>6824</v>
       </c>
       <c r="F1209">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="G1209" t="s">
         <v>6857</v>
@@ -61363,7 +61363,7 @@
         <v>6846</v>
       </c>
       <c r="F1219">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G1219" t="s">
         <v>6857</v>
@@ -61809,7 +61809,7 @@
         <v>6826</v>
       </c>
       <c r="F1241">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G1241" t="s">
         <v>6858</v>
@@ -62129,7 +62129,7 @@
         <v>6828</v>
       </c>
       <c r="F1257">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="G1257" t="s">
         <v>6857</v>
@@ -62221,7 +62221,7 @@
         <v>6828</v>
       </c>
       <c r="F1261">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G1261" t="s">
         <v>6857</v>
@@ -62429,7 +62429,7 @@
         <v>6846</v>
       </c>
       <c r="F1269">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="G1269" t="s">
         <v>6857</v>
@@ -62455,7 +62455,7 @@
         <v>6846</v>
       </c>
       <c r="F1270">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="G1270" t="s">
         <v>6857</v>
@@ -62501,7 +62501,7 @@
         <v>6823</v>
       </c>
       <c r="F1272">
-        <v>1411</v>
+        <v>1381</v>
       </c>
       <c r="G1272" t="s">
         <v>6857</v>
@@ -62527,7 +62527,7 @@
         <v>6823</v>
       </c>
       <c r="F1273">
-        <v>2091</v>
+        <v>2085</v>
       </c>
       <c r="G1273" t="s">
         <v>6857</v>
@@ -62579,7 +62579,7 @@
         <v>6823</v>
       </c>
       <c r="F1275">
-        <v>2015</v>
+        <v>1997</v>
       </c>
       <c r="G1275" t="s">
         <v>6857</v>
@@ -62605,7 +62605,7 @@
         <v>6823</v>
       </c>
       <c r="F1276">
-        <v>1826</v>
+        <v>1820</v>
       </c>
       <c r="G1276" t="s">
         <v>6857</v>
@@ -62631,7 +62631,7 @@
         <v>6823</v>
       </c>
       <c r="F1277">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="G1277" t="s">
         <v>6857</v>
@@ -62657,7 +62657,7 @@
         <v>6823</v>
       </c>
       <c r="F1278">
-        <v>1528</v>
+        <v>1510</v>
       </c>
       <c r="G1278" t="s">
         <v>6857</v>
@@ -64275,7 +64275,7 @@
         <v>6815</v>
       </c>
       <c r="F1343">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G1343" t="s">
         <v>6857</v>
@@ -64327,7 +64327,7 @@
         <v>6815</v>
       </c>
       <c r="F1345">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G1345" t="s">
         <v>6857</v>
@@ -64353,7 +64353,7 @@
         <v>6815</v>
       </c>
       <c r="F1346">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G1346" t="s">
         <v>6857</v>
@@ -64405,7 +64405,7 @@
         <v>6815</v>
       </c>
       <c r="F1348">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1348" t="s">
         <v>6857</v>
@@ -65251,7 +65251,7 @@
         <v>6852</v>
       </c>
       <c r="F1387">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="G1387" t="s">
         <v>6857</v>
@@ -65329,7 +65329,7 @@
         <v>6852</v>
       </c>
       <c r="F1390">
-        <v>3633</v>
+        <v>3615</v>
       </c>
       <c r="G1390" t="s">
         <v>6857</v>
@@ -65355,7 +65355,7 @@
         <v>6852</v>
       </c>
       <c r="F1391">
-        <v>7815</v>
+        <v>7707</v>
       </c>
       <c r="G1391" t="s">
         <v>6857</v>
@@ -65407,7 +65407,7 @@
         <v>6852</v>
       </c>
       <c r="F1393">
-        <v>6774</v>
+        <v>6738</v>
       </c>
       <c r="G1393" t="s">
         <v>6857</v>
@@ -65511,7 +65511,7 @@
         <v>6823</v>
       </c>
       <c r="F1397">
-        <v>2843</v>
+        <v>2833</v>
       </c>
       <c r="G1397" t="s">
         <v>6857</v>
@@ -65537,7 +65537,7 @@
         <v>6823</v>
       </c>
       <c r="F1398">
-        <v>3391</v>
+        <v>3371</v>
       </c>
       <c r="G1398" t="s">
         <v>6857</v>
@@ -65563,7 +65563,7 @@
         <v>6823</v>
       </c>
       <c r="F1399">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="G1399" t="s">
         <v>6857</v>
@@ -65771,7 +65771,7 @@
         <v>6823</v>
       </c>
       <c r="F1407">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="G1407" t="s">
         <v>6857</v>
@@ -65797,7 +65797,7 @@
         <v>6823</v>
       </c>
       <c r="F1408">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="G1408" t="s">
         <v>6857</v>
@@ -65849,7 +65849,7 @@
         <v>6823</v>
       </c>
       <c r="F1410">
-        <v>4881</v>
+        <v>4876</v>
       </c>
       <c r="G1410" t="s">
         <v>6857</v>
@@ -65927,7 +65927,7 @@
         <v>6852</v>
       </c>
       <c r="F1413">
-        <v>3045</v>
+        <v>3027</v>
       </c>
       <c r="G1413" t="s">
         <v>6857</v>
@@ -66161,7 +66161,7 @@
         <v>6853</v>
       </c>
       <c r="F1422">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="G1422" t="s">
         <v>6857</v>
@@ -66559,7 +66559,7 @@
         <v>6853</v>
       </c>
       <c r="F1438">
-        <v>1683</v>
+        <v>1675</v>
       </c>
       <c r="G1438" t="s">
         <v>6857</v>
@@ -66657,7 +66657,7 @@
         <v>6850</v>
       </c>
       <c r="F1442">
-        <v>8063</v>
+        <v>8039</v>
       </c>
       <c r="G1442" t="s">
         <v>6857</v>
@@ -66729,7 +66729,7 @@
         <v>6850</v>
       </c>
       <c r="F1445">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="G1445" t="s">
         <v>6857</v>
@@ -66853,7 +66853,7 @@
         <v>6850</v>
       </c>
       <c r="F1450">
-        <v>2551</v>
+        <v>2527</v>
       </c>
       <c r="G1450" t="s">
         <v>6857</v>
@@ -66879,7 +66879,7 @@
         <v>6850</v>
       </c>
       <c r="F1451">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="G1451" t="s">
         <v>6857</v>
@@ -66983,7 +66983,7 @@
         <v>6850</v>
       </c>
       <c r="F1455">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="G1455" t="s">
         <v>6857</v>
@@ -67035,7 +67035,7 @@
         <v>6850</v>
       </c>
       <c r="F1457">
-        <v>1324</v>
+        <v>1276</v>
       </c>
       <c r="G1457" t="s">
         <v>6857</v>
@@ -67061,7 +67061,7 @@
         <v>6850</v>
       </c>
       <c r="F1458">
-        <v>8078</v>
+        <v>8054</v>
       </c>
       <c r="G1458" t="s">
         <v>6857</v>
@@ -67087,7 +67087,7 @@
         <v>6850</v>
       </c>
       <c r="F1459">
-        <v>1178</v>
+        <v>1154</v>
       </c>
       <c r="G1459" t="s">
         <v>6857</v>
@@ -67113,7 +67113,7 @@
         <v>6850</v>
       </c>
       <c r="F1460">
-        <v>7922</v>
+        <v>7898</v>
       </c>
       <c r="G1460" t="s">
         <v>6857</v>
@@ -67243,7 +67243,7 @@
         <v>6850</v>
       </c>
       <c r="F1465">
-        <v>3069</v>
+        <v>3045</v>
       </c>
       <c r="G1465" t="s">
         <v>6857</v>
@@ -67269,7 +67269,7 @@
         <v>6850</v>
       </c>
       <c r="F1466">
-        <v>5994</v>
+        <v>5946</v>
       </c>
       <c r="G1466" t="s">
         <v>6857</v>
@@ -67295,7 +67295,7 @@
         <v>6850</v>
       </c>
       <c r="F1467">
-        <v>1860</v>
+        <v>1848</v>
       </c>
       <c r="G1467" t="s">
         <v>6857</v>
@@ -67425,7 +67425,7 @@
         <v>6850</v>
       </c>
       <c r="F1472">
-        <v>2328</v>
+        <v>2316</v>
       </c>
       <c r="G1472" t="s">
         <v>6857</v>
@@ -67555,7 +67555,7 @@
         <v>6850</v>
       </c>
       <c r="F1477">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="G1477" t="s">
         <v>6857</v>
@@ -67789,7 +67789,7 @@
         <v>6853</v>
       </c>
       <c r="F1486">
-        <v>2794</v>
+        <v>2779</v>
       </c>
       <c r="G1486" t="s">
         <v>6857</v>
@@ -67971,7 +67971,7 @@
         <v>6853</v>
       </c>
       <c r="F1493">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="G1493" t="s">
         <v>6857</v>
@@ -68127,7 +68127,7 @@
         <v>6853</v>
       </c>
       <c r="F1499">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="G1499" t="s">
         <v>6857</v>
@@ -68283,7 +68283,7 @@
         <v>6850</v>
       </c>
       <c r="F1505">
-        <v>1301</v>
+        <v>1259</v>
       </c>
       <c r="G1505" t="s">
         <v>6857</v>
@@ -68361,7 +68361,7 @@
         <v>6850</v>
       </c>
       <c r="F1508">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="G1508" t="s">
         <v>6857</v>
@@ -68413,7 +68413,7 @@
         <v>6850</v>
       </c>
       <c r="F1510">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="G1510" t="s">
         <v>6857</v>
@@ -68439,7 +68439,7 @@
         <v>6850</v>
       </c>
       <c r="F1511">
-        <v>4405</v>
+        <v>4392</v>
       </c>
       <c r="G1511" t="s">
         <v>6857</v>
@@ -68465,7 +68465,7 @@
         <v>6850</v>
       </c>
       <c r="F1512">
-        <v>4568</v>
+        <v>4556</v>
       </c>
       <c r="G1512" t="s">
         <v>6857</v>
@@ -68491,7 +68491,7 @@
         <v>6850</v>
       </c>
       <c r="F1513">
-        <v>3049</v>
+        <v>3013</v>
       </c>
       <c r="G1513" t="s">
         <v>6857</v>
@@ -68569,7 +68569,7 @@
         <v>6850</v>
       </c>
       <c r="F1516">
-        <v>10835</v>
+        <v>10811</v>
       </c>
       <c r="G1516" t="s">
         <v>6857</v>
@@ -68595,7 +68595,7 @@
         <v>6850</v>
       </c>
       <c r="F1517">
-        <v>10547</v>
+        <v>10535</v>
       </c>
       <c r="G1517" t="s">
         <v>6857</v>
@@ -68621,7 +68621,7 @@
         <v>6850</v>
       </c>
       <c r="F1518">
-        <v>2338</v>
+        <v>2302</v>
       </c>
       <c r="G1518" t="s">
         <v>6857</v>
@@ -68647,7 +68647,7 @@
         <v>6850</v>
       </c>
       <c r="F1519">
-        <v>8644</v>
+        <v>8629</v>
       </c>
       <c r="G1519" t="s">
         <v>6857</v>
@@ -68797,7 +68797,7 @@
         <v>6849</v>
       </c>
       <c r="F1525">
-        <v>9765</v>
+        <v>9747</v>
       </c>
       <c r="G1525" t="s">
         <v>6857</v>
@@ -68999,7 +68999,7 @@
         <v>6831</v>
       </c>
       <c r="F1533">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="G1533" t="s">
         <v>6857</v>
@@ -69051,7 +69051,7 @@
         <v>6831</v>
       </c>
       <c r="F1535">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G1535" t="s">
         <v>6857</v>
@@ -69311,7 +69311,7 @@
         <v>6848</v>
       </c>
       <c r="F1545">
-        <v>3301</v>
+        <v>3289</v>
       </c>
       <c r="G1545" t="s">
         <v>6857</v>
@@ -69363,7 +69363,7 @@
         <v>6848</v>
       </c>
       <c r="F1547">
-        <v>2686</v>
+        <v>2678</v>
       </c>
       <c r="G1547" t="s">
         <v>6857</v>
@@ -69389,7 +69389,7 @@
         <v>6848</v>
       </c>
       <c r="F1548">
-        <v>2191</v>
+        <v>2183</v>
       </c>
       <c r="G1548" t="s">
         <v>6857</v>
@@ -69415,7 +69415,7 @@
         <v>6848</v>
       </c>
       <c r="F1549">
-        <v>2347</v>
+        <v>2323</v>
       </c>
       <c r="G1549" t="s">
         <v>6857</v>
@@ -69441,7 +69441,7 @@
         <v>6835</v>
       </c>
       <c r="F1550">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="G1550" t="s">
         <v>6857</v>
@@ -69467,7 +69467,7 @@
         <v>6814</v>
       </c>
       <c r="F1551">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G1551" t="s">
         <v>6857</v>
@@ -69701,7 +69701,7 @@
         <v>6833</v>
       </c>
       <c r="F1560">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="G1560" t="s">
         <v>6857</v>
@@ -70047,7 +70047,7 @@
         <v>6831</v>
       </c>
       <c r="F1574">
-        <v>2142</v>
+        <v>2134</v>
       </c>
       <c r="G1574" t="s">
         <v>6857</v>
@@ -70151,7 +70151,7 @@
         <v>6831</v>
       </c>
       <c r="F1578">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="G1578" t="s">
         <v>6857</v>
@@ -70255,7 +70255,7 @@
         <v>6831</v>
       </c>
       <c r="F1582">
-        <v>1217</v>
+        <v>1199</v>
       </c>
       <c r="G1582" t="s">
         <v>6857</v>
@@ -70281,7 +70281,7 @@
         <v>6831</v>
       </c>
       <c r="F1583">
-        <v>10447</v>
+        <v>10417</v>
       </c>
       <c r="G1583" t="s">
         <v>6857</v>
@@ -70333,7 +70333,7 @@
         <v>6831</v>
       </c>
       <c r="F1585">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="G1585" t="s">
         <v>6857</v>
@@ -70437,7 +70437,7 @@
         <v>6833</v>
       </c>
       <c r="F1589">
-        <v>4536</v>
+        <v>4530</v>
       </c>
       <c r="G1589" t="s">
         <v>6857</v>
@@ -70763,7 +70763,7 @@
         <v>6851</v>
       </c>
       <c r="F1602">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="G1602" t="s">
         <v>6857</v>
@@ -70997,7 +70997,7 @@
         <v>6851</v>
       </c>
       <c r="F1611">
-        <v>44969</v>
+        <v>44789</v>
       </c>
       <c r="G1611" t="s">
         <v>6857</v>
@@ -71023,7 +71023,7 @@
         <v>6851</v>
       </c>
       <c r="F1612">
-        <v>10773</v>
+        <v>10689</v>
       </c>
       <c r="G1612" t="s">
         <v>6857</v>
@@ -71101,7 +71101,7 @@
         <v>6851</v>
       </c>
       <c r="F1615">
-        <v>2684</v>
+        <v>2659</v>
       </c>
       <c r="G1615" t="s">
         <v>6857</v>
@@ -71127,7 +71127,7 @@
         <v>6851</v>
       </c>
       <c r="F1616">
-        <v>3977</v>
+        <v>3937</v>
       </c>
       <c r="G1616" t="s">
         <v>6857</v>
@@ -71179,7 +71179,7 @@
         <v>6848</v>
       </c>
       <c r="F1618">
-        <v>26221</v>
+        <v>26143</v>
       </c>
       <c r="G1618" t="s">
         <v>6857</v>
@@ -71205,7 +71205,7 @@
         <v>6848</v>
       </c>
       <c r="F1619">
-        <v>18883</v>
+        <v>18865</v>
       </c>
       <c r="G1619" t="s">
         <v>6857</v>
@@ -71257,7 +71257,7 @@
         <v>6846</v>
       </c>
       <c r="F1621">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G1621" t="s">
         <v>6857</v>
@@ -71387,7 +71387,7 @@
         <v>6846</v>
       </c>
       <c r="F1626">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="G1626" t="s">
         <v>6857</v>
@@ -71621,7 +71621,7 @@
         <v>6854</v>
       </c>
       <c r="F1635">
-        <v>2699</v>
+        <v>2675</v>
       </c>
       <c r="G1635" t="s">
         <v>6857</v>
@@ -71647,7 +71647,7 @@
         <v>6854</v>
       </c>
       <c r="F1636">
-        <v>1871</v>
+        <v>1859</v>
       </c>
       <c r="G1636" t="s">
         <v>6857</v>
@@ -71907,7 +71907,7 @@
         <v>6824</v>
       </c>
       <c r="F1646">
-        <v>5618</v>
+        <v>5612</v>
       </c>
       <c r="G1646" t="s">
         <v>6857</v>
@@ -71933,7 +71933,7 @@
         <v>6824</v>
       </c>
       <c r="F1647">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G1647" t="s">
         <v>6857</v>
@@ -72089,7 +72089,7 @@
         <v>6824</v>
       </c>
       <c r="F1653">
-        <v>3035</v>
+        <v>2993</v>
       </c>
       <c r="G1653" t="s">
         <v>6857</v>
@@ -72219,7 +72219,7 @@
         <v>6824</v>
       </c>
       <c r="F1658">
-        <v>1666</v>
+        <v>1648</v>
       </c>
       <c r="G1658" t="s">
         <v>6857</v>
@@ -72453,7 +72453,7 @@
         <v>6824</v>
       </c>
       <c r="F1667">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="G1667" t="s">
         <v>6857</v>
@@ -72479,7 +72479,7 @@
         <v>6824</v>
       </c>
       <c r="F1668">
-        <v>3881</v>
+        <v>3863</v>
       </c>
       <c r="G1668" t="s">
         <v>6857</v>
@@ -72505,7 +72505,7 @@
         <v>6838</v>
       </c>
       <c r="F1669">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="G1669" t="s">
         <v>6857</v>
@@ -72557,7 +72557,7 @@
         <v>6838</v>
       </c>
       <c r="F1671">
-        <v>639</v>
+        <v>615</v>
       </c>
       <c r="G1671" t="s">
         <v>6857</v>
@@ -72583,7 +72583,7 @@
         <v>6838</v>
       </c>
       <c r="F1672">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="G1672" t="s">
         <v>6857</v>
@@ -72609,7 +72609,7 @@
         <v>6838</v>
       </c>
       <c r="F1673">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="G1673" t="s">
         <v>6857</v>
@@ -72635,7 +72635,7 @@
         <v>6838</v>
       </c>
       <c r="F1674">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="G1674" t="s">
         <v>6857</v>
@@ -72661,7 +72661,7 @@
         <v>6838</v>
       </c>
       <c r="F1675">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="G1675" t="s">
         <v>6857</v>
@@ -72739,7 +72739,7 @@
         <v>6838</v>
       </c>
       <c r="F1678">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G1678" t="s">
         <v>6857</v>
@@ -72765,7 +72765,7 @@
         <v>6838</v>
       </c>
       <c r="F1679">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="G1679" t="s">
         <v>6857</v>
@@ -72895,7 +72895,7 @@
         <v>6824</v>
       </c>
       <c r="F1684">
-        <v>3100</v>
+        <v>3076</v>
       </c>
       <c r="G1684" t="s">
         <v>6857</v>
@@ -72947,7 +72947,7 @@
         <v>6824</v>
       </c>
       <c r="F1686">
-        <v>1744</v>
+        <v>1714</v>
       </c>
       <c r="G1686" t="s">
         <v>6857</v>
@@ -73165,7 +73165,7 @@
         <v>6826</v>
       </c>
       <c r="F1696">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="G1696" t="s">
         <v>6857</v>
@@ -73347,7 +73347,7 @@
         <v>6845</v>
       </c>
       <c r="F1703">
-        <v>1501</v>
+        <v>1489</v>
       </c>
       <c r="G1703" t="s">
         <v>6857</v>
@@ -73711,7 +73711,7 @@
         <v>6845</v>
       </c>
       <c r="F1717">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="G1717" t="s">
         <v>6857</v>
@@ -73841,7 +73841,7 @@
         <v>6845</v>
       </c>
       <c r="F1722">
-        <v>2757</v>
+        <v>2733</v>
       </c>
       <c r="G1722" t="s">
         <v>6857</v>
@@ -74179,7 +74179,7 @@
         <v>6824</v>
       </c>
       <c r="F1735">
-        <v>2862</v>
+        <v>2856</v>
       </c>
       <c r="G1735" t="s">
         <v>6857</v>
@@ -74231,7 +74231,7 @@
         <v>6824</v>
       </c>
       <c r="F1737">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="G1737" t="s">
         <v>6857</v>
@@ -77599,7 +77599,7 @@
         <v>6816</v>
       </c>
       <c r="F1870">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G1870" t="s">
         <v>6857</v>
@@ -77651,7 +77651,7 @@
         <v>6816</v>
       </c>
       <c r="F1872">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G1872" t="s">
         <v>6857</v>
@@ -77697,7 +77697,7 @@
         <v>6816</v>
       </c>
       <c r="F1874">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="G1874" t="s">
         <v>6857</v>
@@ -77849,7 +77849,7 @@
         <v>6825</v>
       </c>
       <c r="F1881">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="G1881" t="s">
         <v>6857</v>
@@ -77875,7 +77875,7 @@
         <v>6825</v>
       </c>
       <c r="F1882">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="G1882" t="s">
         <v>6857</v>
@@ -77901,7 +77901,7 @@
         <v>6825</v>
       </c>
       <c r="F1883">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G1883" t="s">
         <v>6857</v>
@@ -77973,7 +77973,7 @@
         <v>6825</v>
       </c>
       <c r="F1886">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="G1886" t="s">
         <v>6857</v>
@@ -78129,7 +78129,7 @@
         <v>6813</v>
       </c>
       <c r="F1892">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="G1892" t="s">
         <v>6857</v>
@@ -78155,7 +78155,7 @@
         <v>6813</v>
       </c>
       <c r="F1893">
-        <v>2164</v>
+        <v>2158</v>
       </c>
       <c r="G1893" t="s">
         <v>6857</v>
@@ -78181,7 +78181,7 @@
         <v>6813</v>
       </c>
       <c r="F1894">
-        <v>2156</v>
+        <v>2144</v>
       </c>
       <c r="G1894" t="s">
         <v>6857</v>
@@ -78311,7 +78311,7 @@
         <v>6813</v>
       </c>
       <c r="F1899">
-        <v>1760</v>
+        <v>1754</v>
       </c>
       <c r="G1899" t="s">
         <v>6857</v>
@@ -78469,7 +78469,7 @@
         <v>6815</v>
       </c>
       <c r="F1906">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="G1906" t="s">
         <v>6857</v>
@@ -78561,7 +78561,7 @@
         <v>6815</v>
       </c>
       <c r="F1910">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G1910" t="s">
         <v>6857</v>
@@ -78587,7 +78587,7 @@
         <v>6815</v>
       </c>
       <c r="F1911">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G1911" t="s">
         <v>6857</v>
@@ -78639,7 +78639,7 @@
         <v>6815</v>
       </c>
       <c r="F1913">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G1913" t="s">
         <v>6857</v>
@@ -78665,7 +78665,7 @@
         <v>6815</v>
       </c>
       <c r="F1914">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="G1914" t="s">
         <v>6858</v>
@@ -78763,7 +78763,7 @@
         <v>6815</v>
       </c>
       <c r="F1918">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G1918" t="s">
         <v>6857</v>
@@ -78841,7 +78841,7 @@
         <v>6815</v>
       </c>
       <c r="F1921">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="G1921" t="s">
         <v>6857</v>
@@ -78867,7 +78867,7 @@
         <v>6815</v>
       </c>
       <c r="F1922">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="G1922" t="s">
         <v>6857</v>
@@ -78919,7 +78919,7 @@
         <v>6815</v>
       </c>
       <c r="F1924">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G1924" t="s">
         <v>6857</v>
@@ -79075,7 +79075,7 @@
         <v>6825</v>
       </c>
       <c r="F1930">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="G1930" t="s">
         <v>6858</v>
@@ -79701,7 +79701,7 @@
         <v>6815</v>
       </c>
       <c r="F1958">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G1958" t="s">
         <v>6857</v>
@@ -79753,7 +79753,7 @@
         <v>6813</v>
       </c>
       <c r="F1960">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G1960" t="s">
         <v>6857</v>
@@ -79831,7 +79831,7 @@
         <v>6816</v>
       </c>
       <c r="F1963">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="G1963" t="s">
         <v>6857</v>
@@ -79857,7 +79857,7 @@
         <v>6816</v>
       </c>
       <c r="F1964">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G1964" t="s">
         <v>6857</v>
@@ -79929,7 +79929,7 @@
         <v>6816</v>
       </c>
       <c r="F1967">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G1967" t="s">
         <v>6857</v>
@@ -79981,7 +79981,7 @@
         <v>6816</v>
       </c>
       <c r="F1969">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G1969" t="s">
         <v>6857</v>
@@ -80007,7 +80007,7 @@
         <v>6816</v>
       </c>
       <c r="F1970">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G1970" t="s">
         <v>6857</v>
@@ -80093,7 +80093,7 @@
         <v>6816</v>
       </c>
       <c r="F1974">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="G1974" t="s">
         <v>6858</v>
@@ -80575,7 +80575,7 @@
         <v>6816</v>
       </c>
       <c r="F1996">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="G1996" t="s">
         <v>6858</v>
@@ -80985,7 +80985,7 @@
         <v>6815</v>
       </c>
       <c r="F2012">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2012" t="s">
         <v>6858</v>
@@ -81025,7 +81025,7 @@
         <v>6815</v>
       </c>
       <c r="F2014">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="G2014" t="s">
         <v>6858</v>
@@ -81737,7 +81737,7 @@
         <v>6815</v>
       </c>
       <c r="F2043">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G2043" t="s">
         <v>6857</v>
@@ -83727,7 +83727,7 @@
         <v>6832</v>
       </c>
       <c r="F2123">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G2123" t="s">
         <v>6858</v>
@@ -83747,7 +83747,7 @@
         <v>6832</v>
       </c>
       <c r="F2124">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G2124" t="s">
         <v>6858</v>
@@ -84091,7 +84091,7 @@
         <v>6832</v>
       </c>
       <c r="F2140">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G2140" t="s">
         <v>6857</v>
@@ -84255,7 +84255,7 @@
         <v>6832</v>
       </c>
       <c r="F2147">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="G2147" t="s">
         <v>6857</v>
@@ -84281,7 +84281,7 @@
         <v>6832</v>
       </c>
       <c r="F2148">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G2148" t="s">
         <v>6857</v>
@@ -84497,7 +84497,7 @@
         <v>6832</v>
       </c>
       <c r="F2157">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G2157" t="s">
         <v>6857</v>
@@ -84523,7 +84523,7 @@
         <v>6832</v>
       </c>
       <c r="F2158">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="G2158" t="s">
         <v>6857</v>
@@ -84549,7 +84549,7 @@
         <v>6832</v>
       </c>
       <c r="F2159">
-        <v>3189</v>
+        <v>3181</v>
       </c>
       <c r="G2159" t="s">
         <v>6857</v>
@@ -84575,7 +84575,7 @@
         <v>6832</v>
       </c>
       <c r="F2160">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="G2160" t="s">
         <v>6857</v>
@@ -84653,7 +84653,7 @@
         <v>6832</v>
       </c>
       <c r="F2163">
-        <v>1871</v>
+        <v>1861</v>
       </c>
       <c r="G2163" t="s">
         <v>6857</v>
@@ -84699,7 +84699,7 @@
         <v>6832</v>
       </c>
       <c r="F2165">
-        <v>1521</v>
+        <v>1501</v>
       </c>
       <c r="G2165" t="s">
         <v>6857</v>
@@ -84725,7 +84725,7 @@
         <v>6832</v>
       </c>
       <c r="F2166">
-        <v>1292</v>
+        <v>1282</v>
       </c>
       <c r="G2166" t="s">
         <v>6857</v>
@@ -84751,7 +84751,7 @@
         <v>6832</v>
       </c>
       <c r="F2167">
-        <v>7471</v>
+        <v>7461</v>
       </c>
       <c r="G2167" t="s">
         <v>6857</v>
@@ -84777,7 +84777,7 @@
         <v>6832</v>
       </c>
       <c r="F2168">
-        <v>1074</v>
+        <v>1044</v>
       </c>
       <c r="G2168" t="s">
         <v>6857</v>
@@ -84803,7 +84803,7 @@
         <v>6832</v>
       </c>
       <c r="F2169">
-        <v>991</v>
+        <v>971</v>
       </c>
       <c r="G2169" t="s">
         <v>6857</v>
@@ -84829,7 +84829,7 @@
         <v>6832</v>
       </c>
       <c r="F2170">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="G2170" t="s">
         <v>6857</v>
@@ -85039,7 +85039,7 @@
         <v>6832</v>
       </c>
       <c r="F2179">
-        <v>6135</v>
+        <v>6123</v>
       </c>
       <c r="G2179" t="s">
         <v>6857</v>
@@ -85091,7 +85091,7 @@
         <v>6832</v>
       </c>
       <c r="F2181">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G2181" t="s">
         <v>6857</v>
@@ -85117,7 +85117,7 @@
         <v>6832</v>
       </c>
       <c r="F2182">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="G2182" t="s">
         <v>6857</v>
@@ -85143,7 +85143,7 @@
         <v>6832</v>
       </c>
       <c r="F2183">
-        <v>2872</v>
+        <v>2868</v>
       </c>
       <c r="G2183" t="s">
         <v>6857</v>
@@ -85275,7 +85275,7 @@
         <v>6832</v>
       </c>
       <c r="F2189">
-        <v>3160</v>
+        <v>3155</v>
       </c>
       <c r="G2189" t="s">
         <v>6857</v>
@@ -86383,7 +86383,7 @@
         <v>6815</v>
       </c>
       <c r="F2236">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G2236" t="s">
         <v>6857</v>
@@ -86821,7 +86821,7 @@
         <v>6815</v>
       </c>
       <c r="F2254">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="G2254" t="s">
         <v>6858</v>
@@ -87329,7 +87329,7 @@
         <v>6816</v>
       </c>
       <c r="F2274">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2274" t="s">
         <v>6857</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -31535,7 +31535,7 @@
         <v>6812</v>
       </c>
       <c r="F6">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
         <v>6854</v>
@@ -31581,7 +31581,7 @@
         <v>6812</v>
       </c>
       <c r="F8">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="G8" t="s">
         <v>6855</v>
@@ -31621,7 +31621,7 @@
         <v>6812</v>
       </c>
       <c r="F10">
-        <v>1452</v>
+        <v>1428</v>
       </c>
       <c r="G10" t="s">
         <v>6854</v>
@@ -31667,7 +31667,7 @@
         <v>6812</v>
       </c>
       <c r="F12">
-        <v>1124</v>
+        <v>1100</v>
       </c>
       <c r="G12" t="s">
         <v>6854</v>
@@ -31765,7 +31765,7 @@
         <v>6812</v>
       </c>
       <c r="F16">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="G16" t="s">
         <v>6854</v>
@@ -31857,7 +31857,7 @@
         <v>6812</v>
       </c>
       <c r="F20">
-        <v>1156</v>
+        <v>1132</v>
       </c>
       <c r="G20" t="s">
         <v>6854</v>
@@ -31975,7 +31975,7 @@
         <v>6814</v>
       </c>
       <c r="F25">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="G25" t="s">
         <v>6854</v>
@@ -32001,7 +32001,7 @@
         <v>6814</v>
       </c>
       <c r="F26">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="G26" t="s">
         <v>6854</v>
@@ -32027,7 +32027,7 @@
         <v>6814</v>
       </c>
       <c r="F27">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="G27" t="s">
         <v>6854</v>
@@ -32053,7 +32053,7 @@
         <v>6814</v>
       </c>
       <c r="F28">
-        <v>1615</v>
+        <v>1603</v>
       </c>
       <c r="G28" t="s">
         <v>6854</v>
@@ -32079,7 +32079,7 @@
         <v>6814</v>
       </c>
       <c r="F29">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="G29" t="s">
         <v>6854</v>
@@ -32105,7 +32105,7 @@
         <v>6814</v>
       </c>
       <c r="F30">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="G30" t="s">
         <v>6854</v>
@@ -32131,7 +32131,7 @@
         <v>6814</v>
       </c>
       <c r="F31">
-        <v>1660</v>
+        <v>1648</v>
       </c>
       <c r="G31" t="s">
         <v>6854</v>
@@ -32157,7 +32157,7 @@
         <v>6813</v>
       </c>
       <c r="F32">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="G32" t="s">
         <v>6854</v>
@@ -32235,7 +32235,7 @@
         <v>6813</v>
       </c>
       <c r="F35">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="G35" t="s">
         <v>6854</v>
@@ -32281,7 +32281,7 @@
         <v>6810</v>
       </c>
       <c r="F37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
         <v>6855</v>
@@ -32399,7 +32399,7 @@
         <v>6815</v>
       </c>
       <c r="F42">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G42" t="s">
         <v>6854</v>
@@ -32565,7 +32565,7 @@
         <v>6815</v>
       </c>
       <c r="F50">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G50" t="s">
         <v>6854</v>
@@ -32591,7 +32591,7 @@
         <v>6815</v>
       </c>
       <c r="F51">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G51" t="s">
         <v>6854</v>
@@ -32617,7 +32617,7 @@
         <v>6812</v>
       </c>
       <c r="F52">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G52" t="s">
         <v>6854</v>
@@ -32643,7 +32643,7 @@
         <v>6815</v>
       </c>
       <c r="F53">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G53" t="s">
         <v>6854</v>
@@ -32669,7 +32669,7 @@
         <v>6813</v>
       </c>
       <c r="F54">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G54" t="s">
         <v>6854</v>
@@ -32695,7 +32695,7 @@
         <v>6816</v>
       </c>
       <c r="F55">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G55" t="s">
         <v>6854</v>
@@ -32721,7 +32721,7 @@
         <v>6816</v>
       </c>
       <c r="F56">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G56" t="s">
         <v>6854</v>
@@ -32825,7 +32825,7 @@
         <v>6816</v>
       </c>
       <c r="F60">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G60" t="s">
         <v>6854</v>
@@ -32851,7 +32851,7 @@
         <v>6812</v>
       </c>
       <c r="F61">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G61" t="s">
         <v>6854</v>
@@ -32877,7 +32877,7 @@
         <v>6812</v>
       </c>
       <c r="F62">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G62" t="s">
         <v>6854</v>
@@ -32903,7 +32903,7 @@
         <v>6813</v>
       </c>
       <c r="F63">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G63" t="s">
         <v>6854</v>
@@ -32929,7 +32929,7 @@
         <v>6813</v>
       </c>
       <c r="F64">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G64" t="s">
         <v>6854</v>
@@ -32955,7 +32955,7 @@
         <v>6813</v>
       </c>
       <c r="F65">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G65" t="s">
         <v>6854</v>
@@ -33033,7 +33033,7 @@
         <v>6818</v>
       </c>
       <c r="F68">
-        <v>3117</v>
+        <v>3101</v>
       </c>
       <c r="G68" t="s">
         <v>6854</v>
@@ -33085,7 +33085,7 @@
         <v>6818</v>
       </c>
       <c r="F70">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="G70" t="s">
         <v>6854</v>
@@ -33137,7 +33137,7 @@
         <v>6818</v>
       </c>
       <c r="F72">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="G72" t="s">
         <v>6854</v>
@@ -33215,7 +33215,7 @@
         <v>6818</v>
       </c>
       <c r="F75">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="G75" t="s">
         <v>6854</v>
@@ -33267,7 +33267,7 @@
         <v>6819</v>
       </c>
       <c r="F77">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="G77" t="s">
         <v>6854</v>
@@ -33293,7 +33293,7 @@
         <v>6819</v>
       </c>
       <c r="F78">
-        <v>2241</v>
+        <v>2205</v>
       </c>
       <c r="G78" t="s">
         <v>6854</v>
@@ -33319,7 +33319,7 @@
         <v>6819</v>
       </c>
       <c r="F79">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G79" t="s">
         <v>6854</v>
@@ -33345,7 +33345,7 @@
         <v>6819</v>
       </c>
       <c r="F80">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G80" t="s">
         <v>6854</v>
@@ -33371,7 +33371,7 @@
         <v>6819</v>
       </c>
       <c r="F81">
-        <v>1614</v>
+        <v>1594</v>
       </c>
       <c r="G81" t="s">
         <v>6854</v>
@@ -33397,7 +33397,7 @@
         <v>6819</v>
       </c>
       <c r="F82">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="G82" t="s">
         <v>6854</v>
@@ -33423,7 +33423,7 @@
         <v>6819</v>
       </c>
       <c r="F83">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="G83" t="s">
         <v>6854</v>
@@ -33475,7 +33475,7 @@
         <v>6819</v>
       </c>
       <c r="F85">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="G85" t="s">
         <v>6854</v>
@@ -33501,7 +33501,7 @@
         <v>6818</v>
       </c>
       <c r="F86">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="G86" t="s">
         <v>6854</v>
@@ -33527,7 +33527,7 @@
         <v>6818</v>
       </c>
       <c r="F87">
-        <v>949</v>
+        <v>933</v>
       </c>
       <c r="G87" t="s">
         <v>6854</v>
@@ -33553,7 +33553,7 @@
         <v>6818</v>
       </c>
       <c r="F88">
-        <v>1695</v>
+        <v>1683</v>
       </c>
       <c r="G88" t="s">
         <v>6854</v>
@@ -33605,7 +33605,7 @@
         <v>6812</v>
       </c>
       <c r="F90">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="G90" t="s">
         <v>6854</v>
@@ -33631,7 +33631,7 @@
         <v>6812</v>
       </c>
       <c r="F91">
-        <v>1744</v>
+        <v>1732</v>
       </c>
       <c r="G91" t="s">
         <v>6854</v>
@@ -33657,7 +33657,7 @@
         <v>6812</v>
       </c>
       <c r="F92">
-        <v>1836</v>
+        <v>1828</v>
       </c>
       <c r="G92" t="s">
         <v>6854</v>
@@ -33683,7 +33683,7 @@
         <v>6812</v>
       </c>
       <c r="F93">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="G93" t="s">
         <v>6854</v>
@@ -33709,7 +33709,7 @@
         <v>6812</v>
       </c>
       <c r="F94">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="G94" t="s">
         <v>6854</v>
@@ -33735,7 +33735,7 @@
         <v>6812</v>
       </c>
       <c r="F95">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="G95" t="s">
         <v>6854</v>
@@ -33761,7 +33761,7 @@
         <v>6812</v>
       </c>
       <c r="F96">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="G96" t="s">
         <v>6854</v>
@@ -33787,7 +33787,7 @@
         <v>6812</v>
       </c>
       <c r="F97">
-        <v>1252</v>
+        <v>1230</v>
       </c>
       <c r="G97" t="s">
         <v>6854</v>
@@ -33813,7 +33813,7 @@
         <v>6812</v>
       </c>
       <c r="F98">
-        <v>1223</v>
+        <v>1205</v>
       </c>
       <c r="G98" t="s">
         <v>6854</v>
@@ -33839,7 +33839,7 @@
         <v>6812</v>
       </c>
       <c r="F99">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="G99" t="s">
         <v>6854</v>
@@ -33865,7 +33865,7 @@
         <v>6812</v>
       </c>
       <c r="F100">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="G100" t="s">
         <v>6854</v>
@@ -33891,7 +33891,7 @@
         <v>6812</v>
       </c>
       <c r="F101">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="G101" t="s">
         <v>6854</v>
@@ -33943,7 +33943,7 @@
         <v>6813</v>
       </c>
       <c r="F103">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G103" t="s">
         <v>6854</v>
@@ -33969,7 +33969,7 @@
         <v>6815</v>
       </c>
       <c r="F104">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G104" t="s">
         <v>6854</v>
@@ -34073,7 +34073,7 @@
         <v>6813</v>
       </c>
       <c r="F108">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G108" t="s">
         <v>6855</v>
@@ -34145,7 +34145,7 @@
         <v>6813</v>
       </c>
       <c r="F111">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G111" t="s">
         <v>6854</v>
@@ -34349,7 +34349,7 @@
         <v>6812</v>
       </c>
       <c r="F120">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G120" t="s">
         <v>6854</v>
@@ -34395,7 +34395,7 @@
         <v>6812</v>
       </c>
       <c r="F122">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G122" t="s">
         <v>6854</v>
@@ -34481,7 +34481,7 @@
         <v>6812</v>
       </c>
       <c r="F126">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G126" t="s">
         <v>6854</v>
@@ -34607,7 +34607,7 @@
         <v>6812</v>
       </c>
       <c r="F132">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G132" t="s">
         <v>6854</v>
@@ -34751,7 +34751,7 @@
         <v>6812</v>
       </c>
       <c r="F138">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="G138" t="s">
         <v>6854</v>
@@ -34777,7 +34777,7 @@
         <v>6812</v>
       </c>
       <c r="F139">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="G139" t="s">
         <v>6854</v>
@@ -34803,7 +34803,7 @@
         <v>6821</v>
       </c>
       <c r="F140">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="G140" t="s">
         <v>6854</v>
@@ -34849,7 +34849,7 @@
         <v>6813</v>
       </c>
       <c r="F142">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G142" t="s">
         <v>6855</v>
@@ -35337,7 +35337,7 @@
         <v>6822</v>
       </c>
       <c r="F161">
-        <v>1668</v>
+        <v>1662</v>
       </c>
       <c r="G161" t="s">
         <v>6854</v>
@@ -35441,7 +35441,7 @@
         <v>6810</v>
       </c>
       <c r="F165">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="G165" t="s">
         <v>6854</v>
@@ -35597,7 +35597,7 @@
         <v>6814</v>
       </c>
       <c r="F171">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="G171" t="s">
         <v>6854</v>
@@ -35649,7 +35649,7 @@
         <v>6814</v>
       </c>
       <c r="F173">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="G173" t="s">
         <v>6854</v>
@@ -35701,7 +35701,7 @@
         <v>6814</v>
       </c>
       <c r="F175">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="G175" t="s">
         <v>6854</v>
@@ -35805,7 +35805,7 @@
         <v>6814</v>
       </c>
       <c r="F179">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="G179" t="s">
         <v>6854</v>
@@ -35883,7 +35883,7 @@
         <v>6813</v>
       </c>
       <c r="F182">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="G182" t="s">
         <v>6854</v>
@@ -35935,7 +35935,7 @@
         <v>6813</v>
       </c>
       <c r="F184">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G184" t="s">
         <v>6854</v>
@@ -35961,7 +35961,7 @@
         <v>6813</v>
       </c>
       <c r="F185">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="G185" t="s">
         <v>6854</v>
@@ -35987,7 +35987,7 @@
         <v>6814</v>
       </c>
       <c r="F186">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="G186" t="s">
         <v>6854</v>
@@ -36091,7 +36091,7 @@
         <v>6821</v>
       </c>
       <c r="F190">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="G190" t="s">
         <v>6855</v>
@@ -36111,7 +36111,7 @@
         <v>6821</v>
       </c>
       <c r="F191">
-        <v>1302</v>
+        <v>1284</v>
       </c>
       <c r="G191" t="s">
         <v>6854</v>
@@ -36137,7 +36137,7 @@
         <v>6821</v>
       </c>
       <c r="F192">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="G192" t="s">
         <v>6854</v>
@@ -36189,7 +36189,7 @@
         <v>6821</v>
       </c>
       <c r="F194">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="G194" t="s">
         <v>6854</v>
@@ -36241,7 +36241,7 @@
         <v>6821</v>
       </c>
       <c r="F196">
-        <v>1767</v>
+        <v>1761</v>
       </c>
       <c r="G196" t="s">
         <v>6854</v>
@@ -36267,7 +36267,7 @@
         <v>6820</v>
       </c>
       <c r="F197">
-        <v>1367</v>
+        <v>1337</v>
       </c>
       <c r="G197" t="s">
         <v>6854</v>
@@ -36373,7 +36373,7 @@
         <v>6820</v>
       </c>
       <c r="F202">
-        <v>1058</v>
+        <v>1008</v>
       </c>
       <c r="G202" t="s">
         <v>6854</v>
@@ -36399,7 +36399,7 @@
         <v>6820</v>
       </c>
       <c r="F203">
-        <v>1227</v>
+        <v>1197</v>
       </c>
       <c r="G203" t="s">
         <v>6854</v>
@@ -36425,7 +36425,7 @@
         <v>6820</v>
       </c>
       <c r="F204">
-        <v>1043</v>
+        <v>1003</v>
       </c>
       <c r="G204" t="s">
         <v>6854</v>
@@ -36451,7 +36451,7 @@
         <v>6820</v>
       </c>
       <c r="F205">
-        <v>2416</v>
+        <v>2406</v>
       </c>
       <c r="G205" t="s">
         <v>6854</v>
@@ -36477,7 +36477,7 @@
         <v>6820</v>
       </c>
       <c r="F206">
-        <v>3442</v>
+        <v>3372</v>
       </c>
       <c r="G206" t="s">
         <v>6854</v>
@@ -36607,7 +36607,7 @@
         <v>6825</v>
       </c>
       <c r="F211">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="G211" t="s">
         <v>6854</v>
@@ -36685,7 +36685,7 @@
         <v>6824</v>
       </c>
       <c r="F214">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="G214" t="s">
         <v>6854</v>
@@ -36789,7 +36789,7 @@
         <v>6824</v>
       </c>
       <c r="F218">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="G218" t="s">
         <v>6854</v>
@@ -36841,7 +36841,7 @@
         <v>6824</v>
       </c>
       <c r="F220">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="G220" t="s">
         <v>6854</v>
@@ -36867,7 +36867,7 @@
         <v>6825</v>
       </c>
       <c r="F221">
-        <v>2304</v>
+        <v>2300</v>
       </c>
       <c r="G221" t="s">
         <v>6854</v>
@@ -36893,7 +36893,7 @@
         <v>6825</v>
       </c>
       <c r="F222">
-        <v>2284</v>
+        <v>2280</v>
       </c>
       <c r="G222" t="s">
         <v>6854</v>
@@ -36919,7 +36919,7 @@
         <v>6813</v>
       </c>
       <c r="F223">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="G223" t="s">
         <v>6854</v>
@@ -36945,7 +36945,7 @@
         <v>6813</v>
       </c>
       <c r="F224">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="G224" t="s">
         <v>6854</v>
@@ -36971,7 +36971,7 @@
         <v>6813</v>
       </c>
       <c r="F225">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G225" t="s">
         <v>6854</v>
@@ -36997,7 +36997,7 @@
         <v>6813</v>
       </c>
       <c r="F226">
-        <v>1137</v>
+        <v>1129</v>
       </c>
       <c r="G226" t="s">
         <v>6854</v>
@@ -37023,7 +37023,7 @@
         <v>6813</v>
       </c>
       <c r="F227">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="G227" t="s">
         <v>6854</v>
@@ -37049,7 +37049,7 @@
         <v>6813</v>
       </c>
       <c r="F228">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="G228" t="s">
         <v>6854</v>
@@ -37075,7 +37075,7 @@
         <v>6813</v>
       </c>
       <c r="F229">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="G229" t="s">
         <v>6854</v>
@@ -37101,7 +37101,7 @@
         <v>6813</v>
       </c>
       <c r="F230">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="G230" t="s">
         <v>6854</v>
@@ -37213,7 +37213,7 @@
         <v>6821</v>
       </c>
       <c r="F235">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G235" t="s">
         <v>6855</v>
@@ -37233,7 +37233,7 @@
         <v>6821</v>
       </c>
       <c r="F236">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="G236" t="s">
         <v>6855</v>
@@ -37253,7 +37253,7 @@
         <v>6821</v>
       </c>
       <c r="F237">
-        <v>1788</v>
+        <v>1782</v>
       </c>
       <c r="G237" t="s">
         <v>6855</v>
@@ -37313,7 +37313,7 @@
         <v>6812</v>
       </c>
       <c r="F240">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G240" t="s">
         <v>6854</v>
@@ -37339,7 +37339,7 @@
         <v>6821</v>
       </c>
       <c r="F241">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="G241" t="s">
         <v>6855</v>
@@ -37359,7 +37359,7 @@
         <v>6812</v>
       </c>
       <c r="F242">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="G242" t="s">
         <v>6854</v>
@@ -37385,7 +37385,7 @@
         <v>6812</v>
       </c>
       <c r="F243">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="G243" t="s">
         <v>6854</v>
@@ -37497,7 +37497,7 @@
         <v>6812</v>
       </c>
       <c r="F248">
-        <v>1514</v>
+        <v>1414</v>
       </c>
       <c r="G248" t="s">
         <v>6855</v>
@@ -37517,7 +37517,7 @@
         <v>6820</v>
       </c>
       <c r="F249">
-        <v>3685</v>
+        <v>3635</v>
       </c>
       <c r="G249" t="s">
         <v>6854</v>
@@ -37543,7 +37543,7 @@
         <v>6812</v>
       </c>
       <c r="F250">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G250" t="s">
         <v>6855</v>
@@ -37643,7 +37643,7 @@
         <v>6820</v>
       </c>
       <c r="F255">
-        <v>3200</v>
+        <v>3190</v>
       </c>
       <c r="G255" t="s">
         <v>6854</v>
@@ -37669,7 +37669,7 @@
         <v>6820</v>
       </c>
       <c r="F256">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="G256" t="s">
         <v>6854</v>
@@ -37695,7 +37695,7 @@
         <v>6820</v>
       </c>
       <c r="F257">
-        <v>3944</v>
+        <v>3924</v>
       </c>
       <c r="G257" t="s">
         <v>6854</v>
@@ -37721,7 +37721,7 @@
         <v>6820</v>
       </c>
       <c r="F258">
-        <v>2740</v>
+        <v>2730</v>
       </c>
       <c r="G258" t="s">
         <v>6854</v>
@@ -37747,7 +37747,7 @@
         <v>6820</v>
       </c>
       <c r="F259">
-        <v>3562</v>
+        <v>3542</v>
       </c>
       <c r="G259" t="s">
         <v>6854</v>
@@ -37839,7 +37839,7 @@
         <v>6824</v>
       </c>
       <c r="F263">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="G263" t="s">
         <v>6854</v>
@@ -37865,7 +37865,7 @@
         <v>6824</v>
       </c>
       <c r="F264">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G264" t="s">
         <v>6854</v>
@@ -37891,7 +37891,7 @@
         <v>6820</v>
       </c>
       <c r="F265">
-        <v>1684</v>
+        <v>1664</v>
       </c>
       <c r="G265" t="s">
         <v>6854</v>
@@ -37917,7 +37917,7 @@
         <v>6824</v>
       </c>
       <c r="F266">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="G266" t="s">
         <v>6854</v>
@@ -37943,7 +37943,7 @@
         <v>6824</v>
       </c>
       <c r="F267">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G267" t="s">
         <v>6854</v>
@@ -37969,7 +37969,7 @@
         <v>6824</v>
       </c>
       <c r="F268">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G268" t="s">
         <v>6854</v>
@@ -37995,7 +37995,7 @@
         <v>6824</v>
       </c>
       <c r="F269">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G269" t="s">
         <v>6854</v>
@@ -38021,7 +38021,7 @@
         <v>6820</v>
       </c>
       <c r="F270">
-        <v>2829</v>
+        <v>2798</v>
       </c>
       <c r="G270" t="s">
         <v>6854</v>
@@ -38047,7 +38047,7 @@
         <v>6820</v>
       </c>
       <c r="F271">
-        <v>3711</v>
+        <v>3681</v>
       </c>
       <c r="G271" t="s">
         <v>6854</v>
@@ -38073,7 +38073,7 @@
         <v>6824</v>
       </c>
       <c r="F272">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G272" t="s">
         <v>6854</v>
@@ -38099,7 +38099,7 @@
         <v>6820</v>
       </c>
       <c r="F273">
-        <v>952</v>
+        <v>932</v>
       </c>
       <c r="G273" t="s">
         <v>6854</v>
@@ -38203,7 +38203,7 @@
         <v>6824</v>
       </c>
       <c r="F277">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="G277" t="s">
         <v>6854</v>
@@ -38229,7 +38229,7 @@
         <v>6824</v>
       </c>
       <c r="F278">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="G278" t="s">
         <v>6854</v>
@@ -38255,7 +38255,7 @@
         <v>6824</v>
       </c>
       <c r="F279">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G279" t="s">
         <v>6854</v>
@@ -38281,7 +38281,7 @@
         <v>6824</v>
       </c>
       <c r="F280">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="G280" t="s">
         <v>6854</v>
@@ -38307,7 +38307,7 @@
         <v>6824</v>
       </c>
       <c r="F281">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="G281" t="s">
         <v>6854</v>
@@ -38333,7 +38333,7 @@
         <v>6813</v>
       </c>
       <c r="F282">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G282" t="s">
         <v>6854</v>
@@ -38359,7 +38359,7 @@
         <v>6812</v>
       </c>
       <c r="F283">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G283" t="s">
         <v>6854</v>
@@ -38385,7 +38385,7 @@
         <v>6813</v>
       </c>
       <c r="F284">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G284" t="s">
         <v>6854</v>
@@ -38411,7 +38411,7 @@
         <v>6812</v>
       </c>
       <c r="F285">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="G285" t="s">
         <v>6855</v>
@@ -38431,7 +38431,7 @@
         <v>6812</v>
       </c>
       <c r="F286">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="G286" t="s">
         <v>6854</v>
@@ -38457,7 +38457,7 @@
         <v>6812</v>
       </c>
       <c r="F287">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="G287" t="s">
         <v>6854</v>
@@ -38483,7 +38483,7 @@
         <v>6812</v>
       </c>
       <c r="F288">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G288" t="s">
         <v>6854</v>
@@ -38509,7 +38509,7 @@
         <v>6812</v>
       </c>
       <c r="F289">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G289" t="s">
         <v>6854</v>
@@ -38561,7 +38561,7 @@
         <v>6820</v>
       </c>
       <c r="F291">
-        <v>2427</v>
+        <v>2397</v>
       </c>
       <c r="G291" t="s">
         <v>6854</v>
@@ -38613,7 +38613,7 @@
         <v>6813</v>
       </c>
       <c r="F293">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G293" t="s">
         <v>6854</v>
@@ -38639,7 +38639,7 @@
         <v>6813</v>
       </c>
       <c r="F294">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G294" t="s">
         <v>6854</v>
@@ -38665,7 +38665,7 @@
         <v>6820</v>
       </c>
       <c r="F295">
-        <v>1459</v>
+        <v>1439</v>
       </c>
       <c r="G295" t="s">
         <v>6854</v>
@@ -38711,7 +38711,7 @@
         <v>6820</v>
       </c>
       <c r="F297">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G297" t="s">
         <v>6854</v>
@@ -38737,7 +38737,7 @@
         <v>6820</v>
       </c>
       <c r="F298">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G298" t="s">
         <v>6854</v>
@@ -38789,7 +38789,7 @@
         <v>6820</v>
       </c>
       <c r="F300">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G300" t="s">
         <v>6854</v>
@@ -38815,7 +38815,7 @@
         <v>6820</v>
       </c>
       <c r="F301">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G301" t="s">
         <v>6854</v>
@@ -38841,7 +38841,7 @@
         <v>6820</v>
       </c>
       <c r="F302">
-        <v>983</v>
+        <v>953</v>
       </c>
       <c r="G302" t="s">
         <v>6854</v>
@@ -38867,7 +38867,7 @@
         <v>6820</v>
       </c>
       <c r="F303">
-        <v>606</v>
+        <v>566</v>
       </c>
       <c r="G303" t="s">
         <v>6854</v>
@@ -38893,7 +38893,7 @@
         <v>6827</v>
       </c>
       <c r="F304">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="G304" t="s">
         <v>6854</v>
@@ -38919,7 +38919,7 @@
         <v>6828</v>
       </c>
       <c r="F305">
-        <v>4263</v>
+        <v>4257</v>
       </c>
       <c r="G305" t="s">
         <v>6854</v>
@@ -38945,7 +38945,7 @@
         <v>6829</v>
       </c>
       <c r="F306">
-        <v>1649</v>
+        <v>1643</v>
       </c>
       <c r="G306" t="s">
         <v>6854</v>
@@ -38971,7 +38971,7 @@
         <v>6830</v>
       </c>
       <c r="F307">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="G307" t="s">
         <v>6854</v>
@@ -38997,7 +38997,7 @@
         <v>6822</v>
       </c>
       <c r="F308">
-        <v>1764</v>
+        <v>1758</v>
       </c>
       <c r="G308" t="s">
         <v>6854</v>
@@ -39023,7 +39023,7 @@
         <v>6822</v>
       </c>
       <c r="F309">
-        <v>1740</v>
+        <v>1734</v>
       </c>
       <c r="G309" t="s">
         <v>6854</v>
@@ -39049,7 +39049,7 @@
         <v>6822</v>
       </c>
       <c r="F310">
-        <v>1722</v>
+        <v>1716</v>
       </c>
       <c r="G310" t="s">
         <v>6854</v>
@@ -39075,7 +39075,7 @@
         <v>6822</v>
       </c>
       <c r="F311">
-        <v>1836</v>
+        <v>1830</v>
       </c>
       <c r="G311" t="s">
         <v>6854</v>
@@ -39153,7 +39153,7 @@
         <v>6822</v>
       </c>
       <c r="F314">
-        <v>1770</v>
+        <v>1752</v>
       </c>
       <c r="G314" t="s">
         <v>6854</v>
@@ -39205,7 +39205,7 @@
         <v>6813</v>
       </c>
       <c r="F316">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G316" t="s">
         <v>6854</v>
@@ -39257,7 +39257,7 @@
         <v>6810</v>
       </c>
       <c r="F318">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="G318" t="s">
         <v>6854</v>
@@ -39355,7 +39355,7 @@
         <v>6812</v>
       </c>
       <c r="F322">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G322" t="s">
         <v>6854</v>
@@ -39461,7 +39461,7 @@
         <v>6810</v>
       </c>
       <c r="F327">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="G327" t="s">
         <v>6854</v>
@@ -39527,7 +39527,7 @@
         <v>6812</v>
       </c>
       <c r="F330">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G330" t="s">
         <v>6854</v>
@@ -39599,7 +39599,7 @@
         <v>6812</v>
       </c>
       <c r="F333">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G333" t="s">
         <v>6854</v>
@@ -39651,7 +39651,7 @@
         <v>6810</v>
       </c>
       <c r="F335">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="G335" t="s">
         <v>6854</v>
@@ -39703,7 +39703,7 @@
         <v>6813</v>
       </c>
       <c r="F337">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G337" t="s">
         <v>6854</v>
@@ -39729,7 +39729,7 @@
         <v>6831</v>
       </c>
       <c r="F338">
-        <v>3975</v>
+        <v>3961</v>
       </c>
       <c r="G338" t="s">
         <v>6854</v>
@@ -39755,7 +39755,7 @@
         <v>6831</v>
       </c>
       <c r="F339">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="G339" t="s">
         <v>6854</v>
@@ -39781,7 +39781,7 @@
         <v>6832</v>
       </c>
       <c r="F340">
-        <v>3187</v>
+        <v>3183</v>
       </c>
       <c r="G340" t="s">
         <v>6854</v>
@@ -39985,7 +39985,7 @@
         <v>6812</v>
       </c>
       <c r="F349">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="G349" t="s">
         <v>6854</v>
@@ -40553,7 +40553,7 @@
         <v>6835</v>
       </c>
       <c r="F375">
-        <v>1536</v>
+        <v>1524</v>
       </c>
       <c r="G375" t="s">
         <v>6854</v>
@@ -40599,7 +40599,7 @@
         <v>6835</v>
       </c>
       <c r="F377">
-        <v>1488</v>
+        <v>1476</v>
       </c>
       <c r="G377" t="s">
         <v>6854</v>
@@ -40737,7 +40737,7 @@
         <v>6819</v>
       </c>
       <c r="F383">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="G383" t="s">
         <v>6854</v>
@@ -40867,7 +40867,7 @@
         <v>6812</v>
       </c>
       <c r="F388">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G388" t="s">
         <v>6854</v>
@@ -43157,7 +43157,7 @@
         <v>6824</v>
       </c>
       <c r="F477">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G477" t="s">
         <v>6854</v>
@@ -43261,7 +43261,7 @@
         <v>6824</v>
       </c>
       <c r="F481">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G481" t="s">
         <v>6854</v>
@@ -43313,7 +43313,7 @@
         <v>6824</v>
       </c>
       <c r="F483">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G483" t="s">
         <v>6854</v>
@@ -43339,7 +43339,7 @@
         <v>6824</v>
       </c>
       <c r="F484">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G484" t="s">
         <v>6854</v>
@@ -43365,7 +43365,7 @@
         <v>6824</v>
       </c>
       <c r="F485">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G485" t="s">
         <v>6854</v>
@@ -43391,7 +43391,7 @@
         <v>6824</v>
       </c>
       <c r="F486">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G486" t="s">
         <v>6854</v>
@@ -44315,7 +44315,7 @@
         <v>6816</v>
       </c>
       <c r="F522">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="G522" t="s">
         <v>6854</v>
@@ -44341,7 +44341,7 @@
         <v>6816</v>
       </c>
       <c r="F523">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="G523" t="s">
         <v>6854</v>
@@ -44367,7 +44367,7 @@
         <v>6834</v>
       </c>
       <c r="F524">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G524" t="s">
         <v>6854</v>
@@ -44539,7 +44539,7 @@
         <v>6816</v>
       </c>
       <c r="F532">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="G532" t="s">
         <v>6854</v>
@@ -44591,7 +44591,7 @@
         <v>6834</v>
       </c>
       <c r="F534">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="G534" t="s">
         <v>6854</v>
@@ -44669,7 +44669,7 @@
         <v>6834</v>
       </c>
       <c r="F537">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G537" t="s">
         <v>6854</v>
@@ -44721,7 +44721,7 @@
         <v>6834</v>
       </c>
       <c r="F539">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="G539" t="s">
         <v>6854</v>
@@ -44747,7 +44747,7 @@
         <v>6834</v>
       </c>
       <c r="F540">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G540" t="s">
         <v>6854</v>
@@ -44799,7 +44799,7 @@
         <v>6834</v>
       </c>
       <c r="F542">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G542" t="s">
         <v>6854</v>
@@ -44903,7 +44903,7 @@
         <v>6834</v>
       </c>
       <c r="F546">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G546" t="s">
         <v>6854</v>
@@ -47471,7 +47471,7 @@
         <v>6834</v>
       </c>
       <c r="F648">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G648" t="s">
         <v>6854</v>
@@ -47497,7 +47497,7 @@
         <v>6834</v>
       </c>
       <c r="F649">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G649" t="s">
         <v>6854</v>
@@ -47827,7 +47827,7 @@
         <v>6838</v>
       </c>
       <c r="F664">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="G664" t="s">
         <v>6854</v>
@@ -47983,7 +47983,7 @@
         <v>6838</v>
       </c>
       <c r="F670">
-        <v>1498</v>
+        <v>1482</v>
       </c>
       <c r="G670" t="s">
         <v>6854</v>
@@ -48685,7 +48685,7 @@
         <v>6825</v>
       </c>
       <c r="F697">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="G697" t="s">
         <v>6854</v>
@@ -48737,7 +48737,7 @@
         <v>6825</v>
       </c>
       <c r="F699">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="G699" t="s">
         <v>6854</v>
@@ -48939,7 +48939,7 @@
         <v>6825</v>
       </c>
       <c r="F707">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="G707" t="s">
         <v>6854</v>
@@ -49095,7 +49095,7 @@
         <v>6825</v>
       </c>
       <c r="F713">
-        <v>1650</v>
+        <v>1644</v>
       </c>
       <c r="G713" t="s">
         <v>6854</v>
@@ -49277,7 +49277,7 @@
         <v>6825</v>
       </c>
       <c r="F720">
-        <v>2917</v>
+        <v>2911</v>
       </c>
       <c r="G720" t="s">
         <v>6854</v>
@@ -49303,7 +49303,7 @@
         <v>6825</v>
       </c>
       <c r="F721">
-        <v>4825</v>
+        <v>4819</v>
       </c>
       <c r="G721" t="s">
         <v>6854</v>
@@ -49563,7 +49563,7 @@
         <v>6825</v>
       </c>
       <c r="F731">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="G731" t="s">
         <v>6854</v>
@@ -49713,7 +49713,7 @@
         <v>6825</v>
       </c>
       <c r="F737">
-        <v>3722</v>
+        <v>3710</v>
       </c>
       <c r="G737" t="s">
         <v>6854</v>
@@ -49765,7 +49765,7 @@
         <v>6825</v>
       </c>
       <c r="F739">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="G739" t="s">
         <v>6854</v>
@@ -49869,7 +49869,7 @@
         <v>6841</v>
       </c>
       <c r="F743">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="G743" t="s">
         <v>6854</v>
@@ -49967,7 +49967,7 @@
         <v>6842</v>
       </c>
       <c r="F747">
-        <v>1263</v>
+        <v>1251</v>
       </c>
       <c r="G747" t="s">
         <v>6854</v>
@@ -49993,7 +49993,7 @@
         <v>6842</v>
       </c>
       <c r="F748">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="G748" t="s">
         <v>6854</v>
@@ -50149,7 +50149,7 @@
         <v>6842</v>
       </c>
       <c r="F754">
-        <v>2021</v>
+        <v>1997</v>
       </c>
       <c r="G754" t="s">
         <v>6854</v>
@@ -50175,7 +50175,7 @@
         <v>6842</v>
       </c>
       <c r="F755">
-        <v>1593</v>
+        <v>1581</v>
       </c>
       <c r="G755" t="s">
         <v>6854</v>
@@ -51189,7 +51189,7 @@
         <v>6811</v>
       </c>
       <c r="F794">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="G794" t="s">
         <v>6855</v>
@@ -51209,7 +51209,7 @@
         <v>6811</v>
       </c>
       <c r="F795">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="G795" t="s">
         <v>6855</v>
@@ -51229,7 +51229,7 @@
         <v>6811</v>
       </c>
       <c r="F796">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="G796" t="s">
         <v>6855</v>
@@ -53075,7 +53075,7 @@
         <v>6842</v>
       </c>
       <c r="F882">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="G882" t="s">
         <v>6854</v>
@@ -53173,7 +53173,7 @@
         <v>6842</v>
       </c>
       <c r="F886">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="G886" t="s">
         <v>6854</v>
@@ -53357,7 +53357,7 @@
         <v>6811</v>
       </c>
       <c r="F894">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G894" t="s">
         <v>6854</v>
@@ -53383,7 +53383,7 @@
         <v>6811</v>
       </c>
       <c r="F895">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G895" t="s">
         <v>6854</v>
@@ -53409,7 +53409,7 @@
         <v>6811</v>
       </c>
       <c r="F896">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G896" t="s">
         <v>6854</v>
@@ -53461,7 +53461,7 @@
         <v>6820</v>
       </c>
       <c r="F898">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="G898" t="s">
         <v>6854</v>
@@ -53663,7 +53663,7 @@
         <v>6811</v>
       </c>
       <c r="F906">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G906" t="s">
         <v>6854</v>
@@ -53787,7 +53787,7 @@
         <v>6842</v>
       </c>
       <c r="F911">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G911" t="s">
         <v>6854</v>
@@ -53943,7 +53943,7 @@
         <v>6842</v>
       </c>
       <c r="F917">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="G917" t="s">
         <v>6854</v>
@@ -54009,7 +54009,7 @@
         <v>6842</v>
       </c>
       <c r="F920">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G920" t="s">
         <v>6854</v>
@@ -54453,7 +54453,7 @@
         <v>6812</v>
       </c>
       <c r="F938">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G938" t="s">
         <v>6854</v>
@@ -54505,7 +54505,7 @@
         <v>6812</v>
       </c>
       <c r="F940">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G940" t="s">
         <v>6854</v>
@@ -54531,7 +54531,7 @@
         <v>6812</v>
       </c>
       <c r="F941">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G941" t="s">
         <v>6854</v>
@@ -54583,7 +54583,7 @@
         <v>6812</v>
       </c>
       <c r="F943">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G943" t="s">
         <v>6854</v>
@@ -54609,7 +54609,7 @@
         <v>6812</v>
       </c>
       <c r="F944">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G944" t="s">
         <v>6854</v>
@@ -54635,7 +54635,7 @@
         <v>6812</v>
       </c>
       <c r="F945">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G945" t="s">
         <v>6854</v>
@@ -54739,7 +54739,7 @@
         <v>6812</v>
       </c>
       <c r="F949">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G949" t="s">
         <v>6854</v>
@@ -54885,7 +54885,7 @@
         <v>6825</v>
       </c>
       <c r="F956">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="G956" t="s">
         <v>6854</v>
@@ -55347,7 +55347,7 @@
         <v>6812</v>
       </c>
       <c r="F974">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G974" t="s">
         <v>6854</v>
@@ -55601,7 +55601,7 @@
         <v>6812</v>
       </c>
       <c r="F984">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G984" t="s">
         <v>6854</v>
@@ -55627,7 +55627,7 @@
         <v>6812</v>
       </c>
       <c r="F985">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G985" t="s">
         <v>6854</v>
@@ -55996,7 +55996,7 @@
         <v>6816</v>
       </c>
       <c r="F1000">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G1000" t="s">
         <v>6854</v>
@@ -56094,7 +56094,7 @@
         <v>6816</v>
       </c>
       <c r="F1004">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G1004" t="s">
         <v>6854</v>
@@ -56215,7 +56215,7 @@
         <v>6812</v>
       </c>
       <c r="F1009">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G1009" t="s">
         <v>6854</v>
@@ -56241,7 +56241,7 @@
         <v>6846</v>
       </c>
       <c r="F1010">
-        <v>5755</v>
+        <v>5739</v>
       </c>
       <c r="G1010" t="s">
         <v>6854</v>
@@ -56339,7 +56339,7 @@
         <v>6812</v>
       </c>
       <c r="F1014">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="G1014" t="s">
         <v>6854</v>
@@ -56391,7 +56391,7 @@
         <v>6812</v>
       </c>
       <c r="F1016">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G1016" t="s">
         <v>6854</v>
@@ -56417,7 +56417,7 @@
         <v>6812</v>
       </c>
       <c r="F1017">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G1017" t="s">
         <v>6854</v>
@@ -56469,7 +56469,7 @@
         <v>6812</v>
       </c>
       <c r="F1019">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G1019" t="s">
         <v>6854</v>
@@ -56521,7 +56521,7 @@
         <v>6812</v>
       </c>
       <c r="F1021">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G1021" t="s">
         <v>6854</v>
@@ -56590,7 +56590,7 @@
         <v>6812</v>
       </c>
       <c r="F1024">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G1024" t="s">
         <v>6855</v>
@@ -56848,7 +56848,7 @@
         <v>6838</v>
       </c>
       <c r="F1036">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="G1036" t="s">
         <v>6855</v>
@@ -56988,7 +56988,7 @@
         <v>6838</v>
       </c>
       <c r="F1043">
-        <v>1405</v>
+        <v>1393</v>
       </c>
       <c r="G1043" t="s">
         <v>6855</v>
@@ -57008,7 +57008,7 @@
         <v>6838</v>
       </c>
       <c r="F1044">
-        <v>1972</v>
+        <v>1960</v>
       </c>
       <c r="G1044" t="s">
         <v>6855</v>
@@ -57256,7 +57256,7 @@
         <v>6838</v>
       </c>
       <c r="F1054">
-        <v>1481</v>
+        <v>1469</v>
       </c>
       <c r="G1054" t="s">
         <v>6855</v>
@@ -57302,7 +57302,7 @@
         <v>6838</v>
       </c>
       <c r="F1056">
-        <v>1371</v>
+        <v>1359</v>
       </c>
       <c r="G1056" t="s">
         <v>6855</v>
@@ -57460,7 +57460,7 @@
         <v>6845</v>
       </c>
       <c r="F1063">
-        <v>679</v>
+        <v>613</v>
       </c>
       <c r="G1063" t="s">
         <v>6854</v>
@@ -57486,7 +57486,7 @@
         <v>6845</v>
       </c>
       <c r="F1064">
-        <v>1097</v>
+        <v>1079</v>
       </c>
       <c r="G1064" t="s">
         <v>6854</v>
@@ -57584,7 +57584,7 @@
         <v>6825</v>
       </c>
       <c r="F1068">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="G1068" t="s">
         <v>6854</v>
@@ -57662,7 +57662,7 @@
         <v>6825</v>
       </c>
       <c r="F1071">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="G1071" t="s">
         <v>6854</v>
@@ -58038,7 +58038,7 @@
         <v>6812</v>
       </c>
       <c r="F1088">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G1088" t="s">
         <v>6854</v>
@@ -58064,7 +58064,7 @@
         <v>6812</v>
       </c>
       <c r="F1089">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G1089" t="s">
         <v>6854</v>
@@ -58318,7 +58318,7 @@
         <v>6812</v>
       </c>
       <c r="F1099">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G1099" t="s">
         <v>6854</v>
@@ -58462,7 +58462,7 @@
         <v>6823</v>
       </c>
       <c r="F1105">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G1105" t="s">
         <v>6854</v>
@@ -58638,7 +58638,7 @@
         <v>6847</v>
       </c>
       <c r="F1112">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="G1112" t="s">
         <v>6854</v>
@@ -58846,7 +58846,7 @@
         <v>6847</v>
       </c>
       <c r="F1120">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="G1120" t="s">
         <v>6854</v>
@@ -59022,7 +59022,7 @@
         <v>6847</v>
       </c>
       <c r="F1127">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="G1127" t="s">
         <v>6854</v>
@@ -59068,7 +59068,7 @@
         <v>6847</v>
       </c>
       <c r="F1129">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="G1129" t="s">
         <v>6854</v>
@@ -59094,7 +59094,7 @@
         <v>6847</v>
       </c>
       <c r="F1130">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="G1130" t="s">
         <v>6854</v>
@@ -59120,7 +59120,7 @@
         <v>6847</v>
       </c>
       <c r="F1131">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G1131" t="s">
         <v>6854</v>
@@ -59146,7 +59146,7 @@
         <v>6847</v>
       </c>
       <c r="F1132">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="G1132" t="s">
         <v>6854</v>
@@ -59250,7 +59250,7 @@
         <v>6847</v>
       </c>
       <c r="F1136">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G1136" t="s">
         <v>6854</v>
@@ -59276,7 +59276,7 @@
         <v>6847</v>
       </c>
       <c r="F1137">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G1137" t="s">
         <v>6854</v>
@@ -59302,7 +59302,7 @@
         <v>6847</v>
       </c>
       <c r="F1138">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G1138" t="s">
         <v>6854</v>
@@ -59512,7 +59512,7 @@
         <v>6834</v>
       </c>
       <c r="F1147">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G1147" t="s">
         <v>6854</v>
@@ -59538,7 +59538,7 @@
         <v>6834</v>
       </c>
       <c r="F1148">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="G1148" t="s">
         <v>6854</v>
@@ -59564,7 +59564,7 @@
         <v>6834</v>
       </c>
       <c r="F1149">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G1149" t="s">
         <v>6854</v>
@@ -59616,7 +59616,7 @@
         <v>6834</v>
       </c>
       <c r="F1151">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G1151" t="s">
         <v>6854</v>
@@ -59642,7 +59642,7 @@
         <v>6834</v>
       </c>
       <c r="F1152">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G1152" t="s">
         <v>6854</v>
@@ -59668,7 +59668,7 @@
         <v>6834</v>
       </c>
       <c r="F1153">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G1153" t="s">
         <v>6854</v>
@@ -59694,7 +59694,7 @@
         <v>6834</v>
       </c>
       <c r="F1154">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G1154" t="s">
         <v>6854</v>
@@ -59720,7 +59720,7 @@
         <v>6834</v>
       </c>
       <c r="F1155">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="G1155" t="s">
         <v>6854</v>
@@ -59772,7 +59772,7 @@
         <v>6834</v>
       </c>
       <c r="F1157">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G1157" t="s">
         <v>6854</v>
@@ -59798,7 +59798,7 @@
         <v>6834</v>
       </c>
       <c r="F1158">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G1158" t="s">
         <v>6854</v>
@@ -59850,7 +59850,7 @@
         <v>6834</v>
       </c>
       <c r="F1160">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G1160" t="s">
         <v>6854</v>
@@ -59876,7 +59876,7 @@
         <v>6834</v>
       </c>
       <c r="F1161">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G1161" t="s">
         <v>6854</v>
@@ -59902,7 +59902,7 @@
         <v>6834</v>
       </c>
       <c r="F1162">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="G1162" t="s">
         <v>6854</v>
@@ -59974,7 +59974,7 @@
         <v>6834</v>
       </c>
       <c r="F1165">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G1165" t="s">
         <v>6854</v>
@@ -60000,7 +60000,7 @@
         <v>6834</v>
       </c>
       <c r="F1166">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G1166" t="s">
         <v>6854</v>
@@ -60130,7 +60130,7 @@
         <v>6812</v>
       </c>
       <c r="F1171">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G1171" t="s">
         <v>6854</v>
@@ -60228,7 +60228,7 @@
         <v>6834</v>
       </c>
       <c r="F1175">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G1175" t="s">
         <v>6854</v>
@@ -60254,7 +60254,7 @@
         <v>6834</v>
       </c>
       <c r="F1176">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G1176" t="s">
         <v>6854</v>
@@ -60358,7 +60358,7 @@
         <v>6834</v>
       </c>
       <c r="F1180">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G1180" t="s">
         <v>6854</v>
@@ -61100,7 +61100,7 @@
         <v>6848</v>
       </c>
       <c r="F1209">
-        <v>8120</v>
+        <v>8078</v>
       </c>
       <c r="G1209" t="s">
         <v>6854</v>
@@ -61860,7 +61860,7 @@
         <v>6823</v>
       </c>
       <c r="F1244">
-        <v>4511</v>
+        <v>4487</v>
       </c>
       <c r="G1244" t="s">
         <v>6855</v>
@@ -62080,7 +62080,7 @@
         <v>6820</v>
       </c>
       <c r="F1255">
-        <v>1368</v>
+        <v>1356</v>
       </c>
       <c r="G1255" t="s">
         <v>6854</v>
@@ -62106,7 +62106,7 @@
         <v>6843</v>
       </c>
       <c r="F1256">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="G1256" t="s">
         <v>6854</v>
@@ -62282,7 +62282,7 @@
         <v>6825</v>
       </c>
       <c r="F1263">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G1263" t="s">
         <v>6854</v>
@@ -62432,7 +62432,7 @@
         <v>6843</v>
       </c>
       <c r="F1269">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="G1269" t="s">
         <v>6854</v>
@@ -62458,7 +62458,7 @@
         <v>6843</v>
       </c>
       <c r="F1270">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="G1270" t="s">
         <v>6854</v>
@@ -62504,7 +62504,7 @@
         <v>6820</v>
       </c>
       <c r="F1272">
-        <v>2067</v>
+        <v>2055</v>
       </c>
       <c r="G1272" t="s">
         <v>6854</v>
@@ -62556,7 +62556,7 @@
         <v>6820</v>
       </c>
       <c r="F1274">
-        <v>1991</v>
+        <v>1985</v>
       </c>
       <c r="G1274" t="s">
         <v>6854</v>
@@ -62582,7 +62582,7 @@
         <v>6820</v>
       </c>
       <c r="F1275">
-        <v>1814</v>
+        <v>1808</v>
       </c>
       <c r="G1275" t="s">
         <v>6854</v>
@@ -62608,7 +62608,7 @@
         <v>6820</v>
       </c>
       <c r="F1276">
-        <v>1282</v>
+        <v>1264</v>
       </c>
       <c r="G1276" t="s">
         <v>6854</v>
@@ -62634,7 +62634,7 @@
         <v>6820</v>
       </c>
       <c r="F1277">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="G1277" t="s">
         <v>6854</v>
@@ -63860,7 +63860,7 @@
         <v>6813</v>
       </c>
       <c r="F1326">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G1326" t="s">
         <v>6855</v>
@@ -64174,7 +64174,7 @@
         <v>6813</v>
       </c>
       <c r="F1339">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G1339" t="s">
         <v>6854</v>
@@ -64200,7 +64200,7 @@
         <v>6813</v>
       </c>
       <c r="F1340">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G1340" t="s">
         <v>6854</v>
@@ -64278,7 +64278,7 @@
         <v>6812</v>
       </c>
       <c r="F1343">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G1343" t="s">
         <v>6854</v>
@@ -64408,7 +64408,7 @@
         <v>6812</v>
       </c>
       <c r="F1348">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G1348" t="s">
         <v>6854</v>
@@ -65228,7 +65228,7 @@
         <v>6849</v>
       </c>
       <c r="F1386">
-        <v>595</v>
+        <v>555</v>
       </c>
       <c r="G1386" t="s">
         <v>6854</v>
@@ -65332,7 +65332,7 @@
         <v>6849</v>
       </c>
       <c r="F1390">
-        <v>7653</v>
+        <v>7563</v>
       </c>
       <c r="G1390" t="s">
         <v>6854</v>
@@ -65384,7 +65384,7 @@
         <v>6849</v>
       </c>
       <c r="F1392">
-        <v>5994</v>
+        <v>5922</v>
       </c>
       <c r="G1392" t="s">
         <v>6854</v>
@@ -65488,7 +65488,7 @@
         <v>6820</v>
       </c>
       <c r="F1396">
-        <v>3341</v>
+        <v>3331</v>
       </c>
       <c r="G1396" t="s">
         <v>6854</v>
@@ -65514,7 +65514,7 @@
         <v>6820</v>
       </c>
       <c r="F1397">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G1397" t="s">
         <v>6854</v>
@@ -65722,7 +65722,7 @@
         <v>6820</v>
       </c>
       <c r="F1405">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="G1405" t="s">
         <v>6854</v>
@@ -65748,7 +65748,7 @@
         <v>6820</v>
       </c>
       <c r="F1406">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="G1406" t="s">
         <v>6854</v>
@@ -65800,7 +65800,7 @@
         <v>6820</v>
       </c>
       <c r="F1408">
-        <v>4876</v>
+        <v>4846</v>
       </c>
       <c r="G1408" t="s">
         <v>6854</v>
@@ -65826,7 +65826,7 @@
         <v>6820</v>
       </c>
       <c r="F1409">
-        <v>2709</v>
+        <v>2679</v>
       </c>
       <c r="G1409" t="s">
         <v>6854</v>
@@ -65852,7 +65852,7 @@
         <v>6849</v>
       </c>
       <c r="F1410">
-        <v>6720</v>
+        <v>6684</v>
       </c>
       <c r="G1410" t="s">
         <v>6854</v>
@@ -65956,7 +65956,7 @@
         <v>6849</v>
       </c>
       <c r="F1414">
-        <v>3009</v>
+        <v>2955</v>
       </c>
       <c r="G1414" t="s">
         <v>6854</v>
@@ -66164,7 +66164,7 @@
         <v>6850</v>
       </c>
       <c r="F1422">
-        <v>1643</v>
+        <v>1627</v>
       </c>
       <c r="G1422" t="s">
         <v>6854</v>
@@ -66328,7 +66328,7 @@
         <v>6820</v>
       </c>
       <c r="F1429">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G1429" t="s">
         <v>6854</v>
@@ -66536,7 +66536,7 @@
         <v>6850</v>
       </c>
       <c r="F1437">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="G1437" t="s">
         <v>6854</v>
@@ -66562,7 +66562,7 @@
         <v>6847</v>
       </c>
       <c r="F1438">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="G1438" t="s">
         <v>6854</v>
@@ -66614,7 +66614,7 @@
         <v>6847</v>
       </c>
       <c r="F1440">
-        <v>7943</v>
+        <v>7919</v>
       </c>
       <c r="G1440" t="s">
         <v>6854</v>
@@ -66732,7 +66732,7 @@
         <v>6847</v>
       </c>
       <c r="F1445">
-        <v>2832</v>
+        <v>2808</v>
       </c>
       <c r="G1445" t="s">
         <v>6854</v>
@@ -66810,7 +66810,7 @@
         <v>6847</v>
       </c>
       <c r="F1448">
-        <v>2455</v>
+        <v>2431</v>
       </c>
       <c r="G1448" t="s">
         <v>6854</v>
@@ -66836,7 +66836,7 @@
         <v>6847</v>
       </c>
       <c r="F1449">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G1449" t="s">
         <v>6854</v>
@@ -67018,7 +67018,7 @@
         <v>6847</v>
       </c>
       <c r="F1456">
-        <v>7982</v>
+        <v>7958</v>
       </c>
       <c r="G1456" t="s">
         <v>6854</v>
@@ -67044,7 +67044,7 @@
         <v>6847</v>
       </c>
       <c r="F1457">
-        <v>1082</v>
+        <v>1058</v>
       </c>
       <c r="G1457" t="s">
         <v>6854</v>
@@ -67096,7 +67096,7 @@
         <v>6847</v>
       </c>
       <c r="F1459">
-        <v>5902</v>
+        <v>5854</v>
       </c>
       <c r="G1459" t="s">
         <v>6854</v>
@@ -67148,7 +67148,7 @@
         <v>6847</v>
       </c>
       <c r="F1461">
-        <v>3045</v>
+        <v>3033</v>
       </c>
       <c r="G1461" t="s">
         <v>6854</v>
@@ -67174,7 +67174,7 @@
         <v>6847</v>
       </c>
       <c r="F1462">
-        <v>5922</v>
+        <v>5886</v>
       </c>
       <c r="G1462" t="s">
         <v>6854</v>
@@ -67304,7 +67304,7 @@
         <v>6847</v>
       </c>
       <c r="F1467">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="G1467" t="s">
         <v>6854</v>
@@ -67330,7 +67330,7 @@
         <v>6847</v>
       </c>
       <c r="F1468">
-        <v>2292</v>
+        <v>2268</v>
       </c>
       <c r="G1468" t="s">
         <v>6854</v>
@@ -67564,7 +67564,7 @@
         <v>6850</v>
       </c>
       <c r="F1477">
-        <v>2447</v>
+        <v>2423</v>
       </c>
       <c r="G1477" t="s">
         <v>6854</v>
@@ -67616,7 +67616,7 @@
         <v>6850</v>
       </c>
       <c r="F1479">
-        <v>3670</v>
+        <v>3662</v>
       </c>
       <c r="G1479" t="s">
         <v>6854</v>
@@ -67642,7 +67642,7 @@
         <v>6850</v>
       </c>
       <c r="F1480">
-        <v>1104</v>
+        <v>1088</v>
       </c>
       <c r="G1480" t="s">
         <v>6854</v>
@@ -67668,7 +67668,7 @@
         <v>6850</v>
       </c>
       <c r="F1481">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="G1481" t="s">
         <v>6854</v>
@@ -68240,7 +68240,7 @@
         <v>6847</v>
       </c>
       <c r="F1503">
-        <v>1247</v>
+        <v>1187</v>
       </c>
       <c r="G1503" t="s">
         <v>6854</v>
@@ -68396,7 +68396,7 @@
         <v>6847</v>
       </c>
       <c r="F1509">
-        <v>4331</v>
+        <v>4319</v>
       </c>
       <c r="G1509" t="s">
         <v>6854</v>
@@ -68422,7 +68422,7 @@
         <v>6847</v>
       </c>
       <c r="F1510">
-        <v>4508</v>
+        <v>4496</v>
       </c>
       <c r="G1510" t="s">
         <v>6854</v>
@@ -68448,7 +68448,7 @@
         <v>6847</v>
       </c>
       <c r="F1511">
-        <v>2953</v>
+        <v>2917</v>
       </c>
       <c r="G1511" t="s">
         <v>6854</v>
@@ -68552,7 +68552,7 @@
         <v>6847</v>
       </c>
       <c r="F1515">
-        <v>10811</v>
+        <v>10810</v>
       </c>
       <c r="G1515" t="s">
         <v>6854</v>
@@ -68604,7 +68604,7 @@
         <v>6847</v>
       </c>
       <c r="F1517">
-        <v>2278</v>
+        <v>2218</v>
       </c>
       <c r="G1517" t="s">
         <v>6854</v>
@@ -68630,7 +68630,7 @@
         <v>6847</v>
       </c>
       <c r="F1518">
-        <v>8617</v>
+        <v>8605</v>
       </c>
       <c r="G1518" t="s">
         <v>6854</v>
@@ -68794,7 +68794,7 @@
         <v>6846</v>
       </c>
       <c r="F1525">
-        <v>9715</v>
+        <v>9701</v>
       </c>
       <c r="G1525" t="s">
         <v>6854</v>
@@ -68924,7 +68924,7 @@
         <v>6846</v>
       </c>
       <c r="F1530">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G1530" t="s">
         <v>6854</v>
@@ -69204,7 +69204,7 @@
         <v>6830</v>
       </c>
       <c r="F1541">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G1541" t="s">
         <v>6854</v>
@@ -69308,7 +69308,7 @@
         <v>6845</v>
       </c>
       <c r="F1545">
-        <v>3217</v>
+        <v>3181</v>
       </c>
       <c r="G1545" t="s">
         <v>6854</v>
@@ -69360,7 +69360,7 @@
         <v>6845</v>
       </c>
       <c r="F1547">
-        <v>2654</v>
+        <v>2630</v>
       </c>
       <c r="G1547" t="s">
         <v>6854</v>
@@ -69386,7 +69386,7 @@
         <v>6845</v>
       </c>
       <c r="F1548">
-        <v>2151</v>
+        <v>2147</v>
       </c>
       <c r="G1548" t="s">
         <v>6854</v>
@@ -69412,7 +69412,7 @@
         <v>6845</v>
       </c>
       <c r="F1549">
-        <v>2299</v>
+        <v>2281</v>
       </c>
       <c r="G1549" t="s">
         <v>6854</v>
@@ -69464,7 +69464,7 @@
         <v>6811</v>
       </c>
       <c r="F1551">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G1551" t="s">
         <v>6854</v>
@@ -69672,7 +69672,7 @@
         <v>6828</v>
       </c>
       <c r="F1559">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="G1559" t="s">
         <v>6854</v>
@@ -70018,7 +70018,7 @@
         <v>6829</v>
       </c>
       <c r="F1573">
-        <v>2094</v>
+        <v>2078</v>
       </c>
       <c r="G1573" t="s">
         <v>6854</v>
@@ -70044,7 +70044,7 @@
         <v>6829</v>
       </c>
       <c r="F1574">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="G1574" t="s">
         <v>6854</v>
@@ -70070,7 +70070,7 @@
         <v>6829</v>
       </c>
       <c r="F1575">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G1575" t="s">
         <v>6854</v>
@@ -70096,7 +70096,7 @@
         <v>6829</v>
       </c>
       <c r="F1576">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G1576" t="s">
         <v>6854</v>
@@ -70200,7 +70200,7 @@
         <v>6829</v>
       </c>
       <c r="F1580">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="G1580" t="s">
         <v>6854</v>
@@ -70226,7 +70226,7 @@
         <v>6829</v>
       </c>
       <c r="F1581">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="G1581" t="s">
         <v>6854</v>
@@ -70252,7 +70252,7 @@
         <v>6829</v>
       </c>
       <c r="F1582">
-        <v>10363</v>
+        <v>10333</v>
       </c>
       <c r="G1582" t="s">
         <v>6854</v>
@@ -70278,7 +70278,7 @@
         <v>6829</v>
       </c>
       <c r="F1583">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="G1583" t="s">
         <v>6854</v>
@@ -70304,7 +70304,7 @@
         <v>6829</v>
       </c>
       <c r="F1584">
-        <v>2033</v>
+        <v>2026</v>
       </c>
       <c r="G1584" t="s">
         <v>6854</v>
@@ -70714,7 +70714,7 @@
         <v>6848</v>
       </c>
       <c r="F1600">
-        <v>2725</v>
+        <v>2713</v>
       </c>
       <c r="G1600" t="s">
         <v>6854</v>
@@ -70740,7 +70740,7 @@
         <v>6848</v>
       </c>
       <c r="F1601">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="G1601" t="s">
         <v>6854</v>
@@ -70766,7 +70766,7 @@
         <v>6848</v>
       </c>
       <c r="F1602">
-        <v>2921</v>
+        <v>2905</v>
       </c>
       <c r="G1602" t="s">
         <v>6854</v>
@@ -70948,7 +70948,7 @@
         <v>6848</v>
       </c>
       <c r="F1609">
-        <v>3552</v>
+        <v>3536</v>
       </c>
       <c r="G1609" t="s">
         <v>6854</v>
@@ -70974,7 +70974,7 @@
         <v>6848</v>
       </c>
       <c r="F1610">
-        <v>44255</v>
+        <v>43829</v>
       </c>
       <c r="G1610" t="s">
         <v>6854</v>
@@ -71000,7 +71000,7 @@
         <v>6848</v>
       </c>
       <c r="F1611">
-        <v>10574</v>
+        <v>10472</v>
       </c>
       <c r="G1611" t="s">
         <v>6854</v>
@@ -71078,7 +71078,7 @@
         <v>6848</v>
       </c>
       <c r="F1614">
-        <v>2629</v>
+        <v>2599</v>
       </c>
       <c r="G1614" t="s">
         <v>6854</v>
@@ -71104,7 +71104,7 @@
         <v>6848</v>
       </c>
       <c r="F1615">
-        <v>3897</v>
+        <v>3857</v>
       </c>
       <c r="G1615" t="s">
         <v>6854</v>
@@ -71156,7 +71156,7 @@
         <v>6845</v>
       </c>
       <c r="F1617">
-        <v>25806</v>
+        <v>25560</v>
       </c>
       <c r="G1617" t="s">
         <v>6854</v>
@@ -71182,7 +71182,7 @@
         <v>6845</v>
       </c>
       <c r="F1618">
-        <v>18763</v>
+        <v>18721</v>
       </c>
       <c r="G1618" t="s">
         <v>6854</v>
@@ -71884,7 +71884,7 @@
         <v>6821</v>
       </c>
       <c r="F1645">
-        <v>2969</v>
+        <v>2957</v>
       </c>
       <c r="G1645" t="s">
         <v>6854</v>
@@ -71910,7 +71910,7 @@
         <v>6821</v>
       </c>
       <c r="F1646">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="G1646" t="s">
         <v>6854</v>
@@ -71936,7 +71936,7 @@
         <v>6821</v>
       </c>
       <c r="F1647">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="G1647" t="s">
         <v>6854</v>
@@ -72040,7 +72040,7 @@
         <v>6821</v>
       </c>
       <c r="F1651">
-        <v>814</v>
+        <v>796</v>
       </c>
       <c r="G1651" t="s">
         <v>6854</v>
@@ -72066,7 +72066,7 @@
         <v>6821</v>
       </c>
       <c r="F1652">
-        <v>5588</v>
+        <v>5570</v>
       </c>
       <c r="G1652" t="s">
         <v>6854</v>
@@ -72222,7 +72222,7 @@
         <v>6821</v>
       </c>
       <c r="F1658">
-        <v>1618</v>
+        <v>1588</v>
       </c>
       <c r="G1658" t="s">
         <v>6854</v>
@@ -72352,7 +72352,7 @@
         <v>6821</v>
       </c>
       <c r="F1663">
-        <v>3830</v>
+        <v>3812</v>
       </c>
       <c r="G1663" t="s">
         <v>6854</v>
@@ -72482,7 +72482,7 @@
         <v>6821</v>
       </c>
       <c r="F1668">
-        <v>3064</v>
+        <v>3058</v>
       </c>
       <c r="G1668" t="s">
         <v>6854</v>
@@ -72638,7 +72638,7 @@
         <v>6835</v>
       </c>
       <c r="F1674">
-        <v>735</v>
+        <v>711</v>
       </c>
       <c r="G1674" t="s">
         <v>6854</v>
@@ -72664,7 +72664,7 @@
         <v>6835</v>
       </c>
       <c r="F1675">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="G1675" t="s">
         <v>6854</v>
@@ -72690,7 +72690,7 @@
         <v>6835</v>
       </c>
       <c r="F1676">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="G1676" t="s">
         <v>6854</v>
@@ -72742,7 +72742,7 @@
         <v>6835</v>
       </c>
       <c r="F1678">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="G1678" t="s">
         <v>6854</v>
@@ -72898,7 +72898,7 @@
         <v>6821</v>
       </c>
       <c r="F1684">
-        <v>1681</v>
+        <v>1657</v>
       </c>
       <c r="G1684" t="s">
         <v>6854</v>
@@ -73278,7 +73278,7 @@
         <v>6842</v>
       </c>
       <c r="F1700">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G1700" t="s">
         <v>6854</v>
@@ -74136,7 +74136,7 @@
         <v>6821</v>
       </c>
       <c r="F1733">
-        <v>2788</v>
+        <v>2782</v>
       </c>
       <c r="G1733" t="s">
         <v>6854</v>
@@ -74214,7 +74214,7 @@
         <v>6821</v>
       </c>
       <c r="F1736">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="G1736" t="s">
         <v>6854</v>
@@ -74344,7 +74344,7 @@
         <v>6821</v>
       </c>
       <c r="F1741">
-        <v>3480</v>
+        <v>3468</v>
       </c>
       <c r="G1741" t="s">
         <v>6854</v>
@@ -74448,7 +74448,7 @@
         <v>6821</v>
       </c>
       <c r="F1745">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G1745" t="s">
         <v>6854</v>
@@ -76076,7 +76076,7 @@
         <v>6817</v>
       </c>
       <c r="F1809">
-        <v>2310</v>
+        <v>2280</v>
       </c>
       <c r="G1809" t="s">
         <v>6854</v>
@@ -76902,7 +76902,7 @@
         <v>6835</v>
       </c>
       <c r="F1841">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G1841" t="s">
         <v>6854</v>
@@ -77314,7 +77314,7 @@
         <v>6813</v>
       </c>
       <c r="F1858">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G1858" t="s">
         <v>6854</v>
@@ -77360,7 +77360,7 @@
         <v>6813</v>
       </c>
       <c r="F1860">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="G1860" t="s">
         <v>6854</v>
@@ -77432,7 +77432,7 @@
         <v>6813</v>
       </c>
       <c r="F1863">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G1863" t="s">
         <v>6854</v>
@@ -77484,7 +77484,7 @@
         <v>6813</v>
       </c>
       <c r="F1865">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G1865" t="s">
         <v>6854</v>
@@ -77536,7 +77536,7 @@
         <v>6813</v>
       </c>
       <c r="F1867">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G1867" t="s">
         <v>6854</v>
@@ -77832,7 +77832,7 @@
         <v>6822</v>
       </c>
       <c r="F1880">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="G1880" t="s">
         <v>6854</v>
@@ -77858,7 +77858,7 @@
         <v>6822</v>
       </c>
       <c r="F1881">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="G1881" t="s">
         <v>6854</v>
@@ -78008,7 +78008,7 @@
         <v>6822</v>
       </c>
       <c r="F1887">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="G1887" t="s">
         <v>6854</v>
@@ -78034,7 +78034,7 @@
         <v>6822</v>
       </c>
       <c r="F1888">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G1888" t="s">
         <v>6854</v>
@@ -78086,7 +78086,7 @@
         <v>6810</v>
       </c>
       <c r="F1890">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="G1890" t="s">
         <v>6854</v>
@@ -78112,7 +78112,7 @@
         <v>6810</v>
       </c>
       <c r="F1891">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="G1891" t="s">
         <v>6854</v>
@@ -78164,7 +78164,7 @@
         <v>6810</v>
       </c>
       <c r="F1893">
-        <v>2144</v>
+        <v>2138</v>
       </c>
       <c r="G1893" t="s">
         <v>6854</v>
@@ -78190,7 +78190,7 @@
         <v>6810</v>
       </c>
       <c r="F1894">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G1894" t="s">
         <v>6854</v>
@@ -78268,7 +78268,7 @@
         <v>6810</v>
       </c>
       <c r="F1897">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="G1897" t="s">
         <v>6854</v>
@@ -78294,7 +78294,7 @@
         <v>6810</v>
       </c>
       <c r="F1898">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="G1898" t="s">
         <v>6854</v>
@@ -78452,7 +78452,7 @@
         <v>6812</v>
       </c>
       <c r="F1905">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G1905" t="s">
         <v>6854</v>
@@ -78596,7 +78596,7 @@
         <v>6812</v>
       </c>
       <c r="F1911">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G1911" t="s">
         <v>6854</v>
@@ -78648,7 +78648,7 @@
         <v>6812</v>
       </c>
       <c r="F1913">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="G1913" t="s">
         <v>6855</v>
@@ -78772,7 +78772,7 @@
         <v>6812</v>
       </c>
       <c r="F1918">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G1918" t="s">
         <v>6854</v>
@@ -78850,7 +78850,7 @@
         <v>6812</v>
       </c>
       <c r="F1921">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="G1921" t="s">
         <v>6854</v>
@@ -78902,7 +78902,7 @@
         <v>6812</v>
       </c>
       <c r="F1923">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G1923" t="s">
         <v>6854</v>
@@ -79632,7 +79632,7 @@
         <v>6812</v>
       </c>
       <c r="F1955">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="G1955" t="s">
         <v>6854</v>
@@ -79684,7 +79684,7 @@
         <v>6812</v>
       </c>
       <c r="F1957">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G1957" t="s">
         <v>6854</v>
@@ -79814,7 +79814,7 @@
         <v>6813</v>
       </c>
       <c r="F1962">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="G1962" t="s">
         <v>6854</v>
@@ -79840,7 +79840,7 @@
         <v>6813</v>
       </c>
       <c r="F1963">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G1963" t="s">
         <v>6854</v>
@@ -80076,7 +80076,7 @@
         <v>6813</v>
       </c>
       <c r="F1973">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G1973" t="s">
         <v>6855</v>
@@ -80656,7 +80656,7 @@
         <v>6812</v>
       </c>
       <c r="F1999">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="G1999" t="s">
         <v>6854</v>
@@ -80682,7 +80682,7 @@
         <v>6812</v>
       </c>
       <c r="F2000">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G2000" t="s">
         <v>6854</v>
@@ -80916,7 +80916,7 @@
         <v>6812</v>
       </c>
       <c r="F2009">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G2009" t="s">
         <v>6854</v>
@@ -80968,7 +80968,7 @@
         <v>6812</v>
       </c>
       <c r="F2011">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G2011" t="s">
         <v>6855</v>
@@ -81694,7 +81694,7 @@
         <v>6812</v>
       </c>
       <c r="F2041">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G2041" t="s">
         <v>6854</v>
@@ -83730,7 +83730,7 @@
         <v>6827</v>
       </c>
       <c r="F2123">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="G2123" t="s">
         <v>6855</v>
@@ -84342,7 +84342,7 @@
         <v>6827</v>
       </c>
       <c r="F2150">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G2150" t="s">
         <v>6854</v>
@@ -84584,7 +84584,7 @@
         <v>6827</v>
       </c>
       <c r="F2160">
-        <v>18346</v>
+        <v>18246</v>
       </c>
       <c r="G2160" t="s">
         <v>6854</v>
@@ -84610,7 +84610,7 @@
         <v>6827</v>
       </c>
       <c r="F2161">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="G2161" t="s">
         <v>6854</v>
@@ -84734,7 +84734,7 @@
         <v>6827</v>
       </c>
       <c r="F2166">
-        <v>7441</v>
+        <v>7431</v>
       </c>
       <c r="G2166" t="s">
         <v>6854</v>
@@ -84760,7 +84760,7 @@
         <v>6827</v>
       </c>
       <c r="F2167">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="G2167" t="s">
         <v>6854</v>
@@ -85022,7 +85022,7 @@
         <v>6827</v>
       </c>
       <c r="F2178">
-        <v>6119</v>
+        <v>6115</v>
       </c>
       <c r="G2178" t="s">
         <v>6854</v>
@@ -85172,7 +85172,7 @@
         <v>6827</v>
       </c>
       <c r="F2184">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2184" t="s">
         <v>6854</v>
@@ -85258,7 +85258,7 @@
         <v>6827</v>
       </c>
       <c r="F2188">
-        <v>3150</v>
+        <v>3145</v>
       </c>
       <c r="G2188" t="s">
         <v>6854</v>
@@ -86366,7 +86366,7 @@
         <v>6812</v>
       </c>
       <c r="F2235">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2235" t="s">
         <v>6854</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -31797,7 +31797,7 @@
         <v>6886</v>
       </c>
       <c r="F2">
-        <v>26898</v>
+        <v>26713</v>
       </c>
       <c r="G2" t="s">
         <v>6930</v>
@@ -31817,7 +31817,7 @@
         <v>6886</v>
       </c>
       <c r="F3">
-        <v>2919</v>
+        <v>2832</v>
       </c>
       <c r="G3" t="s">
         <v>6930</v>
@@ -31837,7 +31837,7 @@
         <v>6886</v>
       </c>
       <c r="F4">
-        <v>26902</v>
+        <v>26713</v>
       </c>
       <c r="G4" t="s">
         <v>6930</v>
@@ -31857,7 +31857,7 @@
         <v>6886</v>
       </c>
       <c r="F5">
-        <v>2908</v>
+        <v>2821</v>
       </c>
       <c r="G5" t="s">
         <v>6930</v>
@@ -31877,7 +31877,7 @@
         <v>6886</v>
       </c>
       <c r="F6">
-        <v>2422</v>
+        <v>2341</v>
       </c>
       <c r="G6" t="s">
         <v>6930</v>
@@ -31897,7 +31897,7 @@
         <v>6886</v>
       </c>
       <c r="F7">
-        <v>2914</v>
+        <v>2833</v>
       </c>
       <c r="G7" t="s">
         <v>6930</v>
@@ -31917,7 +31917,7 @@
         <v>6886</v>
       </c>
       <c r="F8">
-        <v>2669</v>
+        <v>2582</v>
       </c>
       <c r="G8" t="s">
         <v>6930</v>
@@ -31937,7 +31937,7 @@
         <v>6886</v>
       </c>
       <c r="F9">
-        <v>2707</v>
+        <v>2628</v>
       </c>
       <c r="G9" t="s">
         <v>6930</v>
@@ -31957,7 +31957,7 @@
         <v>6886</v>
       </c>
       <c r="F10">
-        <v>2937</v>
+        <v>2861</v>
       </c>
       <c r="G10" t="s">
         <v>6930</v>
@@ -31977,7 +31977,7 @@
         <v>6886</v>
       </c>
       <c r="F11">
-        <v>2908</v>
+        <v>2821</v>
       </c>
       <c r="G11" t="s">
         <v>6930</v>
@@ -31997,7 +31997,7 @@
         <v>6886</v>
       </c>
       <c r="F12">
-        <v>2908</v>
+        <v>2821</v>
       </c>
       <c r="G12" t="s">
         <v>6930</v>
@@ -32017,7 +32017,7 @@
         <v>6886</v>
       </c>
       <c r="F13">
-        <v>2914</v>
+        <v>2844</v>
       </c>
       <c r="G13" t="s">
         <v>6930</v>
@@ -32037,7 +32037,7 @@
         <v>6886</v>
       </c>
       <c r="F14">
-        <v>2908</v>
+        <v>2821</v>
       </c>
       <c r="G14" t="s">
         <v>6930</v>
@@ -32057,7 +32057,7 @@
         <v>6886</v>
       </c>
       <c r="F15">
-        <v>2913</v>
+        <v>2826</v>
       </c>
       <c r="G15" t="s">
         <v>6930</v>
@@ -32077,7 +32077,7 @@
         <v>6887</v>
       </c>
       <c r="F16">
-        <v>2451</v>
+        <v>2337</v>
       </c>
       <c r="G16" t="s">
         <v>6931</v>
@@ -32103,7 +32103,7 @@
         <v>6887</v>
       </c>
       <c r="F17">
-        <v>1911</v>
+        <v>1785</v>
       </c>
       <c r="G17" t="s">
         <v>6931</v>
@@ -32129,7 +32129,7 @@
         <v>6887</v>
       </c>
       <c r="F18">
-        <v>2451</v>
+        <v>2337</v>
       </c>
       <c r="G18" t="s">
         <v>6931</v>
@@ -32155,7 +32155,7 @@
         <v>6887</v>
       </c>
       <c r="F19">
-        <v>2181</v>
+        <v>2049</v>
       </c>
       <c r="G19" t="s">
         <v>6931</v>
@@ -32181,7 +32181,7 @@
         <v>6887</v>
       </c>
       <c r="F20">
-        <v>1321</v>
+        <v>1219</v>
       </c>
       <c r="G20" t="s">
         <v>6931</v>
@@ -32207,7 +32207,7 @@
         <v>6887</v>
       </c>
       <c r="F21">
-        <v>771</v>
+        <v>663</v>
       </c>
       <c r="G21" t="s">
         <v>6931</v>
@@ -32233,7 +32233,7 @@
         <v>6887</v>
       </c>
       <c r="F22">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
         <v>6931</v>
@@ -32259,7 +32259,7 @@
         <v>6887</v>
       </c>
       <c r="F23">
-        <v>651</v>
+        <v>543</v>
       </c>
       <c r="G23" t="s">
         <v>6931</v>
@@ -32285,7 +32285,7 @@
         <v>6887</v>
       </c>
       <c r="F24">
-        <v>1191</v>
+        <v>1077</v>
       </c>
       <c r="G24" t="s">
         <v>6931</v>
@@ -32311,7 +32311,7 @@
         <v>6887</v>
       </c>
       <c r="F25">
-        <v>1431</v>
+        <v>1323</v>
       </c>
       <c r="G25" t="s">
         <v>6931</v>
@@ -32337,7 +32337,7 @@
         <v>6887</v>
       </c>
       <c r="F26">
-        <v>2271</v>
+        <v>2163</v>
       </c>
       <c r="G26" t="s">
         <v>6931</v>
@@ -32363,7 +32363,7 @@
         <v>6887</v>
       </c>
       <c r="F27">
-        <v>1071</v>
+        <v>957</v>
       </c>
       <c r="G27" t="s">
         <v>6931</v>
@@ -32389,7 +32389,7 @@
         <v>6887</v>
       </c>
       <c r="F28">
-        <v>2271</v>
+        <v>2151</v>
       </c>
       <c r="G28" t="s">
         <v>6931</v>
@@ -32415,7 +32415,7 @@
         <v>6887</v>
       </c>
       <c r="F29">
-        <v>1971</v>
+        <v>1863</v>
       </c>
       <c r="G29" t="s">
         <v>6931</v>
@@ -32441,7 +32441,7 @@
         <v>6887</v>
       </c>
       <c r="F30">
-        <v>1083</v>
+        <v>975</v>
       </c>
       <c r="G30" t="s">
         <v>6930</v>
@@ -32461,7 +32461,7 @@
         <v>6887</v>
       </c>
       <c r="F31">
-        <v>1551</v>
+        <v>1437</v>
       </c>
       <c r="G31" t="s">
         <v>6930</v>
@@ -32481,7 +32481,7 @@
         <v>6887</v>
       </c>
       <c r="F32">
-        <v>3531</v>
+        <v>3411</v>
       </c>
       <c r="G32" t="s">
         <v>6931</v>
@@ -32507,7 +32507,7 @@
         <v>6887</v>
       </c>
       <c r="F33">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="G33" t="s">
         <v>6931</v>
@@ -32533,7 +32533,7 @@
         <v>6887</v>
       </c>
       <c r="F34">
-        <v>3531</v>
+        <v>3417</v>
       </c>
       <c r="G34" t="s">
         <v>6931</v>
@@ -32559,7 +32559,7 @@
         <v>6887</v>
       </c>
       <c r="F35">
-        <v>1108</v>
+        <v>968</v>
       </c>
       <c r="G35" t="s">
         <v>6931</v>
@@ -32585,7 +32585,7 @@
         <v>6887</v>
       </c>
       <c r="F36">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G36" t="s">
         <v>6931</v>
@@ -32611,7 +32611,7 @@
         <v>6887</v>
       </c>
       <c r="F37">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G37" t="s">
         <v>6931</v>
@@ -32637,7 +32637,7 @@
         <v>6887</v>
       </c>
       <c r="F38">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="G38" t="s">
         <v>6931</v>
@@ -32663,7 +32663,7 @@
         <v>6887</v>
       </c>
       <c r="F39">
-        <v>582</v>
+        <v>540</v>
       </c>
       <c r="G39" t="s">
         <v>6931</v>
@@ -32689,7 +32689,7 @@
         <v>6887</v>
       </c>
       <c r="F40">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="G40" t="s">
         <v>6931</v>
@@ -32715,7 +32715,7 @@
         <v>6887</v>
       </c>
       <c r="F41">
-        <v>1122</v>
+        <v>1092</v>
       </c>
       <c r="G41" t="s">
         <v>6931</v>
@@ -32741,7 +32741,7 @@
         <v>6887</v>
       </c>
       <c r="F42">
-        <v>942</v>
+        <v>889</v>
       </c>
       <c r="G42" t="s">
         <v>6931</v>
@@ -32767,7 +32767,7 @@
         <v>6887</v>
       </c>
       <c r="F43">
-        <v>1122</v>
+        <v>1062</v>
       </c>
       <c r="G43" t="s">
         <v>6931</v>
@@ -32793,7 +32793,7 @@
         <v>6887</v>
       </c>
       <c r="F44">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="G44" t="s">
         <v>6931</v>
@@ -32819,7 +32819,7 @@
         <v>6887</v>
       </c>
       <c r="F45">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="G45" t="s">
         <v>6931</v>
@@ -32845,7 +32845,7 @@
         <v>6887</v>
       </c>
       <c r="F46">
-        <v>1122</v>
+        <v>1050</v>
       </c>
       <c r="G46" t="s">
         <v>6931</v>
@@ -32871,7 +32871,7 @@
         <v>6887</v>
       </c>
       <c r="F47">
-        <v>1281</v>
+        <v>1161</v>
       </c>
       <c r="G47" t="s">
         <v>6931</v>
@@ -32897,7 +32897,7 @@
         <v>6887</v>
       </c>
       <c r="F48">
-        <v>1708</v>
+        <v>1568</v>
       </c>
       <c r="G48" t="s">
         <v>6931</v>
@@ -32923,7 +32923,7 @@
         <v>6887</v>
       </c>
       <c r="F49">
-        <v>908</v>
+        <v>767</v>
       </c>
       <c r="G49" t="s">
         <v>6931</v>
@@ -32949,7 +32949,7 @@
         <v>6887</v>
       </c>
       <c r="F50">
-        <v>2108</v>
+        <v>1976</v>
       </c>
       <c r="G50" t="s">
         <v>6931</v>
@@ -32975,7 +32975,7 @@
         <v>6887</v>
       </c>
       <c r="F51">
-        <v>708</v>
+        <v>568</v>
       </c>
       <c r="G51" t="s">
         <v>6931</v>
@@ -33001,7 +33001,7 @@
         <v>6887</v>
       </c>
       <c r="F52">
-        <v>908</v>
+        <v>740</v>
       </c>
       <c r="G52" t="s">
         <v>6931</v>
@@ -33027,7 +33027,7 @@
         <v>6887</v>
       </c>
       <c r="F53">
-        <v>921</v>
+        <v>813</v>
       </c>
       <c r="G53" t="s">
         <v>6931</v>
@@ -33053,7 +33053,7 @@
         <v>6887</v>
       </c>
       <c r="F54">
-        <v>291</v>
+        <v>189</v>
       </c>
       <c r="G54" t="s">
         <v>6931</v>
@@ -33079,7 +33079,7 @@
         <v>6887</v>
       </c>
       <c r="F55">
-        <v>908</v>
+        <v>776</v>
       </c>
       <c r="G55" t="s">
         <v>6931</v>
@@ -33105,7 +33105,7 @@
         <v>6887</v>
       </c>
       <c r="F56">
-        <v>1371</v>
+        <v>1257</v>
       </c>
       <c r="G56" t="s">
         <v>6931</v>
@@ -33131,7 +33131,7 @@
         <v>6887</v>
       </c>
       <c r="F57">
-        <v>1785</v>
+        <v>1689</v>
       </c>
       <c r="G57" t="s">
         <v>6931</v>
@@ -33157,7 +33157,7 @@
         <v>6887</v>
       </c>
       <c r="F58">
-        <v>1191</v>
+        <v>1065</v>
       </c>
       <c r="G58" t="s">
         <v>6931</v>
@@ -33183,7 +33183,7 @@
         <v>6887</v>
       </c>
       <c r="F59">
-        <v>908</v>
+        <v>748</v>
       </c>
       <c r="G59" t="s">
         <v>6931</v>
@@ -33209,7 +33209,7 @@
         <v>6887</v>
       </c>
       <c r="F60">
-        <v>2108</v>
+        <v>1968</v>
       </c>
       <c r="G60" t="s">
         <v>6931</v>
@@ -33235,7 +33235,7 @@
         <v>6887</v>
       </c>
       <c r="F61">
-        <v>2908</v>
+        <v>2748</v>
       </c>
       <c r="G61" t="s">
         <v>6931</v>
@@ -33261,7 +33261,7 @@
         <v>6887</v>
       </c>
       <c r="F62">
-        <v>1908</v>
+        <v>1776</v>
       </c>
       <c r="G62" t="s">
         <v>6931</v>
@@ -33287,7 +33287,7 @@
         <v>6887</v>
       </c>
       <c r="F63">
-        <v>1708</v>
+        <v>1560</v>
       </c>
       <c r="G63" t="s">
         <v>6931</v>
@@ -33313,7 +33313,7 @@
         <v>6888</v>
       </c>
       <c r="F64">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G64" t="s">
         <v>6931</v>
@@ -33339,7 +33339,7 @@
         <v>6889</v>
       </c>
       <c r="F65">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="G65" t="s">
         <v>6931</v>
@@ -33365,7 +33365,7 @@
         <v>6889</v>
       </c>
       <c r="F66">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="G66" t="s">
         <v>6931</v>
@@ -33391,7 +33391,7 @@
         <v>6889</v>
       </c>
       <c r="F67">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="G67" t="s">
         <v>6931</v>
@@ -33417,7 +33417,7 @@
         <v>6889</v>
       </c>
       <c r="F68">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="G68" t="s">
         <v>6931</v>
@@ -33443,7 +33443,7 @@
         <v>6889</v>
       </c>
       <c r="F69">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="G69" t="s">
         <v>6931</v>
@@ -33469,7 +33469,7 @@
         <v>6889</v>
       </c>
       <c r="F70">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="G70" t="s">
         <v>6931</v>
@@ -33625,7 +33625,7 @@
         <v>6890</v>
       </c>
       <c r="F76">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G76" t="s">
         <v>6931</v>
@@ -33827,7 +33827,7 @@
         <v>6890</v>
       </c>
       <c r="F84">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G84" t="s">
         <v>6931</v>
@@ -33853,7 +33853,7 @@
         <v>6889</v>
       </c>
       <c r="F85">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="G85" t="s">
         <v>6931</v>
@@ -33905,7 +33905,7 @@
         <v>6890</v>
       </c>
       <c r="F87">
-        <v>862</v>
+        <v>844</v>
       </c>
       <c r="G87" t="s">
         <v>6931</v>
@@ -33951,7 +33951,7 @@
         <v>6890</v>
       </c>
       <c r="F89">
-        <v>1153</v>
+        <v>1113</v>
       </c>
       <c r="G89" t="s">
         <v>6931</v>
@@ -33997,7 +33997,7 @@
         <v>6890</v>
       </c>
       <c r="F91">
-        <v>743</v>
+        <v>700</v>
       </c>
       <c r="G91" t="s">
         <v>6931</v>
@@ -34043,7 +34043,7 @@
         <v>6890</v>
       </c>
       <c r="F93">
-        <v>1036</v>
+        <v>1012</v>
       </c>
       <c r="G93" t="s">
         <v>6931</v>
@@ -34069,7 +34069,7 @@
         <v>6890</v>
       </c>
       <c r="F94">
-        <v>935</v>
+        <v>897</v>
       </c>
       <c r="G94" t="s">
         <v>6931</v>
@@ -34095,7 +34095,7 @@
         <v>6890</v>
       </c>
       <c r="F95">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="G95" t="s">
         <v>6931</v>
@@ -34121,7 +34121,7 @@
         <v>6890</v>
       </c>
       <c r="F96">
-        <v>604</v>
+        <v>575</v>
       </c>
       <c r="G96" t="s">
         <v>6931</v>
@@ -34187,7 +34187,7 @@
         <v>6890</v>
       </c>
       <c r="F99">
-        <v>866</v>
+        <v>840</v>
       </c>
       <c r="G99" t="s">
         <v>6931</v>
@@ -34253,7 +34253,7 @@
         <v>6890</v>
       </c>
       <c r="F102">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G102" t="s">
         <v>6931</v>
@@ -34279,7 +34279,7 @@
         <v>6888</v>
       </c>
       <c r="F103">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="G103" t="s">
         <v>6931</v>
@@ -34305,7 +34305,7 @@
         <v>6892</v>
       </c>
       <c r="F104">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="G104" t="s">
         <v>6931</v>
@@ -34357,7 +34357,7 @@
         <v>6892</v>
       </c>
       <c r="F106">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="G106" t="s">
         <v>6931</v>
@@ -34383,7 +34383,7 @@
         <v>6892</v>
       </c>
       <c r="F107">
-        <v>1440</v>
+        <v>1424</v>
       </c>
       <c r="G107" t="s">
         <v>6931</v>
@@ -34409,7 +34409,7 @@
         <v>6892</v>
       </c>
       <c r="F108">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="G108" t="s">
         <v>6931</v>
@@ -34435,7 +34435,7 @@
         <v>6892</v>
       </c>
       <c r="F109">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="G109" t="s">
         <v>6931</v>
@@ -34461,7 +34461,7 @@
         <v>6892</v>
       </c>
       <c r="F110">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="G110" t="s">
         <v>6931</v>
@@ -34487,7 +34487,7 @@
         <v>6888</v>
       </c>
       <c r="F111">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="G111" t="s">
         <v>6931</v>
@@ -34591,7 +34591,7 @@
         <v>6891</v>
       </c>
       <c r="F115">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G115" t="s">
         <v>6931</v>
@@ -34669,7 +34669,7 @@
         <v>6888</v>
       </c>
       <c r="F118">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="G118" t="s">
         <v>6931</v>
@@ -34721,7 +34721,7 @@
         <v>6888</v>
       </c>
       <c r="F120">
-        <v>1282</v>
+        <v>1274</v>
       </c>
       <c r="G120" t="s">
         <v>6931</v>
@@ -34893,7 +34893,7 @@
         <v>6893</v>
       </c>
       <c r="F128">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G128" t="s">
         <v>6931</v>
@@ -34919,7 +34919,7 @@
         <v>6893</v>
       </c>
       <c r="F129">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G129" t="s">
         <v>6931</v>
@@ -34971,7 +34971,7 @@
         <v>6888</v>
       </c>
       <c r="F131">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G131" t="s">
         <v>6931</v>
@@ -35049,7 +35049,7 @@
         <v>6891</v>
       </c>
       <c r="F134">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G134" t="s">
         <v>6931</v>
@@ -35127,7 +35127,7 @@
         <v>6890</v>
       </c>
       <c r="F137">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G137" t="s">
         <v>6931</v>
@@ -35153,7 +35153,7 @@
         <v>6890</v>
       </c>
       <c r="F138">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G138" t="s">
         <v>6931</v>
@@ -35179,7 +35179,7 @@
         <v>6890</v>
       </c>
       <c r="F139">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G139" t="s">
         <v>6931</v>
@@ -35205,7 +35205,7 @@
         <v>6888</v>
       </c>
       <c r="F140">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G140" t="s">
         <v>6931</v>
@@ -35231,7 +35231,7 @@
         <v>6888</v>
       </c>
       <c r="F141">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G141" t="s">
         <v>6931</v>
@@ -35257,7 +35257,7 @@
         <v>6888</v>
       </c>
       <c r="F142">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G142" t="s">
         <v>6931</v>
@@ -35361,7 +35361,7 @@
         <v>6890</v>
       </c>
       <c r="F146">
-        <v>1715</v>
+        <v>1701</v>
       </c>
       <c r="G146" t="s">
         <v>6931</v>
@@ -35387,7 +35387,7 @@
         <v>6896</v>
       </c>
       <c r="F147">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G147" t="s">
         <v>6931</v>
@@ -35413,7 +35413,7 @@
         <v>6890</v>
       </c>
       <c r="F148">
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="G148" t="s">
         <v>6931</v>
@@ -35439,7 +35439,7 @@
         <v>6897</v>
       </c>
       <c r="F149">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="G149" t="s">
         <v>6931</v>
@@ -35465,7 +35465,7 @@
         <v>6897</v>
       </c>
       <c r="F150">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="G150" t="s">
         <v>6931</v>
@@ -35491,7 +35491,7 @@
         <v>6897</v>
       </c>
       <c r="F151">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="G151" t="s">
         <v>6931</v>
@@ -35517,7 +35517,7 @@
         <v>6897</v>
       </c>
       <c r="F152">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="G152" t="s">
         <v>6931</v>
@@ -35543,7 +35543,7 @@
         <v>6890</v>
       </c>
       <c r="F153">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="G153" t="s">
         <v>6931</v>
@@ -35569,7 +35569,7 @@
         <v>6890</v>
       </c>
       <c r="F154">
-        <v>1164</v>
+        <v>1153</v>
       </c>
       <c r="G154" t="s">
         <v>6931</v>
@@ -35595,7 +35595,7 @@
         <v>6890</v>
       </c>
       <c r="F155">
-        <v>1764</v>
+        <v>1756</v>
       </c>
       <c r="G155" t="s">
         <v>6931</v>
@@ -35647,7 +35647,7 @@
         <v>6897</v>
       </c>
       <c r="F157">
-        <v>1482</v>
+        <v>1466</v>
       </c>
       <c r="G157" t="s">
         <v>6931</v>
@@ -35699,7 +35699,7 @@
         <v>6897</v>
       </c>
       <c r="F159">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="G159" t="s">
         <v>6931</v>
@@ -35725,7 +35725,7 @@
         <v>6897</v>
       </c>
       <c r="F160">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="G160" t="s">
         <v>6931</v>
@@ -35751,7 +35751,7 @@
         <v>6897</v>
       </c>
       <c r="F161">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="G161" t="s">
         <v>6931</v>
@@ -35777,7 +35777,7 @@
         <v>6897</v>
       </c>
       <c r="F162">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="G162" t="s">
         <v>6931</v>
@@ -35803,7 +35803,7 @@
         <v>6890</v>
       </c>
       <c r="F163">
-        <v>1620</v>
+        <v>1596</v>
       </c>
       <c r="G163" t="s">
         <v>6931</v>
@@ -35855,7 +35855,7 @@
         <v>6896</v>
       </c>
       <c r="F165">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="G165" t="s">
         <v>6931</v>
@@ -35881,7 +35881,7 @@
         <v>6896</v>
       </c>
       <c r="F166">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="G166" t="s">
         <v>6931</v>
@@ -35907,7 +35907,7 @@
         <v>6896</v>
       </c>
       <c r="F167">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="G167" t="s">
         <v>6931</v>
@@ -35933,7 +35933,7 @@
         <v>6896</v>
       </c>
       <c r="F168">
-        <v>2953</v>
+        <v>2945</v>
       </c>
       <c r="G168" t="s">
         <v>6931</v>
@@ -35985,7 +35985,7 @@
         <v>6896</v>
       </c>
       <c r="F170">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="G170" t="s">
         <v>6931</v>
@@ -36011,7 +36011,7 @@
         <v>6896</v>
       </c>
       <c r="F171">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="G171" t="s">
         <v>6931</v>
@@ -36037,7 +36037,7 @@
         <v>6896</v>
       </c>
       <c r="F172">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="G172" t="s">
         <v>6931</v>
@@ -36063,7 +36063,7 @@
         <v>6890</v>
       </c>
       <c r="F173">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="G173" t="s">
         <v>6931</v>
@@ -36089,7 +36089,7 @@
         <v>6890</v>
       </c>
       <c r="F174">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="G174" t="s">
         <v>6931</v>
@@ -36115,7 +36115,7 @@
         <v>6890</v>
       </c>
       <c r="F175">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="G175" t="s">
         <v>6931</v>
@@ -36141,7 +36141,7 @@
         <v>6890</v>
       </c>
       <c r="F176">
-        <v>1070</v>
+        <v>1054</v>
       </c>
       <c r="G176" t="s">
         <v>6931</v>
@@ -36167,7 +36167,7 @@
         <v>6896</v>
       </c>
       <c r="F177">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="G177" t="s">
         <v>6931</v>
@@ -36193,7 +36193,7 @@
         <v>6890</v>
       </c>
       <c r="F178">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="G178" t="s">
         <v>6931</v>
@@ -36219,7 +36219,7 @@
         <v>6890</v>
       </c>
       <c r="F179">
-        <v>1035</v>
+        <v>1013</v>
       </c>
       <c r="G179" t="s">
         <v>6931</v>
@@ -36343,7 +36343,7 @@
         <v>6890</v>
       </c>
       <c r="F184">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G184" t="s">
         <v>6931</v>
@@ -36369,7 +36369,7 @@
         <v>6888</v>
       </c>
       <c r="F185">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G185" t="s">
         <v>6931</v>
@@ -36395,7 +36395,7 @@
         <v>6888</v>
       </c>
       <c r="F186">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G186" t="s">
         <v>6930</v>
@@ -36467,7 +36467,7 @@
         <v>6888</v>
       </c>
       <c r="F189">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="G189" t="s">
         <v>6931</v>
@@ -36493,7 +36493,7 @@
         <v>6888</v>
       </c>
       <c r="F190">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G190" t="s">
         <v>6931</v>
@@ -36625,7 +36625,7 @@
         <v>6888</v>
       </c>
       <c r="F196">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G196" t="s">
         <v>6931</v>
@@ -36671,7 +36671,7 @@
         <v>6890</v>
       </c>
       <c r="F198">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G198" t="s">
         <v>6931</v>
@@ -36797,7 +36797,7 @@
         <v>6890</v>
       </c>
       <c r="F204">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G204" t="s">
         <v>6931</v>
@@ -36863,7 +36863,7 @@
         <v>6890</v>
       </c>
       <c r="F207">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G207" t="s">
         <v>6931</v>
@@ -36889,7 +36889,7 @@
         <v>6890</v>
       </c>
       <c r="F208">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G208" t="s">
         <v>6931</v>
@@ -36915,7 +36915,7 @@
         <v>6890</v>
       </c>
       <c r="F209">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G209" t="s">
         <v>6931</v>
@@ -36941,7 +36941,7 @@
         <v>6890</v>
       </c>
       <c r="F210">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G210" t="s">
         <v>6931</v>
@@ -37039,7 +37039,7 @@
         <v>6899</v>
       </c>
       <c r="F214">
-        <v>1902</v>
+        <v>1884</v>
       </c>
       <c r="G214" t="s">
         <v>6931</v>
@@ -37091,7 +37091,7 @@
         <v>6899</v>
       </c>
       <c r="F216">
-        <v>1872</v>
+        <v>1860</v>
       </c>
       <c r="G216" t="s">
         <v>6931</v>
@@ -37117,7 +37117,7 @@
         <v>6899</v>
       </c>
       <c r="F217">
-        <v>1788</v>
+        <v>1782</v>
       </c>
       <c r="G217" t="s">
         <v>6931</v>
@@ -37169,7 +37169,7 @@
         <v>6899</v>
       </c>
       <c r="F219">
-        <v>1878</v>
+        <v>1872</v>
       </c>
       <c r="G219" t="s">
         <v>6931</v>
@@ -37273,7 +37273,7 @@
         <v>6899</v>
       </c>
       <c r="F223">
-        <v>1410</v>
+        <v>1368</v>
       </c>
       <c r="G223" t="s">
         <v>6931</v>
@@ -37299,7 +37299,7 @@
         <v>6891</v>
       </c>
       <c r="F224">
-        <v>1512</v>
+        <v>1494</v>
       </c>
       <c r="G224" t="s">
         <v>6931</v>
@@ -37325,7 +37325,7 @@
         <v>6891</v>
       </c>
       <c r="F225">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="G225" t="s">
         <v>6931</v>
@@ -37351,7 +37351,7 @@
         <v>6891</v>
       </c>
       <c r="F226">
-        <v>1794</v>
+        <v>1788</v>
       </c>
       <c r="G226" t="s">
         <v>6931</v>
@@ -37377,7 +37377,7 @@
         <v>6891</v>
       </c>
       <c r="F227">
-        <v>1254</v>
+        <v>1242</v>
       </c>
       <c r="G227" t="s">
         <v>6931</v>
@@ -37403,7 +37403,7 @@
         <v>6891</v>
       </c>
       <c r="F228">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="G228" t="s">
         <v>6931</v>
@@ -37481,7 +37481,7 @@
         <v>6899</v>
       </c>
       <c r="F231">
-        <v>1860</v>
+        <v>1848</v>
       </c>
       <c r="G231" t="s">
         <v>6931</v>
@@ -37559,7 +37559,7 @@
         <v>6888</v>
       </c>
       <c r="F234">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="G234" t="s">
         <v>6931</v>
@@ -37637,7 +37637,7 @@
         <v>6892</v>
       </c>
       <c r="F237">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="G237" t="s">
         <v>6931</v>
@@ -37663,7 +37663,7 @@
         <v>6892</v>
       </c>
       <c r="F238">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="G238" t="s">
         <v>6931</v>
@@ -37689,7 +37689,7 @@
         <v>6892</v>
       </c>
       <c r="F239">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="G239" t="s">
         <v>6931</v>
@@ -37715,7 +37715,7 @@
         <v>6892</v>
       </c>
       <c r="F240">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="G240" t="s">
         <v>6931</v>
@@ -37741,7 +37741,7 @@
         <v>6892</v>
       </c>
       <c r="F241">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="G241" t="s">
         <v>6931</v>
@@ -37949,7 +37949,7 @@
         <v>6888</v>
       </c>
       <c r="F249">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="G249" t="s">
         <v>6931</v>
@@ -37995,7 +37995,7 @@
         <v>6888</v>
       </c>
       <c r="F251">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G251" t="s">
         <v>6931</v>
@@ -38073,7 +38073,7 @@
         <v>6900</v>
       </c>
       <c r="F254">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="G254" t="s">
         <v>6931</v>
@@ -38269,7 +38269,7 @@
         <v>6888</v>
       </c>
       <c r="F262">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="G262" t="s">
         <v>6931</v>
@@ -38321,7 +38321,7 @@
         <v>6900</v>
       </c>
       <c r="F264">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="G264" t="s">
         <v>6931</v>
@@ -38419,7 +38419,7 @@
         <v>6900</v>
       </c>
       <c r="F268">
-        <v>1755</v>
+        <v>1749</v>
       </c>
       <c r="G268" t="s">
         <v>6931</v>
@@ -38523,7 +38523,7 @@
         <v>6900</v>
       </c>
       <c r="F272">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G272" t="s">
         <v>6931</v>
@@ -38549,7 +38549,7 @@
         <v>6898</v>
       </c>
       <c r="F273">
-        <v>1136</v>
+        <v>1126</v>
       </c>
       <c r="G273" t="s">
         <v>6931</v>
@@ -38575,7 +38575,7 @@
         <v>6898</v>
       </c>
       <c r="F274">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="G274" t="s">
         <v>6931</v>
@@ -38681,7 +38681,7 @@
         <v>6898</v>
       </c>
       <c r="F279">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="G279" t="s">
         <v>6931</v>
@@ -38707,7 +38707,7 @@
         <v>6898</v>
       </c>
       <c r="F280">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="G280" t="s">
         <v>6931</v>
@@ -38733,7 +38733,7 @@
         <v>6898</v>
       </c>
       <c r="F281">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="G281" t="s">
         <v>6931</v>
@@ -38811,7 +38811,7 @@
         <v>6888</v>
       </c>
       <c r="F284">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G284" t="s">
         <v>6931</v>
@@ -38863,7 +38863,7 @@
         <v>6888</v>
       </c>
       <c r="F286">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G286" t="s">
         <v>6931</v>
@@ -38915,7 +38915,7 @@
         <v>6888</v>
       </c>
       <c r="F288">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="G288" t="s">
         <v>6931</v>
@@ -38941,7 +38941,7 @@
         <v>6888</v>
       </c>
       <c r="F289">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G289" t="s">
         <v>6931</v>
@@ -38993,7 +38993,7 @@
         <v>6888</v>
       </c>
       <c r="F291">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G291" t="s">
         <v>6931</v>
@@ -39019,7 +39019,7 @@
         <v>6888</v>
       </c>
       <c r="F292">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="G292" t="s">
         <v>6931</v>
@@ -39045,7 +39045,7 @@
         <v>6888</v>
       </c>
       <c r="F293">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="G293" t="s">
         <v>6931</v>
@@ -39091,7 +39091,7 @@
         <v>6902</v>
       </c>
       <c r="F295">
-        <v>2120</v>
+        <v>2112</v>
       </c>
       <c r="G295" t="s">
         <v>6931</v>
@@ -39143,7 +39143,7 @@
         <v>6904</v>
       </c>
       <c r="F297">
-        <v>1104</v>
+        <v>1080</v>
       </c>
       <c r="G297" t="s">
         <v>6931</v>
@@ -39169,7 +39169,7 @@
         <v>6904</v>
       </c>
       <c r="F298">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="G298" t="s">
         <v>6931</v>
@@ -39247,7 +39247,7 @@
         <v>6904</v>
       </c>
       <c r="F301">
-        <v>1104</v>
+        <v>1080</v>
       </c>
       <c r="G301" t="s">
         <v>6931</v>
@@ -39273,7 +39273,7 @@
         <v>6904</v>
       </c>
       <c r="F302">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="G302" t="s">
         <v>6931</v>
@@ -39299,7 +39299,7 @@
         <v>6904</v>
       </c>
       <c r="F303">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="G303" t="s">
         <v>6931</v>
@@ -39325,7 +39325,7 @@
         <v>6902</v>
       </c>
       <c r="F304">
-        <v>2252</v>
+        <v>2244</v>
       </c>
       <c r="G304" t="s">
         <v>6931</v>
@@ -39351,7 +39351,7 @@
         <v>6904</v>
       </c>
       <c r="F305">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G305" t="s">
         <v>6931</v>
@@ -39377,7 +39377,7 @@
         <v>6904</v>
       </c>
       <c r="F306">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="G306" t="s">
         <v>6931</v>
@@ -39403,7 +39403,7 @@
         <v>6904</v>
       </c>
       <c r="F307">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="G307" t="s">
         <v>6931</v>
@@ -39429,7 +39429,7 @@
         <v>6904</v>
       </c>
       <c r="F308">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="G308" t="s">
         <v>6931</v>
@@ -39455,7 +39455,7 @@
         <v>6900</v>
       </c>
       <c r="F309">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G309" t="s">
         <v>6930</v>
@@ -39475,7 +39475,7 @@
         <v>6900</v>
       </c>
       <c r="F310">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="G310" t="s">
         <v>6930</v>
@@ -39495,7 +39495,7 @@
         <v>6900</v>
       </c>
       <c r="F311">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G311" t="s">
         <v>6930</v>
@@ -39515,7 +39515,7 @@
         <v>6900</v>
       </c>
       <c r="F312">
-        <v>1650</v>
+        <v>1644</v>
       </c>
       <c r="G312" t="s">
         <v>6930</v>
@@ -39535,7 +39535,7 @@
         <v>6900</v>
       </c>
       <c r="F313">
-        <v>1710</v>
+        <v>1704</v>
       </c>
       <c r="G313" t="s">
         <v>6930</v>
@@ -39555,7 +39555,7 @@
         <v>6900</v>
       </c>
       <c r="F314">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G314" t="s">
         <v>6930</v>
@@ -39575,7 +39575,7 @@
         <v>6900</v>
       </c>
       <c r="F315">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="G315" t="s">
         <v>6930</v>
@@ -39595,7 +39595,7 @@
         <v>6900</v>
       </c>
       <c r="F316">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="G316" t="s">
         <v>6930</v>
@@ -39615,7 +39615,7 @@
         <v>6890</v>
       </c>
       <c r="F317">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="G317" t="s">
         <v>6931</v>
@@ -39641,7 +39641,7 @@
         <v>6890</v>
       </c>
       <c r="F318">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="G318" t="s">
         <v>6931</v>
@@ -39693,7 +39693,7 @@
         <v>6890</v>
       </c>
       <c r="F320">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G320" t="s">
         <v>6931</v>
@@ -39739,7 +39739,7 @@
         <v>6900</v>
       </c>
       <c r="F322">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="G322" t="s">
         <v>6930</v>
@@ -39759,7 +39759,7 @@
         <v>6898</v>
       </c>
       <c r="F323">
-        <v>3421</v>
+        <v>3401</v>
       </c>
       <c r="G323" t="s">
         <v>6931</v>
@@ -39931,7 +39931,7 @@
         <v>6898</v>
       </c>
       <c r="F331">
-        <v>1486</v>
+        <v>1466</v>
       </c>
       <c r="G331" t="s">
         <v>6931</v>
@@ -39957,7 +39957,7 @@
         <v>6898</v>
       </c>
       <c r="F332">
-        <v>3424</v>
+        <v>3414</v>
       </c>
       <c r="G332" t="s">
         <v>6931</v>
@@ -39983,7 +39983,7 @@
         <v>6898</v>
       </c>
       <c r="F333">
-        <v>3694</v>
+        <v>3684</v>
       </c>
       <c r="G333" t="s">
         <v>6931</v>
@@ -40009,7 +40009,7 @@
         <v>6898</v>
       </c>
       <c r="F334">
-        <v>2560</v>
+        <v>2530</v>
       </c>
       <c r="G334" t="s">
         <v>6931</v>
@@ -40055,7 +40055,7 @@
         <v>6898</v>
       </c>
       <c r="F336">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="G336" t="s">
         <v>6930</v>
@@ -40173,7 +40173,7 @@
         <v>6904</v>
       </c>
       <c r="F341">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G341" t="s">
         <v>6931</v>
@@ -40329,7 +40329,7 @@
         <v>6898</v>
       </c>
       <c r="F347">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="G347" t="s">
         <v>6931</v>
@@ -40355,7 +40355,7 @@
         <v>6904</v>
       </c>
       <c r="F348">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="G348" t="s">
         <v>6931</v>
@@ -40381,7 +40381,7 @@
         <v>6904</v>
       </c>
       <c r="F349">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="G349" t="s">
         <v>6931</v>
@@ -40407,7 +40407,7 @@
         <v>6904</v>
       </c>
       <c r="F350">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G350" t="s">
         <v>6931</v>
@@ -40433,7 +40433,7 @@
         <v>6904</v>
       </c>
       <c r="F351">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G351" t="s">
         <v>6931</v>
@@ -40459,7 +40459,7 @@
         <v>6904</v>
       </c>
       <c r="F352">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G352" t="s">
         <v>6931</v>
@@ -40485,7 +40485,7 @@
         <v>6904</v>
       </c>
       <c r="F353">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G353" t="s">
         <v>6931</v>
@@ -40537,7 +40537,7 @@
         <v>6904</v>
       </c>
       <c r="F355">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G355" t="s">
         <v>6931</v>
@@ -40589,7 +40589,7 @@
         <v>6904</v>
       </c>
       <c r="F357">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="G357" t="s">
         <v>6931</v>
@@ -40641,7 +40641,7 @@
         <v>6888</v>
       </c>
       <c r="F359">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G359" t="s">
         <v>6931</v>
@@ -40693,7 +40693,7 @@
         <v>6890</v>
       </c>
       <c r="F361">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="G361" t="s">
         <v>6931</v>
@@ -40719,7 +40719,7 @@
         <v>6888</v>
       </c>
       <c r="F362">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G362" t="s">
         <v>6931</v>
@@ -40771,7 +40771,7 @@
         <v>6890</v>
       </c>
       <c r="F364">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G364" t="s">
         <v>6930</v>
@@ -40791,7 +40791,7 @@
         <v>6890</v>
       </c>
       <c r="F365">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="G365" t="s">
         <v>6931</v>
@@ -40869,7 +40869,7 @@
         <v>6888</v>
       </c>
       <c r="F368">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G368" t="s">
         <v>6931</v>
@@ -40921,7 +40921,7 @@
         <v>6890</v>
       </c>
       <c r="F370">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G370" t="s">
         <v>6931</v>
@@ -40947,7 +40947,7 @@
         <v>6898</v>
       </c>
       <c r="F371">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="G371" t="s">
         <v>6930</v>
@@ -40967,7 +40967,7 @@
         <v>6898</v>
       </c>
       <c r="F372">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G372" t="s">
         <v>6931</v>
@@ -41071,7 +41071,7 @@
         <v>6898</v>
       </c>
       <c r="F376">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="G376" t="s">
         <v>6931</v>
@@ -41097,7 +41097,7 @@
         <v>6898</v>
       </c>
       <c r="F377">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="G377" t="s">
         <v>6931</v>
@@ -41149,7 +41149,7 @@
         <v>6890</v>
       </c>
       <c r="F379">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G379" t="s">
         <v>6931</v>
@@ -41175,7 +41175,7 @@
         <v>6905</v>
       </c>
       <c r="F380">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G380" t="s">
         <v>6931</v>
@@ -41201,7 +41201,7 @@
         <v>6906</v>
       </c>
       <c r="F381">
-        <v>1598</v>
+        <v>1589</v>
       </c>
       <c r="G381" t="s">
         <v>6931</v>
@@ -41227,7 +41227,7 @@
         <v>6907</v>
       </c>
       <c r="F382">
-        <v>4224</v>
+        <v>4215</v>
       </c>
       <c r="G382" t="s">
         <v>6931</v>
@@ -41253,7 +41253,7 @@
         <v>6908</v>
       </c>
       <c r="F383">
-        <v>1113</v>
+        <v>1095</v>
       </c>
       <c r="G383" t="s">
         <v>6931</v>
@@ -41325,7 +41325,7 @@
         <v>6891</v>
       </c>
       <c r="F386">
-        <v>1637</v>
+        <v>1625</v>
       </c>
       <c r="G386" t="s">
         <v>6931</v>
@@ -41351,7 +41351,7 @@
         <v>6891</v>
       </c>
       <c r="F387">
-        <v>1782</v>
+        <v>1776</v>
       </c>
       <c r="G387" t="s">
         <v>6931</v>
@@ -41503,7 +41503,7 @@
         <v>6888</v>
       </c>
       <c r="F394">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G394" t="s">
         <v>6931</v>
@@ -41555,7 +41555,7 @@
         <v>6888</v>
       </c>
       <c r="F396">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G396" t="s">
         <v>6931</v>
@@ -41607,7 +41607,7 @@
         <v>6890</v>
       </c>
       <c r="F398">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G398" t="s">
         <v>6931</v>
@@ -41633,7 +41633,7 @@
         <v>6890</v>
       </c>
       <c r="F399">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G399" t="s">
         <v>6931</v>
@@ -41685,7 +41685,7 @@
         <v>6890</v>
       </c>
       <c r="F401">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G401" t="s">
         <v>6931</v>
@@ -41751,7 +41751,7 @@
         <v>6899</v>
       </c>
       <c r="F404">
-        <v>1902</v>
+        <v>1896</v>
       </c>
       <c r="G404" t="s">
         <v>6931</v>
@@ -41777,7 +41777,7 @@
         <v>6891</v>
       </c>
       <c r="F405">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="G405" t="s">
         <v>6931</v>
@@ -41803,7 +41803,7 @@
         <v>6899</v>
       </c>
       <c r="F406">
-        <v>1614</v>
+        <v>1578</v>
       </c>
       <c r="G406" t="s">
         <v>6931</v>
@@ -41829,7 +41829,7 @@
         <v>6899</v>
       </c>
       <c r="F407">
-        <v>1662</v>
+        <v>1650</v>
       </c>
       <c r="G407" t="s">
         <v>6931</v>
@@ -41855,7 +41855,7 @@
         <v>6899</v>
       </c>
       <c r="F408">
-        <v>1773</v>
+        <v>1755</v>
       </c>
       <c r="G408" t="s">
         <v>6931</v>
@@ -41881,7 +41881,7 @@
         <v>6899</v>
       </c>
       <c r="F409">
-        <v>1703</v>
+        <v>1691</v>
       </c>
       <c r="G409" t="s">
         <v>6931</v>
@@ -41907,7 +41907,7 @@
         <v>6899</v>
       </c>
       <c r="F410">
-        <v>1667</v>
+        <v>1655</v>
       </c>
       <c r="G410" t="s">
         <v>6931</v>
@@ -41933,7 +41933,7 @@
         <v>6899</v>
       </c>
       <c r="F411">
-        <v>1554</v>
+        <v>1524</v>
       </c>
       <c r="G411" t="s">
         <v>6931</v>
@@ -41959,7 +41959,7 @@
         <v>6891</v>
       </c>
       <c r="F412">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="G412" t="s">
         <v>6931</v>
@@ -42011,7 +42011,7 @@
         <v>6909</v>
       </c>
       <c r="F414">
-        <v>3881</v>
+        <v>3875</v>
       </c>
       <c r="G414" t="s">
         <v>6931</v>
@@ -42037,7 +42037,7 @@
         <v>6910</v>
       </c>
       <c r="F415">
-        <v>3113</v>
+        <v>3105</v>
       </c>
       <c r="G415" t="s">
         <v>6931</v>
@@ -42089,7 +42089,7 @@
         <v>6909</v>
       </c>
       <c r="F417">
-        <v>4118</v>
+        <v>4116</v>
       </c>
       <c r="G417" t="s">
         <v>6931</v>
@@ -42115,7 +42115,7 @@
         <v>6888</v>
       </c>
       <c r="F418">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G418" t="s">
         <v>6931</v>
@@ -42247,7 +42247,7 @@
         <v>6890</v>
       </c>
       <c r="F424">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G424" t="s">
         <v>6931</v>
@@ -42417,7 +42417,7 @@
         <v>6913</v>
       </c>
       <c r="F431">
-        <v>1536</v>
+        <v>1524</v>
       </c>
       <c r="G431" t="s">
         <v>6931</v>
@@ -42663,7 +42663,7 @@
         <v>6912</v>
       </c>
       <c r="F443">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G443" t="s">
         <v>6930</v>
@@ -42683,7 +42683,7 @@
         <v>6897</v>
       </c>
       <c r="F444">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="G444" t="s">
         <v>6931</v>
@@ -42749,7 +42749,7 @@
         <v>6897</v>
       </c>
       <c r="F447">
-        <v>1223</v>
+        <v>1205</v>
       </c>
       <c r="G447" t="s">
         <v>6931</v>
@@ -42775,7 +42775,7 @@
         <v>6913</v>
       </c>
       <c r="F448">
-        <v>1163</v>
+        <v>1151</v>
       </c>
       <c r="G448" t="s">
         <v>6931</v>
@@ -42853,7 +42853,7 @@
         <v>6913</v>
       </c>
       <c r="F451">
-        <v>1476</v>
+        <v>1452</v>
       </c>
       <c r="G451" t="s">
         <v>6931</v>
@@ -42925,7 +42925,7 @@
         <v>6913</v>
       </c>
       <c r="F454">
-        <v>1536</v>
+        <v>1524</v>
       </c>
       <c r="G454" t="s">
         <v>6931</v>
@@ -43057,7 +43057,7 @@
         <v>6913</v>
       </c>
       <c r="F460">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="G460" t="s">
         <v>6931</v>
@@ -43293,7 +43293,7 @@
         <v>6897</v>
       </c>
       <c r="F470">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="G470" t="s">
         <v>6931</v>
@@ -48457,7 +48457,7 @@
         <v>6886</v>
       </c>
       <c r="F673">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="G673" t="s">
         <v>6931</v>
@@ -49367,7 +49367,7 @@
         <v>6912</v>
       </c>
       <c r="F708">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="G708" t="s">
         <v>6931</v>
@@ -49393,7 +49393,7 @@
         <v>6912</v>
       </c>
       <c r="F709">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G709" t="s">
         <v>6931</v>
@@ -49497,7 +49497,7 @@
         <v>6912</v>
       </c>
       <c r="F713">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G713" t="s">
         <v>6931</v>
@@ -49923,7 +49923,7 @@
         <v>6912</v>
       </c>
       <c r="F731">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="G731" t="s">
         <v>6931</v>
@@ -50079,7 +50079,7 @@
         <v>6912</v>
       </c>
       <c r="F737">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="G737" t="s">
         <v>6931</v>
@@ -50889,7 +50889,7 @@
         <v>6902</v>
       </c>
       <c r="F770">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="G770" t="s">
         <v>6931</v>
@@ -50967,7 +50967,7 @@
         <v>6902</v>
       </c>
       <c r="F773">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G773" t="s">
         <v>6931</v>
@@ -51097,7 +51097,7 @@
         <v>6902</v>
       </c>
       <c r="F778">
-        <v>1614</v>
+        <v>1608</v>
       </c>
       <c r="G778" t="s">
         <v>6931</v>
@@ -51305,7 +51305,7 @@
         <v>6902</v>
       </c>
       <c r="F786">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="G786" t="s">
         <v>6931</v>
@@ -51435,7 +51435,7 @@
         <v>6902</v>
       </c>
       <c r="F791">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="G791" t="s">
         <v>6931</v>
@@ -51819,7 +51819,7 @@
         <v>6902</v>
       </c>
       <c r="F806">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="G806" t="s">
         <v>6931</v>
@@ -52203,7 +52203,7 @@
         <v>6902</v>
       </c>
       <c r="F821">
-        <v>4735</v>
+        <v>4729</v>
       </c>
       <c r="G821" t="s">
         <v>6931</v>
@@ -54347,7 +54347,7 @@
         <v>6898</v>
       </c>
       <c r="F912">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="G912" t="s">
         <v>6931</v>
@@ -54733,7 +54733,7 @@
         <v>6921</v>
       </c>
       <c r="F931">
-        <v>801</v>
+        <v>777</v>
       </c>
       <c r="G931" t="s">
         <v>6931</v>
@@ -55105,7 +55105,7 @@
         <v>6921</v>
       </c>
       <c r="F946">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="G946" t="s">
         <v>6931</v>
@@ -55131,7 +55131,7 @@
         <v>6921</v>
       </c>
       <c r="F947">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="G947" t="s">
         <v>6931</v>
@@ -55243,7 +55243,7 @@
         <v>6889</v>
       </c>
       <c r="F952">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G952" t="s">
         <v>6931</v>
@@ -55413,7 +55413,7 @@
         <v>6921</v>
       </c>
       <c r="F959">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="G959" t="s">
         <v>6930</v>
@@ -55479,7 +55479,7 @@
         <v>6889</v>
       </c>
       <c r="F962">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G962" t="s">
         <v>6931</v>
@@ -55505,7 +55505,7 @@
         <v>6889</v>
       </c>
       <c r="F963">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G963" t="s">
         <v>6931</v>
@@ -55531,7 +55531,7 @@
         <v>6889</v>
       </c>
       <c r="F964">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="G964" t="s">
         <v>6931</v>
@@ -55583,7 +55583,7 @@
         <v>6898</v>
       </c>
       <c r="F966">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G966" t="s">
         <v>6931</v>
@@ -55877,7 +55877,7 @@
         <v>6921</v>
       </c>
       <c r="F978">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="G978" t="s">
         <v>6931</v>
@@ -55981,7 +55981,7 @@
         <v>6921</v>
       </c>
       <c r="F982">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G982" t="s">
         <v>6931</v>
@@ -56151,7 +56151,7 @@
         <v>6890</v>
       </c>
       <c r="F989">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G989" t="s">
         <v>6931</v>
@@ -56607,7 +56607,7 @@
         <v>6890</v>
       </c>
       <c r="F1007">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G1007" t="s">
         <v>6931</v>
@@ -56633,7 +56633,7 @@
         <v>6890</v>
       </c>
       <c r="F1008">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G1008" t="s">
         <v>6931</v>
@@ -56711,7 +56711,7 @@
         <v>6890</v>
       </c>
       <c r="F1011">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G1011" t="s">
         <v>6931</v>
@@ -56737,7 +56737,7 @@
         <v>6890</v>
       </c>
       <c r="F1012">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G1012" t="s">
         <v>6931</v>
@@ -57193,7 +57193,7 @@
         <v>6890</v>
       </c>
       <c r="F1033">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G1033" t="s">
         <v>6931</v>
@@ -57219,7 +57219,7 @@
         <v>6890</v>
       </c>
       <c r="F1034">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1034" t="s">
         <v>6931</v>
@@ -57245,7 +57245,7 @@
         <v>6890</v>
       </c>
       <c r="F1035">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G1035" t="s">
         <v>6931</v>
@@ -57297,7 +57297,7 @@
         <v>6890</v>
       </c>
       <c r="F1037">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G1037" t="s">
         <v>6931</v>
@@ -57401,7 +57401,7 @@
         <v>6890</v>
       </c>
       <c r="F1041">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1041" t="s">
         <v>6931</v>
@@ -57453,7 +57453,7 @@
         <v>6890</v>
       </c>
       <c r="F1043">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G1043" t="s">
         <v>6931</v>
@@ -57796,7 +57796,7 @@
         <v>6890</v>
       </c>
       <c r="F1057">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G1057" t="s">
         <v>6931</v>
@@ -57874,7 +57874,7 @@
         <v>6890</v>
       </c>
       <c r="F1060">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G1060" t="s">
         <v>6931</v>
@@ -58084,7 +58084,7 @@
         <v>6890</v>
       </c>
       <c r="F1069">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G1069" t="s">
         <v>6930</v>
@@ -58130,7 +58130,7 @@
         <v>6890</v>
       </c>
       <c r="F1071">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G1071" t="s">
         <v>6931</v>
@@ -58182,7 +58182,7 @@
         <v>6922</v>
       </c>
       <c r="F1073">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="G1073" t="s">
         <v>6931</v>
@@ -58208,7 +58208,7 @@
         <v>6923</v>
       </c>
       <c r="F1074">
-        <v>5561</v>
+        <v>5549</v>
       </c>
       <c r="G1074" t="s">
         <v>6931</v>
@@ -58234,7 +58234,7 @@
         <v>6888</v>
       </c>
       <c r="F1075">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1075" t="s">
         <v>6931</v>
@@ -58306,7 +58306,7 @@
         <v>6890</v>
       </c>
       <c r="F1078">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G1078" t="s">
         <v>6931</v>
@@ -58410,7 +58410,7 @@
         <v>6890</v>
       </c>
       <c r="F1082">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G1082" t="s">
         <v>6931</v>
@@ -58436,7 +58436,7 @@
         <v>6890</v>
       </c>
       <c r="F1083">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G1083" t="s">
         <v>6931</v>
@@ -58488,7 +58488,7 @@
         <v>6890</v>
       </c>
       <c r="F1085">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="G1085" t="s">
         <v>6931</v>
@@ -59402,7 +59402,7 @@
         <v>6922</v>
       </c>
       <c r="F1125">
-        <v>971</v>
+        <v>953</v>
       </c>
       <c r="G1125" t="s">
         <v>6931</v>
@@ -59980,7 +59980,7 @@
         <v>6890</v>
       </c>
       <c r="F1150">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G1150" t="s">
         <v>6931</v>
@@ -60026,7 +60026,7 @@
         <v>6890</v>
       </c>
       <c r="F1152">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G1152" t="s">
         <v>6931</v>
@@ -60182,7 +60182,7 @@
         <v>6890</v>
       </c>
       <c r="F1158">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G1158" t="s">
         <v>6931</v>
@@ -60260,7 +60260,7 @@
         <v>6890</v>
       </c>
       <c r="F1161">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G1161" t="s">
         <v>6931</v>
@@ -60430,7 +60430,7 @@
         <v>6887</v>
       </c>
       <c r="F1168">
-        <v>1204</v>
+        <v>1008</v>
       </c>
       <c r="G1168" t="s">
         <v>6931</v>
@@ -60482,7 +60482,7 @@
         <v>6887</v>
       </c>
       <c r="F1170">
-        <v>1820</v>
+        <v>1808</v>
       </c>
       <c r="G1170" t="s">
         <v>6931</v>
@@ -60508,7 +60508,7 @@
         <v>6887</v>
       </c>
       <c r="F1171">
-        <v>1696</v>
+        <v>1652</v>
       </c>
       <c r="G1171" t="s">
         <v>6931</v>
@@ -60534,7 +60534,7 @@
         <v>6887</v>
       </c>
       <c r="F1172">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="G1172" t="s">
         <v>6931</v>
@@ -60560,7 +60560,7 @@
         <v>6887</v>
       </c>
       <c r="F1173">
-        <v>1163</v>
+        <v>1151</v>
       </c>
       <c r="G1173" t="s">
         <v>6931</v>
@@ -60586,7 +60586,7 @@
         <v>6887</v>
       </c>
       <c r="F1174">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="G1174" t="s">
         <v>6931</v>
@@ -60612,7 +60612,7 @@
         <v>6887</v>
       </c>
       <c r="F1175">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="G1175" t="s">
         <v>6931</v>
@@ -60638,7 +60638,7 @@
         <v>6887</v>
       </c>
       <c r="F1176">
-        <v>1117</v>
+        <v>917</v>
       </c>
       <c r="G1176" t="s">
         <v>6931</v>
@@ -60684,7 +60684,7 @@
         <v>6887</v>
       </c>
       <c r="F1178">
-        <v>979</v>
+        <v>759</v>
       </c>
       <c r="G1178" t="s">
         <v>6931</v>
@@ -60710,7 +60710,7 @@
         <v>6887</v>
       </c>
       <c r="F1179">
-        <v>1234</v>
+        <v>1038</v>
       </c>
       <c r="G1179" t="s">
         <v>6931</v>
@@ -61010,7 +61010,7 @@
         <v>6887</v>
       </c>
       <c r="F1191">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="G1191" t="s">
         <v>6931</v>
@@ -61036,7 +61036,7 @@
         <v>6887</v>
       </c>
       <c r="F1192">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="G1192" t="s">
         <v>6931</v>
@@ -61062,7 +61062,7 @@
         <v>6887</v>
       </c>
       <c r="F1193">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="G1193" t="s">
         <v>6931</v>
@@ -61088,7 +61088,7 @@
         <v>6887</v>
       </c>
       <c r="F1194">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="G1194" t="s">
         <v>6931</v>
@@ -61114,7 +61114,7 @@
         <v>6887</v>
       </c>
       <c r="F1195">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="G1195" t="s">
         <v>6931</v>
@@ -61140,7 +61140,7 @@
         <v>6887</v>
       </c>
       <c r="F1196">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="G1196" t="s">
         <v>6931</v>
@@ -61166,7 +61166,7 @@
         <v>6887</v>
       </c>
       <c r="F1197">
-        <v>395</v>
+        <v>284</v>
       </c>
       <c r="G1197" t="s">
         <v>6931</v>
@@ -61192,7 +61192,7 @@
         <v>6887</v>
       </c>
       <c r="F1198">
-        <v>315</v>
+        <v>252</v>
       </c>
       <c r="G1198" t="s">
         <v>6931</v>
@@ -61218,7 +61218,7 @@
         <v>6887</v>
       </c>
       <c r="F1199">
-        <v>353</v>
+        <v>227</v>
       </c>
       <c r="G1199" t="s">
         <v>6931</v>
@@ -61244,7 +61244,7 @@
         <v>6887</v>
       </c>
       <c r="F1200">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="G1200" t="s">
         <v>6931</v>
@@ -61408,7 +61408,7 @@
         <v>6912</v>
       </c>
       <c r="F1207">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="G1207" t="s">
         <v>6931</v>
@@ -61434,7 +61434,7 @@
         <v>6912</v>
       </c>
       <c r="F1208">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G1208" t="s">
         <v>6931</v>
@@ -61486,7 +61486,7 @@
         <v>6912</v>
       </c>
       <c r="F1210">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="G1210" t="s">
         <v>6931</v>
@@ -61538,7 +61538,7 @@
         <v>6912</v>
       </c>
       <c r="F1212">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G1212" t="s">
         <v>6931</v>
@@ -61564,7 +61564,7 @@
         <v>6912</v>
       </c>
       <c r="F1213">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G1213" t="s">
         <v>6931</v>
@@ -61720,7 +61720,7 @@
         <v>6912</v>
       </c>
       <c r="F1219">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="G1219" t="s">
         <v>6931</v>
@@ -61746,7 +61746,7 @@
         <v>6912</v>
       </c>
       <c r="F1220">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G1220" t="s">
         <v>6931</v>
@@ -61772,7 +61772,7 @@
         <v>6912</v>
       </c>
       <c r="F1221">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G1221" t="s">
         <v>6931</v>
@@ -61824,7 +61824,7 @@
         <v>6912</v>
       </c>
       <c r="F1223">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G1223" t="s">
         <v>6931</v>
@@ -61850,7 +61850,7 @@
         <v>6912</v>
       </c>
       <c r="F1224">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G1224" t="s">
         <v>6931</v>
@@ -61980,7 +61980,7 @@
         <v>6919</v>
       </c>
       <c r="F1229">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G1229" t="s">
         <v>6931</v>
@@ -62058,7 +62058,7 @@
         <v>6890</v>
       </c>
       <c r="F1232">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G1232" t="s">
         <v>6931</v>
@@ -62084,7 +62084,7 @@
         <v>6912</v>
       </c>
       <c r="F1233">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="G1233" t="s">
         <v>6931</v>
@@ -62156,7 +62156,7 @@
         <v>6912</v>
       </c>
       <c r="F1236">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="G1236" t="s">
         <v>6931</v>
@@ -62208,7 +62208,7 @@
         <v>6912</v>
       </c>
       <c r="F1238">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G1238" t="s">
         <v>6931</v>
@@ -62260,7 +62260,7 @@
         <v>6912</v>
       </c>
       <c r="F1240">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="G1240" t="s">
         <v>6931</v>
@@ -62338,7 +62338,7 @@
         <v>6912</v>
       </c>
       <c r="F1243">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G1243" t="s">
         <v>6931</v>
@@ -63022,7 +63022,7 @@
         <v>6924</v>
       </c>
       <c r="F1270">
-        <v>7657</v>
+        <v>7591</v>
       </c>
       <c r="G1270" t="s">
         <v>6931</v>
@@ -63886,7 +63886,7 @@
         <v>6902</v>
       </c>
       <c r="F1312">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G1312" t="s">
         <v>6931</v>
@@ -64050,7 +64050,7 @@
         <v>6902</v>
       </c>
       <c r="F1319">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G1319" t="s">
         <v>6931</v>
@@ -64200,7 +64200,7 @@
         <v>6898</v>
       </c>
       <c r="F1325">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="G1325" t="s">
         <v>6931</v>
@@ -64226,7 +64226,7 @@
         <v>6898</v>
       </c>
       <c r="F1326">
-        <v>1983</v>
+        <v>1971</v>
       </c>
       <c r="G1326" t="s">
         <v>6931</v>
@@ -64278,7 +64278,7 @@
         <v>6898</v>
       </c>
       <c r="F1328">
-        <v>1895</v>
+        <v>1889</v>
       </c>
       <c r="G1328" t="s">
         <v>6931</v>
@@ -64304,7 +64304,7 @@
         <v>6898</v>
       </c>
       <c r="F1329">
-        <v>1712</v>
+        <v>1700</v>
       </c>
       <c r="G1329" t="s">
         <v>6931</v>
@@ -64330,7 +64330,7 @@
         <v>6898</v>
       </c>
       <c r="F1330">
-        <v>1168</v>
+        <v>1150</v>
       </c>
       <c r="G1330" t="s">
         <v>6931</v>
@@ -64356,7 +64356,7 @@
         <v>6898</v>
       </c>
       <c r="F1331">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="G1331" t="s">
         <v>6931</v>
@@ -65538,7 +65538,7 @@
         <v>6888</v>
       </c>
       <c r="F1379">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G1379" t="s">
         <v>6931</v>
@@ -65668,7 +65668,7 @@
         <v>6890</v>
       </c>
       <c r="F1384">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G1384" t="s">
         <v>6931</v>
@@ -65720,7 +65720,7 @@
         <v>6890</v>
       </c>
       <c r="F1386">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G1386" t="s">
         <v>6931</v>
@@ -65746,7 +65746,7 @@
         <v>6890</v>
       </c>
       <c r="F1387">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G1387" t="s">
         <v>6931</v>
@@ -65772,7 +65772,7 @@
         <v>6890</v>
       </c>
       <c r="F1388">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G1388" t="s">
         <v>6931</v>
@@ -66050,7 +66050,7 @@
         <v>6920</v>
       </c>
       <c r="F1401">
-        <v>4742</v>
+        <v>4712</v>
       </c>
       <c r="G1401" t="s">
         <v>6931</v>
@@ -66644,7 +66644,7 @@
         <v>6925</v>
       </c>
       <c r="F1428">
-        <v>2541</v>
+        <v>2505</v>
       </c>
       <c r="G1428" t="s">
         <v>6931</v>
@@ -66722,7 +66722,7 @@
         <v>6925</v>
       </c>
       <c r="F1431">
-        <v>3273</v>
+        <v>3165</v>
       </c>
       <c r="G1431" t="s">
         <v>6931</v>
@@ -66748,7 +66748,7 @@
         <v>6925</v>
       </c>
       <c r="F1432">
-        <v>5959</v>
+        <v>5761</v>
       </c>
       <c r="G1432" t="s">
         <v>6931</v>
@@ -66800,7 +66800,7 @@
         <v>6925</v>
       </c>
       <c r="F1434">
-        <v>5988</v>
+        <v>5898</v>
       </c>
       <c r="G1434" t="s">
         <v>6931</v>
@@ -66826,7 +66826,7 @@
         <v>6925</v>
       </c>
       <c r="F1435">
-        <v>4734</v>
+        <v>4554</v>
       </c>
       <c r="G1435" t="s">
         <v>6931</v>
@@ -67034,7 +67034,7 @@
         <v>6898</v>
       </c>
       <c r="F1443">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="G1443" t="s">
         <v>6931</v>
@@ -67060,7 +67060,7 @@
         <v>6898</v>
       </c>
       <c r="F1444">
-        <v>4696</v>
+        <v>4666</v>
       </c>
       <c r="G1444" t="s">
         <v>6931</v>
@@ -67086,7 +67086,7 @@
         <v>6898</v>
       </c>
       <c r="F1445">
-        <v>2509</v>
+        <v>2489</v>
       </c>
       <c r="G1445" t="s">
         <v>6931</v>
@@ -67320,7 +67320,7 @@
         <v>6926</v>
       </c>
       <c r="F1454">
-        <v>1387</v>
+        <v>1379</v>
       </c>
       <c r="G1454" t="s">
         <v>6931</v>
@@ -67398,7 +67398,7 @@
         <v>6926</v>
       </c>
       <c r="F1457">
-        <v>1927</v>
+        <v>1895</v>
       </c>
       <c r="G1457" t="s">
         <v>6931</v>
@@ -67450,7 +67450,7 @@
         <v>6926</v>
       </c>
       <c r="F1459">
-        <v>1633</v>
+        <v>1617</v>
       </c>
       <c r="G1459" t="s">
         <v>6931</v>
@@ -67476,7 +67476,7 @@
         <v>6926</v>
       </c>
       <c r="F1460">
-        <v>2049</v>
+        <v>2041</v>
       </c>
       <c r="G1460" t="s">
         <v>6931</v>
@@ -67918,7 +67918,7 @@
         <v>6898</v>
       </c>
       <c r="F1477">
-        <v>3171</v>
+        <v>3131</v>
       </c>
       <c r="G1477" t="s">
         <v>6931</v>
@@ -68674,7 +68674,7 @@
         <v>6887</v>
       </c>
       <c r="F1507">
-        <v>2925</v>
+        <v>2913</v>
       </c>
       <c r="G1507" t="s">
         <v>6931</v>
@@ -68726,7 +68726,7 @@
         <v>6887</v>
       </c>
       <c r="F1509">
-        <v>1692</v>
+        <v>1680</v>
       </c>
       <c r="G1509" t="s">
         <v>6931</v>
@@ -68804,7 +68804,7 @@
         <v>6887</v>
       </c>
       <c r="F1512">
-        <v>1301</v>
+        <v>1277</v>
       </c>
       <c r="G1512" t="s">
         <v>6931</v>
@@ -68856,7 +68856,7 @@
         <v>6887</v>
       </c>
       <c r="F1514">
-        <v>2160</v>
+        <v>2136</v>
       </c>
       <c r="G1514" t="s">
         <v>6931</v>
@@ -69194,7 +69194,7 @@
         <v>6887</v>
       </c>
       <c r="F1527">
-        <v>1879</v>
+        <v>1867</v>
       </c>
       <c r="G1527" t="s">
         <v>6931</v>
@@ -69350,7 +69350,7 @@
         <v>6926</v>
       </c>
       <c r="F1533">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="G1533" t="s">
         <v>6931</v>
@@ -69428,7 +69428,7 @@
         <v>6926</v>
       </c>
       <c r="F1536">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="G1536" t="s">
         <v>6931</v>
@@ -69506,7 +69506,7 @@
         <v>6926</v>
       </c>
       <c r="F1539">
-        <v>3622</v>
+        <v>3614</v>
       </c>
       <c r="G1539" t="s">
         <v>6931</v>
@@ -69532,7 +69532,7 @@
         <v>6926</v>
       </c>
       <c r="F1540">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="G1540" t="s">
         <v>6931</v>
@@ -69558,7 +69558,7 @@
         <v>6926</v>
       </c>
       <c r="F1541">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="G1541" t="s">
         <v>6931</v>
@@ -69584,7 +69584,7 @@
         <v>6926</v>
       </c>
       <c r="F1542">
-        <v>2070</v>
+        <v>2062</v>
       </c>
       <c r="G1542" t="s">
         <v>6931</v>
@@ -69818,7 +69818,7 @@
         <v>6887</v>
       </c>
       <c r="F1551">
-        <v>1983</v>
+        <v>1971</v>
       </c>
       <c r="G1551" t="s">
         <v>6931</v>
@@ -70026,7 +70026,7 @@
         <v>6887</v>
       </c>
       <c r="F1559">
-        <v>2433</v>
+        <v>2421</v>
       </c>
       <c r="G1559" t="s">
         <v>6931</v>
@@ -70052,7 +70052,7 @@
         <v>6887</v>
       </c>
       <c r="F1560">
-        <v>4264</v>
+        <v>4252</v>
       </c>
       <c r="G1560" t="s">
         <v>6931</v>
@@ -70078,7 +70078,7 @@
         <v>6887</v>
       </c>
       <c r="F1561">
-        <v>3959</v>
+        <v>3947</v>
       </c>
       <c r="G1561" t="s">
         <v>6931</v>
@@ -70312,7 +70312,7 @@
         <v>6887</v>
       </c>
       <c r="F1570">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="G1570" t="s">
         <v>6931</v>
@@ -70494,7 +70494,7 @@
         <v>6923</v>
       </c>
       <c r="F1577">
-        <v>9417</v>
+        <v>9391</v>
       </c>
       <c r="G1577" t="s">
         <v>6931</v>
@@ -70540,7 +70540,7 @@
         <v>6906</v>
       </c>
       <c r="F1579">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="G1579" t="s">
         <v>6931</v>
@@ -70748,7 +70748,7 @@
         <v>6923</v>
       </c>
       <c r="F1587">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G1587" t="s">
         <v>6931</v>
@@ -70774,7 +70774,7 @@
         <v>6910</v>
       </c>
       <c r="F1588">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="G1588" t="s">
         <v>6931</v>
@@ -70800,7 +70800,7 @@
         <v>6922</v>
       </c>
       <c r="F1589">
-        <v>2916</v>
+        <v>2904</v>
       </c>
       <c r="G1589" t="s">
         <v>6931</v>
@@ -70826,7 +70826,7 @@
         <v>6922</v>
       </c>
       <c r="F1590">
-        <v>2101</v>
+        <v>2085</v>
       </c>
       <c r="G1590" t="s">
         <v>6931</v>
@@ -70852,7 +70852,7 @@
         <v>6922</v>
       </c>
       <c r="F1591">
-        <v>2031</v>
+        <v>2023</v>
       </c>
       <c r="G1591" t="s">
         <v>6931</v>
@@ -70956,7 +70956,7 @@
         <v>6922</v>
       </c>
       <c r="F1595">
-        <v>2107</v>
+        <v>2100</v>
       </c>
       <c r="G1595" t="s">
         <v>6931</v>
@@ -71164,7 +71164,7 @@
         <v>6907</v>
       </c>
       <c r="F1603">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="G1603" t="s">
         <v>6931</v>
@@ -71432,7 +71432,7 @@
         <v>6906</v>
       </c>
       <c r="F1614">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="G1614" t="s">
         <v>6931</v>
@@ -71562,7 +71562,7 @@
         <v>6906</v>
       </c>
       <c r="F1619">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="G1619" t="s">
         <v>6931</v>
@@ -71588,7 +71588,7 @@
         <v>6906</v>
       </c>
       <c r="F1620">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="G1620" t="s">
         <v>6931</v>
@@ -71614,7 +71614,7 @@
         <v>6906</v>
       </c>
       <c r="F1621">
-        <v>10159</v>
+        <v>10117</v>
       </c>
       <c r="G1621" t="s">
         <v>6931</v>
@@ -71666,7 +71666,7 @@
         <v>6906</v>
       </c>
       <c r="F1623">
-        <v>1852</v>
+        <v>1822</v>
       </c>
       <c r="G1623" t="s">
         <v>6931</v>
@@ -71822,7 +71822,7 @@
         <v>6907</v>
       </c>
       <c r="F1629">
-        <v>4500</v>
+        <v>4488</v>
       </c>
       <c r="G1629" t="s">
         <v>6931</v>
@@ -72024,7 +72024,7 @@
         <v>6922</v>
       </c>
       <c r="F1637">
-        <v>23862</v>
+        <v>23634</v>
       </c>
       <c r="G1637" t="s">
         <v>6931</v>
@@ -72050,7 +72050,7 @@
         <v>6922</v>
       </c>
       <c r="F1638">
-        <v>18186</v>
+        <v>18125</v>
       </c>
       <c r="G1638" t="s">
         <v>6931</v>
@@ -72240,7 +72240,7 @@
         <v>6924</v>
       </c>
       <c r="F1646">
-        <v>9398</v>
+        <v>9206</v>
       </c>
       <c r="G1646" t="s">
         <v>6931</v>
@@ -72448,7 +72448,7 @@
         <v>6924</v>
       </c>
       <c r="F1654">
-        <v>40622</v>
+        <v>40268</v>
       </c>
       <c r="G1654" t="s">
         <v>6931</v>
@@ -72474,7 +72474,7 @@
         <v>6924</v>
       </c>
       <c r="F1655">
-        <v>2560</v>
+        <v>5488</v>
       </c>
       <c r="G1655" t="s">
         <v>6931</v>
@@ -72552,7 +72552,7 @@
         <v>6924</v>
       </c>
       <c r="F1658">
-        <v>2809</v>
+        <v>2745</v>
       </c>
       <c r="G1658" t="s">
         <v>6931</v>
@@ -72604,7 +72604,7 @@
         <v>6924</v>
       </c>
       <c r="F1660">
-        <v>2575</v>
+        <v>2533</v>
       </c>
       <c r="G1660" t="s">
         <v>6931</v>
@@ -72630,7 +72630,7 @@
         <v>6924</v>
       </c>
       <c r="F1661">
-        <v>3445</v>
+        <v>3423</v>
       </c>
       <c r="G1661" t="s">
         <v>6931</v>
@@ -72656,7 +72656,7 @@
         <v>6924</v>
       </c>
       <c r="F1662">
-        <v>2278</v>
+        <v>2266</v>
       </c>
       <c r="G1662" t="s">
         <v>6931</v>
@@ -73306,7 +73306,7 @@
         <v>6900</v>
       </c>
       <c r="F1687">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="G1687" t="s">
         <v>6931</v>
@@ -73748,7 +73748,7 @@
         <v>6900</v>
       </c>
       <c r="F1704">
-        <v>2697</v>
+        <v>2691</v>
       </c>
       <c r="G1704" t="s">
         <v>6931</v>
@@ -73826,7 +73826,7 @@
         <v>6900</v>
       </c>
       <c r="F1707">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="G1707" t="s">
         <v>6931</v>
@@ -74232,7 +74232,7 @@
         <v>6900</v>
       </c>
       <c r="F1724">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="G1724" t="s">
         <v>6931</v>
@@ -74336,7 +74336,7 @@
         <v>6900</v>
       </c>
       <c r="F1728">
-        <v>2681</v>
+        <v>2675</v>
       </c>
       <c r="G1728" t="s">
         <v>6931</v>
@@ -74362,7 +74362,7 @@
         <v>6900</v>
       </c>
       <c r="F1729">
-        <v>5420</v>
+        <v>5384</v>
       </c>
       <c r="G1729" t="s">
         <v>6931</v>
@@ -74388,7 +74388,7 @@
         <v>6900</v>
       </c>
       <c r="F1730">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="G1730" t="s">
         <v>6931</v>
@@ -74414,7 +74414,7 @@
         <v>6900</v>
       </c>
       <c r="F1731">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="G1731" t="s">
         <v>6931</v>
@@ -74544,7 +74544,7 @@
         <v>6900</v>
       </c>
       <c r="F1736">
-        <v>2878</v>
+        <v>2872</v>
       </c>
       <c r="G1736" t="s">
         <v>6931</v>
@@ -74570,7 +74570,7 @@
         <v>6900</v>
       </c>
       <c r="F1737">
-        <v>3602</v>
+        <v>3590</v>
       </c>
       <c r="G1737" t="s">
         <v>6931</v>
@@ -74596,7 +74596,7 @@
         <v>6900</v>
       </c>
       <c r="F1738">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="G1738" t="s">
         <v>6931</v>
@@ -74700,7 +74700,7 @@
         <v>6921</v>
       </c>
       <c r="F1742">
-        <v>2661</v>
+        <v>2649</v>
       </c>
       <c r="G1742" t="s">
         <v>6931</v>
@@ -77492,7 +77492,7 @@
         <v>6913</v>
       </c>
       <c r="F1851">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="G1851" t="s">
         <v>6931</v>
@@ -78632,7 +78632,7 @@
         <v>6890</v>
       </c>
       <c r="F1896">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G1896" t="s">
         <v>6931</v>
@@ -78684,7 +78684,7 @@
         <v>6891</v>
       </c>
       <c r="F1898">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="G1898" t="s">
         <v>6931</v>
@@ -78730,7 +78730,7 @@
         <v>6899</v>
       </c>
       <c r="F1900">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="G1900" t="s">
         <v>6931</v>
@@ -78782,7 +78782,7 @@
         <v>6899</v>
       </c>
       <c r="F1902">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="G1902" t="s">
         <v>6931</v>
@@ -78808,7 +78808,7 @@
         <v>6899</v>
       </c>
       <c r="F1903">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="G1903" t="s">
         <v>6931</v>
@@ -78834,7 +78834,7 @@
         <v>6899</v>
       </c>
       <c r="F1904">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="G1904" t="s">
         <v>6931</v>
@@ -78860,7 +78860,7 @@
         <v>6899</v>
       </c>
       <c r="F1905">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G1905" t="s">
         <v>6931</v>
@@ -78886,7 +78886,7 @@
         <v>6899</v>
       </c>
       <c r="F1906">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G1906" t="s">
         <v>6931</v>
@@ -78912,7 +78912,7 @@
         <v>6899</v>
       </c>
       <c r="F1907">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="G1907" t="s">
         <v>6931</v>
@@ -78964,7 +78964,7 @@
         <v>6891</v>
       </c>
       <c r="F1909">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="G1909" t="s">
         <v>6931</v>
@@ -78990,7 +78990,7 @@
         <v>6891</v>
       </c>
       <c r="F1910">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="G1910" t="s">
         <v>6931</v>
@@ -79016,7 +79016,7 @@
         <v>6891</v>
       </c>
       <c r="F1911">
-        <v>1988</v>
+        <v>1976</v>
       </c>
       <c r="G1911" t="s">
         <v>6931</v>
@@ -79042,7 +79042,7 @@
         <v>6891</v>
       </c>
       <c r="F1912">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="G1912" t="s">
         <v>6931</v>
@@ -79068,7 +79068,7 @@
         <v>6891</v>
       </c>
       <c r="F1913">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="G1913" t="s">
         <v>6931</v>
@@ -79120,7 +79120,7 @@
         <v>6891</v>
       </c>
       <c r="F1915">
-        <v>1558</v>
+        <v>1546</v>
       </c>
       <c r="G1915" t="s">
         <v>6931</v>
@@ -79166,7 +79166,7 @@
         <v>6891</v>
       </c>
       <c r="F1917">
-        <v>1664</v>
+        <v>1646</v>
       </c>
       <c r="G1917" t="s">
         <v>6931</v>
@@ -79430,7 +79430,7 @@
         <v>6890</v>
       </c>
       <c r="F1929">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G1929" t="s">
         <v>6931</v>
@@ -79560,7 +79560,7 @@
         <v>6890</v>
       </c>
       <c r="F1934">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G1934" t="s">
         <v>6931</v>
@@ -80052,7 +80052,7 @@
         <v>6890</v>
       </c>
       <c r="F1955">
-        <v>1161</v>
+        <v>1111</v>
       </c>
       <c r="G1955" t="s">
         <v>6930</v>
@@ -80812,7 +80812,7 @@
         <v>6888</v>
       </c>
       <c r="F1990">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G1990" t="s">
         <v>6931</v>
@@ -80864,7 +80864,7 @@
         <v>6888</v>
       </c>
       <c r="F1992">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G1992" t="s">
         <v>6931</v>
@@ -80968,7 +80968,7 @@
         <v>6888</v>
       </c>
       <c r="F1996">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G1996" t="s">
         <v>6931</v>
@@ -80994,7 +80994,7 @@
         <v>6888</v>
       </c>
       <c r="F1997">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G1997" t="s">
         <v>6931</v>
@@ -81020,7 +81020,7 @@
         <v>6888</v>
       </c>
       <c r="F1998">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G1998" t="s">
         <v>6931</v>
@@ -81046,7 +81046,7 @@
         <v>6888</v>
       </c>
       <c r="F1999">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G1999" t="s">
         <v>6931</v>
@@ -81538,7 +81538,7 @@
         <v>6890</v>
       </c>
       <c r="F2020">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="G2020" t="s">
         <v>6931</v>
@@ -81720,7 +81720,7 @@
         <v>6890</v>
       </c>
       <c r="F2027">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="G2027" t="s">
         <v>6931</v>
@@ -81824,7 +81824,7 @@
         <v>6890</v>
       </c>
       <c r="F2031">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G2031" t="s">
         <v>6931</v>
@@ -82556,7 +82556,7 @@
         <v>6890</v>
       </c>
       <c r="F2061">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G2061" t="s">
         <v>6931</v>
@@ -82582,7 +82582,7 @@
         <v>6890</v>
       </c>
       <c r="F2062">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G2062" t="s">
         <v>6931</v>
@@ -84414,7 +84414,7 @@
         <v>6908</v>
       </c>
       <c r="F2135">
-        <v>2238</v>
+        <v>2230</v>
       </c>
       <c r="G2135" t="s">
         <v>6931</v>
@@ -84440,7 +84440,7 @@
         <v>6908</v>
       </c>
       <c r="F2136">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G2136" t="s">
         <v>6931</v>
@@ -84824,7 +84824,7 @@
         <v>6908</v>
       </c>
       <c r="F2154">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="G2154" t="s">
         <v>6931</v>
@@ -85262,7 +85262,7 @@
         <v>6908</v>
       </c>
       <c r="F2172">
-        <v>2078</v>
+        <v>2074</v>
       </c>
       <c r="G2172" t="s">
         <v>6931</v>
@@ -85288,7 +85288,7 @@
         <v>6908</v>
       </c>
       <c r="F2173">
-        <v>3157</v>
+        <v>3153</v>
       </c>
       <c r="G2173" t="s">
         <v>6931</v>
@@ -85340,7 +85340,7 @@
         <v>6908</v>
       </c>
       <c r="F2175">
-        <v>16308</v>
+        <v>16158</v>
       </c>
       <c r="G2175" t="s">
         <v>6931</v>
@@ -85392,7 +85392,7 @@
         <v>6908</v>
       </c>
       <c r="F2177">
-        <v>1731</v>
+        <v>1721</v>
       </c>
       <c r="G2177" t="s">
         <v>6931</v>
@@ -85542,7 +85542,7 @@
         <v>6908</v>
       </c>
       <c r="F2183">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="G2183" t="s">
         <v>6931</v>
@@ -85778,7 +85778,7 @@
         <v>6908</v>
       </c>
       <c r="F2193">
-        <v>6043</v>
+        <v>6031</v>
       </c>
       <c r="G2193" t="s">
         <v>6931</v>
@@ -85856,7 +85856,7 @@
         <v>6908</v>
       </c>
       <c r="F2196">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G2196" t="s">
         <v>6931</v>
@@ -86466,7 +86466,7 @@
         <v>6899</v>
       </c>
       <c r="F2222">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="G2222" t="s">
         <v>6930</v>
@@ -86512,7 +86512,7 @@
         <v>6899</v>
       </c>
       <c r="F2224">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="G2224" t="s">
         <v>6931</v>
@@ -86538,7 +86538,7 @@
         <v>6899</v>
       </c>
       <c r="F2225">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G2225" t="s">
         <v>6931</v>
@@ -86590,7 +86590,7 @@
         <v>6899</v>
       </c>
       <c r="F2227">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G2227" t="s">
         <v>6931</v>
@@ -86748,7 +86748,7 @@
         <v>6888</v>
       </c>
       <c r="F2234">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2234" t="s">
         <v>6931</v>
@@ -86938,7 +86938,7 @@
         <v>6892</v>
       </c>
       <c r="F2242">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G2242" t="s">
         <v>6931</v>
@@ -87452,7 +87452,7 @@
         <v>6890</v>
       </c>
       <c r="F2262">
-        <v>2152</v>
+        <v>2052</v>
       </c>
       <c r="G2262" t="s">
         <v>6930</v>
@@ -87630,7 +87630,7 @@
         <v>6888</v>
       </c>
       <c r="F2270">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="G2270" t="s">
         <v>6931</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -32160,7 +32160,7 @@
         <v>6943</v>
       </c>
       <c r="F2">
-        <v>1154</v>
+        <v>1109</v>
       </c>
       <c r="G2" t="s">
         <v>6987</v>
@@ -32186,7 +32186,7 @@
         <v>6944</v>
       </c>
       <c r="F3">
-        <v>992</v>
+        <v>952</v>
       </c>
       <c r="G3" t="s">
         <v>6987</v>
@@ -32212,7 +32212,7 @@
         <v>6944</v>
       </c>
       <c r="F4">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="G4" t="s">
         <v>6988</v>
@@ -32232,7 +32232,7 @@
         <v>6945</v>
       </c>
       <c r="F5">
-        <v>8153</v>
+        <v>7877</v>
       </c>
       <c r="G5" t="s">
         <v>6987</v>
@@ -32258,7 +32258,7 @@
         <v>6946</v>
       </c>
       <c r="F6">
-        <v>10548</v>
+        <v>10236</v>
       </c>
       <c r="G6" t="s">
         <v>6987</v>
@@ -32284,7 +32284,7 @@
         <v>6947</v>
       </c>
       <c r="F7">
-        <v>1612</v>
+        <v>1558</v>
       </c>
       <c r="G7" t="s">
         <v>6987</v>
@@ -32310,7 +32310,7 @@
         <v>6948</v>
       </c>
       <c r="F8">
-        <v>1482</v>
+        <v>1440</v>
       </c>
       <c r="G8" t="s">
         <v>6987</v>
@@ -32336,7 +32336,7 @@
         <v>6943</v>
       </c>
       <c r="F9">
-        <v>976</v>
+        <v>942</v>
       </c>
       <c r="G9" t="s">
         <v>6987</v>
@@ -32362,7 +32362,7 @@
         <v>6944</v>
       </c>
       <c r="F10">
-        <v>1174</v>
+        <v>1140</v>
       </c>
       <c r="G10" t="s">
         <v>6987</v>
@@ -32388,7 +32388,7 @@
         <v>6944</v>
       </c>
       <c r="F11">
-        <v>968</v>
+        <v>938</v>
       </c>
       <c r="G11" t="s">
         <v>6987</v>
@@ -32414,7 +32414,7 @@
         <v>6944</v>
       </c>
       <c r="F12">
-        <v>1216</v>
+        <v>1169</v>
       </c>
       <c r="G12" t="s">
         <v>6987</v>
@@ -32440,7 +32440,7 @@
         <v>6944</v>
       </c>
       <c r="F13">
-        <v>1020</v>
+        <v>978</v>
       </c>
       <c r="G13" t="s">
         <v>6987</v>
@@ -32466,7 +32466,7 @@
         <v>6944</v>
       </c>
       <c r="F14">
-        <v>1158</v>
+        <v>1104</v>
       </c>
       <c r="G14" t="s">
         <v>6987</v>
@@ -32492,7 +32492,7 @@
         <v>6944</v>
       </c>
       <c r="F15">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="G15" t="s">
         <v>6988</v>
@@ -32512,7 +32512,7 @@
         <v>6944</v>
       </c>
       <c r="F16">
-        <v>958</v>
+        <v>916</v>
       </c>
       <c r="G16" t="s">
         <v>6987</v>
@@ -32538,7 +32538,7 @@
         <v>6944</v>
       </c>
       <c r="F17">
-        <v>970</v>
+        <v>932</v>
       </c>
       <c r="G17" t="s">
         <v>6987</v>
@@ -32564,7 +32564,7 @@
         <v>6944</v>
       </c>
       <c r="F18">
-        <v>964</v>
+        <v>930</v>
       </c>
       <c r="G18" t="s">
         <v>6987</v>
@@ -32590,7 +32590,7 @@
         <v>6944</v>
       </c>
       <c r="F19">
-        <v>982</v>
+        <v>946</v>
       </c>
       <c r="G19" t="s">
         <v>6987</v>
@@ -32616,7 +32616,7 @@
         <v>6944</v>
       </c>
       <c r="F20">
-        <v>962</v>
+        <v>928</v>
       </c>
       <c r="G20" t="s">
         <v>6987</v>
@@ -32642,7 +32642,7 @@
         <v>6944</v>
       </c>
       <c r="F21">
-        <v>1226</v>
+        <v>1180</v>
       </c>
       <c r="G21" t="s">
         <v>6987</v>
@@ -32668,7 +32668,7 @@
         <v>6943</v>
       </c>
       <c r="F22">
-        <v>1463</v>
+        <v>1417</v>
       </c>
       <c r="G22" t="s">
         <v>6987</v>
@@ -32694,7 +32694,7 @@
         <v>6949</v>
       </c>
       <c r="F23">
-        <v>1957</v>
+        <v>1945</v>
       </c>
       <c r="G23" t="s">
         <v>6987</v>
@@ -32720,7 +32720,7 @@
         <v>6949</v>
       </c>
       <c r="F24">
-        <v>24637</v>
+        <v>24204</v>
       </c>
       <c r="G24" t="s">
         <v>6987</v>
@@ -32746,7 +32746,7 @@
         <v>6949</v>
       </c>
       <c r="F25">
-        <v>24612</v>
+        <v>24180</v>
       </c>
       <c r="G25" t="s">
         <v>6987</v>
@@ -32772,7 +32772,7 @@
         <v>6949</v>
       </c>
       <c r="F26">
-        <v>2437</v>
+        <v>2425</v>
       </c>
       <c r="G26" t="s">
         <v>6987</v>
@@ -32798,7 +32798,7 @@
         <v>6949</v>
       </c>
       <c r="F27">
-        <v>2437</v>
+        <v>2425</v>
       </c>
       <c r="G27" t="s">
         <v>6987</v>
@@ -32824,7 +32824,7 @@
         <v>6949</v>
       </c>
       <c r="F28">
-        <v>2198</v>
+        <v>2162</v>
       </c>
       <c r="G28" t="s">
         <v>6987</v>
@@ -32850,7 +32850,7 @@
         <v>6949</v>
       </c>
       <c r="F29">
-        <v>2437</v>
+        <v>2401</v>
       </c>
       <c r="G29" t="s">
         <v>6987</v>
@@ -32876,7 +32876,7 @@
         <v>6949</v>
       </c>
       <c r="F30">
-        <v>2244</v>
+        <v>2232</v>
       </c>
       <c r="G30" t="s">
         <v>6987</v>
@@ -32902,7 +32902,7 @@
         <v>6949</v>
       </c>
       <c r="F31">
-        <v>2459</v>
+        <v>2447</v>
       </c>
       <c r="G31" t="s">
         <v>6987</v>
@@ -32928,7 +32928,7 @@
         <v>6949</v>
       </c>
       <c r="F32">
-        <v>2442</v>
+        <v>2430</v>
       </c>
       <c r="G32" t="s">
         <v>6987</v>
@@ -32954,7 +32954,7 @@
         <v>6949</v>
       </c>
       <c r="F33">
-        <v>2449</v>
+        <v>2413</v>
       </c>
       <c r="G33" t="s">
         <v>6987</v>
@@ -32980,7 +32980,7 @@
         <v>6949</v>
       </c>
       <c r="F34">
-        <v>2460</v>
+        <v>2448</v>
       </c>
       <c r="G34" t="s">
         <v>6987</v>
@@ -33006,7 +33006,7 @@
         <v>6949</v>
       </c>
       <c r="F35">
-        <v>2489</v>
+        <v>2477</v>
       </c>
       <c r="G35" t="s">
         <v>6987</v>
@@ -33032,7 +33032,7 @@
         <v>6949</v>
       </c>
       <c r="F36">
-        <v>2437</v>
+        <v>2425</v>
       </c>
       <c r="G36" t="s">
         <v>6987</v>
@@ -33058,7 +33058,7 @@
         <v>6950</v>
       </c>
       <c r="F37">
-        <v>2049</v>
+        <v>2043</v>
       </c>
       <c r="G37" t="s">
         <v>6987</v>
@@ -33084,7 +33084,7 @@
         <v>6950</v>
       </c>
       <c r="F38">
-        <v>1323</v>
+        <v>1311</v>
       </c>
       <c r="G38" t="s">
         <v>6988</v>
@@ -33104,7 +33104,7 @@
         <v>6950</v>
       </c>
       <c r="F39">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="G39" t="s">
         <v>6988</v>
@@ -33124,7 +33124,7 @@
         <v>6950</v>
       </c>
       <c r="F40">
-        <v>1749</v>
+        <v>1746</v>
       </c>
       <c r="G40" t="s">
         <v>6987</v>
@@ -33150,7 +33150,7 @@
         <v>6950</v>
       </c>
       <c r="F41">
-        <v>2028</v>
+        <v>2019</v>
       </c>
       <c r="G41" t="s">
         <v>6987</v>
@@ -33176,7 +33176,7 @@
         <v>6950</v>
       </c>
       <c r="F42">
-        <v>843</v>
+        <v>822</v>
       </c>
       <c r="G42" t="s">
         <v>6987</v>
@@ -33202,7 +33202,7 @@
         <v>6950</v>
       </c>
       <c r="F43">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="G43" t="s">
         <v>6987</v>
@@ -33228,7 +33228,7 @@
         <v>6950</v>
       </c>
       <c r="F44">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="G44" t="s">
         <v>6987</v>
@@ -33306,7 +33306,7 @@
         <v>6950</v>
       </c>
       <c r="F47">
-        <v>1893</v>
+        <v>1875</v>
       </c>
       <c r="G47" t="s">
         <v>6987</v>
@@ -33332,7 +33332,7 @@
         <v>6950</v>
       </c>
       <c r="F48">
-        <v>1644</v>
+        <v>1638</v>
       </c>
       <c r="G48" t="s">
         <v>6987</v>
@@ -33358,7 +33358,7 @@
         <v>6950</v>
       </c>
       <c r="F49">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G49" t="s">
         <v>6987</v>
@@ -33384,7 +33384,7 @@
         <v>6950</v>
       </c>
       <c r="F50">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G50" t="s">
         <v>6987</v>
@@ -33410,7 +33410,7 @@
         <v>6950</v>
       </c>
       <c r="F51">
-        <v>2181</v>
+        <v>2169</v>
       </c>
       <c r="G51" t="s">
         <v>6987</v>
@@ -33436,7 +33436,7 @@
         <v>6950</v>
       </c>
       <c r="F52">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="G52" t="s">
         <v>6987</v>
@@ -33462,7 +33462,7 @@
         <v>6950</v>
       </c>
       <c r="F53">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="G53" t="s">
         <v>6987</v>
@@ -33488,7 +33488,7 @@
         <v>6950</v>
       </c>
       <c r="F54">
-        <v>1817</v>
+        <v>1813</v>
       </c>
       <c r="G54" t="s">
         <v>6987</v>
@@ -33514,7 +33514,7 @@
         <v>6950</v>
       </c>
       <c r="F55">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="G55" t="s">
         <v>6987</v>
@@ -33540,7 +33540,7 @@
         <v>6950</v>
       </c>
       <c r="F56">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G56" t="s">
         <v>6987</v>
@@ -33566,7 +33566,7 @@
         <v>6950</v>
       </c>
       <c r="F57">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G57" t="s">
         <v>6987</v>
@@ -33592,7 +33592,7 @@
         <v>6950</v>
       </c>
       <c r="F58">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="G58" t="s">
         <v>6987</v>
@@ -33618,7 +33618,7 @@
         <v>6950</v>
       </c>
       <c r="F59">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="G59" t="s">
         <v>6987</v>
@@ -33644,7 +33644,7 @@
         <v>6950</v>
       </c>
       <c r="F60">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="G60" t="s">
         <v>6987</v>
@@ -33670,7 +33670,7 @@
         <v>6950</v>
       </c>
       <c r="F61">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G61" t="s">
         <v>6987</v>
@@ -33696,7 +33696,7 @@
         <v>6950</v>
       </c>
       <c r="F62">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G62" t="s">
         <v>6987</v>
@@ -33722,7 +33722,7 @@
         <v>6950</v>
       </c>
       <c r="F63">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G63" t="s">
         <v>6987</v>
@@ -33748,7 +33748,7 @@
         <v>6950</v>
       </c>
       <c r="F64">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G64" t="s">
         <v>6987</v>
@@ -33774,7 +33774,7 @@
         <v>6950</v>
       </c>
       <c r="F65">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G65" t="s">
         <v>6987</v>
@@ -33800,7 +33800,7 @@
         <v>6950</v>
       </c>
       <c r="F66">
-        <v>3295</v>
+        <v>3286</v>
       </c>
       <c r="G66" t="s">
         <v>6987</v>
@@ -33878,7 +33878,7 @@
         <v>6950</v>
       </c>
       <c r="F69">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="G69" t="s">
         <v>6987</v>
@@ -33904,7 +33904,7 @@
         <v>6950</v>
       </c>
       <c r="F70">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="G70" t="s">
         <v>6987</v>
@@ -33930,7 +33930,7 @@
         <v>6950</v>
       </c>
       <c r="F71">
-        <v>2199</v>
+        <v>2187</v>
       </c>
       <c r="G71" t="s">
         <v>6987</v>
@@ -33956,7 +33956,7 @@
         <v>6950</v>
       </c>
       <c r="F72">
-        <v>3321</v>
+        <v>3315</v>
       </c>
       <c r="G72" t="s">
         <v>6987</v>
@@ -33982,7 +33982,7 @@
         <v>6950</v>
       </c>
       <c r="F73">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="G73" t="s">
         <v>6987</v>
@@ -34008,7 +34008,7 @@
         <v>6950</v>
       </c>
       <c r="F74">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="G74" t="s">
         <v>6987</v>
@@ -34034,7 +34034,7 @@
         <v>6950</v>
       </c>
       <c r="F75">
-        <v>1397</v>
+        <v>1381</v>
       </c>
       <c r="G75" t="s">
         <v>6987</v>
@@ -34060,7 +34060,7 @@
         <v>6950</v>
       </c>
       <c r="F76">
-        <v>927</v>
+        <v>906</v>
       </c>
       <c r="G76" t="s">
         <v>6987</v>
@@ -34086,7 +34086,7 @@
         <v>6950</v>
       </c>
       <c r="F77">
-        <v>1116</v>
+        <v>1092</v>
       </c>
       <c r="G77" t="s">
         <v>6987</v>
@@ -34112,7 +34112,7 @@
         <v>6950</v>
       </c>
       <c r="F78">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G78" t="s">
         <v>6987</v>
@@ -34138,7 +34138,7 @@
         <v>6950</v>
       </c>
       <c r="F79">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="G79" t="s">
         <v>6987</v>
@@ -34164,7 +34164,7 @@
         <v>6950</v>
       </c>
       <c r="F80">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="G80" t="s">
         <v>6987</v>
@@ -34190,7 +34190,7 @@
         <v>6950</v>
       </c>
       <c r="F81">
-        <v>1780</v>
+        <v>1772</v>
       </c>
       <c r="G81" t="s">
         <v>6987</v>
@@ -34216,7 +34216,7 @@
         <v>6950</v>
       </c>
       <c r="F82">
-        <v>2577</v>
+        <v>2561</v>
       </c>
       <c r="G82" t="s">
         <v>6987</v>
@@ -34242,7 +34242,7 @@
         <v>6950</v>
       </c>
       <c r="F83">
-        <v>1604</v>
+        <v>1592</v>
       </c>
       <c r="G83" t="s">
         <v>6987</v>
@@ -34268,7 +34268,7 @@
         <v>6944</v>
       </c>
       <c r="F84">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="G84" t="s">
         <v>6987</v>
@@ -34294,7 +34294,7 @@
         <v>6951</v>
       </c>
       <c r="F85">
-        <v>1644</v>
+        <v>1584</v>
       </c>
       <c r="G85" t="s">
         <v>6987</v>
@@ -34320,7 +34320,7 @@
         <v>6951</v>
       </c>
       <c r="F86">
-        <v>1691</v>
+        <v>1643</v>
       </c>
       <c r="G86" t="s">
         <v>6987</v>
@@ -34346,7 +34346,7 @@
         <v>6951</v>
       </c>
       <c r="F87">
-        <v>1667</v>
+        <v>1619</v>
       </c>
       <c r="G87" t="s">
         <v>6987</v>
@@ -34372,7 +34372,7 @@
         <v>6951</v>
       </c>
       <c r="F88">
-        <v>1644</v>
+        <v>1584</v>
       </c>
       <c r="G88" t="s">
         <v>6987</v>
@@ -34398,7 +34398,7 @@
         <v>6951</v>
       </c>
       <c r="F89">
-        <v>1644</v>
+        <v>1596</v>
       </c>
       <c r="G89" t="s">
         <v>6987</v>
@@ -34424,7 +34424,7 @@
         <v>6944</v>
       </c>
       <c r="F90">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="G90" t="s">
         <v>6987</v>
@@ -34450,7 +34450,7 @@
         <v>6951</v>
       </c>
       <c r="F91">
-        <v>1609</v>
+        <v>1561</v>
       </c>
       <c r="G91" t="s">
         <v>6987</v>
@@ -34476,7 +34476,7 @@
         <v>6944</v>
       </c>
       <c r="F92">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="G92" t="s">
         <v>6987</v>
@@ -34502,7 +34502,7 @@
         <v>6944</v>
       </c>
       <c r="F93">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="G93" t="s">
         <v>6987</v>
@@ -34528,7 +34528,7 @@
         <v>6944</v>
       </c>
       <c r="F94">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G94" t="s">
         <v>6987</v>
@@ -34554,7 +34554,7 @@
         <v>6943</v>
       </c>
       <c r="F95">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="G95" t="s">
         <v>6987</v>
@@ -34580,7 +34580,7 @@
         <v>6943</v>
       </c>
       <c r="F96">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="G96" t="s">
         <v>6987</v>
@@ -34606,7 +34606,7 @@
         <v>6943</v>
       </c>
       <c r="F97">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G97" t="s">
         <v>6987</v>
@@ -34632,7 +34632,7 @@
         <v>6943</v>
       </c>
       <c r="F98">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="G98" t="s">
         <v>6987</v>
@@ -34658,7 +34658,7 @@
         <v>6943</v>
       </c>
       <c r="F99">
-        <v>951</v>
+        <v>941</v>
       </c>
       <c r="G99" t="s">
         <v>6987</v>
@@ -34684,7 +34684,7 @@
         <v>6944</v>
       </c>
       <c r="F100">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="G100" t="s">
         <v>6987</v>
@@ -34782,7 +34782,7 @@
         <v>6943</v>
       </c>
       <c r="F104">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G104" t="s">
         <v>6987</v>
@@ -34808,7 +34808,7 @@
         <v>6951</v>
       </c>
       <c r="F105">
-        <v>2747</v>
+        <v>2744</v>
       </c>
       <c r="G105" t="s">
         <v>6987</v>
@@ -34860,7 +34860,7 @@
         <v>6943</v>
       </c>
       <c r="F107">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="G107" t="s">
         <v>6987</v>
@@ -34886,7 +34886,7 @@
         <v>6943</v>
       </c>
       <c r="F108">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="G108" t="s">
         <v>6988</v>
@@ -34906,7 +34906,7 @@
         <v>6943</v>
       </c>
       <c r="F109">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="G109" t="s">
         <v>6987</v>
@@ -34952,7 +34952,7 @@
         <v>6943</v>
       </c>
       <c r="F111">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="G111" t="s">
         <v>6987</v>
@@ -34978,7 +34978,7 @@
         <v>6943</v>
       </c>
       <c r="F112">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="G112" t="s">
         <v>6988</v>
@@ -34998,7 +34998,7 @@
         <v>6943</v>
       </c>
       <c r="F113">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="G113" t="s">
         <v>6987</v>
@@ -35024,7 +35024,7 @@
         <v>6943</v>
       </c>
       <c r="F114">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="G114" t="s">
         <v>6988</v>
@@ -35044,7 +35044,7 @@
         <v>6943</v>
       </c>
       <c r="F115">
-        <v>1116</v>
+        <v>1072</v>
       </c>
       <c r="G115" t="s">
         <v>6987</v>
@@ -35070,7 +35070,7 @@
         <v>6943</v>
       </c>
       <c r="F116">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="G116" t="s">
         <v>6987</v>
@@ -35096,7 +35096,7 @@
         <v>6943</v>
       </c>
       <c r="F117">
-        <v>828</v>
+        <v>785</v>
       </c>
       <c r="G117" t="s">
         <v>6987</v>
@@ -35122,7 +35122,7 @@
         <v>6943</v>
       </c>
       <c r="F118">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="G118" t="s">
         <v>6988</v>
@@ -35142,7 +35142,7 @@
         <v>6943</v>
       </c>
       <c r="F119">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="G119" t="s">
         <v>6987</v>
@@ -35168,7 +35168,7 @@
         <v>6943</v>
       </c>
       <c r="F120">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="G120" t="s">
         <v>6988</v>
@@ -35188,7 +35188,7 @@
         <v>6943</v>
       </c>
       <c r="F121">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="G121" t="s">
         <v>6988</v>
@@ -35234,7 +35234,7 @@
         <v>6944</v>
       </c>
       <c r="F123">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G123" t="s">
         <v>6987</v>
@@ -35286,7 +35286,7 @@
         <v>6953</v>
       </c>
       <c r="F125">
-        <v>1592</v>
+        <v>1576</v>
       </c>
       <c r="G125" t="s">
         <v>6987</v>
@@ -35312,7 +35312,7 @@
         <v>6953</v>
       </c>
       <c r="F126">
-        <v>1357</v>
+        <v>1313</v>
       </c>
       <c r="G126" t="s">
         <v>6987</v>
@@ -35338,7 +35338,7 @@
         <v>6953</v>
       </c>
       <c r="F127">
-        <v>1420</v>
+        <v>1392</v>
       </c>
       <c r="G127" t="s">
         <v>6987</v>
@@ -35364,7 +35364,7 @@
         <v>6953</v>
       </c>
       <c r="F128">
-        <v>1580</v>
+        <v>1564</v>
       </c>
       <c r="G128" t="s">
         <v>6987</v>
@@ -35390,7 +35390,7 @@
         <v>6953</v>
       </c>
       <c r="F129">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="G129" t="s">
         <v>6987</v>
@@ -35416,7 +35416,7 @@
         <v>6953</v>
       </c>
       <c r="F130">
-        <v>1508</v>
+        <v>1495</v>
       </c>
       <c r="G130" t="s">
         <v>6987</v>
@@ -35442,7 +35442,7 @@
         <v>6944</v>
       </c>
       <c r="F131">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="G131" t="s">
         <v>6987</v>
@@ -35494,7 +35494,7 @@
         <v>6952</v>
       </c>
       <c r="F133">
-        <v>978</v>
+        <v>944</v>
       </c>
       <c r="G133" t="s">
         <v>6987</v>
@@ -35520,7 +35520,7 @@
         <v>6944</v>
       </c>
       <c r="F134">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G134" t="s">
         <v>6987</v>
@@ -35546,7 +35546,7 @@
         <v>6952</v>
       </c>
       <c r="F135">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="G135" t="s">
         <v>6987</v>
@@ -35572,7 +35572,7 @@
         <v>6952</v>
       </c>
       <c r="F136">
-        <v>998</v>
+        <v>980</v>
       </c>
       <c r="G136" t="s">
         <v>6987</v>
@@ -35598,7 +35598,7 @@
         <v>6944</v>
       </c>
       <c r="F137">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="G137" t="s">
         <v>6987</v>
@@ -35624,7 +35624,7 @@
         <v>6944</v>
       </c>
       <c r="F138">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="G138" t="s">
         <v>6987</v>
@@ -35650,7 +35650,7 @@
         <v>6944</v>
       </c>
       <c r="F139">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="G139" t="s">
         <v>6987</v>
@@ -35702,7 +35702,7 @@
         <v>6954</v>
       </c>
       <c r="F141">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G141" t="s">
         <v>6987</v>
@@ -35848,7 +35848,7 @@
         <v>6954</v>
       </c>
       <c r="F148">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G148" t="s">
         <v>6987</v>
@@ -35874,7 +35874,7 @@
         <v>6954</v>
       </c>
       <c r="F149">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G149" t="s">
         <v>6987</v>
@@ -35900,7 +35900,7 @@
         <v>6954</v>
       </c>
       <c r="F150">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G150" t="s">
         <v>6987</v>
@@ -35926,7 +35926,7 @@
         <v>6944</v>
       </c>
       <c r="F151">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G151" t="s">
         <v>6987</v>
@@ -35952,7 +35952,7 @@
         <v>6955</v>
       </c>
       <c r="F152">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G152" t="s">
         <v>6987</v>
@@ -35978,7 +35978,7 @@
         <v>6955</v>
       </c>
       <c r="F153">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G153" t="s">
         <v>6987</v>
@@ -36004,7 +36004,7 @@
         <v>6952</v>
       </c>
       <c r="F154">
-        <v>941</v>
+        <v>909</v>
       </c>
       <c r="G154" t="s">
         <v>6987</v>
@@ -36030,7 +36030,7 @@
         <v>6952</v>
       </c>
       <c r="F155">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="G155" t="s">
         <v>6987</v>
@@ -36056,7 +36056,7 @@
         <v>6952</v>
       </c>
       <c r="F156">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="G156" t="s">
         <v>6987</v>
@@ -36082,7 +36082,7 @@
         <v>6943</v>
       </c>
       <c r="F157">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G157" t="s">
         <v>6987</v>
@@ -36108,7 +36108,7 @@
         <v>6943</v>
       </c>
       <c r="F158">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G158" t="s">
         <v>6987</v>
@@ -36134,7 +36134,7 @@
         <v>6943</v>
       </c>
       <c r="F159">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G159" t="s">
         <v>6987</v>
@@ -36160,7 +36160,7 @@
         <v>6944</v>
       </c>
       <c r="F160">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G160" t="s">
         <v>6987</v>
@@ -36186,7 +36186,7 @@
         <v>6944</v>
       </c>
       <c r="F161">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="G161" t="s">
         <v>6987</v>
@@ -36212,7 +36212,7 @@
         <v>6944</v>
       </c>
       <c r="F162">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G162" t="s">
         <v>6987</v>
@@ -36238,7 +36238,7 @@
         <v>6955</v>
       </c>
       <c r="F163">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G163" t="s">
         <v>6987</v>
@@ -36316,7 +36316,7 @@
         <v>6943</v>
       </c>
       <c r="F166">
-        <v>1683</v>
+        <v>1667</v>
       </c>
       <c r="G166" t="s">
         <v>6987</v>
@@ -36342,7 +36342,7 @@
         <v>6943</v>
       </c>
       <c r="F167">
-        <v>1214</v>
+        <v>1204</v>
       </c>
       <c r="G167" t="s">
         <v>6987</v>
@@ -36368,7 +36368,7 @@
         <v>6957</v>
       </c>
       <c r="F168">
-        <v>2177</v>
+        <v>2163</v>
       </c>
       <c r="G168" t="s">
         <v>6987</v>
@@ -36446,7 +36446,7 @@
         <v>6957</v>
       </c>
       <c r="F171">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="G171" t="s">
         <v>6987</v>
@@ -36472,7 +36472,7 @@
         <v>6943</v>
       </c>
       <c r="F172">
-        <v>1688</v>
+        <v>1674</v>
       </c>
       <c r="G172" t="s">
         <v>6987</v>
@@ -36498,7 +36498,7 @@
         <v>6943</v>
       </c>
       <c r="F173">
-        <v>1145</v>
+        <v>1136</v>
       </c>
       <c r="G173" t="s">
         <v>6987</v>
@@ -36550,7 +36550,7 @@
         <v>6958</v>
       </c>
       <c r="F175">
-        <v>3290</v>
+        <v>3274</v>
       </c>
       <c r="G175" t="s">
         <v>6987</v>
@@ -36602,7 +36602,7 @@
         <v>6958</v>
       </c>
       <c r="F177">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="G177" t="s">
         <v>6987</v>
@@ -36628,7 +36628,7 @@
         <v>6958</v>
       </c>
       <c r="F178">
-        <v>1990</v>
+        <v>1970</v>
       </c>
       <c r="G178" t="s">
         <v>6987</v>
@@ -36654,7 +36654,7 @@
         <v>6958</v>
       </c>
       <c r="F179">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="G179" t="s">
         <v>6987</v>
@@ -36680,7 +36680,7 @@
         <v>6958</v>
       </c>
       <c r="F180">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G180" t="s">
         <v>6987</v>
@@ -36706,7 +36706,7 @@
         <v>6943</v>
       </c>
       <c r="F181">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="G181" t="s">
         <v>6987</v>
@@ -36732,7 +36732,7 @@
         <v>6957</v>
       </c>
       <c r="F182">
-        <v>2475</v>
+        <v>2465</v>
       </c>
       <c r="G182" t="s">
         <v>6987</v>
@@ -36784,7 +36784,7 @@
         <v>6957</v>
       </c>
       <c r="F184">
-        <v>3703</v>
+        <v>3699</v>
       </c>
       <c r="G184" t="s">
         <v>6987</v>
@@ -36810,7 +36810,7 @@
         <v>6957</v>
       </c>
       <c r="F185">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="G185" t="s">
         <v>6987</v>
@@ -36836,7 +36836,7 @@
         <v>6957</v>
       </c>
       <c r="F186">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G186" t="s">
         <v>6987</v>
@@ -36862,7 +36862,7 @@
         <v>6957</v>
       </c>
       <c r="F187">
-        <v>2246</v>
+        <v>2242</v>
       </c>
       <c r="G187" t="s">
         <v>6987</v>
@@ -36914,7 +36914,7 @@
         <v>6943</v>
       </c>
       <c r="F189">
-        <v>1565</v>
+        <v>1554</v>
       </c>
       <c r="G189" t="s">
         <v>6987</v>
@@ -36940,7 +36940,7 @@
         <v>6943</v>
       </c>
       <c r="F190">
-        <v>1197</v>
+        <v>1186</v>
       </c>
       <c r="G190" t="s">
         <v>6987</v>
@@ -36966,7 +36966,7 @@
         <v>6958</v>
       </c>
       <c r="F191">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="G191" t="s">
         <v>6987</v>
@@ -36992,7 +36992,7 @@
         <v>6958</v>
       </c>
       <c r="F192">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="G192" t="s">
         <v>6987</v>
@@ -37018,7 +37018,7 @@
         <v>6958</v>
       </c>
       <c r="F193">
-        <v>2755</v>
+        <v>2747</v>
       </c>
       <c r="G193" t="s">
         <v>6987</v>
@@ -37044,7 +37044,7 @@
         <v>6943</v>
       </c>
       <c r="F194">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="G194" t="s">
         <v>6987</v>
@@ -37070,7 +37070,7 @@
         <v>6943</v>
       </c>
       <c r="F195">
-        <v>983</v>
+        <v>957</v>
       </c>
       <c r="G195" t="s">
         <v>6987</v>
@@ -37096,7 +37096,7 @@
         <v>6943</v>
       </c>
       <c r="F196">
-        <v>1132</v>
+        <v>1114</v>
       </c>
       <c r="G196" t="s">
         <v>6987</v>
@@ -37122,7 +37122,7 @@
         <v>6943</v>
       </c>
       <c r="F197">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="G197" t="s">
         <v>6987</v>
@@ -37148,7 +37148,7 @@
         <v>6943</v>
       </c>
       <c r="F198">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="G198" t="s">
         <v>6987</v>
@@ -37174,7 +37174,7 @@
         <v>6958</v>
       </c>
       <c r="F199">
-        <v>1776</v>
+        <v>1768</v>
       </c>
       <c r="G199" t="s">
         <v>6987</v>
@@ -37200,7 +37200,7 @@
         <v>6954</v>
       </c>
       <c r="F200">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G200" t="s">
         <v>6987</v>
@@ -37324,7 +37324,7 @@
         <v>6944</v>
       </c>
       <c r="F205">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G205" t="s">
         <v>6987</v>
@@ -37350,7 +37350,7 @@
         <v>6944</v>
       </c>
       <c r="F206">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="G206" t="s">
         <v>6987</v>
@@ -37376,7 +37376,7 @@
         <v>6944</v>
       </c>
       <c r="F207">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="G207" t="s">
         <v>6988</v>
@@ -37396,7 +37396,7 @@
         <v>6944</v>
       </c>
       <c r="F208">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G208" t="s">
         <v>6987</v>
@@ -37422,7 +37422,7 @@
         <v>6944</v>
       </c>
       <c r="F209">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G209" t="s">
         <v>6987</v>
@@ -37468,7 +37468,7 @@
         <v>6944</v>
       </c>
       <c r="F211">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G211" t="s">
         <v>6987</v>
@@ -37494,7 +37494,7 @@
         <v>6944</v>
       </c>
       <c r="F212">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G212" t="s">
         <v>6987</v>
@@ -37600,7 +37600,7 @@
         <v>6943</v>
       </c>
       <c r="F217">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G217" t="s">
         <v>6987</v>
@@ -37626,7 +37626,7 @@
         <v>6943</v>
       </c>
       <c r="F218">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="G218" t="s">
         <v>6987</v>
@@ -37652,7 +37652,7 @@
         <v>6955</v>
       </c>
       <c r="F219">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G219" t="s">
         <v>6988</v>
@@ -37712,7 +37712,7 @@
         <v>6943</v>
       </c>
       <c r="F222">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="G222" t="s">
         <v>6987</v>
@@ -37818,7 +37818,7 @@
         <v>6943</v>
       </c>
       <c r="F227">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G227" t="s">
         <v>6987</v>
@@ -37844,7 +37844,7 @@
         <v>6943</v>
       </c>
       <c r="F228">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G228" t="s">
         <v>6987</v>
@@ -37870,7 +37870,7 @@
         <v>6943</v>
       </c>
       <c r="F229">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G229" t="s">
         <v>6987</v>
@@ -37896,7 +37896,7 @@
         <v>6943</v>
       </c>
       <c r="F230">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G230" t="s">
         <v>6987</v>
@@ -37942,7 +37942,7 @@
         <v>6944</v>
       </c>
       <c r="F232">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="G232" t="s">
         <v>6988</v>
@@ -38066,7 +38066,7 @@
         <v>6960</v>
       </c>
       <c r="F237">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="G237" t="s">
         <v>6987</v>
@@ -38092,7 +38092,7 @@
         <v>6944</v>
       </c>
       <c r="F238">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="G238" t="s">
         <v>6988</v>
@@ -38210,7 +38210,7 @@
         <v>6961</v>
       </c>
       <c r="F243">
-        <v>1854</v>
+        <v>1842</v>
       </c>
       <c r="G243" t="s">
         <v>6987</v>
@@ -38236,7 +38236,7 @@
         <v>6961</v>
       </c>
       <c r="F244">
-        <v>1872</v>
+        <v>1866</v>
       </c>
       <c r="G244" t="s">
         <v>6987</v>
@@ -38522,7 +38522,7 @@
         <v>6953</v>
       </c>
       <c r="F255">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="G255" t="s">
         <v>6987</v>
@@ -38730,7 +38730,7 @@
         <v>6953</v>
       </c>
       <c r="F263">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="G263" t="s">
         <v>6987</v>
@@ -38756,7 +38756,7 @@
         <v>6953</v>
       </c>
       <c r="F264">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="G264" t="s">
         <v>6987</v>
@@ -38782,7 +38782,7 @@
         <v>6953</v>
       </c>
       <c r="F265">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="G265" t="s">
         <v>6987</v>
@@ -38808,7 +38808,7 @@
         <v>6953</v>
       </c>
       <c r="F266">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="G266" t="s">
         <v>6987</v>
@@ -38834,7 +38834,7 @@
         <v>6961</v>
       </c>
       <c r="F267">
-        <v>1818</v>
+        <v>1812</v>
       </c>
       <c r="G267" t="s">
         <v>6987</v>
@@ -38912,7 +38912,7 @@
         <v>6961</v>
       </c>
       <c r="F270">
-        <v>1300</v>
+        <v>1209</v>
       </c>
       <c r="G270" t="s">
         <v>6987</v>
@@ -38964,7 +38964,7 @@
         <v>6944</v>
       </c>
       <c r="F272">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="G272" t="s">
         <v>6987</v>
@@ -38990,7 +38990,7 @@
         <v>6944</v>
       </c>
       <c r="F273">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="G273" t="s">
         <v>6987</v>
@@ -39016,7 +39016,7 @@
         <v>6944</v>
       </c>
       <c r="F274">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G274" t="s">
         <v>6987</v>
@@ -39042,7 +39042,7 @@
         <v>6953</v>
       </c>
       <c r="F275">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="G275" t="s">
         <v>6987</v>
@@ -39120,7 +39120,7 @@
         <v>6961</v>
       </c>
       <c r="F278">
-        <v>1758</v>
+        <v>1746</v>
       </c>
       <c r="G278" t="s">
         <v>6987</v>
@@ -39146,7 +39146,7 @@
         <v>6952</v>
       </c>
       <c r="F279">
-        <v>990</v>
+        <v>966</v>
       </c>
       <c r="G279" t="s">
         <v>6987</v>
@@ -39172,7 +39172,7 @@
         <v>6952</v>
       </c>
       <c r="F280">
-        <v>1788</v>
+        <v>1782</v>
       </c>
       <c r="G280" t="s">
         <v>6987</v>
@@ -39198,7 +39198,7 @@
         <v>6952</v>
       </c>
       <c r="F281">
-        <v>1224</v>
+        <v>1212</v>
       </c>
       <c r="G281" t="s">
         <v>6987</v>
@@ -39224,7 +39224,7 @@
         <v>6952</v>
       </c>
       <c r="F282">
-        <v>1173</v>
+        <v>1143</v>
       </c>
       <c r="G282" t="s">
         <v>6987</v>
@@ -39250,7 +39250,7 @@
         <v>6952</v>
       </c>
       <c r="F283">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="G283" t="s">
         <v>6987</v>
@@ -39276,7 +39276,7 @@
         <v>6960</v>
       </c>
       <c r="F284">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="G284" t="s">
         <v>6987</v>
@@ -39302,7 +39302,7 @@
         <v>6960</v>
       </c>
       <c r="F285">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="G285" t="s">
         <v>6988</v>
@@ -39322,7 +39322,7 @@
         <v>6960</v>
       </c>
       <c r="F286">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="G286" t="s">
         <v>6987</v>
@@ -39348,7 +39348,7 @@
         <v>6960</v>
       </c>
       <c r="F287">
-        <v>1737</v>
+        <v>1731</v>
       </c>
       <c r="G287" t="s">
         <v>6987</v>
@@ -39374,7 +39374,7 @@
         <v>6960</v>
       </c>
       <c r="F288">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="G288" t="s">
         <v>6987</v>
@@ -39426,7 +39426,7 @@
         <v>6960</v>
       </c>
       <c r="F290">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="G290" t="s">
         <v>6987</v>
@@ -39478,7 +39478,7 @@
         <v>6960</v>
       </c>
       <c r="F292">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="G292" t="s">
         <v>6987</v>
@@ -39504,7 +39504,7 @@
         <v>6959</v>
       </c>
       <c r="F293">
-        <v>1106</v>
+        <v>1096</v>
       </c>
       <c r="G293" t="s">
         <v>6987</v>
@@ -39530,7 +39530,7 @@
         <v>6959</v>
       </c>
       <c r="F294">
-        <v>1135</v>
+        <v>1095</v>
       </c>
       <c r="G294" t="s">
         <v>6987</v>
@@ -39636,7 +39636,7 @@
         <v>6959</v>
       </c>
       <c r="F299">
-        <v>637</v>
+        <v>597</v>
       </c>
       <c r="G299" t="s">
         <v>6987</v>
@@ -39662,7 +39662,7 @@
         <v>6959</v>
       </c>
       <c r="F300">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G300" t="s">
         <v>6987</v>
@@ -39688,7 +39688,7 @@
         <v>6959</v>
       </c>
       <c r="F301">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="G301" t="s">
         <v>6987</v>
@@ -39714,7 +39714,7 @@
         <v>6959</v>
       </c>
       <c r="F302">
-        <v>2215</v>
+        <v>2185</v>
       </c>
       <c r="G302" t="s">
         <v>6987</v>
@@ -39740,7 +39740,7 @@
         <v>6959</v>
       </c>
       <c r="F303">
-        <v>3082</v>
+        <v>3042</v>
       </c>
       <c r="G303" t="s">
         <v>6987</v>
@@ -39766,7 +39766,7 @@
         <v>6944</v>
       </c>
       <c r="F304">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="G304" t="s">
         <v>6987</v>
@@ -39818,7 +39818,7 @@
         <v>6963</v>
       </c>
       <c r="F306">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="G306" t="s">
         <v>6987</v>
@@ -39890,7 +39890,7 @@
         <v>6944</v>
       </c>
       <c r="F309">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G309" t="s">
         <v>6987</v>
@@ -39916,7 +39916,7 @@
         <v>6944</v>
       </c>
       <c r="F310">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="G310" t="s">
         <v>6987</v>
@@ -39942,7 +39942,7 @@
         <v>6944</v>
       </c>
       <c r="F311">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="G311" t="s">
         <v>6987</v>
@@ -39968,7 +39968,7 @@
         <v>6944</v>
       </c>
       <c r="F312">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G312" t="s">
         <v>6987</v>
@@ -39994,7 +39994,7 @@
         <v>6944</v>
       </c>
       <c r="F313">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="G313" t="s">
         <v>6987</v>
@@ -40046,7 +40046,7 @@
         <v>6963</v>
       </c>
       <c r="F315">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="G315" t="s">
         <v>6987</v>
@@ -40306,7 +40306,7 @@
         <v>6965</v>
       </c>
       <c r="F325">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="G325" t="s">
         <v>6987</v>
@@ -40332,7 +40332,7 @@
         <v>6965</v>
       </c>
       <c r="F326">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="G326" t="s">
         <v>6987</v>
@@ -40358,7 +40358,7 @@
         <v>6965</v>
       </c>
       <c r="F327">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G327" t="s">
         <v>6987</v>
@@ -40384,7 +40384,7 @@
         <v>6944</v>
       </c>
       <c r="F328">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="G328" t="s">
         <v>6987</v>
@@ -40430,7 +40430,7 @@
         <v>6960</v>
       </c>
       <c r="F330">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G330" t="s">
         <v>6988</v>
@@ -40470,7 +40470,7 @@
         <v>6960</v>
       </c>
       <c r="F332">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="G332" t="s">
         <v>6988</v>
@@ -40510,7 +40510,7 @@
         <v>6960</v>
       </c>
       <c r="F334">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="G334" t="s">
         <v>6988</v>
@@ -40530,7 +40530,7 @@
         <v>6959</v>
       </c>
       <c r="F335">
-        <v>3371</v>
+        <v>3341</v>
       </c>
       <c r="G335" t="s">
         <v>6987</v>
@@ -40556,7 +40556,7 @@
         <v>6959</v>
       </c>
       <c r="F336">
-        <v>2500</v>
+        <v>2460</v>
       </c>
       <c r="G336" t="s">
         <v>6987</v>
@@ -40608,7 +40608,7 @@
         <v>6959</v>
       </c>
       <c r="F338">
-        <v>3384</v>
+        <v>3334</v>
       </c>
       <c r="G338" t="s">
         <v>6987</v>
@@ -40660,7 +40660,7 @@
         <v>6959</v>
       </c>
       <c r="F340">
-        <v>3000</v>
+        <v>2990</v>
       </c>
       <c r="G340" t="s">
         <v>6987</v>
@@ -40746,7 +40746,7 @@
         <v>6943</v>
       </c>
       <c r="F344">
-        <v>1214</v>
+        <v>1014</v>
       </c>
       <c r="G344" t="s">
         <v>6988</v>
@@ -40766,7 +40766,7 @@
         <v>6943</v>
       </c>
       <c r="F345">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G345" t="s">
         <v>6987</v>
@@ -40812,7 +40812,7 @@
         <v>6960</v>
       </c>
       <c r="F347">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="G347" t="s">
         <v>6988</v>
@@ -40832,7 +40832,7 @@
         <v>6960</v>
       </c>
       <c r="F348">
-        <v>1614</v>
+        <v>1590</v>
       </c>
       <c r="G348" t="s">
         <v>6988</v>
@@ -40852,7 +40852,7 @@
         <v>6960</v>
       </c>
       <c r="F349">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G349" t="s">
         <v>6988</v>
@@ -40872,7 +40872,7 @@
         <v>6960</v>
       </c>
       <c r="F350">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="G350" t="s">
         <v>6988</v>
@@ -40912,7 +40912,7 @@
         <v>6960</v>
       </c>
       <c r="F352">
-        <v>1698</v>
+        <v>1686</v>
       </c>
       <c r="G352" t="s">
         <v>6988</v>
@@ -40932,7 +40932,7 @@
         <v>6960</v>
       </c>
       <c r="F353">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="G353" t="s">
         <v>6988</v>
@@ -40952,7 +40952,7 @@
         <v>6943</v>
       </c>
       <c r="F354">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="G354" t="s">
         <v>6987</v>
@@ -40978,7 +40978,7 @@
         <v>6943</v>
       </c>
       <c r="F355">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="G355" t="s">
         <v>6987</v>
@@ -41004,7 +41004,7 @@
         <v>6943</v>
       </c>
       <c r="F356">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G356" t="s">
         <v>6987</v>
@@ -41076,7 +41076,7 @@
         <v>6965</v>
       </c>
       <c r="F359">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G359" t="s">
         <v>6987</v>
@@ -41102,7 +41102,7 @@
         <v>6965</v>
       </c>
       <c r="F360">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G360" t="s">
         <v>6987</v>
@@ -41128,7 +41128,7 @@
         <v>6965</v>
       </c>
       <c r="F361">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G361" t="s">
         <v>6987</v>
@@ -41154,7 +41154,7 @@
         <v>6965</v>
       </c>
       <c r="F362">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="G362" t="s">
         <v>6987</v>
@@ -41180,7 +41180,7 @@
         <v>6965</v>
       </c>
       <c r="F363">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="G363" t="s">
         <v>6987</v>
@@ -41206,7 +41206,7 @@
         <v>6965</v>
       </c>
       <c r="F364">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G364" t="s">
         <v>6987</v>
@@ -41258,7 +41258,7 @@
         <v>6965</v>
       </c>
       <c r="F366">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="G366" t="s">
         <v>6987</v>
@@ -41284,7 +41284,7 @@
         <v>6959</v>
       </c>
       <c r="F367">
-        <v>3460</v>
+        <v>3440</v>
       </c>
       <c r="G367" t="s">
         <v>6987</v>
@@ -41440,7 +41440,7 @@
         <v>6965</v>
       </c>
       <c r="F373">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G373" t="s">
         <v>6987</v>
@@ -41492,7 +41492,7 @@
         <v>6959</v>
       </c>
       <c r="F375">
-        <v>2577</v>
+        <v>2537</v>
       </c>
       <c r="G375" t="s">
         <v>6987</v>
@@ -41518,7 +41518,7 @@
         <v>6965</v>
       </c>
       <c r="F376">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="G376" t="s">
         <v>6987</v>
@@ -41570,7 +41570,7 @@
         <v>6959</v>
       </c>
       <c r="F378">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G378" t="s">
         <v>6987</v>
@@ -41596,7 +41596,7 @@
         <v>6943</v>
       </c>
       <c r="F379">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G379" t="s">
         <v>6987</v>
@@ -41674,7 +41674,7 @@
         <v>6959</v>
       </c>
       <c r="F382">
-        <v>2157</v>
+        <v>2117</v>
       </c>
       <c r="G382" t="s">
         <v>6987</v>
@@ -41700,7 +41700,7 @@
         <v>6959</v>
       </c>
       <c r="F383">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="G383" t="s">
         <v>6987</v>
@@ -41726,7 +41726,7 @@
         <v>6959</v>
       </c>
       <c r="F384">
-        <v>2130</v>
+        <v>2100</v>
       </c>
       <c r="G384" t="s">
         <v>6988</v>
@@ -41746,7 +41746,7 @@
         <v>6943</v>
       </c>
       <c r="F385">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G385" t="s">
         <v>6987</v>
@@ -41798,7 +41798,7 @@
         <v>6943</v>
       </c>
       <c r="F387">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G387" t="s">
         <v>6988</v>
@@ -41818,7 +41818,7 @@
         <v>6959</v>
       </c>
       <c r="F388">
-        <v>1269</v>
+        <v>1249</v>
       </c>
       <c r="G388" t="s">
         <v>6987</v>
@@ -41844,7 +41844,7 @@
         <v>6944</v>
       </c>
       <c r="F389">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G389" t="s">
         <v>6987</v>
@@ -41870,7 +41870,7 @@
         <v>6944</v>
       </c>
       <c r="F390">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G390" t="s">
         <v>6987</v>
@@ -41948,7 +41948,7 @@
         <v>6959</v>
       </c>
       <c r="F393">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="G393" t="s">
         <v>6987</v>
@@ -41974,7 +41974,7 @@
         <v>6959</v>
       </c>
       <c r="F394">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="G394" t="s">
         <v>6987</v>
@@ -42052,7 +42052,7 @@
         <v>6944</v>
       </c>
       <c r="F397">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G397" t="s">
         <v>6987</v>
@@ -42078,7 +42078,7 @@
         <v>6943</v>
       </c>
       <c r="F398">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="G398" t="s">
         <v>6987</v>
@@ -42104,7 +42104,7 @@
         <v>6943</v>
       </c>
       <c r="F399">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="G399" t="s">
         <v>6987</v>
@@ -42156,7 +42156,7 @@
         <v>6967</v>
       </c>
       <c r="F401">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G401" t="s">
         <v>6987</v>
@@ -42182,7 +42182,7 @@
         <v>6968</v>
       </c>
       <c r="F402">
-        <v>4215</v>
+        <v>4209</v>
       </c>
       <c r="G402" t="s">
         <v>6987</v>
@@ -42208,7 +42208,7 @@
         <v>6969</v>
       </c>
       <c r="F403">
-        <v>1077</v>
+        <v>1059</v>
       </c>
       <c r="G403" t="s">
         <v>6987</v>
@@ -42234,7 +42234,7 @@
         <v>6943</v>
       </c>
       <c r="F404">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G404" t="s">
         <v>6987</v>
@@ -42260,7 +42260,7 @@
         <v>6943</v>
       </c>
       <c r="F405">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="G405" t="s">
         <v>6987</v>
@@ -42286,7 +42286,7 @@
         <v>6943</v>
       </c>
       <c r="F406">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G406" t="s">
         <v>6987</v>
@@ -42312,7 +42312,7 @@
         <v>6952</v>
       </c>
       <c r="F407">
-        <v>1739</v>
+        <v>1721</v>
       </c>
       <c r="G407" t="s">
         <v>6987</v>
@@ -42358,7 +42358,7 @@
         <v>6961</v>
       </c>
       <c r="F409">
-        <v>1504</v>
+        <v>1468</v>
       </c>
       <c r="G409" t="s">
         <v>6987</v>
@@ -42384,7 +42384,7 @@
         <v>6952</v>
       </c>
       <c r="F410">
-        <v>1509</v>
+        <v>1473</v>
       </c>
       <c r="G410" t="s">
         <v>6987</v>
@@ -42410,7 +42410,7 @@
         <v>6952</v>
       </c>
       <c r="F411">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="G411" t="s">
         <v>6987</v>
@@ -42436,7 +42436,7 @@
         <v>6952</v>
       </c>
       <c r="F412">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="G412" t="s">
         <v>6987</v>
@@ -42462,7 +42462,7 @@
         <v>6952</v>
       </c>
       <c r="F413">
-        <v>1788</v>
+        <v>1776</v>
       </c>
       <c r="G413" t="s">
         <v>6987</v>
@@ -42488,7 +42488,7 @@
         <v>6952</v>
       </c>
       <c r="F414">
-        <v>1601</v>
+        <v>1583</v>
       </c>
       <c r="G414" t="s">
         <v>6987</v>
@@ -42514,7 +42514,7 @@
         <v>6952</v>
       </c>
       <c r="F415">
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="G415" t="s">
         <v>6987</v>
@@ -42660,7 +42660,7 @@
         <v>6961</v>
       </c>
       <c r="F422">
-        <v>1625</v>
+        <v>1607</v>
       </c>
       <c r="G422" t="s">
         <v>6987</v>
@@ -42686,7 +42686,7 @@
         <v>6961</v>
       </c>
       <c r="F423">
-        <v>1673</v>
+        <v>1649</v>
       </c>
       <c r="G423" t="s">
         <v>6987</v>
@@ -42712,7 +42712,7 @@
         <v>6961</v>
       </c>
       <c r="F424">
-        <v>1554</v>
+        <v>1518</v>
       </c>
       <c r="G424" t="s">
         <v>6987</v>
@@ -42738,7 +42738,7 @@
         <v>6943</v>
       </c>
       <c r="F425">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G425" t="s">
         <v>6987</v>
@@ -42790,7 +42790,7 @@
         <v>6961</v>
       </c>
       <c r="F427">
-        <v>1638</v>
+        <v>1606</v>
       </c>
       <c r="G427" t="s">
         <v>6987</v>
@@ -42816,7 +42816,7 @@
         <v>6961</v>
       </c>
       <c r="F428">
-        <v>1755</v>
+        <v>1736</v>
       </c>
       <c r="G428" t="s">
         <v>6987</v>
@@ -42842,7 +42842,7 @@
         <v>6944</v>
       </c>
       <c r="F429">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G429" t="s">
         <v>6987</v>
@@ -42914,7 +42914,7 @@
         <v>6944</v>
       </c>
       <c r="F432">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G432" t="s">
         <v>6987</v>
@@ -42940,7 +42940,7 @@
         <v>6944</v>
       </c>
       <c r="F433">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G433" t="s">
         <v>6987</v>
@@ -42966,7 +42966,7 @@
         <v>6948</v>
       </c>
       <c r="F434">
-        <v>3853</v>
+        <v>3845</v>
       </c>
       <c r="G434" t="s">
         <v>6987</v>
@@ -42992,7 +42992,7 @@
         <v>6948</v>
       </c>
       <c r="F435">
-        <v>4090</v>
+        <v>4084</v>
       </c>
       <c r="G435" t="s">
         <v>6987</v>
@@ -43018,7 +43018,7 @@
         <v>6970</v>
       </c>
       <c r="F436">
-        <v>3077</v>
+        <v>3073</v>
       </c>
       <c r="G436" t="s">
         <v>6987</v>
@@ -43044,7 +43044,7 @@
         <v>6971</v>
       </c>
       <c r="F437">
-        <v>1773</v>
+        <v>1767</v>
       </c>
       <c r="G437" t="s">
         <v>6987</v>
@@ -43378,7 +43378,7 @@
         <v>6973</v>
       </c>
       <c r="F451">
-        <v>1151</v>
+        <v>1127</v>
       </c>
       <c r="G451" t="s">
         <v>6987</v>
@@ -43404,7 +43404,7 @@
         <v>6973</v>
       </c>
       <c r="F452">
-        <v>1537</v>
+        <v>1525</v>
       </c>
       <c r="G452" t="s">
         <v>6987</v>
@@ -43430,7 +43430,7 @@
         <v>6973</v>
       </c>
       <c r="F453">
-        <v>1404</v>
+        <v>1380</v>
       </c>
       <c r="G453" t="s">
         <v>6987</v>
@@ -43456,7 +43456,7 @@
         <v>6973</v>
       </c>
       <c r="F454">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="G454" t="s">
         <v>6988</v>
@@ -43476,7 +43476,7 @@
         <v>6943</v>
       </c>
       <c r="F455">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G455" t="s">
         <v>6987</v>
@@ -43502,7 +43502,7 @@
         <v>6973</v>
       </c>
       <c r="F456">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="G456" t="s">
         <v>6987</v>
@@ -43830,7 +43830,7 @@
         <v>6958</v>
       </c>
       <c r="F470">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="G470" t="s">
         <v>6987</v>
@@ -43882,7 +43882,7 @@
         <v>6958</v>
       </c>
       <c r="F472">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="G472" t="s">
         <v>6987</v>
@@ -44254,7 +44254,7 @@
         <v>6943</v>
       </c>
       <c r="F490">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="G490" t="s">
         <v>6987</v>
@@ -47956,7 +47956,7 @@
         <v>6954</v>
       </c>
       <c r="F634">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G634" t="s">
         <v>6987</v>
@@ -47982,7 +47982,7 @@
         <v>6954</v>
       </c>
       <c r="F635">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="G635" t="s">
         <v>6987</v>
@@ -48008,7 +48008,7 @@
         <v>6954</v>
       </c>
       <c r="F636">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G636" t="s">
         <v>6987</v>
@@ -48034,7 +48034,7 @@
         <v>6954</v>
       </c>
       <c r="F637">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="G637" t="s">
         <v>6987</v>
@@ -48146,7 +48146,7 @@
         <v>6955</v>
       </c>
       <c r="F642">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="G642" t="s">
         <v>6987</v>
@@ -49334,7 +49334,7 @@
         <v>6949</v>
       </c>
       <c r="F690">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="G690" t="s">
         <v>6987</v>
@@ -50400,7 +50400,7 @@
         <v>6972</v>
       </c>
       <c r="F731">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="G731" t="s">
         <v>6987</v>
@@ -50478,7 +50478,7 @@
         <v>6972</v>
       </c>
       <c r="F734">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G734" t="s">
         <v>6987</v>
@@ -50530,7 +50530,7 @@
         <v>6972</v>
       </c>
       <c r="F736">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G736" t="s">
         <v>6987</v>
@@ -50738,7 +50738,7 @@
         <v>6972</v>
       </c>
       <c r="F744">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G744" t="s">
         <v>6987</v>
@@ -50764,7 +50764,7 @@
         <v>6972</v>
       </c>
       <c r="F745">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G745" t="s">
         <v>6987</v>
@@ -50972,7 +50972,7 @@
         <v>6972</v>
       </c>
       <c r="F753">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G753" t="s">
         <v>6987</v>
@@ -51772,7 +51772,7 @@
         <v>6963</v>
       </c>
       <c r="F787">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G787" t="s">
         <v>6987</v>
@@ -51902,7 +51902,7 @@
         <v>6963</v>
       </c>
       <c r="F792">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G792" t="s">
         <v>6987</v>
@@ -52032,7 +52032,7 @@
         <v>6963</v>
       </c>
       <c r="F797">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G797" t="s">
         <v>6987</v>
@@ -52058,7 +52058,7 @@
         <v>6963</v>
       </c>
       <c r="F798">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G798" t="s">
         <v>6988</v>
@@ -52078,7 +52078,7 @@
         <v>6963</v>
       </c>
       <c r="F799">
-        <v>3662</v>
+        <v>3656</v>
       </c>
       <c r="G799" t="s">
         <v>6987</v>
@@ -52228,7 +52228,7 @@
         <v>6963</v>
       </c>
       <c r="F805">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="G805" t="s">
         <v>6987</v>
@@ -52306,7 +52306,7 @@
         <v>6963</v>
       </c>
       <c r="F808">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="G808" t="s">
         <v>6987</v>
@@ -52332,7 +52332,7 @@
         <v>6963</v>
       </c>
       <c r="F809">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="G809" t="s">
         <v>6987</v>
@@ -52664,7 +52664,7 @@
         <v>6963</v>
       </c>
       <c r="F822">
-        <v>4705</v>
+        <v>4693</v>
       </c>
       <c r="G822" t="s">
         <v>6987</v>
@@ -52820,7 +52820,7 @@
         <v>6963</v>
       </c>
       <c r="F828">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="G828" t="s">
         <v>6987</v>
@@ -52950,7 +52950,7 @@
         <v>6963</v>
       </c>
       <c r="F833">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="G833" t="s">
         <v>6987</v>
@@ -52976,7 +52976,7 @@
         <v>6963</v>
       </c>
       <c r="F834">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="G834" t="s">
         <v>6987</v>
@@ -53054,7 +53054,7 @@
         <v>6963</v>
       </c>
       <c r="F837">
-        <v>1571</v>
+        <v>1553</v>
       </c>
       <c r="G837" t="s">
         <v>6987</v>
@@ -53080,7 +53080,7 @@
         <v>6963</v>
       </c>
       <c r="F838">
-        <v>1851</v>
+        <v>1833</v>
       </c>
       <c r="G838" t="s">
         <v>6987</v>
@@ -54174,7 +54174,7 @@
         <v>6951</v>
       </c>
       <c r="F881">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G881" t="s">
         <v>6987</v>
@@ -54200,7 +54200,7 @@
         <v>6951</v>
       </c>
       <c r="F882">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G882" t="s">
         <v>6987</v>
@@ -54226,7 +54226,7 @@
         <v>6951</v>
       </c>
       <c r="F883">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G883" t="s">
         <v>6987</v>
@@ -54298,7 +54298,7 @@
         <v>6951</v>
       </c>
       <c r="F886">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="G886" t="s">
         <v>6988</v>
@@ -54318,7 +54318,7 @@
         <v>6951</v>
       </c>
       <c r="F887">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="G887" t="s">
         <v>6988</v>
@@ -54572,7 +54572,7 @@
         <v>6959</v>
       </c>
       <c r="F897">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="G897" t="s">
         <v>6987</v>
@@ -55222,7 +55222,7 @@
         <v>6959</v>
       </c>
       <c r="F928">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="G928" t="s">
         <v>6987</v>
@@ -55328,7 +55328,7 @@
         <v>6981</v>
       </c>
       <c r="F933">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="G933" t="s">
         <v>6988</v>
@@ -55388,7 +55388,7 @@
         <v>6981</v>
       </c>
       <c r="F936">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="G936" t="s">
         <v>6988</v>
@@ -55428,7 +55428,7 @@
         <v>6981</v>
       </c>
       <c r="F938">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="G938" t="s">
         <v>6988</v>
@@ -55448,7 +55448,7 @@
         <v>6981</v>
       </c>
       <c r="F939">
-        <v>1756</v>
+        <v>1744</v>
       </c>
       <c r="G939" t="s">
         <v>6987</v>
@@ -55534,7 +55534,7 @@
         <v>6981</v>
       </c>
       <c r="F943">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="G943" t="s">
         <v>6988</v>
@@ -55554,7 +55554,7 @@
         <v>6981</v>
       </c>
       <c r="F944">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="G944" t="s">
         <v>6988</v>
@@ -55574,7 +55574,7 @@
         <v>6981</v>
       </c>
       <c r="F945">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="G945" t="s">
         <v>6988</v>
@@ -55594,7 +55594,7 @@
         <v>6981</v>
       </c>
       <c r="F946">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="G946" t="s">
         <v>6988</v>
@@ -55614,7 +55614,7 @@
         <v>6981</v>
       </c>
       <c r="F947">
-        <v>753</v>
+        <v>729</v>
       </c>
       <c r="G947" t="s">
         <v>6987</v>
@@ -55640,7 +55640,7 @@
         <v>6981</v>
       </c>
       <c r="F948">
-        <v>720</v>
+        <v>696</v>
       </c>
       <c r="G948" t="s">
         <v>6987</v>
@@ -55692,7 +55692,7 @@
         <v>6956</v>
       </c>
       <c r="F950">
-        <v>5816</v>
+        <v>5796</v>
       </c>
       <c r="G950" t="s">
         <v>6987</v>
@@ -55718,7 +55718,7 @@
         <v>6956</v>
       </c>
       <c r="F951">
-        <v>5816</v>
+        <v>5796</v>
       </c>
       <c r="G951" t="s">
         <v>6987</v>
@@ -55744,7 +55744,7 @@
         <v>6956</v>
       </c>
       <c r="F952">
-        <v>9526</v>
+        <v>9506</v>
       </c>
       <c r="G952" t="s">
         <v>6987</v>
@@ -55900,7 +55900,7 @@
         <v>6981</v>
       </c>
       <c r="F958">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="G958" t="s">
         <v>6987</v>
@@ -55986,7 +55986,7 @@
         <v>6981</v>
       </c>
       <c r="F962">
-        <v>1790</v>
+        <v>1767</v>
       </c>
       <c r="G962" t="s">
         <v>6987</v>
@@ -56038,7 +56038,7 @@
         <v>6981</v>
       </c>
       <c r="F964">
-        <v>1232</v>
+        <v>1196</v>
       </c>
       <c r="G964" t="s">
         <v>6987</v>
@@ -56090,7 +56090,7 @@
         <v>6981</v>
       </c>
       <c r="F966">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="G966" t="s">
         <v>6988</v>
@@ -56110,7 +56110,7 @@
         <v>6981</v>
       </c>
       <c r="F967">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="G967" t="s">
         <v>6988</v>
@@ -56130,7 +56130,7 @@
         <v>6981</v>
       </c>
       <c r="F968">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="G968" t="s">
         <v>6988</v>
@@ -56150,7 +56150,7 @@
         <v>6981</v>
       </c>
       <c r="F969">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="G969" t="s">
         <v>6988</v>
@@ -56196,7 +56196,7 @@
         <v>6981</v>
       </c>
       <c r="F971">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="G971" t="s">
         <v>6987</v>
@@ -56222,7 +56222,7 @@
         <v>6981</v>
       </c>
       <c r="F972">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G972" t="s">
         <v>6987</v>
@@ -56274,7 +56274,7 @@
         <v>6981</v>
       </c>
       <c r="F974">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G974" t="s">
         <v>6987</v>
@@ -56300,7 +56300,7 @@
         <v>6981</v>
       </c>
       <c r="F975">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G975" t="s">
         <v>6987</v>
@@ -56346,7 +56346,7 @@
         <v>6981</v>
       </c>
       <c r="F977">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G977" t="s">
         <v>6988</v>
@@ -56366,7 +56366,7 @@
         <v>6981</v>
       </c>
       <c r="F978">
-        <v>1528</v>
+        <v>1521</v>
       </c>
       <c r="G978" t="s">
         <v>6988</v>
@@ -56386,7 +56386,7 @@
         <v>6951</v>
       </c>
       <c r="F979">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G979" t="s">
         <v>6987</v>
@@ -56490,7 +56490,7 @@
         <v>6951</v>
       </c>
       <c r="F983">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="G983" t="s">
         <v>6987</v>
@@ -56542,7 +56542,7 @@
         <v>6959</v>
       </c>
       <c r="F985">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G985" t="s">
         <v>6987</v>
@@ -56568,7 +56568,7 @@
         <v>6981</v>
       </c>
       <c r="F986">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G986" t="s">
         <v>6988</v>
@@ -56588,7 +56588,7 @@
         <v>6981</v>
       </c>
       <c r="F987">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="G987" t="s">
         <v>6987</v>
@@ -56666,7 +56666,7 @@
         <v>6981</v>
       </c>
       <c r="F990">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G990" t="s">
         <v>6988</v>
@@ -56686,7 +56686,7 @@
         <v>6981</v>
       </c>
       <c r="F991">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="G991" t="s">
         <v>6988</v>
@@ -56706,7 +56706,7 @@
         <v>6981</v>
       </c>
       <c r="F992">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="G992" t="s">
         <v>6988</v>
@@ -56726,7 +56726,7 @@
         <v>6981</v>
       </c>
       <c r="F993">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="G993" t="s">
         <v>6988</v>
@@ -56772,7 +56772,7 @@
         <v>6981</v>
       </c>
       <c r="F995">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G995" t="s">
         <v>6987</v>
@@ -56824,7 +56824,7 @@
         <v>6981</v>
       </c>
       <c r="F997">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G997" t="s">
         <v>6987</v>
@@ -56876,7 +56876,7 @@
         <v>6981</v>
       </c>
       <c r="F999">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="G999" t="s">
         <v>6987</v>
@@ -56928,7 +56928,7 @@
         <v>6981</v>
       </c>
       <c r="F1001">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="G1001" t="s">
         <v>6987</v>
@@ -57176,7 +57176,7 @@
         <v>6943</v>
       </c>
       <c r="F1011">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G1011" t="s">
         <v>6987</v>
@@ -57202,7 +57202,7 @@
         <v>6943</v>
       </c>
       <c r="F1012">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G1012" t="s">
         <v>6987</v>
@@ -57254,7 +57254,7 @@
         <v>6943</v>
       </c>
       <c r="F1014">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G1014" t="s">
         <v>6987</v>
@@ -57482,7 +57482,7 @@
         <v>6963</v>
       </c>
       <c r="F1023">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="G1023" t="s">
         <v>6987</v>
@@ -57534,7 +57534,7 @@
         <v>6963</v>
       </c>
       <c r="F1025">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G1025" t="s">
         <v>6988</v>
@@ -57606,7 +57606,7 @@
         <v>6943</v>
       </c>
       <c r="F1028">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G1028" t="s">
         <v>6987</v>
@@ -57632,7 +57632,7 @@
         <v>6943</v>
       </c>
       <c r="F1029">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G1029" t="s">
         <v>6987</v>
@@ -57684,7 +57684,7 @@
         <v>6943</v>
       </c>
       <c r="F1031">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G1031" t="s">
         <v>6987</v>
@@ -58122,7 +58122,7 @@
         <v>6943</v>
       </c>
       <c r="F1052">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G1052" t="s">
         <v>6987</v>
@@ -58148,7 +58148,7 @@
         <v>6943</v>
       </c>
       <c r="F1053">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G1053" t="s">
         <v>6987</v>
@@ -58200,7 +58200,7 @@
         <v>6943</v>
       </c>
       <c r="F1055">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G1055" t="s">
         <v>6987</v>
@@ -58304,7 +58304,7 @@
         <v>6943</v>
       </c>
       <c r="F1059">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G1059" t="s">
         <v>6987</v>
@@ -58330,7 +58330,7 @@
         <v>6943</v>
       </c>
       <c r="F1060">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G1060" t="s">
         <v>6987</v>
@@ -58356,7 +58356,7 @@
         <v>6943</v>
       </c>
       <c r="F1061">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1061" t="s">
         <v>6987</v>
@@ -58408,7 +58408,7 @@
         <v>6943</v>
       </c>
       <c r="F1063">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G1063" t="s">
         <v>6987</v>
@@ -58512,7 +58512,7 @@
         <v>6943</v>
       </c>
       <c r="F1067">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G1067" t="s">
         <v>6987</v>
@@ -58636,7 +58636,7 @@
         <v>6956</v>
       </c>
       <c r="F1072">
-        <v>5122</v>
+        <v>5110</v>
       </c>
       <c r="G1072" t="s">
         <v>6987</v>
@@ -58662,7 +58662,7 @@
         <v>6956</v>
       </c>
       <c r="F1073">
-        <v>4391</v>
+        <v>4390</v>
       </c>
       <c r="G1073" t="s">
         <v>6987</v>
@@ -58688,7 +58688,7 @@
         <v>6956</v>
       </c>
       <c r="F1074">
-        <v>4380</v>
+        <v>4368</v>
       </c>
       <c r="G1074" t="s">
         <v>6987</v>
@@ -58881,7 +58881,7 @@
         <v>6943</v>
       </c>
       <c r="F1082">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="G1082" t="s">
         <v>6987</v>
@@ -58979,7 +58979,7 @@
         <v>6955</v>
       </c>
       <c r="F1086">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G1086" t="s">
         <v>6987</v>
@@ -59091,7 +59091,7 @@
         <v>6943</v>
       </c>
       <c r="F1091">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G1091" t="s">
         <v>6988</v>
@@ -59137,7 +59137,7 @@
         <v>6943</v>
       </c>
       <c r="F1093">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G1093" t="s">
         <v>6987</v>
@@ -59189,7 +59189,7 @@
         <v>6945</v>
       </c>
       <c r="F1095">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G1095" t="s">
         <v>6987</v>
@@ -59215,7 +59215,7 @@
         <v>6947</v>
       </c>
       <c r="F1096">
-        <v>7622</v>
+        <v>7602</v>
       </c>
       <c r="G1096" t="s">
         <v>6987</v>
@@ -59241,7 +59241,7 @@
         <v>6944</v>
       </c>
       <c r="F1097">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G1097" t="s">
         <v>6987</v>
@@ -59287,7 +59287,7 @@
         <v>6943</v>
       </c>
       <c r="F1099">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G1099" t="s">
         <v>6987</v>
@@ -59313,7 +59313,7 @@
         <v>6943</v>
       </c>
       <c r="F1100">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G1100" t="s">
         <v>6987</v>
@@ -59365,7 +59365,7 @@
         <v>6943</v>
       </c>
       <c r="F1102">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G1102" t="s">
         <v>6987</v>
@@ -59391,7 +59391,7 @@
         <v>6943</v>
       </c>
       <c r="F1103">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G1103" t="s">
         <v>6987</v>
@@ -59417,7 +59417,7 @@
         <v>6943</v>
       </c>
       <c r="F1104">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G1104" t="s">
         <v>6987</v>
@@ -59443,7 +59443,7 @@
         <v>6943</v>
       </c>
       <c r="F1105">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G1105" t="s">
         <v>6987</v>
@@ -59495,7 +59495,7 @@
         <v>6943</v>
       </c>
       <c r="F1107">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="G1107" t="s">
         <v>6987</v>
@@ -60159,7 +60159,7 @@
         <v>6972</v>
       </c>
       <c r="F1136">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="G1136" t="s">
         <v>6987</v>
@@ -60389,7 +60389,7 @@
         <v>6945</v>
       </c>
       <c r="F1146">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="G1146" t="s">
         <v>6987</v>
@@ -60441,7 +60441,7 @@
         <v>6956</v>
       </c>
       <c r="F1148">
-        <v>12408</v>
+        <v>12376</v>
       </c>
       <c r="G1148" t="s">
         <v>6987</v>
@@ -60507,7 +60507,7 @@
         <v>6963</v>
       </c>
       <c r="F1151">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="G1151" t="s">
         <v>6987</v>
@@ -60533,7 +60533,7 @@
         <v>6963</v>
       </c>
       <c r="F1152">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="G1152" t="s">
         <v>6987</v>
@@ -60915,7 +60915,7 @@
         <v>6943</v>
       </c>
       <c r="F1169">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G1169" t="s">
         <v>6987</v>
@@ -60967,7 +60967,7 @@
         <v>6943</v>
       </c>
       <c r="F1171">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1171" t="s">
         <v>6987</v>
@@ -61013,7 +61013,7 @@
         <v>6943</v>
       </c>
       <c r="F1173">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G1173" t="s">
         <v>6987</v>
@@ -61039,7 +61039,7 @@
         <v>6943</v>
       </c>
       <c r="F1174">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G1174" t="s">
         <v>6987</v>
@@ -61117,7 +61117,7 @@
         <v>6943</v>
       </c>
       <c r="F1177">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G1177" t="s">
         <v>6987</v>
@@ -61169,7 +61169,7 @@
         <v>6943</v>
       </c>
       <c r="F1179">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G1179" t="s">
         <v>6987</v>
@@ -61221,7 +61221,7 @@
         <v>6943</v>
       </c>
       <c r="F1181">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G1181" t="s">
         <v>6987</v>
@@ -61247,7 +61247,7 @@
         <v>6943</v>
       </c>
       <c r="F1182">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G1182" t="s">
         <v>6987</v>
@@ -61293,7 +61293,7 @@
         <v>6944</v>
       </c>
       <c r="F1184">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G1184" t="s">
         <v>6988</v>
@@ -61417,7 +61417,7 @@
         <v>6950</v>
       </c>
       <c r="F1189">
-        <v>608</v>
+        <v>492</v>
       </c>
       <c r="G1189" t="s">
         <v>6987</v>
@@ -61625,7 +61625,7 @@
         <v>6950</v>
       </c>
       <c r="F1197">
-        <v>580</v>
+        <v>416</v>
       </c>
       <c r="G1197" t="s">
         <v>6987</v>
@@ -61671,7 +61671,7 @@
         <v>6950</v>
       </c>
       <c r="F1199">
-        <v>339</v>
+        <v>175</v>
       </c>
       <c r="G1199" t="s">
         <v>6987</v>
@@ -61697,7 +61697,7 @@
         <v>6950</v>
       </c>
       <c r="F1200">
-        <v>646</v>
+        <v>490</v>
       </c>
       <c r="G1200" t="s">
         <v>6987</v>
@@ -61749,7 +61749,7 @@
         <v>6950</v>
       </c>
       <c r="F1202">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="G1202" t="s">
         <v>6987</v>
@@ -62127,7 +62127,7 @@
         <v>6950</v>
       </c>
       <c r="F1217">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G1217" t="s">
         <v>6987</v>
@@ -62369,7 +62369,7 @@
         <v>6972</v>
       </c>
       <c r="F1227">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="G1227" t="s">
         <v>6987</v>
@@ -62395,7 +62395,7 @@
         <v>6972</v>
       </c>
       <c r="F1228">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="G1228" t="s">
         <v>6987</v>
@@ -62421,7 +62421,7 @@
         <v>6972</v>
       </c>
       <c r="F1229">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G1229" t="s">
         <v>6987</v>
@@ -62447,7 +62447,7 @@
         <v>6972</v>
       </c>
       <c r="F1230">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="G1230" t="s">
         <v>6987</v>
@@ -62473,7 +62473,7 @@
         <v>6972</v>
       </c>
       <c r="F1231">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G1231" t="s">
         <v>6987</v>
@@ -62499,7 +62499,7 @@
         <v>6972</v>
       </c>
       <c r="F1232">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="G1232" t="s">
         <v>6987</v>
@@ -62551,7 +62551,7 @@
         <v>6972</v>
       </c>
       <c r="F1234">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="G1234" t="s">
         <v>6987</v>
@@ -62577,7 +62577,7 @@
         <v>6972</v>
       </c>
       <c r="F1235">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G1235" t="s">
         <v>6987</v>
@@ -62603,7 +62603,7 @@
         <v>6972</v>
       </c>
       <c r="F1236">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G1236" t="s">
         <v>6987</v>
@@ -62629,7 +62629,7 @@
         <v>6972</v>
       </c>
       <c r="F1237">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="G1237" t="s">
         <v>6987</v>
@@ -62655,7 +62655,7 @@
         <v>6972</v>
       </c>
       <c r="F1238">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G1238" t="s">
         <v>6987</v>
@@ -62707,7 +62707,7 @@
         <v>6972</v>
       </c>
       <c r="F1240">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G1240" t="s">
         <v>6987</v>
@@ -62733,7 +62733,7 @@
         <v>6972</v>
       </c>
       <c r="F1241">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G1241" t="s">
         <v>6987</v>
@@ -62811,7 +62811,7 @@
         <v>6972</v>
       </c>
       <c r="F1244">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G1244" t="s">
         <v>6987</v>
@@ -62837,7 +62837,7 @@
         <v>6972</v>
       </c>
       <c r="F1245">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="G1245" t="s">
         <v>6987</v>
@@ -62883,7 +62883,7 @@
         <v>6943</v>
       </c>
       <c r="F1247">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G1247" t="s">
         <v>6987</v>
@@ -62909,7 +62909,7 @@
         <v>6979</v>
       </c>
       <c r="F1248">
-        <v>341</v>
+        <v>281</v>
       </c>
       <c r="G1248" t="s">
         <v>6987</v>
@@ -62935,7 +62935,7 @@
         <v>6979</v>
       </c>
       <c r="F1249">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G1249" t="s">
         <v>6987</v>
@@ -63163,7 +63163,7 @@
         <v>6972</v>
       </c>
       <c r="F1258">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="G1258" t="s">
         <v>6987</v>
@@ -63215,7 +63215,7 @@
         <v>6972</v>
       </c>
       <c r="F1260">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G1260" t="s">
         <v>6987</v>
@@ -63553,7 +63553,7 @@
         <v>6972</v>
       </c>
       <c r="F1273">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G1273" t="s">
         <v>6987</v>
@@ -63631,7 +63631,7 @@
         <v>6956</v>
       </c>
       <c r="F1276">
-        <v>5488</v>
+        <v>5476</v>
       </c>
       <c r="G1276" t="s">
         <v>6987</v>
@@ -63657,7 +63657,7 @@
         <v>6956</v>
       </c>
       <c r="F1277">
-        <v>5490</v>
+        <v>5478</v>
       </c>
       <c r="G1277" t="s">
         <v>6987</v>
@@ -63683,7 +63683,7 @@
         <v>6956</v>
       </c>
       <c r="F1278">
-        <v>6569</v>
+        <v>6553</v>
       </c>
       <c r="G1278" t="s">
         <v>6987</v>
@@ -63709,7 +63709,7 @@
         <v>6956</v>
       </c>
       <c r="F1279">
-        <v>6978</v>
+        <v>6966</v>
       </c>
       <c r="G1279" t="s">
         <v>6987</v>
@@ -63735,7 +63735,7 @@
         <v>6956</v>
       </c>
       <c r="F1280">
-        <v>6978</v>
+        <v>6966</v>
       </c>
       <c r="G1280" t="s">
         <v>6987</v>
@@ -63977,7 +63977,7 @@
         <v>6946</v>
       </c>
       <c r="F1290">
-        <v>7525</v>
+        <v>7453</v>
       </c>
       <c r="G1290" t="s">
         <v>6987</v>
@@ -64029,7 +64029,7 @@
         <v>6979</v>
       </c>
       <c r="F1292">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="G1292" t="s">
         <v>6987</v>
@@ -65069,7 +65069,7 @@
         <v>6962</v>
       </c>
       <c r="F1341">
-        <v>3605</v>
+        <v>3593</v>
       </c>
       <c r="G1341" t="s">
         <v>6987</v>
@@ -65155,7 +65155,7 @@
         <v>6959</v>
       </c>
       <c r="F1345">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="G1345" t="s">
         <v>6987</v>
@@ -65181,7 +65181,7 @@
         <v>6959</v>
       </c>
       <c r="F1346">
-        <v>1941</v>
+        <v>1929</v>
       </c>
       <c r="G1346" t="s">
         <v>6987</v>
@@ -65285,7 +65285,7 @@
         <v>6959</v>
       </c>
       <c r="F1350">
-        <v>1132</v>
+        <v>1108</v>
       </c>
       <c r="G1350" t="s">
         <v>6987</v>
@@ -65311,7 +65311,7 @@
         <v>6959</v>
       </c>
       <c r="F1351">
-        <v>1289</v>
+        <v>1247</v>
       </c>
       <c r="G1351" t="s">
         <v>6987</v>
@@ -66597,7 +66597,7 @@
         <v>6943</v>
       </c>
       <c r="F1403">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G1403" t="s">
         <v>6987</v>
@@ -66649,7 +66649,7 @@
         <v>6943</v>
       </c>
       <c r="F1405">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G1405" t="s">
         <v>6987</v>
@@ -66701,7 +66701,7 @@
         <v>6943</v>
       </c>
       <c r="F1407">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G1407" t="s">
         <v>6987</v>
@@ -66727,7 +66727,7 @@
         <v>6943</v>
       </c>
       <c r="F1408">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G1408" t="s">
         <v>6987</v>
@@ -67599,7 +67599,7 @@
         <v>6982</v>
       </c>
       <c r="F1448">
-        <v>5419</v>
+        <v>5094</v>
       </c>
       <c r="G1448" t="s">
         <v>6987</v>
@@ -67651,7 +67651,7 @@
         <v>6982</v>
       </c>
       <c r="F1450">
-        <v>5718</v>
+        <v>5574</v>
       </c>
       <c r="G1450" t="s">
         <v>6987</v>
@@ -67677,7 +67677,7 @@
         <v>6982</v>
       </c>
       <c r="F1451">
-        <v>4410</v>
+        <v>4158</v>
       </c>
       <c r="G1451" t="s">
         <v>6987</v>
@@ -67703,7 +67703,7 @@
         <v>6982</v>
       </c>
       <c r="F1452">
-        <v>4608</v>
+        <v>4536</v>
       </c>
       <c r="G1452" t="s">
         <v>6987</v>
@@ -67729,7 +67729,7 @@
         <v>6982</v>
       </c>
       <c r="F1453">
-        <v>2414</v>
+        <v>2306</v>
       </c>
       <c r="G1453" t="s">
         <v>6987</v>
@@ -67937,7 +67937,7 @@
         <v>6982</v>
       </c>
       <c r="F1461">
-        <v>3075</v>
+        <v>3039</v>
       </c>
       <c r="G1461" t="s">
         <v>6987</v>
@@ -68015,7 +68015,7 @@
         <v>6959</v>
       </c>
       <c r="F1464">
-        <v>4656</v>
+        <v>4616</v>
       </c>
       <c r="G1464" t="s">
         <v>6987</v>
@@ -68041,7 +68041,7 @@
         <v>6959</v>
       </c>
       <c r="F1465">
-        <v>2479</v>
+        <v>2449</v>
       </c>
       <c r="G1465" t="s">
         <v>6987</v>
@@ -68223,7 +68223,7 @@
         <v>6983</v>
       </c>
       <c r="F1472">
-        <v>1323</v>
+        <v>1259</v>
       </c>
       <c r="G1472" t="s">
         <v>6987</v>
@@ -68249,7 +68249,7 @@
         <v>6983</v>
       </c>
       <c r="F1473">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="G1473" t="s">
         <v>6987</v>
@@ -68275,7 +68275,7 @@
         <v>6983</v>
       </c>
       <c r="F1474">
-        <v>2115</v>
+        <v>2083</v>
       </c>
       <c r="G1474" t="s">
         <v>6987</v>
@@ -68301,7 +68301,7 @@
         <v>6983</v>
       </c>
       <c r="F1475">
-        <v>1879</v>
+        <v>1855</v>
       </c>
       <c r="G1475" t="s">
         <v>6987</v>
@@ -68327,7 +68327,7 @@
         <v>6983</v>
       </c>
       <c r="F1476">
-        <v>1609</v>
+        <v>1585</v>
       </c>
       <c r="G1476" t="s">
         <v>6987</v>
@@ -68353,7 +68353,7 @@
         <v>6983</v>
       </c>
       <c r="F1477">
-        <v>2025</v>
+        <v>1993</v>
       </c>
       <c r="G1477" t="s">
         <v>6987</v>
@@ -68457,7 +68457,7 @@
         <v>6959</v>
       </c>
       <c r="F1481">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G1481" t="s">
         <v>6987</v>
@@ -68821,7 +68821,7 @@
         <v>6959</v>
       </c>
       <c r="F1495">
-        <v>3111</v>
+        <v>3091</v>
       </c>
       <c r="G1495" t="s">
         <v>6987</v>
@@ -68847,7 +68847,7 @@
         <v>6959</v>
       </c>
       <c r="F1496">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="G1496" t="s">
         <v>6987</v>
@@ -68977,7 +68977,7 @@
         <v>6959</v>
       </c>
       <c r="F1501">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="G1501" t="s">
         <v>6987</v>
@@ -69629,7 +69629,7 @@
         <v>6950</v>
       </c>
       <c r="F1527">
-        <v>5577</v>
+        <v>5565</v>
       </c>
       <c r="G1527" t="s">
         <v>6987</v>
@@ -70097,7 +70097,7 @@
         <v>6983</v>
       </c>
       <c r="F1545">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G1545" t="s">
         <v>6987</v>
@@ -70149,7 +70149,7 @@
         <v>6950</v>
       </c>
       <c r="F1547">
-        <v>10310</v>
+        <v>10298</v>
       </c>
       <c r="G1547" t="s">
         <v>6987</v>
@@ -70175,7 +70175,7 @@
         <v>6950</v>
       </c>
       <c r="F1548">
-        <v>1867</v>
+        <v>1855</v>
       </c>
       <c r="G1548" t="s">
         <v>6987</v>
@@ -70357,7 +70357,7 @@
         <v>6983</v>
       </c>
       <c r="F1555">
-        <v>2207</v>
+        <v>2175</v>
       </c>
       <c r="G1555" t="s">
         <v>6987</v>
@@ -70409,7 +70409,7 @@
         <v>6983</v>
       </c>
       <c r="F1557">
-        <v>3595</v>
+        <v>3571</v>
       </c>
       <c r="G1557" t="s">
         <v>6987</v>
@@ -70435,7 +70435,7 @@
         <v>6983</v>
       </c>
       <c r="F1558">
-        <v>3614</v>
+        <v>3590</v>
       </c>
       <c r="G1558" t="s">
         <v>6987</v>
@@ -70461,7 +70461,7 @@
         <v>6983</v>
       </c>
       <c r="F1559">
-        <v>1040</v>
+        <v>1016</v>
       </c>
       <c r="G1559" t="s">
         <v>6987</v>
@@ -70487,7 +70487,7 @@
         <v>6983</v>
       </c>
       <c r="F1560">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="G1560" t="s">
         <v>6987</v>
@@ -70513,7 +70513,7 @@
         <v>6983</v>
       </c>
       <c r="F1561">
-        <v>2054</v>
+        <v>2022</v>
       </c>
       <c r="G1561" t="s">
         <v>6987</v>
@@ -70565,7 +70565,7 @@
         <v>6983</v>
       </c>
       <c r="F1563">
-        <v>4299</v>
+        <v>4284</v>
       </c>
       <c r="G1563" t="s">
         <v>6987</v>
@@ -70773,7 +70773,7 @@
         <v>6950</v>
       </c>
       <c r="F1571">
-        <v>1959</v>
+        <v>1947</v>
       </c>
       <c r="G1571" t="s">
         <v>6987</v>
@@ -71007,7 +71007,7 @@
         <v>6950</v>
       </c>
       <c r="F1580">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="G1580" t="s">
         <v>6987</v>
@@ -71033,7 +71033,7 @@
         <v>6950</v>
       </c>
       <c r="F1581">
-        <v>7533</v>
+        <v>7509</v>
       </c>
       <c r="G1581" t="s">
         <v>6987</v>
@@ -71345,7 +71345,7 @@
         <v>6950</v>
       </c>
       <c r="F1593">
-        <v>2409</v>
+        <v>2397</v>
       </c>
       <c r="G1593" t="s">
         <v>6987</v>
@@ -71423,7 +71423,7 @@
         <v>6947</v>
       </c>
       <c r="F1596">
-        <v>9337</v>
+        <v>9293</v>
       </c>
       <c r="G1596" t="s">
         <v>6987</v>
@@ -71599,7 +71599,7 @@
         <v>6966</v>
       </c>
       <c r="F1603">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="G1603" t="s">
         <v>6987</v>
@@ -71651,7 +71651,7 @@
         <v>6966</v>
       </c>
       <c r="F1605">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G1605" t="s">
         <v>6987</v>
@@ -71703,7 +71703,7 @@
         <v>6967</v>
       </c>
       <c r="F1607">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G1607" t="s">
         <v>6987</v>
@@ -71781,7 +71781,7 @@
         <v>6947</v>
       </c>
       <c r="F1610">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G1610" t="s">
         <v>6987</v>
@@ -71833,7 +71833,7 @@
         <v>6945</v>
       </c>
       <c r="F1612">
-        <v>2838</v>
+        <v>2808</v>
       </c>
       <c r="G1612" t="s">
         <v>6987</v>
@@ -71859,7 +71859,7 @@
         <v>6945</v>
       </c>
       <c r="F1613">
-        <v>2029</v>
+        <v>1949</v>
       </c>
       <c r="G1613" t="s">
         <v>6987</v>
@@ -71885,7 +71885,7 @@
         <v>6945</v>
       </c>
       <c r="F1614">
-        <v>1995</v>
+        <v>1963</v>
       </c>
       <c r="G1614" t="s">
         <v>6987</v>
@@ -72015,7 +72015,7 @@
         <v>6945</v>
       </c>
       <c r="F1619">
-        <v>2046</v>
+        <v>2016</v>
       </c>
       <c r="G1619" t="s">
         <v>6987</v>
@@ -72093,7 +72093,7 @@
         <v>6945</v>
       </c>
       <c r="F1622">
-        <v>17945</v>
+        <v>17879</v>
       </c>
       <c r="G1622" t="s">
         <v>6987</v>
@@ -72197,7 +72197,7 @@
         <v>6968</v>
       </c>
       <c r="F1626">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G1626" t="s">
         <v>6987</v>
@@ -72439,7 +72439,7 @@
         <v>6966</v>
       </c>
       <c r="F1636">
-        <v>1989</v>
+        <v>1973</v>
       </c>
       <c r="G1636" t="s">
         <v>6987</v>
@@ -72517,7 +72517,7 @@
         <v>6966</v>
       </c>
       <c r="F1639">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G1639" t="s">
         <v>6987</v>
@@ -72543,7 +72543,7 @@
         <v>6966</v>
       </c>
       <c r="F1640">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="G1640" t="s">
         <v>6987</v>
@@ -72621,7 +72621,7 @@
         <v>6966</v>
       </c>
       <c r="F1643">
-        <v>1022</v>
+        <v>998</v>
       </c>
       <c r="G1643" t="s">
         <v>6987</v>
@@ -72647,7 +72647,7 @@
         <v>6966</v>
       </c>
       <c r="F1644">
-        <v>1066</v>
+        <v>1036</v>
       </c>
       <c r="G1644" t="s">
         <v>6987</v>
@@ -72673,7 +72673,7 @@
         <v>6966</v>
       </c>
       <c r="F1645">
-        <v>10069</v>
+        <v>10033</v>
       </c>
       <c r="G1645" t="s">
         <v>6987</v>
@@ -72699,7 +72699,7 @@
         <v>6966</v>
       </c>
       <c r="F1646">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="G1646" t="s">
         <v>6987</v>
@@ -72725,7 +72725,7 @@
         <v>6966</v>
       </c>
       <c r="F1647">
-        <v>1810</v>
+        <v>1780</v>
       </c>
       <c r="G1647" t="s">
         <v>6987</v>
@@ -72907,7 +72907,7 @@
         <v>6968</v>
       </c>
       <c r="F1654">
-        <v>4482</v>
+        <v>4476</v>
       </c>
       <c r="G1654" t="s">
         <v>6987</v>
@@ -72933,7 +72933,7 @@
         <v>6968</v>
       </c>
       <c r="F1655">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G1655" t="s">
         <v>6987</v>
@@ -73083,7 +73083,7 @@
         <v>6945</v>
       </c>
       <c r="F1661">
-        <v>23194</v>
+        <v>22990</v>
       </c>
       <c r="G1661" t="s">
         <v>6987</v>
@@ -73403,7 +73403,7 @@
         <v>6946</v>
       </c>
       <c r="F1674">
-        <v>54920</v>
+        <v>54565</v>
       </c>
       <c r="G1674" t="s">
         <v>6987</v>
@@ -73429,7 +73429,7 @@
         <v>6946</v>
       </c>
       <c r="F1675">
-        <v>8990</v>
+        <v>8942</v>
       </c>
       <c r="G1675" t="s">
         <v>6987</v>
@@ -73507,7 +73507,7 @@
         <v>6984</v>
       </c>
       <c r="F1678">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G1678" t="s">
         <v>6987</v>
@@ -73533,7 +73533,7 @@
         <v>6984</v>
       </c>
       <c r="F1679">
-        <v>2651</v>
+        <v>2627</v>
       </c>
       <c r="G1679" t="s">
         <v>6987</v>
@@ -73559,7 +73559,7 @@
         <v>6984</v>
       </c>
       <c r="F1680">
-        <v>1823</v>
+        <v>1787</v>
       </c>
       <c r="G1680" t="s">
         <v>6987</v>
@@ -73611,7 +73611,7 @@
         <v>6946</v>
       </c>
       <c r="F1682">
-        <v>2616</v>
+        <v>2536</v>
       </c>
       <c r="G1682" t="s">
         <v>6987</v>
@@ -73637,7 +73637,7 @@
         <v>6946</v>
       </c>
       <c r="F1683">
-        <v>3335</v>
+        <v>3295</v>
       </c>
       <c r="G1683" t="s">
         <v>6987</v>
@@ -73663,7 +73663,7 @@
         <v>6946</v>
       </c>
       <c r="F1684">
-        <v>2206</v>
+        <v>2176</v>
       </c>
       <c r="G1684" t="s">
         <v>6987</v>
@@ -73767,7 +73767,7 @@
         <v>6984</v>
       </c>
       <c r="F1688">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="G1688" t="s">
         <v>6987</v>
@@ -73819,7 +73819,7 @@
         <v>6984</v>
       </c>
       <c r="F1690">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G1690" t="s">
         <v>6987</v>
@@ -73871,7 +73871,7 @@
         <v>6979</v>
       </c>
       <c r="F1692">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="G1692" t="s">
         <v>6987</v>
@@ -74651,7 +74651,7 @@
         <v>6960</v>
       </c>
       <c r="F1722">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G1722" t="s">
         <v>6987</v>
@@ -74729,7 +74729,7 @@
         <v>6960</v>
       </c>
       <c r="F1725">
-        <v>2673</v>
+        <v>2667</v>
       </c>
       <c r="G1725" t="s">
         <v>6987</v>
@@ -74755,7 +74755,7 @@
         <v>6960</v>
       </c>
       <c r="F1726">
-        <v>2790</v>
+        <v>2784</v>
       </c>
       <c r="G1726" t="s">
         <v>6987</v>
@@ -74781,7 +74781,7 @@
         <v>6960</v>
       </c>
       <c r="F1727">
-        <v>3996</v>
+        <v>3990</v>
       </c>
       <c r="G1727" t="s">
         <v>6987</v>
@@ -74807,7 +74807,7 @@
         <v>6960</v>
       </c>
       <c r="F1728">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="G1728" t="s">
         <v>6987</v>
@@ -74833,7 +74833,7 @@
         <v>6960</v>
       </c>
       <c r="F1729">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="G1729" t="s">
         <v>6987</v>
@@ -74937,7 +74937,7 @@
         <v>6960</v>
       </c>
       <c r="F1733">
-        <v>3414</v>
+        <v>3402</v>
       </c>
       <c r="G1733" t="s">
         <v>6987</v>
@@ -75317,7 +75317,7 @@
         <v>6960</v>
       </c>
       <c r="F1749">
-        <v>2621</v>
+        <v>2585</v>
       </c>
       <c r="G1749" t="s">
         <v>6987</v>
@@ -75343,7 +75343,7 @@
         <v>6960</v>
       </c>
       <c r="F1750">
-        <v>5366</v>
+        <v>5348</v>
       </c>
       <c r="G1750" t="s">
         <v>6987</v>
@@ -75369,7 +75369,7 @@
         <v>6960</v>
       </c>
       <c r="F1751">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G1751" t="s">
         <v>6987</v>
@@ -75395,7 +75395,7 @@
         <v>6960</v>
       </c>
       <c r="F1752">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G1752" t="s">
         <v>6987</v>
@@ -75473,7 +75473,7 @@
         <v>6960</v>
       </c>
       <c r="F1755">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="G1755" t="s">
         <v>6987</v>
@@ -75551,7 +75551,7 @@
         <v>6960</v>
       </c>
       <c r="F1758">
-        <v>1342</v>
+        <v>1306</v>
       </c>
       <c r="G1758" t="s">
         <v>6987</v>
@@ -75603,7 +75603,7 @@
         <v>6960</v>
       </c>
       <c r="F1760">
-        <v>1275</v>
+        <v>1238</v>
       </c>
       <c r="G1760" t="s">
         <v>6987</v>
@@ -75629,7 +75629,7 @@
         <v>6960</v>
       </c>
       <c r="F1761">
-        <v>2866</v>
+        <v>2854</v>
       </c>
       <c r="G1761" t="s">
         <v>6987</v>
@@ -75655,7 +75655,7 @@
         <v>6960</v>
       </c>
       <c r="F1762">
-        <v>3548</v>
+        <v>3518</v>
       </c>
       <c r="G1762" t="s">
         <v>6987</v>
@@ -75681,7 +75681,7 @@
         <v>6960</v>
       </c>
       <c r="F1763">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="G1763" t="s">
         <v>6987</v>
@@ -76331,7 +76331,7 @@
         <v>6981</v>
       </c>
       <c r="F1788">
-        <v>987</v>
+        <v>963</v>
       </c>
       <c r="G1788" t="s">
         <v>6987</v>
@@ -76409,7 +76409,7 @@
         <v>6981</v>
       </c>
       <c r="F1791">
-        <v>2480</v>
+        <v>2468</v>
       </c>
       <c r="G1791" t="s">
         <v>6987</v>
@@ -76435,7 +76435,7 @@
         <v>6981</v>
       </c>
       <c r="F1792">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="G1792" t="s">
         <v>6987</v>
@@ -76865,7 +76865,7 @@
         <v>6981</v>
       </c>
       <c r="F1809">
-        <v>1405</v>
+        <v>1393</v>
       </c>
       <c r="G1809" t="s">
         <v>6987</v>
@@ -78629,7 +78629,7 @@
         <v>6973</v>
       </c>
       <c r="F1878">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G1878" t="s">
         <v>6987</v>
@@ -78785,7 +78785,7 @@
         <v>6973</v>
       </c>
       <c r="F1884">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="G1884" t="s">
         <v>6987</v>
@@ -79253,7 +79253,7 @@
         <v>6973</v>
       </c>
       <c r="F1902">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G1902" t="s">
         <v>6987</v>
@@ -79325,7 +79325,7 @@
         <v>6973</v>
       </c>
       <c r="F1905">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G1905" t="s">
         <v>6988</v>
@@ -79365,7 +79365,7 @@
         <v>6973</v>
       </c>
       <c r="F1907">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G1907" t="s">
         <v>6988</v>
@@ -79587,7 +79587,7 @@
         <v>6943</v>
       </c>
       <c r="F1916">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="G1916" t="s">
         <v>6987</v>
@@ -80009,7 +80009,7 @@
         <v>6961</v>
       </c>
       <c r="F1935">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="G1935" t="s">
         <v>6987</v>
@@ -80061,7 +80061,7 @@
         <v>6943</v>
       </c>
       <c r="F1937">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G1937" t="s">
         <v>6987</v>
@@ -80087,7 +80087,7 @@
         <v>6943</v>
       </c>
       <c r="F1938">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G1938" t="s">
         <v>6987</v>
@@ -80113,7 +80113,7 @@
         <v>6943</v>
       </c>
       <c r="F1939">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="G1939" t="s">
         <v>6987</v>
@@ -80165,7 +80165,7 @@
         <v>6943</v>
       </c>
       <c r="F1941">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="G1941" t="s">
         <v>6987</v>
@@ -80217,7 +80217,7 @@
         <v>6961</v>
       </c>
       <c r="F1943">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G1943" t="s">
         <v>6987</v>
@@ -80243,7 +80243,7 @@
         <v>6961</v>
       </c>
       <c r="F1944">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="G1944" t="s">
         <v>6987</v>
@@ -80269,7 +80269,7 @@
         <v>6944</v>
       </c>
       <c r="F1945">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G1945" t="s">
         <v>6987</v>
@@ -80321,7 +80321,7 @@
         <v>6944</v>
       </c>
       <c r="F1947">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G1947" t="s">
         <v>6987</v>
@@ -80347,7 +80347,7 @@
         <v>6944</v>
       </c>
       <c r="F1948">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G1948" t="s">
         <v>6987</v>
@@ -80373,7 +80373,7 @@
         <v>6944</v>
       </c>
       <c r="F1949">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G1949" t="s">
         <v>6987</v>
@@ -80399,7 +80399,7 @@
         <v>6944</v>
       </c>
       <c r="F1950">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G1950" t="s">
         <v>6987</v>
@@ -80549,7 +80549,7 @@
         <v>6961</v>
       </c>
       <c r="F1956">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="G1956" t="s">
         <v>6987</v>
@@ -80833,7 +80833,7 @@
         <v>6944</v>
       </c>
       <c r="F1969">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="G1969" t="s">
         <v>6987</v>
@@ -80859,7 +80859,7 @@
         <v>6944</v>
       </c>
       <c r="F1970">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="G1970" t="s">
         <v>6987</v>
@@ -80885,7 +80885,7 @@
         <v>6944</v>
       </c>
       <c r="F1971">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G1971" t="s">
         <v>6987</v>
@@ -80911,7 +80911,7 @@
         <v>6944</v>
       </c>
       <c r="F1972">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G1972" t="s">
         <v>6987</v>
@@ -80937,7 +80937,7 @@
         <v>6944</v>
       </c>
       <c r="F1973">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G1973" t="s">
         <v>6987</v>
@@ -80963,7 +80963,7 @@
         <v>6944</v>
       </c>
       <c r="F1974">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G1974" t="s">
         <v>6987</v>
@@ -81327,7 +81327,7 @@
         <v>6944</v>
       </c>
       <c r="F1991">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G1991" t="s">
         <v>6987</v>
@@ -81379,7 +81379,7 @@
         <v>6952</v>
       </c>
       <c r="F1993">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="G1993" t="s">
         <v>6987</v>
@@ -81405,7 +81405,7 @@
         <v>6961</v>
       </c>
       <c r="F1994">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G1994" t="s">
         <v>6987</v>
@@ -81457,7 +81457,7 @@
         <v>6961</v>
       </c>
       <c r="F1996">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="G1996" t="s">
         <v>6987</v>
@@ -81483,7 +81483,7 @@
         <v>6961</v>
       </c>
       <c r="F1997">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="G1997" t="s">
         <v>6987</v>
@@ -81535,7 +81535,7 @@
         <v>6952</v>
       </c>
       <c r="F1999">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="G1999" t="s">
         <v>6987</v>
@@ -81561,7 +81561,7 @@
         <v>6952</v>
       </c>
       <c r="F2000">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="G2000" t="s">
         <v>6987</v>
@@ -81587,7 +81587,7 @@
         <v>6952</v>
       </c>
       <c r="F2001">
-        <v>2086</v>
+        <v>2044</v>
       </c>
       <c r="G2001" t="s">
         <v>6987</v>
@@ -81613,7 +81613,7 @@
         <v>6952</v>
       </c>
       <c r="F2002">
-        <v>1970</v>
+        <v>1922</v>
       </c>
       <c r="G2002" t="s">
         <v>6987</v>
@@ -81639,7 +81639,7 @@
         <v>6952</v>
       </c>
       <c r="F2003">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="G2003" t="s">
         <v>6987</v>
@@ -81691,7 +81691,7 @@
         <v>6944</v>
       </c>
       <c r="F2005">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2005" t="s">
         <v>6987</v>
@@ -81717,7 +81717,7 @@
         <v>6952</v>
       </c>
       <c r="F2006">
-        <v>1540</v>
+        <v>1510</v>
       </c>
       <c r="G2006" t="s">
         <v>6987</v>
@@ -81743,7 +81743,7 @@
         <v>6952</v>
       </c>
       <c r="F2007">
-        <v>1640</v>
+        <v>1610</v>
       </c>
       <c r="G2007" t="s">
         <v>6987</v>
@@ -81881,7 +81881,7 @@
         <v>6943</v>
       </c>
       <c r="F2013">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G2013" t="s">
         <v>6987</v>
@@ -81907,7 +81907,7 @@
         <v>6943</v>
       </c>
       <c r="F2014">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="G2014" t="s">
         <v>6987</v>
@@ -82135,7 +82135,7 @@
         <v>6943</v>
       </c>
       <c r="F2023">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="G2023" t="s">
         <v>6987</v>
@@ -82187,7 +82187,7 @@
         <v>6943</v>
       </c>
       <c r="F2025">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="G2025" t="s">
         <v>6987</v>
@@ -82343,7 +82343,7 @@
         <v>6943</v>
       </c>
       <c r="F2031">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G2031" t="s">
         <v>6987</v>
@@ -82369,7 +82369,7 @@
         <v>6943</v>
       </c>
       <c r="F2032">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="G2032" t="s">
         <v>6987</v>
@@ -83173,7 +83173,7 @@
         <v>6943</v>
       </c>
       <c r="F2065">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G2065" t="s">
         <v>6987</v>
@@ -83199,7 +83199,7 @@
         <v>6943</v>
       </c>
       <c r="F2066">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G2066" t="s">
         <v>6987</v>
@@ -85091,7 +85091,7 @@
         <v>6969</v>
       </c>
       <c r="F2142">
-        <v>2218</v>
+        <v>2214</v>
       </c>
       <c r="G2142" t="s">
         <v>6987</v>
@@ -85183,7 +85183,7 @@
         <v>6969</v>
       </c>
       <c r="F2146">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G2146" t="s">
         <v>6988</v>
@@ -85203,7 +85203,7 @@
         <v>6969</v>
       </c>
       <c r="F2147">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G2147" t="s">
         <v>6988</v>
@@ -85481,7 +85481,7 @@
         <v>6969</v>
       </c>
       <c r="F2160">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="G2160" t="s">
         <v>6987</v>
@@ -85507,7 +85507,7 @@
         <v>6969</v>
       </c>
       <c r="F2161">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G2161" t="s">
         <v>6987</v>
@@ -85619,7 +85619,7 @@
         <v>6969</v>
       </c>
       <c r="F2166">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G2166" t="s">
         <v>6987</v>
@@ -85697,7 +85697,7 @@
         <v>6969</v>
       </c>
       <c r="F2169">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G2169" t="s">
         <v>6987</v>
@@ -85749,7 +85749,7 @@
         <v>6969</v>
       </c>
       <c r="F2171">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="G2171" t="s">
         <v>6987</v>
@@ -85841,7 +85841,7 @@
         <v>6969</v>
       </c>
       <c r="F2175">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G2175" t="s">
         <v>6987</v>
@@ -85919,7 +85919,7 @@
         <v>6969</v>
       </c>
       <c r="F2178">
-        <v>2066</v>
+        <v>2058</v>
       </c>
       <c r="G2178" t="s">
         <v>6987</v>
@@ -85997,7 +85997,7 @@
         <v>6969</v>
       </c>
       <c r="F2181">
-        <v>15001</v>
+        <v>14801</v>
       </c>
       <c r="G2181" t="s">
         <v>6987</v>
@@ -86049,7 +86049,7 @@
         <v>6969</v>
       </c>
       <c r="F2183">
-        <v>1666</v>
+        <v>1631</v>
       </c>
       <c r="G2183" t="s">
         <v>6987</v>
@@ -86095,7 +86095,7 @@
         <v>6969</v>
       </c>
       <c r="F2185">
-        <v>1410</v>
+        <v>1400</v>
       </c>
       <c r="G2185" t="s">
         <v>6987</v>
@@ -86121,7 +86121,7 @@
         <v>6969</v>
       </c>
       <c r="F2186">
-        <v>1247</v>
+        <v>1217</v>
       </c>
       <c r="G2186" t="s">
         <v>6987</v>
@@ -86147,7 +86147,7 @@
         <v>6969</v>
       </c>
       <c r="F2187">
-        <v>7263</v>
+        <v>7250</v>
       </c>
       <c r="G2187" t="s">
         <v>6987</v>
@@ -86199,7 +86199,7 @@
         <v>6969</v>
       </c>
       <c r="F2189">
-        <v>836</v>
+        <v>801</v>
       </c>
       <c r="G2189" t="s">
         <v>6987</v>
@@ -86225,7 +86225,7 @@
         <v>6969</v>
       </c>
       <c r="F2190">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="G2190" t="s">
         <v>6987</v>
@@ -86251,7 +86251,7 @@
         <v>6969</v>
       </c>
       <c r="F2191">
-        <v>2276</v>
+        <v>2226</v>
       </c>
       <c r="G2191" t="s">
         <v>6987</v>
@@ -86435,7 +86435,7 @@
         <v>6969</v>
       </c>
       <c r="F2199">
-        <v>6007</v>
+        <v>5995</v>
       </c>
       <c r="G2199" t="s">
         <v>6987</v>
@@ -86645,7 +86645,7 @@
         <v>6969</v>
       </c>
       <c r="F2208">
-        <v>3094</v>
+        <v>3084</v>
       </c>
       <c r="G2208" t="s">
         <v>6987</v>
@@ -86717,7 +86717,7 @@
         <v>6944</v>
       </c>
       <c r="F2211">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G2211" t="s">
         <v>6987</v>
@@ -86895,7 +86895,7 @@
         <v>6961</v>
       </c>
       <c r="F2219">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G2219" t="s">
         <v>6988</v>
@@ -86967,7 +86967,7 @@
         <v>6961</v>
       </c>
       <c r="F2222">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G2222" t="s">
         <v>6987</v>
@@ -87071,7 +87071,7 @@
         <v>6952</v>
       </c>
       <c r="F2226">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G2226" t="s">
         <v>6987</v>
@@ -87735,7 +87735,7 @@
         <v>6943</v>
       </c>
       <c r="F2255">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G2255" t="s">
         <v>6987</v>
@@ -87787,7 +87787,7 @@
         <v>6943</v>
       </c>
       <c r="F2257">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G2257" t="s">
         <v>6987</v>
@@ -88061,7 +88061,7 @@
         <v>6943</v>
       </c>
       <c r="F2268">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="G2268" t="s">
         <v>6988</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -33283,7 +33283,7 @@
         <v>7102</v>
       </c>
       <c r="F31">
-        <v>7847</v>
+        <v>7763</v>
       </c>
       <c r="G31" t="s">
         <v>7143</v>
@@ -33309,7 +33309,7 @@
         <v>7101</v>
       </c>
       <c r="F32">
-        <v>10182</v>
+        <v>10068</v>
       </c>
       <c r="G32" t="s">
         <v>7143</v>
@@ -33841,7 +33841,7 @@
         <v>7105</v>
       </c>
       <c r="F58">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="G58" t="s">
         <v>7143</v>
@@ -33867,7 +33867,7 @@
         <v>7100</v>
       </c>
       <c r="F59">
-        <v>3222</v>
+        <v>3203</v>
       </c>
       <c r="G59" t="s">
         <v>7143</v>
@@ -33893,7 +33893,7 @@
         <v>7098</v>
       </c>
       <c r="F60">
-        <v>1434</v>
+        <v>1422</v>
       </c>
       <c r="G60" t="s">
         <v>7143</v>
@@ -33919,7 +33919,7 @@
         <v>7105</v>
       </c>
       <c r="F61">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="G61" t="s">
         <v>7143</v>
@@ -33945,7 +33945,7 @@
         <v>7106</v>
       </c>
       <c r="F62">
-        <v>1136</v>
+        <v>1126</v>
       </c>
       <c r="G62" t="s">
         <v>7143</v>
@@ -33971,7 +33971,7 @@
         <v>7106</v>
       </c>
       <c r="F63">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="G63" t="s">
         <v>7143</v>
@@ -33997,7 +33997,7 @@
         <v>7106</v>
       </c>
       <c r="F64">
-        <v>1167</v>
+        <v>1159</v>
       </c>
       <c r="G64" t="s">
         <v>7143</v>
@@ -34023,7 +34023,7 @@
         <v>7106</v>
       </c>
       <c r="F65">
-        <v>1100</v>
+        <v>1086</v>
       </c>
       <c r="G65" t="s">
         <v>7143</v>
@@ -34069,7 +34069,7 @@
         <v>7106</v>
       </c>
       <c r="F67">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="G67" t="s">
         <v>7143</v>
@@ -34115,7 +34115,7 @@
         <v>7106</v>
       </c>
       <c r="F69">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="G69" t="s">
         <v>7143</v>
@@ -34141,7 +34141,7 @@
         <v>7106</v>
       </c>
       <c r="F70">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="G70" t="s">
         <v>7143</v>
@@ -34167,7 +34167,7 @@
         <v>7106</v>
       </c>
       <c r="F71">
-        <v>945</v>
+        <v>935</v>
       </c>
       <c r="G71" t="s">
         <v>7143</v>
@@ -34193,7 +34193,7 @@
         <v>7106</v>
       </c>
       <c r="F72">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="G72" t="s">
         <v>7143</v>
@@ -34219,7 +34219,7 @@
         <v>7106</v>
       </c>
       <c r="F73">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="G73" t="s">
         <v>7143</v>
@@ -34245,7 +34245,7 @@
         <v>7106</v>
       </c>
       <c r="F74">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="G74" t="s">
         <v>7143</v>
@@ -34271,7 +34271,7 @@
         <v>7106</v>
       </c>
       <c r="F75">
-        <v>944</v>
+        <v>930</v>
       </c>
       <c r="G75" t="s">
         <v>7143</v>
@@ -34297,7 +34297,7 @@
         <v>7105</v>
       </c>
       <c r="F76">
-        <v>1417</v>
+        <v>1401</v>
       </c>
       <c r="G76" t="s">
         <v>7143</v>
@@ -34349,7 +34349,7 @@
         <v>7107</v>
       </c>
       <c r="F78">
-        <v>24084</v>
+        <v>24012</v>
       </c>
       <c r="G78" t="s">
         <v>7143</v>
@@ -34531,7 +34531,7 @@
         <v>7107</v>
       </c>
       <c r="F85">
-        <v>24060</v>
+        <v>23988</v>
       </c>
       <c r="G85" t="s">
         <v>7143</v>
@@ -34779,7 +34779,7 @@
         <v>7108</v>
       </c>
       <c r="F95">
-        <v>1992</v>
+        <v>1986</v>
       </c>
       <c r="G95" t="s">
         <v>7143</v>
@@ -34805,7 +34805,7 @@
         <v>7108</v>
       </c>
       <c r="F96">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="G96" t="s">
         <v>7143</v>
@@ -34987,7 +34987,7 @@
         <v>7108</v>
       </c>
       <c r="F103">
-        <v>1857</v>
+        <v>1854</v>
       </c>
       <c r="G103" t="s">
         <v>7143</v>
@@ -35481,7 +35481,7 @@
         <v>7108</v>
       </c>
       <c r="F122">
-        <v>3259</v>
+        <v>3256</v>
       </c>
       <c r="G122" t="s">
         <v>7143</v>
@@ -35559,7 +35559,7 @@
         <v>7108</v>
       </c>
       <c r="F125">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="G125" t="s">
         <v>7143</v>
@@ -35845,7 +35845,7 @@
         <v>7108</v>
       </c>
       <c r="F136">
-        <v>2537</v>
+        <v>2529</v>
       </c>
       <c r="G136" t="s">
         <v>7143</v>
@@ -35949,7 +35949,7 @@
         <v>7109</v>
       </c>
       <c r="F140">
-        <v>1548</v>
+        <v>1536</v>
       </c>
       <c r="G140" t="s">
         <v>7143</v>
@@ -35975,7 +35975,7 @@
         <v>7109</v>
       </c>
       <c r="F141">
-        <v>1619</v>
+        <v>1607</v>
       </c>
       <c r="G141" t="s">
         <v>7143</v>
@@ -36027,7 +36027,7 @@
         <v>7109</v>
       </c>
       <c r="F143">
-        <v>1560</v>
+        <v>1548</v>
       </c>
       <c r="G143" t="s">
         <v>7143</v>
@@ -36313,7 +36313,7 @@
         <v>7106</v>
       </c>
       <c r="F154">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G154" t="s">
         <v>7143</v>
@@ -36411,7 +36411,7 @@
         <v>7105</v>
       </c>
       <c r="F158">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G158" t="s">
         <v>7143</v>
@@ -36581,7 +36581,7 @@
         <v>7105</v>
       </c>
       <c r="F165">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G165" t="s">
         <v>7143</v>
@@ -36627,7 +36627,7 @@
         <v>7105</v>
       </c>
       <c r="F167">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="G167" t="s">
         <v>7143</v>
@@ -36673,7 +36673,7 @@
         <v>7105</v>
       </c>
       <c r="F169">
-        <v>1065</v>
+        <v>1043</v>
       </c>
       <c r="G169" t="s">
         <v>7143</v>
@@ -36699,7 +36699,7 @@
         <v>7105</v>
       </c>
       <c r="F170">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G170" t="s">
         <v>7143</v>
@@ -36745,7 +36745,7 @@
         <v>7105</v>
       </c>
       <c r="F172">
-        <v>781</v>
+        <v>757</v>
       </c>
       <c r="G172" t="s">
         <v>7143</v>
@@ -36771,7 +36771,7 @@
         <v>7105</v>
       </c>
       <c r="F173">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="G173" t="s">
         <v>7143</v>
@@ -36837,7 +36837,7 @@
         <v>7105</v>
       </c>
       <c r="F176">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="G176" t="s">
         <v>7143</v>
@@ -36863,7 +36863,7 @@
         <v>7106</v>
       </c>
       <c r="F177">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="G177" t="s">
         <v>7143</v>
@@ -36915,7 +36915,7 @@
         <v>7111</v>
       </c>
       <c r="F179">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="G179" t="s">
         <v>7143</v>
@@ -36941,7 +36941,7 @@
         <v>7111</v>
       </c>
       <c r="F180">
-        <v>1556</v>
+        <v>1544</v>
       </c>
       <c r="G180" t="s">
         <v>7143</v>
@@ -36993,7 +36993,7 @@
         <v>7111</v>
       </c>
       <c r="F182">
-        <v>1301</v>
+        <v>1281</v>
       </c>
       <c r="G182" t="s">
         <v>7143</v>
@@ -37019,7 +37019,7 @@
         <v>7111</v>
       </c>
       <c r="F183">
-        <v>1576</v>
+        <v>1560</v>
       </c>
       <c r="G183" t="s">
         <v>7143</v>
@@ -37045,7 +37045,7 @@
         <v>7111</v>
       </c>
       <c r="F184">
-        <v>1491</v>
+        <v>1479</v>
       </c>
       <c r="G184" t="s">
         <v>7143</v>
@@ -37071,7 +37071,7 @@
         <v>7106</v>
       </c>
       <c r="F185">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="G185" t="s">
         <v>7143</v>
@@ -37123,7 +37123,7 @@
         <v>7106</v>
       </c>
       <c r="F187">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="G187" t="s">
         <v>7143</v>
@@ -37149,7 +37149,7 @@
         <v>7110</v>
       </c>
       <c r="F188">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="G188" t="s">
         <v>7143</v>
@@ -37175,7 +37175,7 @@
         <v>7110</v>
       </c>
       <c r="F189">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="G189" t="s">
         <v>7143</v>
@@ -37201,7 +37201,7 @@
         <v>7110</v>
       </c>
       <c r="F190">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G190" t="s">
         <v>7143</v>
@@ -37227,7 +37227,7 @@
         <v>7106</v>
       </c>
       <c r="F191">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="G191" t="s">
         <v>7143</v>
@@ -37253,7 +37253,7 @@
         <v>7106</v>
       </c>
       <c r="F192">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="G192" t="s">
         <v>7143</v>
@@ -37789,7 +37789,7 @@
         <v>7106</v>
       </c>
       <c r="F214">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G214" t="s">
         <v>7143</v>
@@ -37815,7 +37815,7 @@
         <v>7105</v>
       </c>
       <c r="F215">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G215" t="s">
         <v>7143</v>
@@ -38257,7 +38257,7 @@
         <v>7113</v>
       </c>
       <c r="F232">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="G232" t="s">
         <v>7143</v>
@@ -38387,7 +38387,7 @@
         <v>7114</v>
       </c>
       <c r="F237">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="G237" t="s">
         <v>7143</v>
@@ -38517,7 +38517,7 @@
         <v>7105</v>
       </c>
       <c r="F242">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="G242" t="s">
         <v>7143</v>
@@ -38543,7 +38543,7 @@
         <v>7105</v>
       </c>
       <c r="F243">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="G243" t="s">
         <v>7143</v>
@@ -38595,7 +38595,7 @@
         <v>7105</v>
       </c>
       <c r="F245">
-        <v>1672</v>
+        <v>1666</v>
       </c>
       <c r="G245" t="s">
         <v>7143</v>
@@ -38621,7 +38621,7 @@
         <v>7105</v>
       </c>
       <c r="F246">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="G246" t="s">
         <v>7143</v>
@@ -38647,7 +38647,7 @@
         <v>7105</v>
       </c>
       <c r="F247">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="G247" t="s">
         <v>7143</v>
@@ -38673,7 +38673,7 @@
         <v>7105</v>
       </c>
       <c r="F248">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G248" t="s">
         <v>7143</v>
@@ -38699,7 +38699,7 @@
         <v>7105</v>
       </c>
       <c r="F249">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="G249" t="s">
         <v>7143</v>
@@ -38725,7 +38725,7 @@
         <v>7105</v>
       </c>
       <c r="F250">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="G250" t="s">
         <v>7143</v>
@@ -38751,7 +38751,7 @@
         <v>7105</v>
       </c>
       <c r="F251">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="G251" t="s">
         <v>7143</v>
@@ -38927,7 +38927,7 @@
         <v>7105</v>
       </c>
       <c r="F258">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G258" t="s">
         <v>7143</v>
@@ -38979,7 +38979,7 @@
         <v>7106</v>
       </c>
       <c r="F260">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G260" t="s">
         <v>7143</v>
@@ -39077,7 +39077,7 @@
         <v>7106</v>
       </c>
       <c r="F264">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G264" t="s">
         <v>7143</v>
@@ -39473,7 +39473,7 @@
         <v>7105</v>
       </c>
       <c r="F282">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G282" t="s">
         <v>7143</v>
@@ -39917,7 +39917,7 @@
         <v>7117</v>
       </c>
       <c r="F300">
-        <v>1866</v>
+        <v>1860</v>
       </c>
       <c r="G300" t="s">
         <v>7143</v>
@@ -39969,7 +39969,7 @@
         <v>7117</v>
       </c>
       <c r="F302">
-        <v>1836</v>
+        <v>1824</v>
       </c>
       <c r="G302" t="s">
         <v>7143</v>
@@ -39995,7 +39995,7 @@
         <v>7117</v>
       </c>
       <c r="F303">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="G303" t="s">
         <v>7143</v>
@@ -40047,7 +40047,7 @@
         <v>7117</v>
       </c>
       <c r="F305">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="G305" t="s">
         <v>7143</v>
@@ -40073,7 +40073,7 @@
         <v>7117</v>
       </c>
       <c r="F306">
-        <v>1190</v>
+        <v>1176</v>
       </c>
       <c r="G306" t="s">
         <v>7143</v>
@@ -40099,7 +40099,7 @@
         <v>7117</v>
       </c>
       <c r="F307">
-        <v>1746</v>
+        <v>1740</v>
       </c>
       <c r="G307" t="s">
         <v>7143</v>
@@ -40125,7 +40125,7 @@
         <v>7110</v>
       </c>
       <c r="F308">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="G308" t="s">
         <v>7143</v>
@@ -40151,7 +40151,7 @@
         <v>7110</v>
       </c>
       <c r="F309">
-        <v>1782</v>
+        <v>1776</v>
       </c>
       <c r="G309" t="s">
         <v>7143</v>
@@ -40177,7 +40177,7 @@
         <v>7110</v>
       </c>
       <c r="F310">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="G310" t="s">
         <v>7143</v>
@@ -40281,7 +40281,7 @@
         <v>7110</v>
       </c>
       <c r="F314">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="G314" t="s">
         <v>7143</v>
@@ -40359,7 +40359,7 @@
         <v>7111</v>
       </c>
       <c r="F317">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="G317" t="s">
         <v>7143</v>
@@ -40385,7 +40385,7 @@
         <v>7111</v>
       </c>
       <c r="F318">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="G318" t="s">
         <v>7143</v>
@@ -40723,7 +40723,7 @@
         <v>7111</v>
       </c>
       <c r="F331">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="G331" t="s">
         <v>7143</v>
@@ -40775,7 +40775,7 @@
         <v>7106</v>
       </c>
       <c r="F333">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="G333" t="s">
         <v>7143</v>
@@ -41055,7 +41055,7 @@
         <v>7116</v>
       </c>
       <c r="F344">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="G344" t="s">
         <v>7143</v>
@@ -41133,7 +41133,7 @@
         <v>7115</v>
       </c>
       <c r="F347">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="G347" t="s">
         <v>7143</v>
@@ -41239,7 +41239,7 @@
         <v>7115</v>
       </c>
       <c r="F352">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="G352" t="s">
         <v>7143</v>
@@ -41265,7 +41265,7 @@
         <v>7115</v>
       </c>
       <c r="F353">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="G353" t="s">
         <v>7143</v>
@@ -41291,7 +41291,7 @@
         <v>7115</v>
       </c>
       <c r="F354">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="G354" t="s">
         <v>7143</v>
@@ -41317,7 +41317,7 @@
         <v>7115</v>
       </c>
       <c r="F355">
-        <v>3022</v>
+        <v>3012</v>
       </c>
       <c r="G355" t="s">
         <v>7143</v>
@@ -41343,7 +41343,7 @@
         <v>7115</v>
       </c>
       <c r="F356">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="G356" t="s">
         <v>7143</v>
@@ -41681,7 +41681,7 @@
         <v>7106</v>
       </c>
       <c r="F369">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G369" t="s">
         <v>7143</v>
@@ -41785,7 +41785,7 @@
         <v>7106</v>
       </c>
       <c r="F373">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="G373" t="s">
         <v>7143</v>
@@ -41935,7 +41935,7 @@
         <v>7106</v>
       </c>
       <c r="F379">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="G379" t="s">
         <v>7143</v>
@@ -41961,7 +41961,7 @@
         <v>7106</v>
       </c>
       <c r="F380">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G380" t="s">
         <v>7143</v>
@@ -42059,7 +42059,7 @@
         <v>7115</v>
       </c>
       <c r="F384">
-        <v>3314</v>
+        <v>3304</v>
       </c>
       <c r="G384" t="s">
         <v>7143</v>
@@ -42125,7 +42125,7 @@
         <v>7115</v>
       </c>
       <c r="F387">
-        <v>3341</v>
+        <v>3335</v>
       </c>
       <c r="G387" t="s">
         <v>7143</v>
@@ -42151,7 +42151,7 @@
         <v>7115</v>
       </c>
       <c r="F388">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="G388" t="s">
         <v>7143</v>
@@ -42415,7 +42415,7 @@
         <v>7116</v>
       </c>
       <c r="F400">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="G400" t="s">
         <v>7142</v>
@@ -42455,7 +42455,7 @@
         <v>7116</v>
       </c>
       <c r="F402">
-        <v>1668</v>
+        <v>1662</v>
       </c>
       <c r="G402" t="s">
         <v>7142</v>
@@ -42527,7 +42527,7 @@
         <v>7105</v>
       </c>
       <c r="F405">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G405" t="s">
         <v>7143</v>
@@ -42553,7 +42553,7 @@
         <v>7105</v>
       </c>
       <c r="F406">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G406" t="s">
         <v>7143</v>
@@ -42731,7 +42731,7 @@
         <v>7115</v>
       </c>
       <c r="F414">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="G414" t="s">
         <v>7143</v>
@@ -42887,7 +42887,7 @@
         <v>7120</v>
       </c>
       <c r="F420">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G420" t="s">
         <v>7143</v>
@@ -42913,7 +42913,7 @@
         <v>7120</v>
       </c>
       <c r="F421">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G421" t="s">
         <v>7143</v>
@@ -42939,7 +42939,7 @@
         <v>7120</v>
       </c>
       <c r="F422">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G422" t="s">
         <v>7143</v>
@@ -43251,7 +43251,7 @@
         <v>7106</v>
       </c>
       <c r="F434">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G434" t="s">
         <v>7143</v>
@@ -43407,7 +43407,7 @@
         <v>7115</v>
       </c>
       <c r="F440">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="G440" t="s">
         <v>7142</v>
@@ -43583,7 +43583,7 @@
         <v>7115</v>
       </c>
       <c r="F447">
-        <v>1239</v>
+        <v>1229</v>
       </c>
       <c r="G447" t="s">
         <v>7143</v>
@@ -43609,7 +43609,7 @@
         <v>7105</v>
       </c>
       <c r="F448">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G448" t="s">
         <v>7143</v>
@@ -43759,7 +43759,7 @@
         <v>7122</v>
       </c>
       <c r="F454">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G454" t="s">
         <v>7143</v>
@@ -43837,7 +43837,7 @@
         <v>7125</v>
       </c>
       <c r="F457">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="G457" t="s">
         <v>7143</v>
@@ -43941,7 +43941,7 @@
         <v>7106</v>
       </c>
       <c r="F461">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G461" t="s">
         <v>7143</v>
@@ -43967,7 +43967,7 @@
         <v>7106</v>
       </c>
       <c r="F462">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G462" t="s">
         <v>7143</v>
@@ -44019,7 +44019,7 @@
         <v>7105</v>
       </c>
       <c r="F464">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G464" t="s">
         <v>7143</v>
@@ -44071,7 +44071,7 @@
         <v>7117</v>
       </c>
       <c r="F466">
-        <v>1723</v>
+        <v>1715</v>
       </c>
       <c r="G466" t="s">
         <v>7143</v>
@@ -44123,7 +44123,7 @@
         <v>7117</v>
       </c>
       <c r="F468">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="G468" t="s">
         <v>7143</v>
@@ -44149,7 +44149,7 @@
         <v>7110</v>
       </c>
       <c r="F469">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="G469" t="s">
         <v>7143</v>
@@ -44175,7 +44175,7 @@
         <v>7110</v>
       </c>
       <c r="F470">
-        <v>1770</v>
+        <v>1764</v>
       </c>
       <c r="G470" t="s">
         <v>7143</v>
@@ -44287,7 +44287,7 @@
         <v>7110</v>
       </c>
       <c r="F475">
-        <v>1764</v>
+        <v>1758</v>
       </c>
       <c r="G475" t="s">
         <v>7143</v>
@@ -44365,7 +44365,7 @@
         <v>7117</v>
       </c>
       <c r="F478">
-        <v>1649</v>
+        <v>1643</v>
       </c>
       <c r="G478" t="s">
         <v>7143</v>
@@ -44391,7 +44391,7 @@
         <v>7117</v>
       </c>
       <c r="F479">
-        <v>1461</v>
+        <v>1440</v>
       </c>
       <c r="G479" t="s">
         <v>7143</v>
@@ -44417,7 +44417,7 @@
         <v>7117</v>
       </c>
       <c r="F480">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="G480" t="s">
         <v>7143</v>
@@ -44595,7 +44595,7 @@
         <v>7126</v>
       </c>
       <c r="F488">
-        <v>3071</v>
+        <v>3063</v>
       </c>
       <c r="G488" t="s">
         <v>7143</v>
@@ -44621,7 +44621,7 @@
         <v>7098</v>
       </c>
       <c r="F489">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="G489" t="s">
         <v>7143</v>
@@ -45125,7 +45125,7 @@
         <v>7114</v>
       </c>
       <c r="F510">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="G510" t="s">
         <v>7143</v>
@@ -45217,7 +45217,7 @@
         <v>7128</v>
       </c>
       <c r="F514">
-        <v>1717</v>
+        <v>1705</v>
       </c>
       <c r="G514" t="s">
         <v>7142</v>
@@ -45687,7 +45687,7 @@
         <v>7128</v>
       </c>
       <c r="F536">
-        <v>1620</v>
+        <v>1608</v>
       </c>
       <c r="G536" t="s">
         <v>7142</v>
@@ -53167,7 +53167,7 @@
         <v>7119</v>
       </c>
       <c r="F832">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G832" t="s">
         <v>7143</v>
@@ -53421,7 +53421,7 @@
         <v>7119</v>
       </c>
       <c r="F842">
-        <v>3656</v>
+        <v>3650</v>
       </c>
       <c r="G842" t="s">
         <v>7143</v>
@@ -54377,7 +54377,7 @@
         <v>7119</v>
       </c>
       <c r="F879">
-        <v>2102</v>
+        <v>2096</v>
       </c>
       <c r="G879" t="s">
         <v>7143</v>
@@ -57023,7 +57023,7 @@
         <v>7136</v>
       </c>
       <c r="F987">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="G987" t="s">
         <v>7142</v>
@@ -57083,7 +57083,7 @@
         <v>7136</v>
       </c>
       <c r="F990">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="G990" t="s">
         <v>7142</v>
@@ -57143,7 +57143,7 @@
         <v>7136</v>
       </c>
       <c r="F993">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="G993" t="s">
         <v>7142</v>
@@ -57203,7 +57203,7 @@
         <v>7136</v>
       </c>
       <c r="F996">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G996" t="s">
         <v>7142</v>
@@ -57719,7 +57719,7 @@
         <v>7136</v>
       </c>
       <c r="F1017">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="G1017" t="s">
         <v>7142</v>
@@ -57791,7 +57791,7 @@
         <v>7136</v>
       </c>
       <c r="F1020">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G1020" t="s">
         <v>7143</v>
@@ -58125,7 +58125,7 @@
         <v>7109</v>
       </c>
       <c r="F1034">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G1034" t="s">
         <v>7143</v>
@@ -58177,7 +58177,7 @@
         <v>7136</v>
       </c>
       <c r="F1036">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="G1036" t="s">
         <v>7143</v>
@@ -58249,7 +58249,7 @@
         <v>7136</v>
       </c>
       <c r="F1039">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="G1039" t="s">
         <v>7142</v>
@@ -58309,7 +58309,7 @@
         <v>7136</v>
       </c>
       <c r="F1042">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G1042" t="s">
         <v>7142</v>
@@ -58369,7 +58369,7 @@
         <v>7136</v>
       </c>
       <c r="F1045">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="G1045" t="s">
         <v>7142</v>
@@ -58455,7 +58455,7 @@
         <v>7136</v>
       </c>
       <c r="F1049">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G1049" t="s">
         <v>7143</v>
@@ -58507,7 +58507,7 @@
         <v>7136</v>
       </c>
       <c r="F1051">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G1051" t="s">
         <v>7143</v>
@@ -59009,7 +59009,7 @@
         <v>7105</v>
       </c>
       <c r="F1071">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G1071" t="s">
         <v>7143</v>
@@ -59185,7 +59185,7 @@
         <v>7105</v>
       </c>
       <c r="F1078">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G1078" t="s">
         <v>7143</v>
@@ -60141,7 +60141,7 @@
         <v>7105</v>
       </c>
       <c r="F1121">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G1121" t="s">
         <v>7143</v>
@@ -60409,7 +60409,7 @@
         <v>7105</v>
       </c>
       <c r="F1132">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G1132" t="s">
         <v>7143</v>
@@ -60752,7 +60752,7 @@
         <v>7105</v>
       </c>
       <c r="F1146">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G1146" t="s">
         <v>7142</v>
@@ -60772,7 +60772,7 @@
         <v>7105</v>
       </c>
       <c r="F1147">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G1147" t="s">
         <v>7143</v>
@@ -60850,7 +60850,7 @@
         <v>7102</v>
       </c>
       <c r="F1150">
-        <v>893</v>
+        <v>857</v>
       </c>
       <c r="G1150" t="s">
         <v>7143</v>
@@ -60928,7 +60928,7 @@
         <v>7100</v>
       </c>
       <c r="F1153">
-        <v>7594</v>
+        <v>7592</v>
       </c>
       <c r="G1153" t="s">
         <v>7143</v>
@@ -61026,7 +61026,7 @@
         <v>7105</v>
       </c>
       <c r="F1157">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G1157" t="s">
         <v>7143</v>
@@ -62842,7 +62842,7 @@
         <v>7105</v>
       </c>
       <c r="F1234">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G1234" t="s">
         <v>7143</v>
@@ -63292,7 +63292,7 @@
         <v>7108</v>
       </c>
       <c r="F1252">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="G1252" t="s">
         <v>7143</v>
@@ -63318,7 +63318,7 @@
         <v>7108</v>
       </c>
       <c r="F1253">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="G1253" t="s">
         <v>7143</v>
@@ -63370,7 +63370,7 @@
         <v>7108</v>
       </c>
       <c r="F1255">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="G1255" t="s">
         <v>7143</v>
@@ -64692,7 +64692,7 @@
         <v>7105</v>
       </c>
       <c r="F1307">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G1307" t="s">
         <v>7143</v>
@@ -65232,7 +65232,7 @@
         <v>7101</v>
       </c>
       <c r="F1328">
-        <v>7453</v>
+        <v>7441</v>
       </c>
       <c r="G1328" t="s">
         <v>7143</v>
@@ -65310,7 +65310,7 @@
         <v>7099</v>
       </c>
       <c r="F1331">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G1331" t="s">
         <v>7143</v>
@@ -66712,7 +66712,7 @@
         <v>7115</v>
       </c>
       <c r="F1396">
-        <v>1929</v>
+        <v>1923</v>
       </c>
       <c r="G1396" t="s">
         <v>7143</v>
@@ -66764,7 +66764,7 @@
         <v>7115</v>
       </c>
       <c r="F1398">
-        <v>1877</v>
+        <v>1871</v>
       </c>
       <c r="G1398" t="s">
         <v>7143</v>
@@ -66842,7 +66842,7 @@
         <v>7115</v>
       </c>
       <c r="F1401">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="G1401" t="s">
         <v>7143</v>
@@ -68022,7 +68022,7 @@
         <v>7105</v>
       </c>
       <c r="F1448">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G1448" t="s">
         <v>7143</v>
@@ -68206,7 +68206,7 @@
         <v>7105</v>
       </c>
       <c r="F1456">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G1456" t="s">
         <v>7143</v>
@@ -69520,7 +69520,7 @@
         <v>7138</v>
       </c>
       <c r="F1513">
-        <v>5022</v>
+        <v>4950</v>
       </c>
       <c r="G1513" t="s">
         <v>7143</v>
@@ -69572,7 +69572,7 @@
         <v>7138</v>
       </c>
       <c r="F1515">
-        <v>5520</v>
+        <v>5502</v>
       </c>
       <c r="G1515" t="s">
         <v>7143</v>
@@ -69598,7 +69598,7 @@
         <v>7138</v>
       </c>
       <c r="F1516">
-        <v>4140</v>
+        <v>4068</v>
       </c>
       <c r="G1516" t="s">
         <v>7143</v>
@@ -69884,7 +69884,7 @@
         <v>7137</v>
       </c>
       <c r="F1527">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="G1527" t="s">
         <v>7143</v>
@@ -70014,7 +70014,7 @@
         <v>7137</v>
       </c>
       <c r="F1532">
-        <v>2175</v>
+        <v>2167</v>
       </c>
       <c r="G1532" t="s">
         <v>7143</v>
@@ -70248,7 +70248,7 @@
         <v>7115</v>
       </c>
       <c r="F1541">
-        <v>2643</v>
+        <v>2633</v>
       </c>
       <c r="G1541" t="s">
         <v>7143</v>
@@ -70274,7 +70274,7 @@
         <v>7115</v>
       </c>
       <c r="F1542">
-        <v>3091</v>
+        <v>3081</v>
       </c>
       <c r="G1542" t="s">
         <v>7143</v>
@@ -70534,7 +70534,7 @@
         <v>7115</v>
       </c>
       <c r="F1552">
-        <v>2430</v>
+        <v>2410</v>
       </c>
       <c r="G1552" t="s">
         <v>7143</v>
@@ -70560,7 +70560,7 @@
         <v>7115</v>
       </c>
       <c r="F1553">
-        <v>4616</v>
+        <v>4606</v>
       </c>
       <c r="G1553" t="s">
         <v>7143</v>
@@ -71940,7 +71940,7 @@
         <v>7137</v>
       </c>
       <c r="F1607">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G1607" t="s">
         <v>7143</v>
@@ -73370,7 +73370,7 @@
         <v>7100</v>
       </c>
       <c r="F1662">
-        <v>9289</v>
+        <v>9277</v>
       </c>
       <c r="G1662" t="s">
         <v>7143</v>
@@ -73474,7 +73474,7 @@
         <v>7102</v>
       </c>
       <c r="F1666">
-        <v>2808</v>
+        <v>2784</v>
       </c>
       <c r="G1666" t="s">
         <v>7143</v>
@@ -73500,7 +73500,7 @@
         <v>7102</v>
       </c>
       <c r="F1667">
-        <v>1949</v>
+        <v>1941</v>
       </c>
       <c r="G1667" t="s">
         <v>7143</v>
@@ -73578,7 +73578,7 @@
         <v>7102</v>
       </c>
       <c r="F1670">
-        <v>22948</v>
+        <v>22894</v>
       </c>
       <c r="G1670" t="s">
         <v>7143</v>
@@ -73708,7 +73708,7 @@
         <v>7102</v>
       </c>
       <c r="F1675">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="G1675" t="s">
         <v>7143</v>
@@ -74204,7 +74204,7 @@
         <v>7123</v>
       </c>
       <c r="F1695">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="G1695" t="s">
         <v>7143</v>
@@ -74934,7 +74934,7 @@
         <v>7101</v>
       </c>
       <c r="F1724">
-        <v>54427</v>
+        <v>54324</v>
       </c>
       <c r="G1724" t="s">
         <v>7143</v>
@@ -74960,7 +74960,7 @@
         <v>7101</v>
       </c>
       <c r="F1725">
-        <v>8906</v>
+        <v>8894</v>
       </c>
       <c r="G1725" t="s">
         <v>7143</v>
@@ -75246,7 +75246,7 @@
         <v>7101</v>
       </c>
       <c r="F1736">
-        <v>3287</v>
+        <v>3271</v>
       </c>
       <c r="G1736" t="s">
         <v>7143</v>
@@ -75272,7 +75272,7 @@
         <v>7101</v>
       </c>
       <c r="F1737">
-        <v>2170</v>
+        <v>2158</v>
       </c>
       <c r="G1737" t="s">
         <v>7143</v>
@@ -75402,7 +75402,7 @@
         <v>7101</v>
       </c>
       <c r="F1742">
-        <v>2536</v>
+        <v>2520</v>
       </c>
       <c r="G1742" t="s">
         <v>7143</v>
@@ -75688,7 +75688,7 @@
         <v>7134</v>
       </c>
       <c r="F1753">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G1753" t="s">
         <v>7143</v>
@@ -75740,7 +75740,7 @@
         <v>7134</v>
       </c>
       <c r="F1755">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G1755" t="s">
         <v>7143</v>
@@ -76104,7 +76104,7 @@
         <v>7116</v>
       </c>
       <c r="F1769">
-        <v>3396</v>
+        <v>3390</v>
       </c>
       <c r="G1769" t="s">
         <v>7143</v>
@@ -76722,7 +76722,7 @@
         <v>7116</v>
       </c>
       <c r="F1793">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="G1793" t="s">
         <v>7143</v>
@@ -76748,7 +76748,7 @@
         <v>7116</v>
       </c>
       <c r="F1794">
-        <v>2842</v>
+        <v>2824</v>
       </c>
       <c r="G1794" t="s">
         <v>7143</v>
@@ -76774,7 +76774,7 @@
         <v>7116</v>
       </c>
       <c r="F1795">
-        <v>3500</v>
+        <v>3488</v>
       </c>
       <c r="G1795" t="s">
         <v>7143</v>
@@ -76930,7 +76930,7 @@
         <v>7116</v>
       </c>
       <c r="F1801">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="G1801" t="s">
         <v>7143</v>
@@ -77210,7 +77210,7 @@
         <v>7116</v>
       </c>
       <c r="F1812">
-        <v>2561</v>
+        <v>2555</v>
       </c>
       <c r="G1812" t="s">
         <v>7143</v>
@@ -77236,7 +77236,7 @@
         <v>7116</v>
       </c>
       <c r="F1813">
-        <v>5336</v>
+        <v>5330</v>
       </c>
       <c r="G1813" t="s">
         <v>7143</v>
@@ -77444,7 +77444,7 @@
         <v>7136</v>
       </c>
       <c r="F1821">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="G1821" t="s">
         <v>7143</v>
@@ -77470,7 +77470,7 @@
         <v>7136</v>
       </c>
       <c r="F1822">
-        <v>2468</v>
+        <v>2456</v>
       </c>
       <c r="G1822" t="s">
         <v>7143</v>
@@ -78290,7 +78290,7 @@
         <v>7136</v>
       </c>
       <c r="F1854">
-        <v>1393</v>
+        <v>1381</v>
       </c>
       <c r="G1854" t="s">
         <v>7143</v>
@@ -78342,7 +78342,7 @@
         <v>7136</v>
       </c>
       <c r="F1856">
-        <v>2751</v>
+        <v>2739</v>
       </c>
       <c r="G1856" t="s">
         <v>7143</v>
@@ -78368,7 +78368,7 @@
         <v>7136</v>
       </c>
       <c r="F1857">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="G1857" t="s">
         <v>7143</v>
@@ -81164,7 +81164,7 @@
         <v>7105</v>
       </c>
       <c r="F1968">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G1968" t="s">
         <v>7143</v>
@@ -81690,7 +81690,7 @@
         <v>7105</v>
       </c>
       <c r="F1991">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G1991" t="s">
         <v>7143</v>
@@ -82226,7 +82226,7 @@
         <v>7105</v>
       </c>
       <c r="F2013">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G2013" t="s">
         <v>7143</v>
@@ -83226,7 +83226,7 @@
         <v>7106</v>
       </c>
       <c r="F2054">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G2054" t="s">
         <v>7143</v>
@@ -83278,7 +83278,7 @@
         <v>7106</v>
       </c>
       <c r="F2056">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G2056" t="s">
         <v>7143</v>
@@ -83546,7 +83546,7 @@
         <v>7117</v>
       </c>
       <c r="F2067">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="G2067" t="s">
         <v>7143</v>
@@ -83572,7 +83572,7 @@
         <v>7117</v>
       </c>
       <c r="F2068">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="G2068" t="s">
         <v>7143</v>
@@ -83598,7 +83598,7 @@
         <v>7117</v>
       </c>
       <c r="F2069">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="G2069" t="s">
         <v>7143</v>
@@ -83624,7 +83624,7 @@
         <v>7117</v>
       </c>
       <c r="F2070">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G2070" t="s">
         <v>7143</v>
@@ -83676,7 +83676,7 @@
         <v>7117</v>
       </c>
       <c r="F2072">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G2072" t="s">
         <v>7143</v>
@@ -83832,7 +83832,7 @@
         <v>7110</v>
       </c>
       <c r="F2078">
-        <v>1922</v>
+        <v>1916</v>
       </c>
       <c r="G2078" t="s">
         <v>7143</v>
@@ -84114,7 +84114,7 @@
         <v>7105</v>
       </c>
       <c r="F2090">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2090" t="s">
         <v>7142</v>
@@ -84616,7 +84616,7 @@
         <v>7105</v>
       </c>
       <c r="F2110">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G2110" t="s">
         <v>7143</v>
@@ -87524,7 +87524,7 @@
         <v>7125</v>
       </c>
       <c r="F2229">
-        <v>1217</v>
+        <v>1207</v>
       </c>
       <c r="G2229" t="s">
         <v>7143</v>
@@ -87628,7 +87628,7 @@
         <v>7125</v>
       </c>
       <c r="F2233">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G2233" t="s">
         <v>7143</v>
@@ -87654,7 +87654,7 @@
         <v>7125</v>
       </c>
       <c r="F2234">
-        <v>2226</v>
+        <v>2216</v>
       </c>
       <c r="G2234" t="s">
         <v>7143</v>
@@ -88736,7 +88736,7 @@
         <v>7106</v>
       </c>
       <c r="F2280">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G2280" t="s">
         <v>7143</v>
@@ -88866,7 +88866,7 @@
         <v>7117</v>
       </c>
       <c r="F2285">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="G2285" t="s">
         <v>7142</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -33189,7 +33189,7 @@
         <v>7171</v>
       </c>
       <c r="F5">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G5" t="s">
         <v>7212</v>
@@ -33373,7 +33373,7 @@
         <v>7171</v>
       </c>
       <c r="F13">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G13" t="s">
         <v>7213</v>
@@ -33419,7 +33419,7 @@
         <v>7171</v>
       </c>
       <c r="F15">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G15" t="s">
         <v>7213</v>
@@ -33439,7 +33439,7 @@
         <v>7171</v>
       </c>
       <c r="F16">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G16" t="s">
         <v>7213</v>
@@ -33847,7 +33847,7 @@
         <v>7179</v>
       </c>
       <c r="F34">
-        <v>3468</v>
+        <v>3402</v>
       </c>
       <c r="G34" t="s">
         <v>7212</v>
@@ -33873,7 +33873,7 @@
         <v>7179</v>
       </c>
       <c r="F35">
-        <v>3076</v>
+        <v>3070</v>
       </c>
       <c r="G35" t="s">
         <v>7213</v>
@@ -33945,7 +33945,7 @@
         <v>7180</v>
       </c>
       <c r="F38">
-        <v>3369</v>
+        <v>3363</v>
       </c>
       <c r="G38" t="s">
         <v>7212</v>
@@ -34023,7 +34023,7 @@
         <v>7182</v>
       </c>
       <c r="F41">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G41" t="s">
         <v>7212</v>
@@ -34049,7 +34049,7 @@
         <v>7182</v>
       </c>
       <c r="F42">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G42" t="s">
         <v>7212</v>
@@ -34075,7 +34075,7 @@
         <v>7169</v>
       </c>
       <c r="F43">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s">
         <v>7213</v>
@@ -34095,7 +34095,7 @@
         <v>7182</v>
       </c>
       <c r="F44">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G44" t="s">
         <v>7212</v>
@@ -34121,7 +34121,7 @@
         <v>7182</v>
       </c>
       <c r="F45">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G45" t="s">
         <v>7212</v>
@@ -34173,7 +34173,7 @@
         <v>7183</v>
       </c>
       <c r="F47">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
         <v>7212</v>
@@ -34219,7 +34219,7 @@
         <v>7183</v>
       </c>
       <c r="F49">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G49" t="s">
         <v>7212</v>
@@ -34245,7 +34245,7 @@
         <v>7183</v>
       </c>
       <c r="F50">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G50" t="s">
         <v>7212</v>
@@ -34271,7 +34271,7 @@
         <v>7184</v>
       </c>
       <c r="F51">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="G51" t="s">
         <v>7212</v>
@@ -34297,7 +34297,7 @@
         <v>7169</v>
       </c>
       <c r="F52">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G52" t="s">
         <v>7213</v>
@@ -34317,7 +34317,7 @@
         <v>7179</v>
       </c>
       <c r="F53">
-        <v>7055</v>
+        <v>7013</v>
       </c>
       <c r="G53" t="s">
         <v>7212</v>
@@ -34343,7 +34343,7 @@
         <v>7178</v>
       </c>
       <c r="F54">
-        <v>9125</v>
+        <v>9029</v>
       </c>
       <c r="G54" t="s">
         <v>7212</v>
@@ -34369,7 +34369,7 @@
         <v>7184</v>
       </c>
       <c r="F55">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="G55" t="s">
         <v>7212</v>
@@ -34441,7 +34441,7 @@
         <v>7171</v>
       </c>
       <c r="F58">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s">
         <v>7212</v>
@@ -34493,7 +34493,7 @@
         <v>7169</v>
       </c>
       <c r="F60">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G60" t="s">
         <v>7212</v>
@@ -34519,7 +34519,7 @@
         <v>7184</v>
       </c>
       <c r="F61">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G61" t="s">
         <v>7212</v>
@@ -34565,7 +34565,7 @@
         <v>7184</v>
       </c>
       <c r="F63">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="G63" t="s">
         <v>7212</v>
@@ -34611,7 +34611,7 @@
         <v>7171</v>
       </c>
       <c r="F65">
-        <v>1255</v>
+        <v>1155</v>
       </c>
       <c r="G65" t="s">
         <v>7213</v>
@@ -34631,7 +34631,7 @@
         <v>7171</v>
       </c>
       <c r="F66">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G66" t="s">
         <v>7212</v>
@@ -34657,7 +34657,7 @@
         <v>7171</v>
       </c>
       <c r="F67">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G67" t="s">
         <v>7213</v>
@@ -34703,7 +34703,7 @@
         <v>7171</v>
       </c>
       <c r="F69">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="G69" t="s">
         <v>7212</v>
@@ -34875,7 +34875,7 @@
         <v>7184</v>
       </c>
       <c r="F77">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G77" t="s">
         <v>7212</v>
@@ -34921,7 +34921,7 @@
         <v>7184</v>
       </c>
       <c r="F79">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G79" t="s">
         <v>7212</v>
@@ -34947,7 +34947,7 @@
         <v>7184</v>
       </c>
       <c r="F80">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G80" t="s">
         <v>7212</v>
@@ -35025,7 +35025,7 @@
         <v>7184</v>
       </c>
       <c r="F83">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G83" t="s">
         <v>7212</v>
@@ -35077,7 +35077,7 @@
         <v>7184</v>
       </c>
       <c r="F85">
-        <v>1748</v>
+        <v>1745</v>
       </c>
       <c r="G85" t="s">
         <v>7212</v>
@@ -35129,7 +35129,7 @@
         <v>7184</v>
       </c>
       <c r="F87">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G87" t="s">
         <v>7212</v>
@@ -35155,7 +35155,7 @@
         <v>7184</v>
       </c>
       <c r="F88">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G88" t="s">
         <v>7212</v>
@@ -35181,7 +35181,7 @@
         <v>7184</v>
       </c>
       <c r="F89">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="G89" t="s">
         <v>7212</v>
@@ -35207,7 +35207,7 @@
         <v>7184</v>
       </c>
       <c r="F90">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G90" t="s">
         <v>7212</v>
@@ -35259,7 +35259,7 @@
         <v>7184</v>
       </c>
       <c r="F92">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G92" t="s">
         <v>7212</v>
@@ -35285,7 +35285,7 @@
         <v>7184</v>
       </c>
       <c r="F93">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G93" t="s">
         <v>7212</v>
@@ -35311,7 +35311,7 @@
         <v>7184</v>
       </c>
       <c r="F94">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G94" t="s">
         <v>7212</v>
@@ -35441,7 +35441,7 @@
         <v>7180</v>
       </c>
       <c r="F99">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="G99" t="s">
         <v>7212</v>
@@ -35467,7 +35467,7 @@
         <v>7171</v>
       </c>
       <c r="F100">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="G100" t="s">
         <v>7212</v>
@@ -35493,7 +35493,7 @@
         <v>7181</v>
       </c>
       <c r="F101">
-        <v>2972</v>
+        <v>2963</v>
       </c>
       <c r="G101" t="s">
         <v>7212</v>
@@ -35519,7 +35519,7 @@
         <v>7171</v>
       </c>
       <c r="F102">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="G102" t="s">
         <v>7212</v>
@@ -35545,7 +35545,7 @@
         <v>7169</v>
       </c>
       <c r="F103">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="G103" t="s">
         <v>7212</v>
@@ -35591,7 +35591,7 @@
         <v>7169</v>
       </c>
       <c r="F105">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="G105" t="s">
         <v>7212</v>
@@ -35617,7 +35617,7 @@
         <v>7169</v>
       </c>
       <c r="F106">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="G106" t="s">
         <v>7212</v>
@@ -35643,7 +35643,7 @@
         <v>7169</v>
       </c>
       <c r="F107">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="G107" t="s">
         <v>7212</v>
@@ -35669,7 +35669,7 @@
         <v>7169</v>
       </c>
       <c r="F108">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="G108" t="s">
         <v>7212</v>
@@ -35695,7 +35695,7 @@
         <v>7169</v>
       </c>
       <c r="F109">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="G109" t="s">
         <v>7212</v>
@@ -35741,7 +35741,7 @@
         <v>7169</v>
       </c>
       <c r="F111">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="G111" t="s">
         <v>7212</v>
@@ -35767,7 +35767,7 @@
         <v>7169</v>
       </c>
       <c r="F112">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="G112" t="s">
         <v>7212</v>
@@ -35793,7 +35793,7 @@
         <v>7169</v>
       </c>
       <c r="F113">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="G113" t="s">
         <v>7212</v>
@@ -35819,7 +35819,7 @@
         <v>7169</v>
       </c>
       <c r="F114">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="G114" t="s">
         <v>7212</v>
@@ -35845,7 +35845,7 @@
         <v>7169</v>
       </c>
       <c r="F115">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="G115" t="s">
         <v>7212</v>
@@ -35871,7 +35871,7 @@
         <v>7169</v>
       </c>
       <c r="F116">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="G116" t="s">
         <v>7212</v>
@@ -35897,7 +35897,7 @@
         <v>7185</v>
       </c>
       <c r="F117">
-        <v>23227</v>
+        <v>23116</v>
       </c>
       <c r="G117" t="s">
         <v>7212</v>
@@ -35975,7 +35975,7 @@
         <v>7185</v>
       </c>
       <c r="F120">
-        <v>2291</v>
+        <v>2279</v>
       </c>
       <c r="G120" t="s">
         <v>7212</v>
@@ -36001,7 +36001,7 @@
         <v>7185</v>
       </c>
       <c r="F121">
-        <v>2338</v>
+        <v>2326</v>
       </c>
       <c r="G121" t="s">
         <v>7212</v>
@@ -36079,7 +36079,7 @@
         <v>7185</v>
       </c>
       <c r="F124">
-        <v>2355</v>
+        <v>2343</v>
       </c>
       <c r="G124" t="s">
         <v>7212</v>
@@ -36105,7 +36105,7 @@
         <v>7185</v>
       </c>
       <c r="F125">
-        <v>2098</v>
+        <v>2086</v>
       </c>
       <c r="G125" t="s">
         <v>7212</v>
@@ -36131,7 +36131,7 @@
         <v>7185</v>
       </c>
       <c r="F126">
-        <v>2028</v>
+        <v>2016</v>
       </c>
       <c r="G126" t="s">
         <v>7212</v>
@@ -36209,7 +36209,7 @@
         <v>7185</v>
       </c>
       <c r="F129">
-        <v>23143</v>
+        <v>23056</v>
       </c>
       <c r="G129" t="s">
         <v>7212</v>
@@ -36261,7 +36261,7 @@
         <v>7186</v>
       </c>
       <c r="F131">
-        <v>2459</v>
+        <v>2451</v>
       </c>
       <c r="G131" t="s">
         <v>7212</v>
@@ -36313,7 +36313,7 @@
         <v>7186</v>
       </c>
       <c r="F133">
-        <v>2775</v>
+        <v>2772</v>
       </c>
       <c r="G133" t="s">
         <v>7213</v>
@@ -36379,7 +36379,7 @@
         <v>7186</v>
       </c>
       <c r="F136">
-        <v>4425</v>
+        <v>4417</v>
       </c>
       <c r="G136" t="s">
         <v>7212</v>
@@ -36405,7 +36405,7 @@
         <v>7186</v>
       </c>
       <c r="F137">
-        <v>1970</v>
+        <v>1962</v>
       </c>
       <c r="G137" t="s">
         <v>7212</v>
@@ -36457,7 +36457,7 @@
         <v>7186</v>
       </c>
       <c r="F139">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="G139" t="s">
         <v>7212</v>
@@ -36483,7 +36483,7 @@
         <v>7186</v>
       </c>
       <c r="F140">
-        <v>1939</v>
+        <v>1923</v>
       </c>
       <c r="G140" t="s">
         <v>7212</v>
@@ -36847,7 +36847,7 @@
         <v>7186</v>
       </c>
       <c r="F154">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="G154" t="s">
         <v>7212</v>
@@ -36873,7 +36873,7 @@
         <v>7186</v>
       </c>
       <c r="F155">
-        <v>2520</v>
+        <v>2508</v>
       </c>
       <c r="G155" t="s">
         <v>7212</v>
@@ -36977,7 +36977,7 @@
         <v>7186</v>
       </c>
       <c r="F159">
-        <v>3462</v>
+        <v>3444</v>
       </c>
       <c r="G159" t="s">
         <v>7212</v>
@@ -37003,7 +37003,7 @@
         <v>7186</v>
       </c>
       <c r="F160">
-        <v>3513</v>
+        <v>3504</v>
       </c>
       <c r="G160" t="s">
         <v>7212</v>
@@ -37029,7 +37029,7 @@
         <v>7186</v>
       </c>
       <c r="F161">
-        <v>4357</v>
+        <v>4341</v>
       </c>
       <c r="G161" t="s">
         <v>7212</v>
@@ -37081,7 +37081,7 @@
         <v>7186</v>
       </c>
       <c r="F163">
-        <v>4354</v>
+        <v>4346</v>
       </c>
       <c r="G163" t="s">
         <v>7212</v>
@@ -37107,7 +37107,7 @@
         <v>7186</v>
       </c>
       <c r="F164">
-        <v>4309</v>
+        <v>4253</v>
       </c>
       <c r="G164" t="s">
         <v>7212</v>
@@ -37133,7 +37133,7 @@
         <v>7186</v>
       </c>
       <c r="F165">
-        <v>2514</v>
+        <v>2502</v>
       </c>
       <c r="G165" t="s">
         <v>7212</v>
@@ -37237,7 +37237,7 @@
         <v>7186</v>
       </c>
       <c r="F169">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="G169" t="s">
         <v>7212</v>
@@ -37263,7 +37263,7 @@
         <v>7186</v>
       </c>
       <c r="F170">
-        <v>2002</v>
+        <v>1990</v>
       </c>
       <c r="G170" t="s">
         <v>7212</v>
@@ -37289,7 +37289,7 @@
         <v>7186</v>
       </c>
       <c r="F171">
-        <v>3542</v>
+        <v>3536</v>
       </c>
       <c r="G171" t="s">
         <v>7212</v>
@@ -37315,7 +37315,7 @@
         <v>7186</v>
       </c>
       <c r="F172">
-        <v>2517</v>
+        <v>2502</v>
       </c>
       <c r="G172" t="s">
         <v>7212</v>
@@ -37341,7 +37341,7 @@
         <v>7186</v>
       </c>
       <c r="F173">
-        <v>3968</v>
+        <v>3957</v>
       </c>
       <c r="G173" t="s">
         <v>7212</v>
@@ -37367,7 +37367,7 @@
         <v>7186</v>
       </c>
       <c r="F174">
-        <v>3473</v>
+        <v>3461</v>
       </c>
       <c r="G174" t="s">
         <v>7212</v>
@@ -37419,7 +37419,7 @@
         <v>7186</v>
       </c>
       <c r="F176">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="G176" t="s">
         <v>7212</v>
@@ -37471,7 +37471,7 @@
         <v>7186</v>
       </c>
       <c r="F178">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="G178" t="s">
         <v>7212</v>
@@ -37705,7 +37705,7 @@
         <v>7187</v>
       </c>
       <c r="F187">
-        <v>1384</v>
+        <v>1370</v>
       </c>
       <c r="G187" t="s">
         <v>7212</v>
@@ -37887,7 +37887,7 @@
         <v>7187</v>
       </c>
       <c r="F194">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="G194" t="s">
         <v>7212</v>
@@ -37991,7 +37991,7 @@
         <v>7187</v>
       </c>
       <c r="F198">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="G198" t="s">
         <v>7212</v>
@@ -38109,7 +38109,7 @@
         <v>7171</v>
       </c>
       <c r="F203">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G203" t="s">
         <v>7212</v>
@@ -38135,7 +38135,7 @@
         <v>7171</v>
       </c>
       <c r="F204">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="G204" t="s">
         <v>7212</v>
@@ -38161,7 +38161,7 @@
         <v>7169</v>
       </c>
       <c r="F205">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="G205" t="s">
         <v>7212</v>
@@ -38187,7 +38187,7 @@
         <v>7171</v>
       </c>
       <c r="F206">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="G206" t="s">
         <v>7212</v>
@@ -38253,7 +38253,7 @@
         <v>7171</v>
       </c>
       <c r="F209">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="G209" t="s">
         <v>7212</v>
@@ -38299,7 +38299,7 @@
         <v>7171</v>
       </c>
       <c r="F211">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="G211" t="s">
         <v>7212</v>
@@ -38345,7 +38345,7 @@
         <v>7171</v>
       </c>
       <c r="F213">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G213" t="s">
         <v>7212</v>
@@ -38371,7 +38371,7 @@
         <v>7171</v>
       </c>
       <c r="F214">
-        <v>845</v>
+        <v>827</v>
       </c>
       <c r="G214" t="s">
         <v>7212</v>
@@ -38397,7 +38397,7 @@
         <v>7171</v>
       </c>
       <c r="F215">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G215" t="s">
         <v>7212</v>
@@ -38423,7 +38423,7 @@
         <v>7171</v>
       </c>
       <c r="F216">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="G216" t="s">
         <v>7212</v>
@@ -38489,7 +38489,7 @@
         <v>7188</v>
       </c>
       <c r="F219">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="G219" t="s">
         <v>7212</v>
@@ -38515,7 +38515,7 @@
         <v>7172</v>
       </c>
       <c r="F220">
-        <v>1547</v>
+        <v>1535</v>
       </c>
       <c r="G220" t="s">
         <v>7212</v>
@@ -38567,7 +38567,7 @@
         <v>7172</v>
       </c>
       <c r="F222">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="G222" t="s">
         <v>7212</v>
@@ -38593,7 +38593,7 @@
         <v>7172</v>
       </c>
       <c r="F223">
-        <v>1119</v>
+        <v>1095</v>
       </c>
       <c r="G223" t="s">
         <v>7212</v>
@@ -38619,7 +38619,7 @@
         <v>7172</v>
       </c>
       <c r="F224">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="G224" t="s">
         <v>7212</v>
@@ -38645,7 +38645,7 @@
         <v>7172</v>
       </c>
       <c r="F225">
-        <v>1470</v>
+        <v>1458</v>
       </c>
       <c r="G225" t="s">
         <v>7212</v>
@@ -38671,7 +38671,7 @@
         <v>7172</v>
       </c>
       <c r="F226">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="G226" t="s">
         <v>7212</v>
@@ -38697,7 +38697,7 @@
         <v>7172</v>
       </c>
       <c r="F227">
-        <v>1410</v>
+        <v>1394</v>
       </c>
       <c r="G227" t="s">
         <v>7212</v>
@@ -38749,7 +38749,7 @@
         <v>7169</v>
       </c>
       <c r="F229">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="G229" t="s">
         <v>7212</v>
@@ -38853,7 +38853,7 @@
         <v>7169</v>
       </c>
       <c r="F233">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="G233" t="s">
         <v>7212</v>
@@ -38879,7 +38879,7 @@
         <v>7188</v>
       </c>
       <c r="F234">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="G234" t="s">
         <v>7212</v>
@@ -38905,7 +38905,7 @@
         <v>7188</v>
       </c>
       <c r="F235">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="G235" t="s">
         <v>7212</v>
@@ -39009,7 +39009,7 @@
         <v>7188</v>
       </c>
       <c r="F239">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="G239" t="s">
         <v>7212</v>
@@ -39035,7 +39035,7 @@
         <v>7169</v>
       </c>
       <c r="F240">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G240" t="s">
         <v>7212</v>
@@ -39061,7 +39061,7 @@
         <v>7171</v>
       </c>
       <c r="F241">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G241" t="s">
         <v>7212</v>
@@ -39087,7 +39087,7 @@
         <v>7188</v>
       </c>
       <c r="F242">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="G242" t="s">
         <v>7212</v>
@@ -39173,7 +39173,7 @@
         <v>7182</v>
       </c>
       <c r="F246">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G246" t="s">
         <v>7212</v>
@@ -39199,7 +39199,7 @@
         <v>7182</v>
       </c>
       <c r="F247">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G247" t="s">
         <v>7212</v>
@@ -39303,7 +39303,7 @@
         <v>7171</v>
       </c>
       <c r="F251">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G251" t="s">
         <v>7212</v>
@@ -39519,7 +39519,7 @@
         <v>7190</v>
       </c>
       <c r="F260">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="G260" t="s">
         <v>7212</v>
@@ -39727,7 +39727,7 @@
         <v>7190</v>
       </c>
       <c r="F268">
-        <v>2863</v>
+        <v>2861</v>
       </c>
       <c r="G268" t="s">
         <v>7212</v>
@@ -39753,7 +39753,7 @@
         <v>7190</v>
       </c>
       <c r="F269">
-        <v>2920</v>
+        <v>2908</v>
       </c>
       <c r="G269" t="s">
         <v>7212</v>
@@ -39779,7 +39779,7 @@
         <v>7190</v>
       </c>
       <c r="F270">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G270" t="s">
         <v>7212</v>
@@ -39831,7 +39831,7 @@
         <v>7190</v>
       </c>
       <c r="F272">
-        <v>4862</v>
+        <v>4856</v>
       </c>
       <c r="G272" t="s">
         <v>7212</v>
@@ -39857,7 +39857,7 @@
         <v>7190</v>
       </c>
       <c r="F273">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="G273" t="s">
         <v>7212</v>
@@ -39883,7 +39883,7 @@
         <v>7191</v>
       </c>
       <c r="F274">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="G274" t="s">
         <v>7212</v>
@@ -40013,7 +40013,7 @@
         <v>7190</v>
       </c>
       <c r="F279">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="G279" t="s">
         <v>7212</v>
@@ -40091,7 +40091,7 @@
         <v>7171</v>
       </c>
       <c r="F282">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="G282" t="s">
         <v>7212</v>
@@ -40117,7 +40117,7 @@
         <v>7171</v>
       </c>
       <c r="F283">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G283" t="s">
         <v>7212</v>
@@ -40169,7 +40169,7 @@
         <v>7171</v>
       </c>
       <c r="F285">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="G285" t="s">
         <v>7212</v>
@@ -40195,7 +40195,7 @@
         <v>7171</v>
       </c>
       <c r="F286">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="G286" t="s">
         <v>7212</v>
@@ -40221,7 +40221,7 @@
         <v>7171</v>
       </c>
       <c r="F287">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G287" t="s">
         <v>7212</v>
@@ -40273,7 +40273,7 @@
         <v>7171</v>
       </c>
       <c r="F289">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G289" t="s">
         <v>7212</v>
@@ -40351,7 +40351,7 @@
         <v>7171</v>
       </c>
       <c r="F292">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="G292" t="s">
         <v>7212</v>
@@ -40377,7 +40377,7 @@
         <v>7171</v>
       </c>
       <c r="F293">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="G293" t="s">
         <v>7212</v>
@@ -40423,7 +40423,7 @@
         <v>7171</v>
       </c>
       <c r="F295">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G295" t="s">
         <v>7212</v>
@@ -40475,7 +40475,7 @@
         <v>7171</v>
       </c>
       <c r="F297">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G297" t="s">
         <v>7212</v>
@@ -40501,7 +40501,7 @@
         <v>7171</v>
       </c>
       <c r="F298">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G298" t="s">
         <v>7212</v>
@@ -40627,7 +40627,7 @@
         <v>7169</v>
       </c>
       <c r="F304">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G304" t="s">
         <v>7212</v>
@@ -41119,7 +41119,7 @@
         <v>7171</v>
       </c>
       <c r="F325">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G325" t="s">
         <v>7212</v>
@@ -41165,7 +41165,7 @@
         <v>7188</v>
       </c>
       <c r="F327">
-        <v>1003</v>
+        <v>988</v>
       </c>
       <c r="G327" t="s">
         <v>7212</v>
@@ -41191,7 +41191,7 @@
         <v>7188</v>
       </c>
       <c r="F328">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="G328" t="s">
         <v>7212</v>
@@ -41243,7 +41243,7 @@
         <v>7172</v>
       </c>
       <c r="F330">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="G330" t="s">
         <v>7212</v>
@@ -41321,7 +41321,7 @@
         <v>7193</v>
       </c>
       <c r="F333">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="G333" t="s">
         <v>7212</v>
@@ -41373,7 +41373,7 @@
         <v>7172</v>
       </c>
       <c r="F335">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="G335" t="s">
         <v>7212</v>
@@ -41399,7 +41399,7 @@
         <v>7172</v>
       </c>
       <c r="F336">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="G336" t="s">
         <v>7212</v>
@@ -41425,7 +41425,7 @@
         <v>7172</v>
       </c>
       <c r="F337">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="G337" t="s">
         <v>7212</v>
@@ -41451,7 +41451,7 @@
         <v>7172</v>
       </c>
       <c r="F338">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="G338" t="s">
         <v>7212</v>
@@ -41477,7 +41477,7 @@
         <v>7172</v>
       </c>
       <c r="F339">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="G339" t="s">
         <v>7212</v>
@@ -41503,7 +41503,7 @@
         <v>7172</v>
       </c>
       <c r="F340">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="G340" t="s">
         <v>7212</v>
@@ -41529,7 +41529,7 @@
         <v>7169</v>
       </c>
       <c r="F341">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="G341" t="s">
         <v>7212</v>
@@ -41581,7 +41581,7 @@
         <v>7169</v>
       </c>
       <c r="F343">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="G343" t="s">
         <v>7212</v>
@@ -41607,7 +41607,7 @@
         <v>7169</v>
       </c>
       <c r="F344">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="G344" t="s">
         <v>7212</v>
@@ -41633,7 +41633,7 @@
         <v>7169</v>
       </c>
       <c r="F345">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="G345" t="s">
         <v>7212</v>
@@ -41659,7 +41659,7 @@
         <v>7169</v>
       </c>
       <c r="F346">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="G346" t="s">
         <v>7212</v>
@@ -41875,7 +41875,7 @@
         <v>7193</v>
       </c>
       <c r="F355">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="G355" t="s">
         <v>7212</v>
@@ -41901,7 +41901,7 @@
         <v>7194</v>
       </c>
       <c r="F356">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="G356" t="s">
         <v>7212</v>
@@ -41927,7 +41927,7 @@
         <v>7194</v>
       </c>
       <c r="F357">
-        <v>1708</v>
+        <v>1702</v>
       </c>
       <c r="G357" t="s">
         <v>7212</v>
@@ -41953,7 +41953,7 @@
         <v>7194</v>
       </c>
       <c r="F358">
-        <v>1716</v>
+        <v>1707</v>
       </c>
       <c r="G358" t="s">
         <v>7212</v>
@@ -41979,7 +41979,7 @@
         <v>7194</v>
       </c>
       <c r="F359">
-        <v>1708</v>
+        <v>1702</v>
       </c>
       <c r="G359" t="s">
         <v>7212</v>
@@ -42005,7 +42005,7 @@
         <v>7194</v>
       </c>
       <c r="F360">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="G360" t="s">
         <v>7212</v>
@@ -42057,7 +42057,7 @@
         <v>7194</v>
       </c>
       <c r="F362">
-        <v>1899</v>
+        <v>1893</v>
       </c>
       <c r="G362" t="s">
         <v>7212</v>
@@ -42083,7 +42083,7 @@
         <v>7194</v>
       </c>
       <c r="F363">
-        <v>928</v>
+        <v>902</v>
       </c>
       <c r="G363" t="s">
         <v>7212</v>
@@ -42447,7 +42447,7 @@
         <v>7188</v>
       </c>
       <c r="F377">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="G377" t="s">
         <v>7212</v>
@@ -42571,7 +42571,7 @@
         <v>7193</v>
       </c>
       <c r="F382">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="G382" t="s">
         <v>7212</v>
@@ -42597,7 +42597,7 @@
         <v>7193</v>
       </c>
       <c r="F383">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="G383" t="s">
         <v>7212</v>
@@ -42675,7 +42675,7 @@
         <v>7193</v>
       </c>
       <c r="F386">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="G386" t="s">
         <v>7212</v>
@@ -42701,7 +42701,7 @@
         <v>7193</v>
       </c>
       <c r="F387">
-        <v>1668</v>
+        <v>1662</v>
       </c>
       <c r="G387" t="s">
         <v>7212</v>
@@ -42727,7 +42727,7 @@
         <v>7192</v>
       </c>
       <c r="F388">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="G388" t="s">
         <v>7212</v>
@@ -42753,7 +42753,7 @@
         <v>7192</v>
       </c>
       <c r="F389">
-        <v>927</v>
+        <v>917</v>
       </c>
       <c r="G389" t="s">
         <v>7212</v>
@@ -42865,7 +42865,7 @@
         <v>7192</v>
       </c>
       <c r="F394">
-        <v>852</v>
+        <v>827</v>
       </c>
       <c r="G394" t="s">
         <v>7212</v>
@@ -42937,7 +42937,7 @@
         <v>7192</v>
       </c>
       <c r="F397">
-        <v>742</v>
+        <v>717</v>
       </c>
       <c r="G397" t="s">
         <v>7212</v>
@@ -42963,7 +42963,7 @@
         <v>7192</v>
       </c>
       <c r="F398">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="G398" t="s">
         <v>7212</v>
@@ -43041,7 +43041,7 @@
         <v>7169</v>
       </c>
       <c r="F401">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G401" t="s">
         <v>7212</v>
@@ -43093,7 +43093,7 @@
         <v>7169</v>
       </c>
       <c r="F403">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G403" t="s">
         <v>7212</v>
@@ -43119,7 +43119,7 @@
         <v>7169</v>
       </c>
       <c r="F404">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G404" t="s">
         <v>7212</v>
@@ -43145,7 +43145,7 @@
         <v>7169</v>
       </c>
       <c r="F405">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G405" t="s">
         <v>7212</v>
@@ -43197,7 +43197,7 @@
         <v>7169</v>
       </c>
       <c r="F407">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="G407" t="s">
         <v>7212</v>
@@ -43379,7 +43379,7 @@
         <v>7175</v>
       </c>
       <c r="F414">
-        <v>2220</v>
+        <v>2212</v>
       </c>
       <c r="G414" t="s">
         <v>7212</v>
@@ -43633,7 +43633,7 @@
         <v>7171</v>
       </c>
       <c r="F424">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G424" t="s">
         <v>7212</v>
@@ -43903,7 +43903,7 @@
         <v>7192</v>
       </c>
       <c r="F436">
-        <v>2340</v>
+        <v>2310</v>
       </c>
       <c r="G436" t="s">
         <v>7212</v>
@@ -44041,7 +44041,7 @@
         <v>7171</v>
       </c>
       <c r="F442">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G442" t="s">
         <v>7212</v>
@@ -44067,7 +44067,7 @@
         <v>7171</v>
       </c>
       <c r="F443">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G443" t="s">
         <v>7212</v>
@@ -44133,7 +44133,7 @@
         <v>7193</v>
       </c>
       <c r="F446">
-        <v>1626</v>
+        <v>1620</v>
       </c>
       <c r="G446" t="s">
         <v>7213</v>
@@ -44173,7 +44173,7 @@
         <v>7193</v>
       </c>
       <c r="F448">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G448" t="s">
         <v>7213</v>
@@ -44455,7 +44455,7 @@
         <v>7192</v>
       </c>
       <c r="F460">
-        <v>2386</v>
+        <v>2381</v>
       </c>
       <c r="G460" t="s">
         <v>7212</v>
@@ -44839,7 +44839,7 @@
         <v>7169</v>
       </c>
       <c r="F475">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G475" t="s">
         <v>7212</v>
@@ -44891,7 +44891,7 @@
         <v>7171</v>
       </c>
       <c r="F477">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="G477" t="s">
         <v>7212</v>
@@ -44995,7 +44995,7 @@
         <v>7171</v>
       </c>
       <c r="F481">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G481" t="s">
         <v>7212</v>
@@ -45047,7 +45047,7 @@
         <v>7169</v>
       </c>
       <c r="F483">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G483" t="s">
         <v>7212</v>
@@ -45125,7 +45125,7 @@
         <v>7192</v>
       </c>
       <c r="F486">
-        <v>1114</v>
+        <v>1099</v>
       </c>
       <c r="G486" t="s">
         <v>7212</v>
@@ -45151,7 +45151,7 @@
         <v>7192</v>
       </c>
       <c r="F487">
-        <v>2054</v>
+        <v>2044</v>
       </c>
       <c r="G487" t="s">
         <v>7213</v>
@@ -45249,7 +45249,7 @@
         <v>7192</v>
       </c>
       <c r="F491">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G491" t="s">
         <v>7212</v>
@@ -45275,7 +45275,7 @@
         <v>7192</v>
       </c>
       <c r="F492">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G492" t="s">
         <v>7212</v>
@@ -45301,7 +45301,7 @@
         <v>7192</v>
       </c>
       <c r="F493">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G493" t="s">
         <v>7212</v>
@@ -45431,7 +45431,7 @@
         <v>7173</v>
       </c>
       <c r="F498">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="G498" t="s">
         <v>7212</v>
@@ -45483,7 +45483,7 @@
         <v>7171</v>
       </c>
       <c r="F500">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G500" t="s">
         <v>7212</v>
@@ -45509,7 +45509,7 @@
         <v>7171</v>
       </c>
       <c r="F501">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G501" t="s">
         <v>7212</v>
@@ -45535,7 +45535,7 @@
         <v>7171</v>
       </c>
       <c r="F502">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G502" t="s">
         <v>7212</v>
@@ -45561,7 +45561,7 @@
         <v>7171</v>
       </c>
       <c r="F503">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G503" t="s">
         <v>7212</v>
@@ -45613,7 +45613,7 @@
         <v>7169</v>
       </c>
       <c r="F505">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G505" t="s">
         <v>7212</v>
@@ -45639,7 +45639,7 @@
         <v>7194</v>
       </c>
       <c r="F506">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="G506" t="s">
         <v>7212</v>
@@ -45665,7 +45665,7 @@
         <v>7194</v>
       </c>
       <c r="F507">
-        <v>1619</v>
+        <v>1607</v>
       </c>
       <c r="G507" t="s">
         <v>7212</v>
@@ -45691,7 +45691,7 @@
         <v>7194</v>
       </c>
       <c r="F508">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="G508" t="s">
         <v>7212</v>
@@ -45857,7 +45857,7 @@
         <v>7188</v>
       </c>
       <c r="F516">
-        <v>1716</v>
+        <v>1710</v>
       </c>
       <c r="G516" t="s">
         <v>7212</v>
@@ -45883,7 +45883,7 @@
         <v>7188</v>
       </c>
       <c r="F517">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="G517" t="s">
         <v>7212</v>
@@ -45909,7 +45909,7 @@
         <v>7188</v>
       </c>
       <c r="F518">
-        <v>1698</v>
+        <v>1692</v>
       </c>
       <c r="G518" t="s">
         <v>7212</v>
@@ -45935,7 +45935,7 @@
         <v>7188</v>
       </c>
       <c r="F519">
-        <v>1691</v>
+        <v>1685</v>
       </c>
       <c r="G519" t="s">
         <v>7212</v>
@@ -45961,7 +45961,7 @@
         <v>7188</v>
       </c>
       <c r="F520">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="G520" t="s">
         <v>7212</v>
@@ -46013,7 +46013,7 @@
         <v>7188</v>
       </c>
       <c r="F522">
-        <v>1331</v>
+        <v>1321</v>
       </c>
       <c r="G522" t="s">
         <v>7212</v>
@@ -46039,7 +46039,7 @@
         <v>7194</v>
       </c>
       <c r="F523">
-        <v>1317</v>
+        <v>1295</v>
       </c>
       <c r="G523" t="s">
         <v>7212</v>
@@ -46065,7 +46065,7 @@
         <v>7194</v>
       </c>
       <c r="F524">
-        <v>1484</v>
+        <v>1469</v>
       </c>
       <c r="G524" t="s">
         <v>7212</v>
@@ -46091,7 +46091,7 @@
         <v>7194</v>
       </c>
       <c r="F525">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="G525" t="s">
         <v>7212</v>
@@ -46215,7 +46215,7 @@
         <v>7198</v>
       </c>
       <c r="F530">
-        <v>2961</v>
+        <v>2949</v>
       </c>
       <c r="G530" t="s">
         <v>7212</v>
@@ -46267,7 +46267,7 @@
         <v>7180</v>
       </c>
       <c r="F532">
-        <v>4000</v>
+        <v>3996</v>
       </c>
       <c r="G532" t="s">
         <v>7212</v>
@@ -46379,7 +46379,7 @@
         <v>7171</v>
       </c>
       <c r="F537">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="G537" t="s">
         <v>7212</v>
@@ -46653,7 +46653,7 @@
         <v>7190</v>
       </c>
       <c r="F548">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="G548" t="s">
         <v>7212</v>
@@ -46725,7 +46725,7 @@
         <v>7184</v>
       </c>
       <c r="F551">
-        <v>1344</v>
+        <v>1296</v>
       </c>
       <c r="G551" t="s">
         <v>7213</v>
@@ -51079,7 +51079,7 @@
         <v>7183</v>
       </c>
       <c r="F724">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="G724" t="s">
         <v>7212</v>
@@ -51295,7 +51295,7 @@
         <v>7183</v>
       </c>
       <c r="F733">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G733" t="s">
         <v>7212</v>
@@ -51321,7 +51321,7 @@
         <v>7183</v>
       </c>
       <c r="F734">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G734" t="s">
         <v>7212</v>
@@ -51347,7 +51347,7 @@
         <v>7183</v>
       </c>
       <c r="F735">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G735" t="s">
         <v>7212</v>
@@ -53227,7 +53227,7 @@
         <v>7185</v>
       </c>
       <c r="F811">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="G811" t="s">
         <v>7212</v>
@@ -53489,7 +53489,7 @@
         <v>7182</v>
       </c>
       <c r="F822">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="G822" t="s">
         <v>7212</v>
@@ -53691,7 +53691,7 @@
         <v>7184</v>
       </c>
       <c r="F830">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G830" t="s">
         <v>7212</v>
@@ -53743,7 +53743,7 @@
         <v>7184</v>
       </c>
       <c r="F832">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="G832" t="s">
         <v>7212</v>
@@ -53769,7 +53769,7 @@
         <v>7184</v>
       </c>
       <c r="F833">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G833" t="s">
         <v>7212</v>
@@ -53795,7 +53795,7 @@
         <v>7184</v>
       </c>
       <c r="F834">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G834" t="s">
         <v>7212</v>
@@ -53987,7 +53987,7 @@
         <v>7184</v>
       </c>
       <c r="F843">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G843" t="s">
         <v>7212</v>
@@ -54195,7 +54195,7 @@
         <v>7184</v>
       </c>
       <c r="F851">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G851" t="s">
         <v>7212</v>
@@ -55261,7 +55261,7 @@
         <v>7175</v>
       </c>
       <c r="F892">
-        <v>1689</v>
+        <v>1682</v>
       </c>
       <c r="G892" t="s">
         <v>7212</v>
@@ -55313,7 +55313,7 @@
         <v>7175</v>
       </c>
       <c r="F894">
-        <v>4611</v>
+        <v>4593</v>
       </c>
       <c r="G894" t="s">
         <v>7212</v>
@@ -55521,7 +55521,7 @@
         <v>7175</v>
       </c>
       <c r="F902">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="G902" t="s">
         <v>7212</v>
@@ -55573,7 +55573,7 @@
         <v>7175</v>
       </c>
       <c r="F904">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G904" t="s">
         <v>7212</v>
@@ -55801,7 +55801,7 @@
         <v>7175</v>
       </c>
       <c r="F913">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="G913" t="s">
         <v>7212</v>
@@ -55957,7 +55957,7 @@
         <v>7175</v>
       </c>
       <c r="F919">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="G919" t="s">
         <v>7212</v>
@@ -56061,7 +56061,7 @@
         <v>7175</v>
       </c>
       <c r="F923">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G923" t="s">
         <v>7212</v>
@@ -56087,7 +56087,7 @@
         <v>7175</v>
       </c>
       <c r="F924">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="G924" t="s">
         <v>7212</v>
@@ -56393,7 +56393,7 @@
         <v>7175</v>
       </c>
       <c r="F936">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G936" t="s">
         <v>7212</v>
@@ -57603,7 +57603,7 @@
         <v>7206</v>
       </c>
       <c r="F983">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="G983" t="s">
         <v>7213</v>
@@ -57721,7 +57721,7 @@
         <v>7187</v>
       </c>
       <c r="F988">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G988" t="s">
         <v>7212</v>
@@ -57747,7 +57747,7 @@
         <v>7187</v>
       </c>
       <c r="F989">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G989" t="s">
         <v>7212</v>
@@ -58293,7 +58293,7 @@
         <v>7187</v>
       </c>
       <c r="F1013">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G1013" t="s">
         <v>7213</v>
@@ -58313,7 +58313,7 @@
         <v>7187</v>
       </c>
       <c r="F1014">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G1014" t="s">
         <v>7213</v>
@@ -58333,7 +58333,7 @@
         <v>7187</v>
       </c>
       <c r="F1015">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="G1015" t="s">
         <v>7213</v>
@@ -58399,7 +58399,7 @@
         <v>7206</v>
       </c>
       <c r="F1018">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="G1018" t="s">
         <v>7212</v>
@@ -58425,7 +58425,7 @@
         <v>7189</v>
       </c>
       <c r="F1019">
-        <v>7310</v>
+        <v>7290</v>
       </c>
       <c r="G1019" t="s">
         <v>7212</v>
@@ -58511,7 +58511,7 @@
         <v>7206</v>
       </c>
       <c r="F1023">
-        <v>1709</v>
+        <v>1697</v>
       </c>
       <c r="G1023" t="s">
         <v>7212</v>
@@ -58563,7 +58563,7 @@
         <v>7206</v>
       </c>
       <c r="F1025">
-        <v>1099</v>
+        <v>1075</v>
       </c>
       <c r="G1025" t="s">
         <v>7212</v>
@@ -58693,7 +58693,7 @@
         <v>7206</v>
       </c>
       <c r="F1030">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="G1030" t="s">
         <v>7212</v>
@@ -58719,7 +58719,7 @@
         <v>7206</v>
       </c>
       <c r="F1031">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="G1031" t="s">
         <v>7213</v>
@@ -58739,7 +58739,7 @@
         <v>7206</v>
       </c>
       <c r="F1032">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="G1032" t="s">
         <v>7213</v>
@@ -58759,7 +58759,7 @@
         <v>7206</v>
       </c>
       <c r="F1033">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="G1033" t="s">
         <v>7213</v>
@@ -58779,7 +58779,7 @@
         <v>7206</v>
       </c>
       <c r="F1034">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="G1034" t="s">
         <v>7213</v>
@@ -58799,7 +58799,7 @@
         <v>7189</v>
       </c>
       <c r="F1035">
-        <v>7310</v>
+        <v>7290</v>
       </c>
       <c r="G1035" t="s">
         <v>7212</v>
@@ -58825,7 +58825,7 @@
         <v>7189</v>
       </c>
       <c r="F1036">
-        <v>7319</v>
+        <v>7299</v>
       </c>
       <c r="G1036" t="s">
         <v>7212</v>
@@ -58851,7 +58851,7 @@
         <v>7206</v>
       </c>
       <c r="F1037">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="G1037" t="s">
         <v>7213</v>
@@ -58871,7 +58871,7 @@
         <v>7189</v>
       </c>
       <c r="F1038">
-        <v>4386</v>
+        <v>4374</v>
       </c>
       <c r="G1038" t="s">
         <v>7212</v>
@@ -59235,7 +59235,7 @@
         <v>7189</v>
       </c>
       <c r="F1052">
-        <v>4386</v>
+        <v>4374</v>
       </c>
       <c r="G1052" t="s">
         <v>7212</v>
@@ -59261,7 +59261,7 @@
         <v>7189</v>
       </c>
       <c r="F1053">
-        <v>4418</v>
+        <v>4406</v>
       </c>
       <c r="G1053" t="s">
         <v>7212</v>
@@ -59287,7 +59287,7 @@
         <v>7206</v>
       </c>
       <c r="F1054">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="G1054" t="s">
         <v>7213</v>
@@ -59353,7 +59353,7 @@
         <v>7206</v>
       </c>
       <c r="F1057">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="G1057" t="s">
         <v>7212</v>
@@ -59379,7 +59379,7 @@
         <v>7206</v>
       </c>
       <c r="F1058">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G1058" t="s">
         <v>7212</v>
@@ -59431,7 +59431,7 @@
         <v>7206</v>
       </c>
       <c r="F1060">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="G1060" t="s">
         <v>7212</v>
@@ -59483,7 +59483,7 @@
         <v>7206</v>
       </c>
       <c r="F1062">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="G1062" t="s">
         <v>7212</v>
@@ -59561,7 +59561,7 @@
         <v>7206</v>
       </c>
       <c r="F1065">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="G1065" t="s">
         <v>7212</v>
@@ -59633,7 +59633,7 @@
         <v>7206</v>
       </c>
       <c r="F1068">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="G1068" t="s">
         <v>7212</v>
@@ -59659,7 +59659,7 @@
         <v>7206</v>
       </c>
       <c r="F1069">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G1069" t="s">
         <v>7212</v>
@@ -59737,7 +59737,7 @@
         <v>7206</v>
       </c>
       <c r="F1072">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="G1072" t="s">
         <v>7213</v>
@@ -59757,7 +59757,7 @@
         <v>7206</v>
       </c>
       <c r="F1073">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="G1073" t="s">
         <v>7213</v>
@@ -59777,7 +59777,7 @@
         <v>7206</v>
       </c>
       <c r="F1074">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="G1074" t="s">
         <v>7213</v>
@@ -59817,7 +59817,7 @@
         <v>7206</v>
       </c>
       <c r="F1076">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="G1076" t="s">
         <v>7213</v>
@@ -59837,7 +59837,7 @@
         <v>7206</v>
       </c>
       <c r="F1077">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="G1077" t="s">
         <v>7213</v>
@@ -59857,7 +59857,7 @@
         <v>7206</v>
       </c>
       <c r="F1078">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="G1078" t="s">
         <v>7213</v>
@@ -59877,7 +59877,7 @@
         <v>7206</v>
       </c>
       <c r="F1079">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="G1079" t="s">
         <v>7213</v>
@@ -59897,7 +59897,7 @@
         <v>7206</v>
       </c>
       <c r="F1080">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="G1080" t="s">
         <v>7213</v>
@@ -59917,7 +59917,7 @@
         <v>7206</v>
       </c>
       <c r="F1081">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="G1081" t="s">
         <v>7213</v>
@@ -59957,7 +59957,7 @@
         <v>7206</v>
       </c>
       <c r="F1083">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="G1083" t="s">
         <v>7213</v>
@@ -59997,7 +59997,7 @@
         <v>7206</v>
       </c>
       <c r="F1085">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="G1085" t="s">
         <v>7213</v>
@@ -60017,7 +60017,7 @@
         <v>7206</v>
       </c>
       <c r="F1086">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="G1086" t="s">
         <v>7213</v>
@@ -60057,7 +60057,7 @@
         <v>7206</v>
       </c>
       <c r="F1088">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="G1088" t="s">
         <v>7213</v>
@@ -60189,7 +60189,7 @@
         <v>7171</v>
       </c>
       <c r="F1094">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G1094" t="s">
         <v>7212</v>
@@ -60371,7 +60371,7 @@
         <v>7171</v>
       </c>
       <c r="F1101">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G1101" t="s">
         <v>7212</v>
@@ -60527,7 +60527,7 @@
         <v>7171</v>
       </c>
       <c r="F1107">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1107" t="s">
         <v>7212</v>
@@ -61767,7 +61767,7 @@
         <v>7171</v>
       </c>
       <c r="F1163">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G1163" t="s">
         <v>7212</v>
@@ -61793,7 +61793,7 @@
         <v>7171</v>
       </c>
       <c r="F1164">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G1164" t="s">
         <v>7212</v>
@@ -61819,7 +61819,7 @@
         <v>7171</v>
       </c>
       <c r="F1165">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G1165" t="s">
         <v>7212</v>
@@ -62346,7 +62346,7 @@
         <v>7171</v>
       </c>
       <c r="F1187">
-        <v>384</v>
+        <v>474</v>
       </c>
       <c r="G1187" t="s">
         <v>7212</v>
@@ -62372,7 +62372,7 @@
         <v>7171</v>
       </c>
       <c r="F1188">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G1188" t="s">
         <v>7212</v>
@@ -62502,7 +62502,7 @@
         <v>7179</v>
       </c>
       <c r="F1193">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="G1193" t="s">
         <v>7212</v>
@@ -62554,7 +62554,7 @@
         <v>7169</v>
       </c>
       <c r="F1195">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G1195" t="s">
         <v>7212</v>
@@ -62672,7 +62672,7 @@
         <v>7171</v>
       </c>
       <c r="F1200">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1200" t="s">
         <v>7212</v>
@@ -62698,7 +62698,7 @@
         <v>7171</v>
       </c>
       <c r="F1201">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G1201" t="s">
         <v>7212</v>
@@ -62724,7 +62724,7 @@
         <v>7171</v>
       </c>
       <c r="F1202">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="G1202" t="s">
         <v>7212</v>
@@ -62750,7 +62750,7 @@
         <v>7171</v>
       </c>
       <c r="F1203">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G1203" t="s">
         <v>7212</v>
@@ -62776,7 +62776,7 @@
         <v>7182</v>
       </c>
       <c r="F1204">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G1204" t="s">
         <v>7212</v>
@@ -62822,7 +62822,7 @@
         <v>7182</v>
       </c>
       <c r="F1206">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G1206" t="s">
         <v>7212</v>
@@ -63152,7 +63152,7 @@
         <v>7195</v>
       </c>
       <c r="F1221">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G1221" t="s">
         <v>7213</v>
@@ -63258,7 +63258,7 @@
         <v>7182</v>
       </c>
       <c r="F1226">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G1226" t="s">
         <v>7212</v>
@@ -64180,7 +64180,7 @@
         <v>7171</v>
       </c>
       <c r="F1264">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G1264" t="s">
         <v>7212</v>
@@ -64304,7 +64304,7 @@
         <v>7171</v>
       </c>
       <c r="F1269">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G1269" t="s">
         <v>7212</v>
@@ -64434,7 +64434,7 @@
         <v>7171</v>
       </c>
       <c r="F1274">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G1274" t="s">
         <v>7212</v>
@@ -64728,7 +64728,7 @@
         <v>7186</v>
       </c>
       <c r="F1286">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="G1286" t="s">
         <v>7212</v>
@@ -64936,7 +64936,7 @@
         <v>7186</v>
       </c>
       <c r="F1294">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="G1294" t="s">
         <v>7212</v>
@@ -65204,7 +65204,7 @@
         <v>7186</v>
       </c>
       <c r="F1305">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G1305" t="s">
         <v>7212</v>
@@ -65308,7 +65308,7 @@
         <v>7186</v>
       </c>
       <c r="F1309">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G1309" t="s">
         <v>7212</v>
@@ -65556,7 +65556,7 @@
         <v>7184</v>
       </c>
       <c r="F1319">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G1319" t="s">
         <v>7212</v>
@@ -65634,7 +65634,7 @@
         <v>7184</v>
       </c>
       <c r="F1322">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="G1322" t="s">
         <v>7212</v>
@@ -65738,7 +65738,7 @@
         <v>7184</v>
       </c>
       <c r="F1326">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="G1326" t="s">
         <v>7212</v>
@@ -65764,7 +65764,7 @@
         <v>7184</v>
       </c>
       <c r="F1327">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="G1327" t="s">
         <v>7212</v>
@@ -65816,7 +65816,7 @@
         <v>7184</v>
       </c>
       <c r="F1329">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G1329" t="s">
         <v>7212</v>
@@ -65842,7 +65842,7 @@
         <v>7184</v>
       </c>
       <c r="F1330">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="G1330" t="s">
         <v>7212</v>
@@ -66408,7 +66408,7 @@
         <v>7178</v>
       </c>
       <c r="F1352">
-        <v>7110</v>
+        <v>7080</v>
       </c>
       <c r="G1352" t="s">
         <v>7212</v>
@@ -66798,7 +66798,7 @@
         <v>7184</v>
       </c>
       <c r="F1367">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G1367" t="s">
         <v>7212</v>
@@ -66928,7 +66928,7 @@
         <v>7184</v>
       </c>
       <c r="F1372">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G1372" t="s">
         <v>7212</v>
@@ -66980,7 +66980,7 @@
         <v>7184</v>
       </c>
       <c r="F1374">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G1374" t="s">
         <v>7212</v>
@@ -67838,7 +67838,7 @@
         <v>7175</v>
       </c>
       <c r="F1416">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G1416" t="s">
         <v>7212</v>
@@ -68260,7 +68260,7 @@
         <v>7192</v>
       </c>
       <c r="F1435">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="G1435" t="s">
         <v>7212</v>
@@ -68286,7 +68286,7 @@
         <v>7192</v>
       </c>
       <c r="F1436">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="G1436" t="s">
         <v>7212</v>
@@ -69212,7 +69212,7 @@
         <v>7171</v>
       </c>
       <c r="F1473">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G1473" t="s">
         <v>7212</v>
@@ -69264,7 +69264,7 @@
         <v>7171</v>
       </c>
       <c r="F1475">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G1475" t="s">
         <v>7212</v>
@@ -69316,7 +69316,7 @@
         <v>7171</v>
       </c>
       <c r="F1477">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G1477" t="s">
         <v>7212</v>
@@ -70638,7 +70638,7 @@
         <v>7208</v>
       </c>
       <c r="F1535">
-        <v>2612</v>
+        <v>2594</v>
       </c>
       <c r="G1535" t="s">
         <v>7212</v>
@@ -70664,7 +70664,7 @@
         <v>7208</v>
       </c>
       <c r="F1536">
-        <v>3640</v>
+        <v>3496</v>
       </c>
       <c r="G1536" t="s">
         <v>7212</v>
@@ -70716,7 +70716,7 @@
         <v>7208</v>
       </c>
       <c r="F1538">
-        <v>4828</v>
+        <v>4774</v>
       </c>
       <c r="G1538" t="s">
         <v>7212</v>
@@ -70742,7 +70742,7 @@
         <v>7208</v>
       </c>
       <c r="F1539">
-        <v>3106</v>
+        <v>3052</v>
       </c>
       <c r="G1539" t="s">
         <v>7212</v>
@@ -70794,7 +70794,7 @@
         <v>7208</v>
       </c>
       <c r="F1541">
-        <v>1856</v>
+        <v>1802</v>
       </c>
       <c r="G1541" t="s">
         <v>7212</v>
@@ -70872,7 +70872,7 @@
         <v>7207</v>
       </c>
       <c r="F1544">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="G1544" t="s">
         <v>7212</v>
@@ -71288,7 +71288,7 @@
         <v>7207</v>
       </c>
       <c r="F1560">
-        <v>1052</v>
+        <v>1036</v>
       </c>
       <c r="G1560" t="s">
         <v>7212</v>
@@ -71314,7 +71314,7 @@
         <v>7207</v>
       </c>
       <c r="F1561">
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="G1561" t="s">
         <v>7212</v>
@@ -71340,7 +71340,7 @@
         <v>7207</v>
       </c>
       <c r="F1562">
-        <v>2010</v>
+        <v>1994</v>
       </c>
       <c r="G1562" t="s">
         <v>7212</v>
@@ -71392,7 +71392,7 @@
         <v>7207</v>
       </c>
       <c r="F1564">
-        <v>1911</v>
+        <v>1903</v>
       </c>
       <c r="G1564" t="s">
         <v>7212</v>
@@ -72024,7 +72024,7 @@
         <v>7192</v>
       </c>
       <c r="F1589">
-        <v>2359</v>
+        <v>2349</v>
       </c>
       <c r="G1589" t="s">
         <v>7212</v>
@@ -72362,7 +72362,7 @@
         <v>7192</v>
       </c>
       <c r="F1602">
-        <v>2550</v>
+        <v>2530</v>
       </c>
       <c r="G1602" t="s">
         <v>7212</v>
@@ -72492,7 +72492,7 @@
         <v>7186</v>
       </c>
       <c r="F1607">
-        <v>5515</v>
+        <v>5503</v>
       </c>
       <c r="G1607" t="s">
         <v>7212</v>
@@ -73324,7 +73324,7 @@
         <v>7186</v>
       </c>
       <c r="F1639">
-        <v>3867</v>
+        <v>3831</v>
       </c>
       <c r="G1639" t="s">
         <v>7212</v>
@@ -73350,7 +73350,7 @@
         <v>7186</v>
       </c>
       <c r="F1640">
-        <v>4206</v>
+        <v>4146</v>
       </c>
       <c r="G1640" t="s">
         <v>7212</v>
@@ -73376,7 +73376,7 @@
         <v>7186</v>
       </c>
       <c r="F1641">
-        <v>2328</v>
+        <v>2280</v>
       </c>
       <c r="G1641" t="s">
         <v>7212</v>
@@ -73558,7 +73558,7 @@
         <v>7186</v>
       </c>
       <c r="F1648">
-        <v>10248</v>
+        <v>10236</v>
       </c>
       <c r="G1648" t="s">
         <v>7212</v>
@@ -73584,7 +73584,7 @@
         <v>7186</v>
       </c>
       <c r="F1649">
-        <v>1787</v>
+        <v>1763</v>
       </c>
       <c r="G1649" t="s">
         <v>7212</v>
@@ -73610,7 +73610,7 @@
         <v>7186</v>
       </c>
       <c r="F1650">
-        <v>8424</v>
+        <v>8412</v>
       </c>
       <c r="G1650" t="s">
         <v>7212</v>
@@ -73994,7 +73994,7 @@
         <v>7186</v>
       </c>
       <c r="F1665">
-        <v>1790</v>
+        <v>1778</v>
       </c>
       <c r="G1665" t="s">
         <v>7212</v>
@@ -74020,7 +74020,7 @@
         <v>7186</v>
       </c>
       <c r="F1666">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="G1666" t="s">
         <v>7212</v>
@@ -74722,7 +74722,7 @@
         <v>7181</v>
       </c>
       <c r="F1693">
-        <v>8931</v>
+        <v>8871</v>
       </c>
       <c r="G1693" t="s">
         <v>7212</v>
@@ -74748,7 +74748,7 @@
         <v>7179</v>
       </c>
       <c r="F1694">
-        <v>1749</v>
+        <v>1693</v>
       </c>
       <c r="G1694" t="s">
         <v>7212</v>
@@ -74774,7 +74774,7 @@
         <v>7179</v>
       </c>
       <c r="F1695">
-        <v>1769</v>
+        <v>1745</v>
       </c>
       <c r="G1695" t="s">
         <v>7212</v>
@@ -74852,7 +74852,7 @@
         <v>7179</v>
       </c>
       <c r="F1698">
-        <v>21741</v>
+        <v>21489</v>
       </c>
       <c r="G1698" t="s">
         <v>7212</v>
@@ -74878,7 +74878,7 @@
         <v>7179</v>
       </c>
       <c r="F1699">
-        <v>17467</v>
+        <v>17419</v>
       </c>
       <c r="G1699" t="s">
         <v>7212</v>
@@ -74930,7 +74930,7 @@
         <v>7179</v>
       </c>
       <c r="F1701">
-        <v>2501</v>
+        <v>2489</v>
       </c>
       <c r="G1701" t="s">
         <v>7212</v>
@@ -75008,7 +75008,7 @@
         <v>7179</v>
       </c>
       <c r="F1704">
-        <v>1860</v>
+        <v>1848</v>
       </c>
       <c r="G1704" t="s">
         <v>7212</v>
@@ -75060,7 +75060,7 @@
         <v>7177</v>
       </c>
       <c r="F1706">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="G1706" t="s">
         <v>7212</v>
@@ -75530,7 +75530,7 @@
         <v>7177</v>
       </c>
       <c r="F1725">
-        <v>887</v>
+        <v>869</v>
       </c>
       <c r="G1725" t="s">
         <v>7212</v>
@@ -75582,7 +75582,7 @@
         <v>7177</v>
       </c>
       <c r="F1727">
-        <v>9746</v>
+        <v>9704</v>
       </c>
       <c r="G1727" t="s">
         <v>7212</v>
@@ -75634,7 +75634,7 @@
         <v>7177</v>
       </c>
       <c r="F1729">
-        <v>1628</v>
+        <v>1622</v>
       </c>
       <c r="G1729" t="s">
         <v>7212</v>
@@ -75790,7 +75790,7 @@
         <v>7177</v>
       </c>
       <c r="F1735">
-        <v>1935</v>
+        <v>1927</v>
       </c>
       <c r="G1735" t="s">
         <v>7212</v>
@@ -75894,7 +75894,7 @@
         <v>7176</v>
       </c>
       <c r="F1739">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G1739" t="s">
         <v>7212</v>
@@ -76286,7 +76286,7 @@
         <v>7209</v>
       </c>
       <c r="F1755">
-        <v>2520</v>
+        <v>2496</v>
       </c>
       <c r="G1755" t="s">
         <v>7212</v>
@@ -76312,7 +76312,7 @@
         <v>7209</v>
       </c>
       <c r="F1756">
-        <v>1727</v>
+        <v>1715</v>
       </c>
       <c r="G1756" t="s">
         <v>7212</v>
@@ -76338,7 +76338,7 @@
         <v>7209</v>
       </c>
       <c r="F1757">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G1757" t="s">
         <v>7212</v>
@@ -76520,7 +76520,7 @@
         <v>7178</v>
       </c>
       <c r="F1764">
-        <v>8415</v>
+        <v>8373</v>
       </c>
       <c r="G1764" t="s">
         <v>7212</v>
@@ -76546,7 +76546,7 @@
         <v>7178</v>
       </c>
       <c r="F1765">
-        <v>52362</v>
+        <v>52158</v>
       </c>
       <c r="G1765" t="s">
         <v>7212</v>
@@ -76572,7 +76572,7 @@
         <v>7178</v>
       </c>
       <c r="F1766">
-        <v>2752</v>
+        <v>2657</v>
       </c>
       <c r="G1766" t="s">
         <v>7212</v>
@@ -76598,7 +76598,7 @@
         <v>7178</v>
       </c>
       <c r="F1767">
-        <v>2894</v>
+        <v>2889</v>
       </c>
       <c r="G1767" t="s">
         <v>7212</v>
@@ -76676,7 +76676,7 @@
         <v>7178</v>
       </c>
       <c r="F1770">
-        <v>2473</v>
+        <v>2443</v>
       </c>
       <c r="G1770" t="s">
         <v>7212</v>
@@ -76754,7 +76754,7 @@
         <v>7178</v>
       </c>
       <c r="F1773">
-        <v>2389</v>
+        <v>2325</v>
       </c>
       <c r="G1773" t="s">
         <v>7212</v>
@@ -76962,7 +76962,7 @@
         <v>7205</v>
       </c>
       <c r="F1781">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G1781" t="s">
         <v>7212</v>
@@ -77144,7 +77144,7 @@
         <v>7205</v>
       </c>
       <c r="F1788">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="G1788" t="s">
         <v>7212</v>
@@ -77482,7 +77482,7 @@
         <v>7193</v>
       </c>
       <c r="F1801">
-        <v>2569</v>
+        <v>2563</v>
       </c>
       <c r="G1801" t="s">
         <v>7212</v>
@@ -77560,7 +77560,7 @@
         <v>7193</v>
       </c>
       <c r="F1804">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="G1804" t="s">
         <v>7212</v>
@@ -77586,7 +77586,7 @@
         <v>7193</v>
       </c>
       <c r="F1805">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="G1805" t="s">
         <v>7212</v>
@@ -77690,7 +77690,7 @@
         <v>7193</v>
       </c>
       <c r="F1809">
-        <v>3318</v>
+        <v>3300</v>
       </c>
       <c r="G1809" t="s">
         <v>7212</v>
@@ -78094,7 +78094,7 @@
         <v>7193</v>
       </c>
       <c r="F1825">
-        <v>2304</v>
+        <v>2274</v>
       </c>
       <c r="G1825" t="s">
         <v>7212</v>
@@ -78120,7 +78120,7 @@
         <v>7193</v>
       </c>
       <c r="F1826">
-        <v>5196</v>
+        <v>5190</v>
       </c>
       <c r="G1826" t="s">
         <v>7212</v>
@@ -78276,7 +78276,7 @@
         <v>7193</v>
       </c>
       <c r="F1832">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="G1832" t="s">
         <v>7212</v>
@@ -78380,7 +78380,7 @@
         <v>7193</v>
       </c>
       <c r="F1836">
-        <v>1013</v>
+        <v>995</v>
       </c>
       <c r="G1836" t="s">
         <v>7212</v>
@@ -78406,7 +78406,7 @@
         <v>7193</v>
       </c>
       <c r="F1837">
-        <v>2620</v>
+        <v>2608</v>
       </c>
       <c r="G1837" t="s">
         <v>7212</v>
@@ -78432,7 +78432,7 @@
         <v>7193</v>
       </c>
       <c r="F1838">
-        <v>3261</v>
+        <v>3243</v>
       </c>
       <c r="G1838" t="s">
         <v>7212</v>
@@ -78588,7 +78588,7 @@
         <v>7193</v>
       </c>
       <c r="F1844">
-        <v>1040</v>
+        <v>1004</v>
       </c>
       <c r="G1844" t="s">
         <v>7212</v>
@@ -78790,7 +78790,7 @@
         <v>7206</v>
       </c>
       <c r="F1852">
-        <v>1436</v>
+        <v>1412</v>
       </c>
       <c r="G1852" t="s">
         <v>7212</v>
@@ -78842,7 +78842,7 @@
         <v>7206</v>
       </c>
       <c r="F1854">
-        <v>1023</v>
+        <v>987</v>
       </c>
       <c r="G1854" t="s">
         <v>7212</v>
@@ -78894,7 +78894,7 @@
         <v>7206</v>
       </c>
       <c r="F1856">
-        <v>2420</v>
+        <v>2408</v>
       </c>
       <c r="G1856" t="s">
         <v>7212</v>
@@ -79024,7 +79024,7 @@
         <v>7206</v>
       </c>
       <c r="F1861">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="G1861" t="s">
         <v>7212</v>
@@ -79128,7 +79128,7 @@
         <v>7206</v>
       </c>
       <c r="F1865">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="G1865" t="s">
         <v>7212</v>
@@ -80912,7 +80912,7 @@
         <v>7189</v>
       </c>
       <c r="F1935">
-        <v>1440</v>
+        <v>1380</v>
       </c>
       <c r="G1935" t="s">
         <v>7212</v>
@@ -82510,7 +82510,7 @@
         <v>7171</v>
       </c>
       <c r="F1999">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G1999" t="s">
         <v>7212</v>
@@ -82662,7 +82662,7 @@
         <v>7171</v>
       </c>
       <c r="F2006">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="G2006" t="s">
         <v>7213</v>
@@ -82814,7 +82814,7 @@
         <v>7171</v>
       </c>
       <c r="F2013">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G2013" t="s">
         <v>7213</v>
@@ -83062,7 +83062,7 @@
         <v>7171</v>
       </c>
       <c r="F2023">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G2023" t="s">
         <v>7212</v>
@@ -83166,7 +83166,7 @@
         <v>7171</v>
       </c>
       <c r="F2027">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="G2027" t="s">
         <v>7212</v>
@@ -83434,7 +83434,7 @@
         <v>7169</v>
       </c>
       <c r="F2038">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G2038" t="s">
         <v>7212</v>
@@ -83460,7 +83460,7 @@
         <v>7169</v>
       </c>
       <c r="F2039">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G2039" t="s">
         <v>7212</v>
@@ -83486,7 +83486,7 @@
         <v>7169</v>
       </c>
       <c r="F2040">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G2040" t="s">
         <v>7212</v>
@@ -83656,7 +83656,7 @@
         <v>7188</v>
       </c>
       <c r="F2047">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="G2047" t="s">
         <v>7212</v>
@@ -83682,7 +83682,7 @@
         <v>7188</v>
       </c>
       <c r="F2048">
-        <v>1413</v>
+        <v>1403</v>
       </c>
       <c r="G2048" t="s">
         <v>7212</v>
@@ -83734,7 +83734,7 @@
         <v>7194</v>
       </c>
       <c r="F2050">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="G2050" t="s">
         <v>7212</v>
@@ -83786,7 +83786,7 @@
         <v>7194</v>
       </c>
       <c r="F2052">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="G2052" t="s">
         <v>7212</v>
@@ -83812,7 +83812,7 @@
         <v>7194</v>
       </c>
       <c r="F2053">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="G2053" t="s">
         <v>7212</v>
@@ -83838,7 +83838,7 @@
         <v>7188</v>
       </c>
       <c r="F2054">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G2054" t="s">
         <v>7212</v>
@@ -83864,7 +83864,7 @@
         <v>7194</v>
       </c>
       <c r="F2055">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="G2055" t="s">
         <v>7212</v>
@@ -83916,7 +83916,7 @@
         <v>7194</v>
       </c>
       <c r="F2057">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="G2057" t="s">
         <v>7212</v>
@@ -83942,7 +83942,7 @@
         <v>7194</v>
       </c>
       <c r="F2058">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G2058" t="s">
         <v>7212</v>
@@ -84046,7 +84046,7 @@
         <v>7188</v>
       </c>
       <c r="F2062">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="G2062" t="s">
         <v>7212</v>
@@ -84072,7 +84072,7 @@
         <v>7188</v>
       </c>
       <c r="F2063">
-        <v>1755</v>
+        <v>1743</v>
       </c>
       <c r="G2063" t="s">
         <v>7212</v>
@@ -84098,7 +84098,7 @@
         <v>7188</v>
       </c>
       <c r="F2064">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="G2064" t="s">
         <v>7212</v>
@@ -84270,7 +84270,7 @@
         <v>7171</v>
       </c>
       <c r="F2072">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G2072" t="s">
         <v>7212</v>
@@ -84462,7 +84462,7 @@
         <v>7171</v>
       </c>
       <c r="F2081">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G2081" t="s">
         <v>7212</v>
@@ -85054,7 +85054,7 @@
         <v>7169</v>
       </c>
       <c r="F2104">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G2104" t="s">
         <v>7212</v>
@@ -87280,7 +87280,7 @@
         <v>7171</v>
       </c>
       <c r="F2194">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="G2194" t="s">
         <v>7213</v>
@@ -87450,7 +87450,7 @@
         <v>7171</v>
       </c>
       <c r="F2201">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G2201" t="s">
         <v>7212</v>
@@ -88128,7 +88128,7 @@
         <v>7173</v>
       </c>
       <c r="F2228">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G2228" t="s">
         <v>7213</v>
@@ -88844,7 +88844,7 @@
         <v>7173</v>
       </c>
       <c r="F2259">
-        <v>10562</v>
+        <v>10322</v>
       </c>
       <c r="G2259" t="s">
         <v>7212</v>
@@ -88896,7 +88896,7 @@
         <v>7173</v>
       </c>
       <c r="F2261">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="G2261" t="s">
         <v>7212</v>
@@ -88994,7 +88994,7 @@
         <v>7173</v>
       </c>
       <c r="F2265">
-        <v>7146</v>
+        <v>7136</v>
       </c>
       <c r="G2265" t="s">
         <v>7212</v>
@@ -89072,7 +89072,7 @@
         <v>7173</v>
       </c>
       <c r="F2268">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G2268" t="s">
         <v>7212</v>
@@ -89302,7 +89302,7 @@
         <v>7173</v>
       </c>
       <c r="F2278">
-        <v>5886</v>
+        <v>5882</v>
       </c>
       <c r="G2278" t="s">
         <v>7212</v>
@@ -89720,7 +89720,7 @@
         <v>7194</v>
       </c>
       <c r="F2295">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G2295" t="s">
         <v>7213</v>
@@ -89960,7 +89960,7 @@
         <v>7171</v>
       </c>
       <c r="F2307">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="G2307" t="s">
         <v>7213</v>
@@ -90020,7 +90020,7 @@
         <v>7171</v>
       </c>
       <c r="F2310">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="G2310" t="s">
         <v>7213</v>
@@ -90060,7 +90060,7 @@
         <v>7171</v>
       </c>
       <c r="F2312">
-        <v>611</v>
+        <v>511</v>
       </c>
       <c r="G2312" t="s">
         <v>7213</v>
@@ -90080,7 +90080,7 @@
         <v>7171</v>
       </c>
       <c r="F2313">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G2313" t="s">
         <v>7213</v>
@@ -90682,7 +90682,7 @@
         <v>7169</v>
       </c>
       <c r="F2338">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G2338" t="s">
         <v>7212</v>
@@ -91272,7 +91272,7 @@
         <v>7169</v>
       </c>
       <c r="F2363">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G2363" t="s">
         <v>7212</v>
@@ -91298,7 +91298,7 @@
         <v>7169</v>
       </c>
       <c r="F2364">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G2364" t="s">
         <v>7212</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -35262,7 +35262,7 @@
         <v>7184</v>
       </c>
       <c r="F86">
-        <v>7209</v>
+        <v>7149</v>
       </c>
       <c r="G86" t="s">
         <v>7215</v>
@@ -35288,7 +35288,7 @@
         <v>7182</v>
       </c>
       <c r="F87">
-        <v>5909</v>
+        <v>5867</v>
       </c>
       <c r="G87" t="s">
         <v>7215</v>
@@ -35680,7 +35680,7 @@
         <v>7186</v>
       </c>
       <c r="F103">
-        <v>3256</v>
+        <v>3246</v>
       </c>
       <c r="G103" t="s">
         <v>7215</v>
@@ -36064,7 +36064,7 @@
         <v>7171</v>
       </c>
       <c r="F118">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G118" t="s">
         <v>7215</v>
@@ -36090,7 +36090,7 @@
         <v>7187</v>
       </c>
       <c r="F119">
-        <v>3257</v>
+        <v>3247</v>
       </c>
       <c r="G119" t="s">
         <v>7215</v>
@@ -36614,7 +36614,7 @@
         <v>7186</v>
       </c>
       <c r="F141">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="G141" t="s">
         <v>7215</v>
@@ -36692,7 +36692,7 @@
         <v>7173</v>
       </c>
       <c r="F144">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G144" t="s">
         <v>7215</v>
@@ -36744,7 +36744,7 @@
         <v>7173</v>
       </c>
       <c r="F146">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G146" t="s">
         <v>7215</v>
@@ -36770,7 +36770,7 @@
         <v>7173</v>
       </c>
       <c r="F147">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G147" t="s">
         <v>7215</v>
@@ -36796,7 +36796,7 @@
         <v>7173</v>
       </c>
       <c r="F148">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="G148" t="s">
         <v>7215</v>
@@ -36874,7 +36874,7 @@
         <v>7173</v>
       </c>
       <c r="F151">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G151" t="s">
         <v>7216</v>
@@ -36894,7 +36894,7 @@
         <v>7173</v>
       </c>
       <c r="F152">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G152" t="s">
         <v>7215</v>
@@ -36946,7 +36946,7 @@
         <v>7173</v>
       </c>
       <c r="F154">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="G154" t="s">
         <v>7216</v>
@@ -37486,7 +37486,7 @@
         <v>7189</v>
       </c>
       <c r="F175">
-        <v>4242</v>
+        <v>4234</v>
       </c>
       <c r="G175" t="s">
         <v>7215</v>
@@ -37720,7 +37720,7 @@
         <v>7189</v>
       </c>
       <c r="F184">
-        <v>2292</v>
+        <v>2286</v>
       </c>
       <c r="G184" t="s">
         <v>7215</v>
@@ -38188,7 +38188,7 @@
         <v>7189</v>
       </c>
       <c r="F202">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="G202" t="s">
         <v>7215</v>
@@ -38292,7 +38292,7 @@
         <v>7189</v>
       </c>
       <c r="F206">
-        <v>2661</v>
+        <v>2655</v>
       </c>
       <c r="G206" t="s">
         <v>7216</v>
@@ -38312,7 +38312,7 @@
         <v>7189</v>
       </c>
       <c r="F207">
-        <v>2862</v>
+        <v>2856</v>
       </c>
       <c r="G207" t="s">
         <v>7215</v>
@@ -38364,7 +38364,7 @@
         <v>7189</v>
       </c>
       <c r="F209">
-        <v>2319</v>
+        <v>2313</v>
       </c>
       <c r="G209" t="s">
         <v>7215</v>
@@ -38462,7 +38462,7 @@
         <v>7189</v>
       </c>
       <c r="F213">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G213" t="s">
         <v>7215</v>
@@ -38592,7 +38592,7 @@
         <v>7189</v>
       </c>
       <c r="F218">
-        <v>3275</v>
+        <v>3269</v>
       </c>
       <c r="G218" t="s">
         <v>7215</v>
@@ -39896,7 +39896,7 @@
         <v>7191</v>
       </c>
       <c r="F270">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G270" t="s">
         <v>7215</v>
@@ -39922,7 +39922,7 @@
         <v>7191</v>
       </c>
       <c r="F271">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G271" t="s">
         <v>7215</v>
@@ -39948,7 +39948,7 @@
         <v>7191</v>
       </c>
       <c r="F272">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="G272" t="s">
         <v>7215</v>
@@ -40334,7 +40334,7 @@
         <v>7191</v>
       </c>
       <c r="F288">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="G288" t="s">
         <v>7215</v>
@@ -41742,7 +41742,7 @@
         <v>7171</v>
       </c>
       <c r="F344">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G344" t="s">
         <v>7215</v>
@@ -42410,7 +42410,7 @@
         <v>7177</v>
       </c>
       <c r="F372">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G372" t="s">
         <v>7215</v>
@@ -42436,7 +42436,7 @@
         <v>7177</v>
       </c>
       <c r="F373">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G373" t="s">
         <v>7215</v>
@@ -42462,7 +42462,7 @@
         <v>7177</v>
       </c>
       <c r="F374">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G374" t="s">
         <v>7215</v>
@@ -42488,7 +42488,7 @@
         <v>7191</v>
       </c>
       <c r="F375">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="G375" t="s">
         <v>7215</v>
@@ -42696,7 +42696,7 @@
         <v>7177</v>
       </c>
       <c r="F383">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="G383" t="s">
         <v>7215</v>
@@ -42982,7 +42982,7 @@
         <v>7177</v>
       </c>
       <c r="F394">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G394" t="s">
         <v>7215</v>
@@ -43034,7 +43034,7 @@
         <v>7177</v>
       </c>
       <c r="F396">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="G396" t="s">
         <v>7215</v>
@@ -43138,7 +43138,7 @@
         <v>7191</v>
       </c>
       <c r="F400">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="G400" t="s">
         <v>7215</v>
@@ -43190,7 +43190,7 @@
         <v>7196</v>
       </c>
       <c r="F402">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G402" t="s">
         <v>7215</v>
@@ -43268,7 +43268,7 @@
         <v>7177</v>
       </c>
       <c r="F405">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="G405" t="s">
         <v>7215</v>
@@ -43372,7 +43372,7 @@
         <v>7196</v>
       </c>
       <c r="F409">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="G409" t="s">
         <v>7215</v>
@@ -43438,7 +43438,7 @@
         <v>7173</v>
       </c>
       <c r="F412">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G412" t="s">
         <v>7215</v>
@@ -43464,7 +43464,7 @@
         <v>7173</v>
       </c>
       <c r="F413">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G413" t="s">
         <v>7215</v>
@@ -43516,7 +43516,7 @@
         <v>7173</v>
       </c>
       <c r="F415">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="G415" t="s">
         <v>7215</v>
@@ -43542,7 +43542,7 @@
         <v>7173</v>
       </c>
       <c r="F416">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="G416" t="s">
         <v>7215</v>
@@ -43568,7 +43568,7 @@
         <v>7173</v>
       </c>
       <c r="F417">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="G417" t="s">
         <v>7216</v>
@@ -43614,7 +43614,7 @@
         <v>7173</v>
       </c>
       <c r="F419">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="G419" t="s">
         <v>7215</v>
@@ -46142,7 +46142,7 @@
         <v>7171</v>
       </c>
       <c r="F522">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G522" t="s">
         <v>7215</v>
@@ -46422,7 +46422,7 @@
         <v>7171</v>
       </c>
       <c r="F533">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G533" t="s">
         <v>7215</v>
@@ -46578,7 +46578,7 @@
         <v>7171</v>
       </c>
       <c r="F539">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G539" t="s">
         <v>7215</v>
@@ -46874,7 +46874,7 @@
         <v>7196</v>
       </c>
       <c r="F552">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="G552" t="s">
         <v>7215</v>
@@ -46900,7 +46900,7 @@
         <v>7196</v>
       </c>
       <c r="F553">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="G553" t="s">
         <v>7215</v>
@@ -46926,7 +46926,7 @@
         <v>7196</v>
       </c>
       <c r="F554">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="G554" t="s">
         <v>7215</v>
@@ -46978,7 +46978,7 @@
         <v>7196</v>
       </c>
       <c r="F556">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="G556" t="s">
         <v>7215</v>
@@ -47030,7 +47030,7 @@
         <v>7196</v>
       </c>
       <c r="F558">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="G558" t="s">
         <v>7215</v>
@@ -47186,7 +47186,7 @@
         <v>7191</v>
       </c>
       <c r="F564">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="G564" t="s">
         <v>7215</v>
@@ -47238,7 +47238,7 @@
         <v>7191</v>
       </c>
       <c r="F566">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="G566" t="s">
         <v>7215</v>
@@ -47264,7 +47264,7 @@
         <v>7196</v>
       </c>
       <c r="F567">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="G567" t="s">
         <v>7215</v>
@@ -47310,7 +47310,7 @@
         <v>7186</v>
       </c>
       <c r="F569">
-        <v>3655</v>
+        <v>3651</v>
       </c>
       <c r="G569" t="s">
         <v>7215</v>
@@ -59222,7 +59222,7 @@
         <v>7190</v>
       </c>
       <c r="F1044">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G1044" t="s">
         <v>7216</v>
@@ -59320,7 +59320,7 @@
         <v>7190</v>
       </c>
       <c r="F1048">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G1048" t="s">
         <v>7216</v>
@@ -59340,7 +59340,7 @@
         <v>7190</v>
       </c>
       <c r="F1049">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G1049" t="s">
         <v>7216</v>
@@ -63415,7 +63415,7 @@
         <v>7189</v>
       </c>
       <c r="F1225">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G1225" t="s">
         <v>7215</v>
@@ -63467,7 +63467,7 @@
         <v>7189</v>
       </c>
       <c r="F1227">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="G1227" t="s">
         <v>7215</v>
@@ -64671,7 +64671,7 @@
         <v>7189</v>
       </c>
       <c r="F1277">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G1277" t="s">
         <v>7215</v>
@@ -64723,7 +64723,7 @@
         <v>7189</v>
       </c>
       <c r="F1279">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="G1279" t="s">
         <v>7215</v>
@@ -65731,7 +65731,7 @@
         <v>7189</v>
       </c>
       <c r="F1321">
-        <v>1476</v>
+        <v>1464</v>
       </c>
       <c r="G1321" t="s">
         <v>7215</v>
@@ -65809,7 +65809,7 @@
         <v>7189</v>
       </c>
       <c r="F1324">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="G1324" t="s">
         <v>7215</v>
@@ -65991,7 +65991,7 @@
         <v>7189</v>
       </c>
       <c r="F1331">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G1331" t="s">
         <v>7215</v>
@@ -66129,7 +66129,7 @@
         <v>7189</v>
       </c>
       <c r="F1337">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G1337" t="s">
         <v>7215</v>
@@ -66155,7 +66155,7 @@
         <v>7189</v>
       </c>
       <c r="F1338">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="G1338" t="s">
         <v>7215</v>
@@ -66207,7 +66207,7 @@
         <v>7189</v>
       </c>
       <c r="F1340">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G1340" t="s">
         <v>7215</v>
@@ -66259,7 +66259,7 @@
         <v>7189</v>
       </c>
       <c r="F1342">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G1342" t="s">
         <v>7215</v>
@@ -72103,7 +72103,7 @@
         <v>7211</v>
       </c>
       <c r="F1588">
-        <v>3829</v>
+        <v>3811</v>
       </c>
       <c r="G1588" t="s">
         <v>7215</v>
@@ -72519,7 +72519,7 @@
         <v>7211</v>
       </c>
       <c r="F1604">
-        <v>1964</v>
+        <v>1946</v>
       </c>
       <c r="G1604" t="s">
         <v>7215</v>
@@ -72545,7 +72545,7 @@
         <v>7211</v>
       </c>
       <c r="F1605">
-        <v>1371</v>
+        <v>1335</v>
       </c>
       <c r="G1605" t="s">
         <v>7215</v>
@@ -72597,7 +72597,7 @@
         <v>7211</v>
       </c>
       <c r="F1607">
-        <v>3351</v>
+        <v>3333</v>
       </c>
       <c r="G1607" t="s">
         <v>7215</v>
@@ -72623,7 +72623,7 @@
         <v>7211</v>
       </c>
       <c r="F1608">
-        <v>2170</v>
+        <v>2152</v>
       </c>
       <c r="G1608" t="s">
         <v>7215</v>
@@ -75603,7 +75603,7 @@
         <v>7178</v>
       </c>
       <c r="F1724">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G1724" t="s">
         <v>7215</v>
@@ -83185,7 +83185,7 @@
         <v>7171</v>
       </c>
       <c r="F2023">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G2023" t="s">
         <v>7216</v>
@@ -83205,7 +83205,7 @@
         <v>7171</v>
       </c>
       <c r="F2024">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G2024" t="s">
         <v>7216</v>
@@ -83511,7 +83511,7 @@
         <v>7196</v>
       </c>
       <c r="F2036">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="G2036" t="s">
         <v>7215</v>
@@ -83733,7 +83733,7 @@
         <v>7196</v>
       </c>
       <c r="F2045">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="G2045" t="s">
         <v>7215</v>
@@ -83811,7 +83811,7 @@
         <v>7196</v>
       </c>
       <c r="F2048">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G2048" t="s">
         <v>7215</v>
@@ -85729,7 +85729,7 @@
         <v>7191</v>
       </c>
       <c r="F2125">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="G2125" t="s">
         <v>7215</v>
@@ -86095,7 +86095,7 @@
         <v>7171</v>
       </c>
       <c r="F2140">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2140" t="s">
         <v>7216</v>
@@ -89239,7 +89239,7 @@
         <v>7173</v>
       </c>
       <c r="F2269">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2269" t="s">
         <v>7215</v>
@@ -91079,7 +91079,7 @@
         <v>7196</v>
       </c>
       <c r="F2349">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G2349" t="s">
         <v>7215</v>
@@ -92019,7 +92019,7 @@
         <v>7177</v>
       </c>
       <c r="F2387">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G2387" t="s">
         <v>7215</v>
@@ -92149,7 +92149,7 @@
         <v>7177</v>
       </c>
       <c r="F2392">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G2392" t="s">
         <v>7215</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -63972,7 +63972,7 @@
         <v>7191</v>
       </c>
       <c r="F1247">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="G1247" t="s">
         <v>7219</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -34139,7 +34139,7 @@
         <v>7168</v>
       </c>
       <c r="F39">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G39" t="s">
         <v>7213</v>
@@ -34217,7 +34217,7 @@
         <v>7168</v>
       </c>
       <c r="F42">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G42" t="s">
         <v>7213</v>
@@ -40533,7 +40533,7 @@
         <v>7171</v>
       </c>
       <c r="F296">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G296" t="s">
         <v>7213</v>
@@ -41017,7 +41017,7 @@
         <v>7169</v>
       </c>
       <c r="F316">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G316" t="s">
         <v>7213</v>
@@ -41239,7 +41239,7 @@
         <v>7178</v>
       </c>
       <c r="F325">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="G325" t="s">
         <v>7213</v>
@@ -41265,7 +41265,7 @@
         <v>7178</v>
       </c>
       <c r="F326">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G326" t="s">
         <v>7213</v>
@@ -41343,7 +41343,7 @@
         <v>7178</v>
       </c>
       <c r="F329">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G329" t="s">
         <v>7213</v>
@@ -42763,7 +42763,7 @@
         <v>7169</v>
       </c>
       <c r="F385">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="G385" t="s">
         <v>7213</v>
@@ -42841,7 +42841,7 @@
         <v>7169</v>
       </c>
       <c r="F388">
-        <v>780</v>
+        <v>757</v>
       </c>
       <c r="G388" t="s">
         <v>7213</v>
@@ -42893,7 +42893,7 @@
         <v>7169</v>
       </c>
       <c r="F390">
-        <v>662</v>
+        <v>643</v>
       </c>
       <c r="G390" t="s">
         <v>7213</v>
@@ -42945,7 +42945,7 @@
         <v>7169</v>
       </c>
       <c r="F392">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="G392" t="s">
         <v>7213</v>
@@ -42971,7 +42971,7 @@
         <v>7169</v>
       </c>
       <c r="F393">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="G393" t="s">
         <v>7213</v>
@@ -42997,7 +42997,7 @@
         <v>7169</v>
       </c>
       <c r="F394">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="G394" t="s">
         <v>7213</v>
@@ -44019,7 +44019,7 @@
         <v>7178</v>
       </c>
       <c r="F437">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G437" t="s">
         <v>7213</v>
@@ -44071,7 +44071,7 @@
         <v>7178</v>
       </c>
       <c r="F439">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G439" t="s">
         <v>7213</v>
@@ -44097,7 +44097,7 @@
         <v>7178</v>
       </c>
       <c r="F440">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G440" t="s">
         <v>7213</v>
@@ -44227,7 +44227,7 @@
         <v>7171</v>
       </c>
       <c r="F445">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G445" t="s">
         <v>7213</v>
@@ -45503,7 +45503,7 @@
         <v>7193</v>
       </c>
       <c r="F495">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G495" t="s">
         <v>7213</v>
@@ -45687,7 +45687,7 @@
         <v>7171</v>
       </c>
       <c r="F503">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="G503" t="s">
         <v>7213</v>
@@ -45713,7 +45713,7 @@
         <v>7171</v>
       </c>
       <c r="F504">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G504" t="s">
         <v>7213</v>
@@ -45791,7 +45791,7 @@
         <v>7171</v>
       </c>
       <c r="F507">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G507" t="s">
         <v>7213</v>
@@ -46071,7 +46071,7 @@
         <v>7171</v>
       </c>
       <c r="F518">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G518" t="s">
         <v>7213</v>
@@ -46097,7 +46097,7 @@
         <v>7171</v>
       </c>
       <c r="F519">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="G519" t="s">
         <v>7213</v>
@@ -47329,7 +47329,7 @@
         <v>7169</v>
       </c>
       <c r="F568">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G568" t="s">
         <v>7213</v>
@@ -70784,7 +70784,7 @@
         <v>7169</v>
       </c>
       <c r="F1530">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G1530" t="s">
         <v>7213</v>
@@ -83756,7 +83756,7 @@
         <v>7194</v>
       </c>
       <c r="F2046">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G2046" t="s">
         <v>7213</v>
@@ -84250,7 +84250,7 @@
         <v>7169</v>
       </c>
       <c r="F2065">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="G2065" t="s">
         <v>7213</v>
@@ -85882,7 +85882,7 @@
         <v>7169</v>
       </c>
       <c r="F2131">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2131" t="s">
         <v>7213</v>
@@ -91440,7 +91440,7 @@
         <v>7194</v>
       </c>
       <c r="F2363">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G2363" t="s">
         <v>7212</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -33237,7 +33237,7 @@
         <v>7184</v>
       </c>
       <c r="F2">
-        <v>19796</v>
+        <v>19316</v>
       </c>
       <c r="G2" t="s">
         <v>7228</v>
@@ -33289,7 +33289,7 @@
         <v>7185</v>
       </c>
       <c r="F4">
-        <v>49397</v>
+        <v>48851</v>
       </c>
       <c r="G4" t="s">
         <v>7228</v>
@@ -33721,7 +33721,7 @@
         <v>7187</v>
       </c>
       <c r="F22">
-        <v>2435</v>
+        <v>2429</v>
       </c>
       <c r="G22" t="s">
         <v>7228</v>
@@ -33865,7 +33865,7 @@
         <v>7187</v>
       </c>
       <c r="F28">
-        <v>1254</v>
+        <v>1224</v>
       </c>
       <c r="G28" t="s">
         <v>7229</v>
@@ -33925,7 +33925,7 @@
         <v>7187</v>
       </c>
       <c r="F31">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G31" t="s">
         <v>7229</v>
@@ -33945,7 +33945,7 @@
         <v>7187</v>
       </c>
       <c r="F32">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="G32" t="s">
         <v>7229</v>
@@ -34005,7 +34005,7 @@
         <v>7187</v>
       </c>
       <c r="F35">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="G35" t="s">
         <v>7228</v>
@@ -34031,7 +34031,7 @@
         <v>7187</v>
       </c>
       <c r="F36">
-        <v>1984</v>
+        <v>1929</v>
       </c>
       <c r="G36" t="s">
         <v>7228</v>
@@ -34057,7 +34057,7 @@
         <v>7187</v>
       </c>
       <c r="F37">
-        <v>2517</v>
+        <v>2463</v>
       </c>
       <c r="G37" t="s">
         <v>7228</v>
@@ -34187,7 +34187,7 @@
         <v>7187</v>
       </c>
       <c r="F42">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="G42" t="s">
         <v>7228</v>
@@ -34265,7 +34265,7 @@
         <v>7187</v>
       </c>
       <c r="F45">
-        <v>1654</v>
+        <v>1636</v>
       </c>
       <c r="G45" t="s">
         <v>7228</v>
@@ -34291,7 +34291,7 @@
         <v>7187</v>
       </c>
       <c r="F46">
-        <v>4493</v>
+        <v>4457</v>
       </c>
       <c r="G46" t="s">
         <v>7228</v>
@@ -34519,7 +34519,7 @@
         <v>7187</v>
       </c>
       <c r="F55">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G55" t="s">
         <v>7228</v>
@@ -34715,7 +34715,7 @@
         <v>7187</v>
       </c>
       <c r="F63">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
         <v>7228</v>
@@ -35027,7 +35027,7 @@
         <v>7187</v>
       </c>
       <c r="F75">
-        <v>1199</v>
+        <v>1163</v>
       </c>
       <c r="G75" t="s">
         <v>7229</v>
@@ -35047,7 +35047,7 @@
         <v>7186</v>
       </c>
       <c r="F76">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G76" t="s">
         <v>7228</v>
@@ -35133,7 +35133,7 @@
         <v>7186</v>
       </c>
       <c r="F80">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G80" t="s">
         <v>7228</v>
@@ -35237,7 +35237,7 @@
         <v>7186</v>
       </c>
       <c r="F84">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s">
         <v>7228</v>
@@ -35263,7 +35263,7 @@
         <v>7186</v>
       </c>
       <c r="F85">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G85" t="s">
         <v>7228</v>
@@ -35289,7 +35289,7 @@
         <v>7189</v>
       </c>
       <c r="F86">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G86" t="s">
         <v>7228</v>
@@ -35335,7 +35335,7 @@
         <v>7186</v>
       </c>
       <c r="F88">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s">
         <v>7228</v>
@@ -35361,7 +35361,7 @@
         <v>7189</v>
       </c>
       <c r="F89">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G89" t="s">
         <v>7228</v>
@@ -35433,7 +35433,7 @@
         <v>7189</v>
       </c>
       <c r="F92">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G92" t="s">
         <v>7228</v>
@@ -35459,7 +35459,7 @@
         <v>7186</v>
       </c>
       <c r="F93">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G93" t="s">
         <v>7228</v>
@@ -35531,7 +35531,7 @@
         <v>7186</v>
       </c>
       <c r="F96">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G96" t="s">
         <v>7228</v>
@@ -35655,7 +35655,7 @@
         <v>7186</v>
       </c>
       <c r="F101">
-        <v>315</v>
+        <v>265</v>
       </c>
       <c r="G101" t="s">
         <v>7229</v>
@@ -35695,7 +35695,7 @@
         <v>7186</v>
       </c>
       <c r="F103">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G103" t="s">
         <v>7228</v>
@@ -35741,7 +35741,7 @@
         <v>7186</v>
       </c>
       <c r="F105">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G105" t="s">
         <v>7228</v>
@@ -35767,7 +35767,7 @@
         <v>7186</v>
       </c>
       <c r="F106">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G106" t="s">
         <v>7228</v>
@@ -35793,7 +35793,7 @@
         <v>7186</v>
       </c>
       <c r="F107">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G107" t="s">
         <v>7228</v>
@@ -35819,7 +35819,7 @@
         <v>7186</v>
       </c>
       <c r="F108">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G108" t="s">
         <v>7228</v>
@@ -36145,7 +36145,7 @@
         <v>7186</v>
       </c>
       <c r="F121">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="G121" t="s">
         <v>7228</v>
@@ -36191,7 +36191,7 @@
         <v>7191</v>
       </c>
       <c r="F123">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="G123" t="s">
         <v>7228</v>
@@ -36217,7 +36217,7 @@
         <v>7191</v>
       </c>
       <c r="F124">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="G124" t="s">
         <v>7228</v>
@@ -36243,7 +36243,7 @@
         <v>7191</v>
       </c>
       <c r="F125">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="G125" t="s">
         <v>7228</v>
@@ -36543,7 +36543,7 @@
         <v>7191</v>
       </c>
       <c r="F137">
-        <v>2296</v>
+        <v>2292</v>
       </c>
       <c r="G137" t="s">
         <v>7228</v>
@@ -36589,7 +36589,7 @@
         <v>7191</v>
       </c>
       <c r="F139">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="G139" t="s">
         <v>7228</v>
@@ -36675,7 +36675,7 @@
         <v>7186</v>
       </c>
       <c r="F143">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G143" t="s">
         <v>7228</v>
@@ -36727,7 +36727,7 @@
         <v>7195</v>
       </c>
       <c r="F145">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G145" t="s">
         <v>7228</v>
@@ -36753,7 +36753,7 @@
         <v>7189</v>
       </c>
       <c r="F146">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="G146" t="s">
         <v>7228</v>
@@ -36779,7 +36779,7 @@
         <v>7191</v>
       </c>
       <c r="F147">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="G147" t="s">
         <v>7228</v>
@@ -36891,7 +36891,7 @@
         <v>7189</v>
       </c>
       <c r="F152">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G152" t="s">
         <v>7228</v>
@@ -36917,7 +36917,7 @@
         <v>7189</v>
       </c>
       <c r="F153">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G153" t="s">
         <v>7229</v>
@@ -36937,7 +36937,7 @@
         <v>7189</v>
       </c>
       <c r="F154">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G154" t="s">
         <v>7229</v>
@@ -36957,7 +36957,7 @@
         <v>7189</v>
       </c>
       <c r="F155">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G155" t="s">
         <v>7229</v>
@@ -36977,7 +36977,7 @@
         <v>7186</v>
       </c>
       <c r="F156">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G156" t="s">
         <v>7228</v>
@@ -37101,7 +37101,7 @@
         <v>7198</v>
       </c>
       <c r="F161">
-        <v>3442</v>
+        <v>3440</v>
       </c>
       <c r="G161" t="s">
         <v>7228</v>
@@ -37127,7 +37127,7 @@
         <v>7198</v>
       </c>
       <c r="F162">
-        <v>3413</v>
+        <v>3403</v>
       </c>
       <c r="G162" t="s">
         <v>7228</v>
@@ -37153,7 +37153,7 @@
         <v>7198</v>
       </c>
       <c r="F163">
-        <v>3429</v>
+        <v>3425</v>
       </c>
       <c r="G163" t="s">
         <v>7228</v>
@@ -37199,7 +37199,7 @@
         <v>7198</v>
       </c>
       <c r="F165">
-        <v>3414</v>
+        <v>3406</v>
       </c>
       <c r="G165" t="s">
         <v>7228</v>
@@ -37251,7 +37251,7 @@
         <v>7199</v>
       </c>
       <c r="F167">
-        <v>3131</v>
+        <v>3111</v>
       </c>
       <c r="G167" t="s">
         <v>7228</v>
@@ -37277,7 +37277,7 @@
         <v>7199</v>
       </c>
       <c r="F168">
-        <v>3070</v>
+        <v>3040</v>
       </c>
       <c r="G168" t="s">
         <v>7228</v>
@@ -37303,7 +37303,7 @@
         <v>7200</v>
       </c>
       <c r="F169">
-        <v>3142</v>
+        <v>3130</v>
       </c>
       <c r="G169" t="s">
         <v>7228</v>
@@ -37329,7 +37329,7 @@
         <v>7200</v>
       </c>
       <c r="F170">
-        <v>3124</v>
+        <v>3088</v>
       </c>
       <c r="G170" t="s">
         <v>7228</v>
@@ -37381,7 +37381,7 @@
         <v>7198</v>
       </c>
       <c r="F172">
-        <v>3434</v>
+        <v>3424</v>
       </c>
       <c r="G172" t="s">
         <v>7228</v>
@@ -37453,7 +37453,7 @@
         <v>7184</v>
       </c>
       <c r="F175">
-        <v>916</v>
+        <v>784</v>
       </c>
       <c r="G175" t="s">
         <v>7228</v>
@@ -37505,7 +37505,7 @@
         <v>7201</v>
       </c>
       <c r="F177">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G177" t="s">
         <v>7228</v>
@@ -37557,7 +37557,7 @@
         <v>7201</v>
       </c>
       <c r="F179">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G179" t="s">
         <v>7228</v>
@@ -37681,7 +37681,7 @@
         <v>7198</v>
       </c>
       <c r="F184">
-        <v>3441</v>
+        <v>3431</v>
       </c>
       <c r="G184" t="s">
         <v>7228</v>
@@ -37707,7 +37707,7 @@
         <v>7198</v>
       </c>
       <c r="F185">
-        <v>3374</v>
+        <v>3364</v>
       </c>
       <c r="G185" t="s">
         <v>7228</v>
@@ -37733,7 +37733,7 @@
         <v>7198</v>
       </c>
       <c r="F186">
-        <v>3405</v>
+        <v>3391</v>
       </c>
       <c r="G186" t="s">
         <v>7228</v>
@@ -37785,7 +37785,7 @@
         <v>7186</v>
       </c>
       <c r="F188">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G188" t="s">
         <v>7229</v>
@@ -37805,7 +37805,7 @@
         <v>7186</v>
       </c>
       <c r="F189">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G189" t="s">
         <v>7228</v>
@@ -37831,7 +37831,7 @@
         <v>7186</v>
       </c>
       <c r="F190">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G190" t="s">
         <v>7228</v>
@@ -37969,7 +37969,7 @@
         <v>7198</v>
       </c>
       <c r="F196">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="G196" t="s">
         <v>7228</v>
@@ -37995,7 +37995,7 @@
         <v>7198</v>
       </c>
       <c r="F197">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="G197" t="s">
         <v>7228</v>
@@ -38067,7 +38067,7 @@
         <v>7198</v>
       </c>
       <c r="F200">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="G200" t="s">
         <v>7228</v>
@@ -38145,7 +38145,7 @@
         <v>7198</v>
       </c>
       <c r="F203">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="G203" t="s">
         <v>7228</v>
@@ -38197,7 +38197,7 @@
         <v>7198</v>
       </c>
       <c r="F205">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G205" t="s">
         <v>7228</v>
@@ -38249,7 +38249,7 @@
         <v>7198</v>
       </c>
       <c r="F207">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="G207" t="s">
         <v>7228</v>
@@ -38275,7 +38275,7 @@
         <v>7198</v>
       </c>
       <c r="F208">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="G208" t="s">
         <v>7228</v>
@@ -38327,7 +38327,7 @@
         <v>7198</v>
       </c>
       <c r="F210">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="G210" t="s">
         <v>7228</v>
@@ -38353,7 +38353,7 @@
         <v>7198</v>
       </c>
       <c r="F211">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G211" t="s">
         <v>7228</v>
@@ -38379,7 +38379,7 @@
         <v>7186</v>
       </c>
       <c r="F212">
-        <v>843</v>
+        <v>819</v>
       </c>
       <c r="G212" t="s">
         <v>7228</v>
@@ -38405,7 +38405,7 @@
         <v>7189</v>
       </c>
       <c r="F213">
-        <v>648</v>
+        <v>598</v>
       </c>
       <c r="G213" t="s">
         <v>7228</v>
@@ -38431,7 +38431,7 @@
         <v>7199</v>
       </c>
       <c r="F214">
-        <v>2620</v>
+        <v>2601</v>
       </c>
       <c r="G214" t="s">
         <v>7228</v>
@@ -38457,7 +38457,7 @@
         <v>7200</v>
       </c>
       <c r="F215">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="G215" t="s">
         <v>7228</v>
@@ -38483,7 +38483,7 @@
         <v>7186</v>
       </c>
       <c r="F216">
-        <v>715</v>
+        <v>691</v>
       </c>
       <c r="G216" t="s">
         <v>7228</v>
@@ -38509,7 +38509,7 @@
         <v>7186</v>
       </c>
       <c r="F217">
-        <v>1130</v>
+        <v>1107</v>
       </c>
       <c r="G217" t="s">
         <v>7228</v>
@@ -38535,7 +38535,7 @@
         <v>7189</v>
       </c>
       <c r="F218">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="G218" t="s">
         <v>7228</v>
@@ -38561,7 +38561,7 @@
         <v>7189</v>
       </c>
       <c r="F219">
-        <v>648</v>
+        <v>602</v>
       </c>
       <c r="G219" t="s">
         <v>7228</v>
@@ -38587,7 +38587,7 @@
         <v>7189</v>
       </c>
       <c r="F220">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="G220" t="s">
         <v>7228</v>
@@ -38613,7 +38613,7 @@
         <v>7189</v>
       </c>
       <c r="F221">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="G221" t="s">
         <v>7228</v>
@@ -38639,7 +38639,7 @@
         <v>7189</v>
       </c>
       <c r="F222">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="G222" t="s">
         <v>7228</v>
@@ -38665,7 +38665,7 @@
         <v>7189</v>
       </c>
       <c r="F223">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="G223" t="s">
         <v>7229</v>
@@ -38685,7 +38685,7 @@
         <v>7189</v>
       </c>
       <c r="F224">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="G224" t="s">
         <v>7228</v>
@@ -38711,7 +38711,7 @@
         <v>7189</v>
       </c>
       <c r="F225">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="G225" t="s">
         <v>7228</v>
@@ -38737,7 +38737,7 @@
         <v>7189</v>
       </c>
       <c r="F226">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="G226" t="s">
         <v>7228</v>
@@ -38763,7 +38763,7 @@
         <v>7189</v>
       </c>
       <c r="F227">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="G227" t="s">
         <v>7228</v>
@@ -38789,7 +38789,7 @@
         <v>7189</v>
       </c>
       <c r="F228">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G228" t="s">
         <v>7229</v>
@@ -38809,7 +38809,7 @@
         <v>7189</v>
       </c>
       <c r="F229">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="G229" t="s">
         <v>7228</v>
@@ -38835,7 +38835,7 @@
         <v>7189</v>
       </c>
       <c r="F230">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="G230" t="s">
         <v>7228</v>
@@ -38887,7 +38887,7 @@
         <v>7202</v>
       </c>
       <c r="F232">
-        <v>22476</v>
+        <v>22463</v>
       </c>
       <c r="G232" t="s">
         <v>7228</v>
@@ -38913,7 +38913,7 @@
         <v>7202</v>
       </c>
       <c r="F233">
-        <v>2137</v>
+        <v>2125</v>
       </c>
       <c r="G233" t="s">
         <v>7228</v>
@@ -38939,7 +38939,7 @@
         <v>7202</v>
       </c>
       <c r="F234">
-        <v>2213</v>
+        <v>2189</v>
       </c>
       <c r="G234" t="s">
         <v>7228</v>
@@ -38965,7 +38965,7 @@
         <v>7202</v>
       </c>
       <c r="F235">
-        <v>2248</v>
+        <v>2224</v>
       </c>
       <c r="G235" t="s">
         <v>7228</v>
@@ -38991,7 +38991,7 @@
         <v>7202</v>
       </c>
       <c r="F236">
-        <v>2146</v>
+        <v>2122</v>
       </c>
       <c r="G236" t="s">
         <v>7228</v>
@@ -39017,7 +39017,7 @@
         <v>7202</v>
       </c>
       <c r="F237">
-        <v>2254</v>
+        <v>2242</v>
       </c>
       <c r="G237" t="s">
         <v>7228</v>
@@ -39069,7 +39069,7 @@
         <v>7202</v>
       </c>
       <c r="F239">
-        <v>22548</v>
+        <v>22547</v>
       </c>
       <c r="G239" t="s">
         <v>7228</v>
@@ -39095,7 +39095,7 @@
         <v>7202</v>
       </c>
       <c r="F240">
-        <v>2195</v>
+        <v>2171</v>
       </c>
       <c r="G240" t="s">
         <v>7228</v>
@@ -39173,7 +39173,7 @@
         <v>7202</v>
       </c>
       <c r="F243">
-        <v>1871</v>
+        <v>1859</v>
       </c>
       <c r="G243" t="s">
         <v>7228</v>
@@ -39199,7 +39199,7 @@
         <v>7202</v>
       </c>
       <c r="F244">
-        <v>1966</v>
+        <v>1954</v>
       </c>
       <c r="G244" t="s">
         <v>7228</v>
@@ -39225,7 +39225,7 @@
         <v>7203</v>
       </c>
       <c r="F245">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="G245" t="s">
         <v>7228</v>
@@ -39251,7 +39251,7 @@
         <v>7203</v>
       </c>
       <c r="F246">
-        <v>2534</v>
+        <v>2522</v>
       </c>
       <c r="G246" t="s">
         <v>7229</v>
@@ -39271,7 +39271,7 @@
         <v>7203</v>
       </c>
       <c r="F247">
-        <v>2579</v>
+        <v>2558</v>
       </c>
       <c r="G247" t="s">
         <v>7228</v>
@@ -39297,7 +39297,7 @@
         <v>7203</v>
       </c>
       <c r="F248">
-        <v>3138</v>
+        <v>3132</v>
       </c>
       <c r="G248" t="s">
         <v>7229</v>
@@ -39317,7 +39317,7 @@
         <v>7203</v>
       </c>
       <c r="F249">
-        <v>2132</v>
+        <v>2111</v>
       </c>
       <c r="G249" t="s">
         <v>7228</v>
@@ -39343,7 +39343,7 @@
         <v>7203</v>
       </c>
       <c r="F250">
-        <v>2846</v>
+        <v>2843</v>
       </c>
       <c r="G250" t="s">
         <v>7228</v>
@@ -39369,7 +39369,7 @@
         <v>7203</v>
       </c>
       <c r="F251">
-        <v>3200</v>
+        <v>3191</v>
       </c>
       <c r="G251" t="s">
         <v>7228</v>
@@ -39395,7 +39395,7 @@
         <v>7203</v>
       </c>
       <c r="F252">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="G252" t="s">
         <v>7228</v>
@@ -39447,7 +39447,7 @@
         <v>7203</v>
       </c>
       <c r="F254">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="G254" t="s">
         <v>7228</v>
@@ -39473,7 +39473,7 @@
         <v>7203</v>
       </c>
       <c r="F255">
-        <v>1206</v>
+        <v>1173</v>
       </c>
       <c r="G255" t="s">
         <v>7228</v>
@@ -39499,7 +39499,7 @@
         <v>7203</v>
       </c>
       <c r="F256">
-        <v>1504</v>
+        <v>1486</v>
       </c>
       <c r="G256" t="s">
         <v>7228</v>
@@ -39525,7 +39525,7 @@
         <v>7203</v>
       </c>
       <c r="F257">
-        <v>3048</v>
+        <v>3027</v>
       </c>
       <c r="G257" t="s">
         <v>7228</v>
@@ -39551,7 +39551,7 @@
         <v>7203</v>
       </c>
       <c r="F258">
-        <v>1797</v>
+        <v>1764</v>
       </c>
       <c r="G258" t="s">
         <v>7228</v>
@@ -39577,7 +39577,7 @@
         <v>7203</v>
       </c>
       <c r="F259">
-        <v>1600</v>
+        <v>1572</v>
       </c>
       <c r="G259" t="s">
         <v>7228</v>
@@ -39603,7 +39603,7 @@
         <v>7203</v>
       </c>
       <c r="F260">
-        <v>3112</v>
+        <v>3097</v>
       </c>
       <c r="G260" t="s">
         <v>7228</v>
@@ -39629,7 +39629,7 @@
         <v>7203</v>
       </c>
       <c r="F261">
-        <v>1749</v>
+        <v>1729</v>
       </c>
       <c r="G261" t="s">
         <v>7228</v>
@@ -39655,7 +39655,7 @@
         <v>7203</v>
       </c>
       <c r="F262">
-        <v>1619</v>
+        <v>1591</v>
       </c>
       <c r="G262" t="s">
         <v>7228</v>
@@ -39681,7 +39681,7 @@
         <v>7203</v>
       </c>
       <c r="F263">
-        <v>3473</v>
+        <v>3446</v>
       </c>
       <c r="G263" t="s">
         <v>7228</v>
@@ -39707,7 +39707,7 @@
         <v>7203</v>
       </c>
       <c r="F264">
-        <v>2297</v>
+        <v>2269</v>
       </c>
       <c r="G264" t="s">
         <v>7228</v>
@@ -39733,7 +39733,7 @@
         <v>7203</v>
       </c>
       <c r="F265">
-        <v>1691</v>
+        <v>1673</v>
       </c>
       <c r="G265" t="s">
         <v>7228</v>
@@ -39759,7 +39759,7 @@
         <v>7203</v>
       </c>
       <c r="F266">
-        <v>1768</v>
+        <v>1744</v>
       </c>
       <c r="G266" t="s">
         <v>7228</v>
@@ -39785,7 +39785,7 @@
         <v>7203</v>
       </c>
       <c r="F267">
-        <v>1549</v>
+        <v>1525</v>
       </c>
       <c r="G267" t="s">
         <v>7228</v>
@@ -39811,7 +39811,7 @@
         <v>7203</v>
       </c>
       <c r="F268">
-        <v>1255</v>
+        <v>1229</v>
       </c>
       <c r="G268" t="s">
         <v>7228</v>
@@ -39837,7 +39837,7 @@
         <v>7203</v>
       </c>
       <c r="F269">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="G269" t="s">
         <v>7228</v>
@@ -39863,7 +39863,7 @@
         <v>7203</v>
       </c>
       <c r="F270">
-        <v>1333</v>
+        <v>1319</v>
       </c>
       <c r="G270" t="s">
         <v>7228</v>
@@ -39889,7 +39889,7 @@
         <v>7203</v>
       </c>
       <c r="F271">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="G271" t="s">
         <v>7228</v>
@@ -39915,7 +39915,7 @@
         <v>7203</v>
       </c>
       <c r="F272">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="G272" t="s">
         <v>7228</v>
@@ -39941,7 +39941,7 @@
         <v>7203</v>
       </c>
       <c r="F273">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="G273" t="s">
         <v>7228</v>
@@ -39967,7 +39967,7 @@
         <v>7203</v>
       </c>
       <c r="F274">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="G274" t="s">
         <v>7228</v>
@@ -39993,7 +39993,7 @@
         <v>7203</v>
       </c>
       <c r="F275">
-        <v>850</v>
+        <v>824</v>
       </c>
       <c r="G275" t="s">
         <v>7228</v>
@@ -40019,7 +40019,7 @@
         <v>7203</v>
       </c>
       <c r="F276">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="G276" t="s">
         <v>7228</v>
@@ -40045,7 +40045,7 @@
         <v>7203</v>
       </c>
       <c r="F277">
-        <v>1848</v>
+        <v>1828</v>
       </c>
       <c r="G277" t="s">
         <v>7228</v>
@@ -40071,7 +40071,7 @@
         <v>7203</v>
       </c>
       <c r="F278">
-        <v>2175</v>
+        <v>2143</v>
       </c>
       <c r="G278" t="s">
         <v>7228</v>
@@ -40097,7 +40097,7 @@
         <v>7203</v>
       </c>
       <c r="F279">
-        <v>1184</v>
+        <v>1163</v>
       </c>
       <c r="G279" t="s">
         <v>7228</v>
@@ -40123,7 +40123,7 @@
         <v>7203</v>
       </c>
       <c r="F280">
-        <v>2158</v>
+        <v>2137</v>
       </c>
       <c r="G280" t="s">
         <v>7228</v>
@@ -40149,7 +40149,7 @@
         <v>7203</v>
       </c>
       <c r="F281">
-        <v>2109</v>
+        <v>2088</v>
       </c>
       <c r="G281" t="s">
         <v>7228</v>
@@ -40175,7 +40175,7 @@
         <v>7203</v>
       </c>
       <c r="F282">
-        <v>3110</v>
+        <v>3077</v>
       </c>
       <c r="G282" t="s">
         <v>7228</v>
@@ -40201,7 +40201,7 @@
         <v>7203</v>
       </c>
       <c r="F283">
-        <v>1574</v>
+        <v>1559</v>
       </c>
       <c r="G283" t="s">
         <v>7228</v>
@@ -40227,7 +40227,7 @@
         <v>7203</v>
       </c>
       <c r="F284">
-        <v>4044</v>
+        <v>4024</v>
       </c>
       <c r="G284" t="s">
         <v>7228</v>
@@ -40253,7 +40253,7 @@
         <v>7203</v>
       </c>
       <c r="F285">
-        <v>1368</v>
+        <v>1347</v>
       </c>
       <c r="G285" t="s">
         <v>7228</v>
@@ -40279,7 +40279,7 @@
         <v>7203</v>
       </c>
       <c r="F286">
-        <v>1080</v>
+        <v>1059</v>
       </c>
       <c r="G286" t="s">
         <v>7228</v>
@@ -40305,7 +40305,7 @@
         <v>7203</v>
       </c>
       <c r="F287">
-        <v>2778</v>
+        <v>2769</v>
       </c>
       <c r="G287" t="s">
         <v>7228</v>
@@ -40331,7 +40331,7 @@
         <v>7203</v>
       </c>
       <c r="F288">
-        <v>3625</v>
+        <v>3597</v>
       </c>
       <c r="G288" t="s">
         <v>7228</v>
@@ -40357,7 +40357,7 @@
         <v>7203</v>
       </c>
       <c r="F289">
-        <v>3961</v>
+        <v>3937</v>
       </c>
       <c r="G289" t="s">
         <v>7228</v>
@@ -40383,7 +40383,7 @@
         <v>7203</v>
       </c>
       <c r="F290">
-        <v>4089</v>
+        <v>4061</v>
       </c>
       <c r="G290" t="s">
         <v>7228</v>
@@ -40409,7 +40409,7 @@
         <v>7203</v>
       </c>
       <c r="F291">
-        <v>3901</v>
+        <v>3877</v>
       </c>
       <c r="G291" t="s">
         <v>7228</v>
@@ -40435,7 +40435,7 @@
         <v>7203</v>
       </c>
       <c r="F292">
-        <v>3121</v>
+        <v>3085</v>
       </c>
       <c r="G292" t="s">
         <v>7228</v>
@@ -40461,7 +40461,7 @@
         <v>7189</v>
       </c>
       <c r="F293">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G293" t="s">
         <v>7228</v>
@@ -40487,7 +40487,7 @@
         <v>7186</v>
       </c>
       <c r="F294">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G294" t="s">
         <v>7228</v>
@@ -40513,7 +40513,7 @@
         <v>7189</v>
       </c>
       <c r="F295">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G295" t="s">
         <v>7228</v>
@@ -40539,7 +40539,7 @@
         <v>7186</v>
       </c>
       <c r="F296">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G296" t="s">
         <v>7228</v>
@@ -40565,7 +40565,7 @@
         <v>7189</v>
       </c>
       <c r="F297">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G297" t="s">
         <v>7228</v>
@@ -40591,7 +40591,7 @@
         <v>7189</v>
       </c>
       <c r="F298">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G298" t="s">
         <v>7228</v>
@@ -40669,7 +40669,7 @@
         <v>7204</v>
       </c>
       <c r="F301">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G301" t="s">
         <v>7228</v>
@@ -40695,7 +40695,7 @@
         <v>7204</v>
       </c>
       <c r="F302">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="G302" t="s">
         <v>7228</v>
@@ -40773,7 +40773,7 @@
         <v>7204</v>
       </c>
       <c r="F305">
-        <v>1131</v>
+        <v>1117</v>
       </c>
       <c r="G305" t="s">
         <v>7228</v>
@@ -40799,7 +40799,7 @@
         <v>7204</v>
       </c>
       <c r="F306">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="G306" t="s">
         <v>7228</v>
@@ -40825,7 +40825,7 @@
         <v>7204</v>
       </c>
       <c r="F307">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="G307" t="s">
         <v>7228</v>
@@ -40877,7 +40877,7 @@
         <v>7186</v>
       </c>
       <c r="F309">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G309" t="s">
         <v>7228</v>
@@ -40955,7 +40955,7 @@
         <v>7204</v>
       </c>
       <c r="F312">
-        <v>3579</v>
+        <v>3567</v>
       </c>
       <c r="G312" t="s">
         <v>7228</v>
@@ -40981,7 +40981,7 @@
         <v>7204</v>
       </c>
       <c r="F313">
-        <v>2538</v>
+        <v>2529</v>
       </c>
       <c r="G313" t="s">
         <v>7228</v>
@@ -41007,7 +41007,7 @@
         <v>7186</v>
       </c>
       <c r="F314">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G314" t="s">
         <v>7228</v>
@@ -41053,7 +41053,7 @@
         <v>7186</v>
       </c>
       <c r="F316">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="G316" t="s">
         <v>7228</v>
@@ -41079,7 +41079,7 @@
         <v>7186</v>
       </c>
       <c r="F317">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="G317" t="s">
         <v>7229</v>
@@ -41099,7 +41099,7 @@
         <v>7186</v>
       </c>
       <c r="F318">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="G318" t="s">
         <v>7229</v>
@@ -41145,7 +41145,7 @@
         <v>7186</v>
       </c>
       <c r="F320">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="G320" t="s">
         <v>7229</v>
@@ -41165,7 +41165,7 @@
         <v>7186</v>
       </c>
       <c r="F321">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="G321" t="s">
         <v>7228</v>
@@ -41191,7 +41191,7 @@
         <v>7186</v>
       </c>
       <c r="F322">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="G322" t="s">
         <v>7229</v>
@@ -41211,7 +41211,7 @@
         <v>7186</v>
       </c>
       <c r="F323">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G323" t="s">
         <v>7228</v>
@@ -41237,7 +41237,7 @@
         <v>7186</v>
       </c>
       <c r="F324">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="G324" t="s">
         <v>7228</v>
@@ -41263,7 +41263,7 @@
         <v>7186</v>
       </c>
       <c r="F325">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="G325" t="s">
         <v>7229</v>
@@ -41283,7 +41283,7 @@
         <v>7186</v>
       </c>
       <c r="F326">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="G326" t="s">
         <v>7228</v>
@@ -41309,7 +41309,7 @@
         <v>7186</v>
       </c>
       <c r="F327">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="G327" t="s">
         <v>7228</v>
@@ -41335,7 +41335,7 @@
         <v>7189</v>
       </c>
       <c r="F328">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="G328" t="s">
         <v>7228</v>
@@ -41361,7 +41361,7 @@
         <v>7186</v>
       </c>
       <c r="F329">
-        <v>1341</v>
+        <v>1323</v>
       </c>
       <c r="G329" t="s">
         <v>7229</v>
@@ -41381,7 +41381,7 @@
         <v>7186</v>
       </c>
       <c r="F330">
-        <v>759</v>
+        <v>731</v>
       </c>
       <c r="G330" t="s">
         <v>7228</v>
@@ -41407,7 +41407,7 @@
         <v>7186</v>
       </c>
       <c r="F331">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="G331" t="s">
         <v>7229</v>
@@ -41427,7 +41427,7 @@
         <v>7186</v>
       </c>
       <c r="F332">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="G332" t="s">
         <v>7228</v>
@@ -41453,7 +41453,7 @@
         <v>7189</v>
       </c>
       <c r="F333">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="G333" t="s">
         <v>7228</v>
@@ -41479,7 +41479,7 @@
         <v>7196</v>
       </c>
       <c r="F334">
-        <v>1136</v>
+        <v>1084</v>
       </c>
       <c r="G334" t="s">
         <v>7228</v>
@@ -41505,7 +41505,7 @@
         <v>7196</v>
       </c>
       <c r="F335">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G335" t="s">
         <v>7228</v>
@@ -41531,7 +41531,7 @@
         <v>7196</v>
       </c>
       <c r="F336">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G336" t="s">
         <v>7228</v>
@@ -41557,7 +41557,7 @@
         <v>7196</v>
       </c>
       <c r="F337">
-        <v>1309</v>
+        <v>1289</v>
       </c>
       <c r="G337" t="s">
         <v>7228</v>
@@ -41583,7 +41583,7 @@
         <v>7196</v>
       </c>
       <c r="F338">
-        <v>975</v>
+        <v>934</v>
       </c>
       <c r="G338" t="s">
         <v>7228</v>
@@ -41609,7 +41609,7 @@
         <v>7196</v>
       </c>
       <c r="F339">
-        <v>1211</v>
+        <v>1195</v>
       </c>
       <c r="G339" t="s">
         <v>7228</v>
@@ -41635,7 +41635,7 @@
         <v>7196</v>
       </c>
       <c r="F340">
-        <v>1030</v>
+        <v>974</v>
       </c>
       <c r="G340" t="s">
         <v>7228</v>
@@ -41661,7 +41661,7 @@
         <v>7189</v>
       </c>
       <c r="F341">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="G341" t="s">
         <v>7228</v>
@@ -41687,7 +41687,7 @@
         <v>7189</v>
       </c>
       <c r="F342">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="G342" t="s">
         <v>7228</v>
@@ -41713,7 +41713,7 @@
         <v>7189</v>
       </c>
       <c r="F343">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="G343" t="s">
         <v>7228</v>
@@ -41739,7 +41739,7 @@
         <v>7189</v>
       </c>
       <c r="F344">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="G344" t="s">
         <v>7228</v>
@@ -41765,7 +41765,7 @@
         <v>7189</v>
       </c>
       <c r="F345">
-        <v>1079</v>
+        <v>1059</v>
       </c>
       <c r="G345" t="s">
         <v>7228</v>
@@ -41791,7 +41791,7 @@
         <v>7189</v>
       </c>
       <c r="F346">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="G346" t="s">
         <v>7228</v>
@@ -41817,7 +41817,7 @@
         <v>7205</v>
       </c>
       <c r="F347">
-        <v>526</v>
+        <v>490</v>
       </c>
       <c r="G347" t="s">
         <v>7228</v>
@@ -41843,7 +41843,7 @@
         <v>7205</v>
       </c>
       <c r="F348">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="G348" t="s">
         <v>7228</v>
@@ -41869,7 +41869,7 @@
         <v>7205</v>
       </c>
       <c r="F349">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="G349" t="s">
         <v>7228</v>
@@ -42059,7 +42059,7 @@
         <v>7186</v>
       </c>
       <c r="F357">
-        <v>1351</v>
+        <v>1201</v>
       </c>
       <c r="G357" t="s">
         <v>7229</v>
@@ -42125,7 +42125,7 @@
         <v>7205</v>
       </c>
       <c r="F360">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="G360" t="s">
         <v>7228</v>
@@ -42151,7 +42151,7 @@
         <v>7201</v>
       </c>
       <c r="F361">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G361" t="s">
         <v>7228</v>
@@ -42203,7 +42203,7 @@
         <v>7205</v>
       </c>
       <c r="F363">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="G363" t="s">
         <v>7228</v>
@@ -42255,7 +42255,7 @@
         <v>7186</v>
       </c>
       <c r="F365">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G365" t="s">
         <v>7228</v>
@@ -42281,7 +42281,7 @@
         <v>7186</v>
       </c>
       <c r="F366">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="G366" t="s">
         <v>7228</v>
@@ -42307,7 +42307,7 @@
         <v>7189</v>
       </c>
       <c r="F367">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G367" t="s">
         <v>7228</v>
@@ -42359,7 +42359,7 @@
         <v>7189</v>
       </c>
       <c r="F369">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G369" t="s">
         <v>7228</v>
@@ -42385,7 +42385,7 @@
         <v>7189</v>
       </c>
       <c r="F370">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G370" t="s">
         <v>7228</v>
@@ -42483,7 +42483,7 @@
         <v>7186</v>
       </c>
       <c r="F374">
-        <v>1259</v>
+        <v>1239</v>
       </c>
       <c r="G374" t="s">
         <v>7228</v>
@@ -42509,7 +42509,7 @@
         <v>7186</v>
       </c>
       <c r="F375">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="G375" t="s">
         <v>7228</v>
@@ -42587,7 +42587,7 @@
         <v>7186</v>
       </c>
       <c r="F378">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G378" t="s">
         <v>7228</v>
@@ -42613,7 +42613,7 @@
         <v>7186</v>
       </c>
       <c r="F379">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G379" t="s">
         <v>7228</v>
@@ -42639,7 +42639,7 @@
         <v>7186</v>
       </c>
       <c r="F380">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="G380" t="s">
         <v>7228</v>
@@ -42691,7 +42691,7 @@
         <v>7186</v>
       </c>
       <c r="F382">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="G382" t="s">
         <v>7228</v>
@@ -42717,7 +42717,7 @@
         <v>7186</v>
       </c>
       <c r="F383">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G383" t="s">
         <v>7228</v>
@@ -42743,7 +42743,7 @@
         <v>7186</v>
       </c>
       <c r="F384">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="G384" t="s">
         <v>7228</v>
@@ -42769,7 +42769,7 @@
         <v>7186</v>
       </c>
       <c r="F385">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="G385" t="s">
         <v>7228</v>
@@ -42847,7 +42847,7 @@
         <v>7208</v>
       </c>
       <c r="F388">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="G388" t="s">
         <v>7228</v>
@@ -42873,7 +42873,7 @@
         <v>7208</v>
       </c>
       <c r="F389">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="G389" t="s">
         <v>7228</v>
@@ -42899,7 +42899,7 @@
         <v>7208</v>
       </c>
       <c r="F390">
-        <v>2007</v>
+        <v>1994</v>
       </c>
       <c r="G390" t="s">
         <v>7228</v>
@@ -42925,7 +42925,7 @@
         <v>7207</v>
       </c>
       <c r="F391">
-        <v>3400</v>
+        <v>3364</v>
       </c>
       <c r="G391" t="s">
         <v>7228</v>
@@ -42951,7 +42951,7 @@
         <v>7207</v>
       </c>
       <c r="F392">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="G392" t="s">
         <v>7228</v>
@@ -42977,7 +42977,7 @@
         <v>7207</v>
       </c>
       <c r="F393">
-        <v>1131</v>
+        <v>1109</v>
       </c>
       <c r="G393" t="s">
         <v>7228</v>
@@ -43003,7 +43003,7 @@
         <v>7207</v>
       </c>
       <c r="F394">
-        <v>4582</v>
+        <v>4562</v>
       </c>
       <c r="G394" t="s">
         <v>7228</v>
@@ -43029,7 +43029,7 @@
         <v>7207</v>
       </c>
       <c r="F395">
-        <v>2710</v>
+        <v>2674</v>
       </c>
       <c r="G395" t="s">
         <v>7228</v>
@@ -43055,7 +43055,7 @@
         <v>7207</v>
       </c>
       <c r="F396">
-        <v>2027</v>
+        <v>2007</v>
       </c>
       <c r="G396" t="s">
         <v>7228</v>
@@ -43081,7 +43081,7 @@
         <v>7208</v>
       </c>
       <c r="F397">
-        <v>2130</v>
+        <v>2124</v>
       </c>
       <c r="G397" t="s">
         <v>7228</v>
@@ -43107,7 +43107,7 @@
         <v>7208</v>
       </c>
       <c r="F398">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="G398" t="s">
         <v>7228</v>
@@ -43133,7 +43133,7 @@
         <v>7208</v>
       </c>
       <c r="F399">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="G399" t="s">
         <v>7228</v>
@@ -43159,7 +43159,7 @@
         <v>7208</v>
       </c>
       <c r="F400">
-        <v>3462</v>
+        <v>3434</v>
       </c>
       <c r="G400" t="s">
         <v>7228</v>
@@ -43185,7 +43185,7 @@
         <v>7208</v>
       </c>
       <c r="F401">
-        <v>2412</v>
+        <v>2404</v>
       </c>
       <c r="G401" t="s">
         <v>7228</v>
@@ -43211,7 +43211,7 @@
         <v>7208</v>
       </c>
       <c r="F402">
-        <v>2292</v>
+        <v>2270</v>
       </c>
       <c r="G402" t="s">
         <v>7228</v>
@@ -43237,7 +43237,7 @@
         <v>7207</v>
       </c>
       <c r="F403">
-        <v>1555</v>
+        <v>1531</v>
       </c>
       <c r="G403" t="s">
         <v>7228</v>
@@ -43263,7 +43263,7 @@
         <v>7207</v>
       </c>
       <c r="F404">
-        <v>2602</v>
+        <v>2578</v>
       </c>
       <c r="G404" t="s">
         <v>7228</v>
@@ -43289,7 +43289,7 @@
         <v>7207</v>
       </c>
       <c r="F405">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="G405" t="s">
         <v>7228</v>
@@ -43315,7 +43315,7 @@
         <v>7207</v>
       </c>
       <c r="F406">
-        <v>1287</v>
+        <v>1267</v>
       </c>
       <c r="G406" t="s">
         <v>7228</v>
@@ -43341,7 +43341,7 @@
         <v>7208</v>
       </c>
       <c r="F407">
-        <v>1035</v>
+        <v>1015</v>
       </c>
       <c r="G407" t="s">
         <v>7228</v>
@@ -43393,7 +43393,7 @@
         <v>7189</v>
       </c>
       <c r="F409">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G409" t="s">
         <v>7228</v>
@@ -43459,7 +43459,7 @@
         <v>7189</v>
       </c>
       <c r="F412">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G412" t="s">
         <v>7228</v>
@@ -43511,7 +43511,7 @@
         <v>7189</v>
       </c>
       <c r="F414">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G414" t="s">
         <v>7228</v>
@@ -43537,7 +43537,7 @@
         <v>7189</v>
       </c>
       <c r="F415">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G415" t="s">
         <v>7228</v>
@@ -43563,7 +43563,7 @@
         <v>7189</v>
       </c>
       <c r="F416">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G416" t="s">
         <v>7229</v>
@@ -43583,7 +43583,7 @@
         <v>7186</v>
       </c>
       <c r="F417">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="G417" t="s">
         <v>7228</v>
@@ -43609,7 +43609,7 @@
         <v>7189</v>
       </c>
       <c r="F418">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G418" t="s">
         <v>7228</v>
@@ -43733,7 +43733,7 @@
         <v>7186</v>
       </c>
       <c r="F423">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G423" t="s">
         <v>7228</v>
@@ -43759,7 +43759,7 @@
         <v>7186</v>
       </c>
       <c r="F424">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G424" t="s">
         <v>7228</v>
@@ -43785,7 +43785,7 @@
         <v>7186</v>
       </c>
       <c r="F425">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G425" t="s">
         <v>7228</v>
@@ -43871,7 +43871,7 @@
         <v>7186</v>
       </c>
       <c r="F429">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G429" t="s">
         <v>7228</v>
@@ -43897,7 +43897,7 @@
         <v>7186</v>
       </c>
       <c r="F430">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G430" t="s">
         <v>7228</v>
@@ -44043,7 +44043,7 @@
         <v>7201</v>
       </c>
       <c r="F437">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G437" t="s">
         <v>7229</v>
@@ -44129,7 +44129,7 @@
         <v>7196</v>
       </c>
       <c r="F441">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G441" t="s">
         <v>7228</v>
@@ -44155,7 +44155,7 @@
         <v>7196</v>
       </c>
       <c r="F442">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="G442" t="s">
         <v>7228</v>
@@ -44181,7 +44181,7 @@
         <v>7196</v>
       </c>
       <c r="F443">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="G443" t="s">
         <v>7228</v>
@@ -44207,7 +44207,7 @@
         <v>7186</v>
       </c>
       <c r="F444">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="G444" t="s">
         <v>7228</v>
@@ -44233,7 +44233,7 @@
         <v>7196</v>
       </c>
       <c r="F445">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G445" t="s">
         <v>7228</v>
@@ -44493,7 +44493,7 @@
         <v>7196</v>
       </c>
       <c r="F455">
-        <v>830</v>
+        <v>806</v>
       </c>
       <c r="G455" t="s">
         <v>7228</v>
@@ -44519,7 +44519,7 @@
         <v>7196</v>
       </c>
       <c r="F456">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="G456" t="s">
         <v>7228</v>
@@ -44545,7 +44545,7 @@
         <v>7189</v>
       </c>
       <c r="F457">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="G457" t="s">
         <v>7229</v>
@@ -44565,7 +44565,7 @@
         <v>7196</v>
       </c>
       <c r="F458">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="G458" t="s">
         <v>7228</v>
@@ -44591,7 +44591,7 @@
         <v>7189</v>
       </c>
       <c r="F459">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="G459" t="s">
         <v>7228</v>
@@ -44617,7 +44617,7 @@
         <v>7189</v>
       </c>
       <c r="F460">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G460" t="s">
         <v>7228</v>
@@ -44643,7 +44643,7 @@
         <v>7189</v>
       </c>
       <c r="F461">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G461" t="s">
         <v>7228</v>
@@ -44669,7 +44669,7 @@
         <v>7189</v>
       </c>
       <c r="F462">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="G462" t="s">
         <v>7228</v>
@@ -44695,7 +44695,7 @@
         <v>7189</v>
       </c>
       <c r="F463">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="G463" t="s">
         <v>7228</v>
@@ -44747,7 +44747,7 @@
         <v>7189</v>
       </c>
       <c r="F465">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="G465" t="s">
         <v>7229</v>
@@ -44767,7 +44767,7 @@
         <v>7189</v>
       </c>
       <c r="F466">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="G466" t="s">
         <v>7229</v>
@@ -44813,7 +44813,7 @@
         <v>7189</v>
       </c>
       <c r="F468">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G468" t="s">
         <v>7228</v>
@@ -44839,7 +44839,7 @@
         <v>7186</v>
       </c>
       <c r="F469">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="G469" t="s">
         <v>7228</v>
@@ -44865,7 +44865,7 @@
         <v>7187</v>
       </c>
       <c r="F470">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="G470" t="s">
         <v>7228</v>
@@ -44891,7 +44891,7 @@
         <v>7187</v>
       </c>
       <c r="F471">
-        <v>596</v>
+        <v>554</v>
       </c>
       <c r="G471" t="s">
         <v>7228</v>
@@ -44943,7 +44943,7 @@
         <v>7210</v>
       </c>
       <c r="F473">
-        <v>1347</v>
+        <v>1317</v>
       </c>
       <c r="G473" t="s">
         <v>7228</v>
@@ -45021,7 +45021,7 @@
         <v>7205</v>
       </c>
       <c r="F476">
-        <v>640</v>
+        <v>598</v>
       </c>
       <c r="G476" t="s">
         <v>7228</v>
@@ -45047,7 +45047,7 @@
         <v>7205</v>
       </c>
       <c r="F477">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="G477" t="s">
         <v>7228</v>
@@ -45073,7 +45073,7 @@
         <v>7205</v>
       </c>
       <c r="F478">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="G478" t="s">
         <v>7228</v>
@@ -45099,7 +45099,7 @@
         <v>7205</v>
       </c>
       <c r="F479">
-        <v>1527</v>
+        <v>1497</v>
       </c>
       <c r="G479" t="s">
         <v>7228</v>
@@ -45125,7 +45125,7 @@
         <v>7205</v>
       </c>
       <c r="F480">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="G480" t="s">
         <v>7228</v>
@@ -45151,7 +45151,7 @@
         <v>7210</v>
       </c>
       <c r="F481">
-        <v>1362</v>
+        <v>1314</v>
       </c>
       <c r="G481" t="s">
         <v>7228</v>
@@ -45177,7 +45177,7 @@
         <v>7210</v>
       </c>
       <c r="F482">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G482" t="s">
         <v>7228</v>
@@ -45203,7 +45203,7 @@
         <v>7210</v>
       </c>
       <c r="F483">
-        <v>1632</v>
+        <v>1620</v>
       </c>
       <c r="G483" t="s">
         <v>7228</v>
@@ -45229,7 +45229,7 @@
         <v>7210</v>
       </c>
       <c r="F484">
-        <v>1683</v>
+        <v>1659</v>
       </c>
       <c r="G484" t="s">
         <v>7228</v>
@@ -45255,7 +45255,7 @@
         <v>7210</v>
       </c>
       <c r="F485">
-        <v>1385</v>
+        <v>1367</v>
       </c>
       <c r="G485" t="s">
         <v>7228</v>
@@ -45281,7 +45281,7 @@
         <v>7210</v>
       </c>
       <c r="F486">
-        <v>1404</v>
+        <v>1374</v>
       </c>
       <c r="G486" t="s">
         <v>7228</v>
@@ -45307,7 +45307,7 @@
         <v>7210</v>
       </c>
       <c r="F487">
-        <v>1524</v>
+        <v>1512</v>
       </c>
       <c r="G487" t="s">
         <v>7228</v>
@@ -45463,7 +45463,7 @@
         <v>7187</v>
       </c>
       <c r="F493">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="G493" t="s">
         <v>7228</v>
@@ -45489,7 +45489,7 @@
         <v>7187</v>
       </c>
       <c r="F494">
-        <v>731</v>
+        <v>689</v>
       </c>
       <c r="G494" t="s">
         <v>7228</v>
@@ -45515,7 +45515,7 @@
         <v>7187</v>
       </c>
       <c r="F495">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="G495" t="s">
         <v>7228</v>
@@ -45541,7 +45541,7 @@
         <v>7187</v>
       </c>
       <c r="F496">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="G496" t="s">
         <v>7228</v>
@@ -45587,7 +45587,7 @@
         <v>7187</v>
       </c>
       <c r="F498">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="G498" t="s">
         <v>7228</v>
@@ -45639,7 +45639,7 @@
         <v>7187</v>
       </c>
       <c r="F500">
-        <v>1325</v>
+        <v>1313</v>
       </c>
       <c r="G500" t="s">
         <v>7228</v>
@@ -45665,7 +45665,7 @@
         <v>7187</v>
       </c>
       <c r="F501">
-        <v>1576</v>
+        <v>1567</v>
       </c>
       <c r="G501" t="s">
         <v>7228</v>
@@ -45737,7 +45737,7 @@
         <v>7209</v>
       </c>
       <c r="F504">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="G504" t="s">
         <v>7228</v>
@@ -45783,7 +45783,7 @@
         <v>7209</v>
       </c>
       <c r="F506">
-        <v>1921</v>
+        <v>1911</v>
       </c>
       <c r="G506" t="s">
         <v>7228</v>
@@ -45809,7 +45809,7 @@
         <v>7209</v>
       </c>
       <c r="F507">
-        <v>2532</v>
+        <v>2502</v>
       </c>
       <c r="G507" t="s">
         <v>7228</v>
@@ -45861,7 +45861,7 @@
         <v>7209</v>
       </c>
       <c r="F509">
-        <v>696</v>
+        <v>646</v>
       </c>
       <c r="G509" t="s">
         <v>7228</v>
@@ -45927,7 +45927,7 @@
         <v>7209</v>
       </c>
       <c r="F512">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="G512" t="s">
         <v>7228</v>
@@ -45979,7 +45979,7 @@
         <v>7189</v>
       </c>
       <c r="F514">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G514" t="s">
         <v>7228</v>
@@ -46031,7 +46031,7 @@
         <v>7191</v>
       </c>
       <c r="F516">
-        <v>2196</v>
+        <v>2184</v>
       </c>
       <c r="G516" t="s">
         <v>7228</v>
@@ -46083,7 +46083,7 @@
         <v>7191</v>
       </c>
       <c r="F518">
-        <v>1800</v>
+        <v>1788</v>
       </c>
       <c r="G518" t="s">
         <v>7228</v>
@@ -46343,7 +46343,7 @@
         <v>7189</v>
       </c>
       <c r="F528">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="G528" t="s">
         <v>7228</v>
@@ -46369,7 +46369,7 @@
         <v>7189</v>
       </c>
       <c r="F529">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G529" t="s">
         <v>7228</v>
@@ -46421,7 +46421,7 @@
         <v>7189</v>
       </c>
       <c r="F531">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="G531" t="s">
         <v>7228</v>
@@ -46473,7 +46473,7 @@
         <v>7189</v>
       </c>
       <c r="F533">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G533" t="s">
         <v>7228</v>
@@ -46499,7 +46499,7 @@
         <v>7189</v>
       </c>
       <c r="F534">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="G534" t="s">
         <v>7228</v>
@@ -46525,7 +46525,7 @@
         <v>7189</v>
       </c>
       <c r="F535">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G535" t="s">
         <v>7228</v>
@@ -46571,7 +46571,7 @@
         <v>7189</v>
       </c>
       <c r="F537">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G537" t="s">
         <v>7228</v>
@@ -46597,7 +46597,7 @@
         <v>7209</v>
       </c>
       <c r="F538">
-        <v>2795</v>
+        <v>2755</v>
       </c>
       <c r="G538" t="s">
         <v>7228</v>
@@ -46643,7 +46643,7 @@
         <v>7186</v>
       </c>
       <c r="F540">
-        <v>357</v>
+        <v>257</v>
       </c>
       <c r="G540" t="s">
         <v>7229</v>
@@ -46743,7 +46743,7 @@
         <v>7209</v>
       </c>
       <c r="F545">
-        <v>2753</v>
+        <v>2733</v>
       </c>
       <c r="G545" t="s">
         <v>7228</v>
@@ -46769,7 +46769,7 @@
         <v>7209</v>
       </c>
       <c r="F546">
-        <v>1259</v>
+        <v>1249</v>
       </c>
       <c r="G546" t="s">
         <v>7228</v>
@@ -46795,7 +46795,7 @@
         <v>7209</v>
       </c>
       <c r="F547">
-        <v>3273</v>
+        <v>3253</v>
       </c>
       <c r="G547" t="s">
         <v>7228</v>
@@ -46821,7 +46821,7 @@
         <v>7209</v>
       </c>
       <c r="F548">
-        <v>2057</v>
+        <v>2027</v>
       </c>
       <c r="G548" t="s">
         <v>7228</v>
@@ -46847,7 +46847,7 @@
         <v>7209</v>
       </c>
       <c r="F549">
-        <v>3085</v>
+        <v>3035</v>
       </c>
       <c r="G549" t="s">
         <v>7228</v>
@@ -46893,7 +46893,7 @@
         <v>7186</v>
       </c>
       <c r="F551">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="G551" t="s">
         <v>7228</v>
@@ -46919,7 +46919,7 @@
         <v>7186</v>
       </c>
       <c r="F552">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="G552" t="s">
         <v>7228</v>
@@ -46945,7 +46945,7 @@
         <v>7186</v>
       </c>
       <c r="F553">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G553" t="s">
         <v>7228</v>
@@ -47153,7 +47153,7 @@
         <v>7209</v>
       </c>
       <c r="F561">
-        <v>1343</v>
+        <v>1333</v>
       </c>
       <c r="G561" t="s">
         <v>7228</v>
@@ -47179,7 +47179,7 @@
         <v>7209</v>
       </c>
       <c r="F562">
-        <v>3066</v>
+        <v>3056</v>
       </c>
       <c r="G562" t="s">
         <v>7228</v>
@@ -47205,7 +47205,7 @@
         <v>7209</v>
       </c>
       <c r="F563">
-        <v>2048</v>
+        <v>2028</v>
       </c>
       <c r="G563" t="s">
         <v>7228</v>
@@ -47563,7 +47563,7 @@
         <v>7186</v>
       </c>
       <c r="F577">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G577" t="s">
         <v>7228</v>
@@ -47641,7 +47641,7 @@
         <v>7209</v>
       </c>
       <c r="F580">
-        <v>839</v>
+        <v>799</v>
       </c>
       <c r="G580" t="s">
         <v>7228</v>
@@ -47667,7 +47667,7 @@
         <v>7186</v>
       </c>
       <c r="F581">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="G581" t="s">
         <v>7228</v>
@@ -47823,7 +47823,7 @@
         <v>7189</v>
       </c>
       <c r="F587">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G587" t="s">
         <v>7228</v>
@@ -47901,7 +47901,7 @@
         <v>7209</v>
       </c>
       <c r="F590">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="G590" t="s">
         <v>7229</v>
@@ -47921,7 +47921,7 @@
         <v>7209</v>
       </c>
       <c r="F591">
-        <v>1750</v>
+        <v>1710</v>
       </c>
       <c r="G591" t="s">
         <v>7228</v>
@@ -48025,7 +48025,7 @@
         <v>7209</v>
       </c>
       <c r="F595">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="G595" t="s">
         <v>7228</v>
@@ -48051,7 +48051,7 @@
         <v>7192</v>
       </c>
       <c r="F596">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G596" t="s">
         <v>7228</v>
@@ -48129,7 +48129,7 @@
         <v>7194</v>
       </c>
       <c r="F599">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="G599" t="s">
         <v>7228</v>
@@ -48181,7 +48181,7 @@
         <v>7189</v>
       </c>
       <c r="F601">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="G601" t="s">
         <v>7228</v>
@@ -48207,7 +48207,7 @@
         <v>7189</v>
       </c>
       <c r="F602">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="G602" t="s">
         <v>7228</v>
@@ -48233,7 +48233,7 @@
         <v>7189</v>
       </c>
       <c r="F603">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="G603" t="s">
         <v>7228</v>
@@ -48259,7 +48259,7 @@
         <v>7186</v>
       </c>
       <c r="F604">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G604" t="s">
         <v>7228</v>
@@ -48285,7 +48285,7 @@
         <v>7186</v>
       </c>
       <c r="F605">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G605" t="s">
         <v>7228</v>
@@ -48311,7 +48311,7 @@
         <v>7186</v>
       </c>
       <c r="F606">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G606" t="s">
         <v>7228</v>
@@ -48337,7 +48337,7 @@
         <v>7186</v>
       </c>
       <c r="F607">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G607" t="s">
         <v>7228</v>
@@ -48383,7 +48383,7 @@
         <v>7205</v>
       </c>
       <c r="F609">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="G609" t="s">
         <v>7228</v>
@@ -48429,7 +48429,7 @@
         <v>7186</v>
       </c>
       <c r="F611">
-        <v>460</v>
+        <v>410</v>
       </c>
       <c r="G611" t="s">
         <v>7229</v>
@@ -48529,7 +48529,7 @@
         <v>7205</v>
       </c>
       <c r="F616">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="G616" t="s">
         <v>7228</v>
@@ -48555,7 +48555,7 @@
         <v>7205</v>
       </c>
       <c r="F617">
-        <v>1048</v>
+        <v>1024</v>
       </c>
       <c r="G617" t="s">
         <v>7228</v>
@@ -48581,7 +48581,7 @@
         <v>7205</v>
       </c>
       <c r="F618">
-        <v>1530</v>
+        <v>1518</v>
       </c>
       <c r="G618" t="s">
         <v>7228</v>
@@ -48607,7 +48607,7 @@
         <v>7205</v>
       </c>
       <c r="F619">
-        <v>1535</v>
+        <v>1523</v>
       </c>
       <c r="G619" t="s">
         <v>7228</v>
@@ -48633,7 +48633,7 @@
         <v>7205</v>
       </c>
       <c r="F620">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="G620" t="s">
         <v>7228</v>
@@ -48679,7 +48679,7 @@
         <v>7205</v>
       </c>
       <c r="F622">
-        <v>821</v>
+        <v>779</v>
       </c>
       <c r="G622" t="s">
         <v>7228</v>
@@ -48705,7 +48705,7 @@
         <v>7210</v>
       </c>
       <c r="F623">
-        <v>964</v>
+        <v>916</v>
       </c>
       <c r="G623" t="s">
         <v>7228</v>
@@ -48731,7 +48731,7 @@
         <v>7210</v>
       </c>
       <c r="F624">
-        <v>1125</v>
+        <v>1083</v>
       </c>
       <c r="G624" t="s">
         <v>7228</v>
@@ -48783,7 +48783,7 @@
         <v>7210</v>
       </c>
       <c r="F626">
-        <v>1295</v>
+        <v>1265</v>
       </c>
       <c r="G626" t="s">
         <v>7228</v>
@@ -48809,7 +48809,7 @@
         <v>7210</v>
       </c>
       <c r="F627">
-        <v>1011</v>
+        <v>987</v>
       </c>
       <c r="G627" t="s">
         <v>7228</v>
@@ -48835,7 +48835,7 @@
         <v>7210</v>
       </c>
       <c r="F628">
-        <v>713</v>
+        <v>641</v>
       </c>
       <c r="G628" t="s">
         <v>7228</v>
@@ -48861,7 +48861,7 @@
         <v>7210</v>
       </c>
       <c r="F629">
-        <v>689</v>
+        <v>611</v>
       </c>
       <c r="G629" t="s">
         <v>7228</v>
@@ -48887,7 +48887,7 @@
         <v>7214</v>
       </c>
       <c r="F630">
-        <v>1580</v>
+        <v>1562</v>
       </c>
       <c r="G630" t="s">
         <v>7228</v>
@@ -48913,7 +48913,7 @@
         <v>7215</v>
       </c>
       <c r="F631">
-        <v>2750</v>
+        <v>2740</v>
       </c>
       <c r="G631" t="s">
         <v>7228</v>
@@ -48939,7 +48939,7 @@
         <v>7200</v>
       </c>
       <c r="F632">
-        <v>3784</v>
+        <v>3774</v>
       </c>
       <c r="G632" t="s">
         <v>7228</v>
@@ -48965,7 +48965,7 @@
         <v>7200</v>
       </c>
       <c r="F633">
-        <v>3585</v>
+        <v>3575</v>
       </c>
       <c r="G633" t="s">
         <v>7228</v>
@@ -49037,7 +49037,7 @@
         <v>7189</v>
       </c>
       <c r="F636">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G636" t="s">
         <v>7228</v>
@@ -49103,7 +49103,7 @@
         <v>7186</v>
       </c>
       <c r="F639">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G639" t="s">
         <v>7228</v>
@@ -49435,7 +49435,7 @@
         <v>7207</v>
       </c>
       <c r="F655">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="G655" t="s">
         <v>7228</v>
@@ -49881,7 +49881,7 @@
         <v>7207</v>
       </c>
       <c r="F674">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="G674" t="s">
         <v>7228</v>
@@ -49907,7 +49907,7 @@
         <v>7216</v>
       </c>
       <c r="F675">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="G675" t="s">
         <v>7228</v>
@@ -53143,7 +53143,7 @@
         <v>7198</v>
       </c>
       <c r="F802">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G802" t="s">
         <v>7228</v>
@@ -53347,7 +53347,7 @@
         <v>7198</v>
       </c>
       <c r="F811">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G811" t="s">
         <v>7228</v>
@@ -53373,7 +53373,7 @@
         <v>7198</v>
       </c>
       <c r="F812">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G812" t="s">
         <v>7228</v>
@@ -54033,7 +54033,7 @@
         <v>7198</v>
       </c>
       <c r="F839">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G839" t="s">
         <v>7228</v>
@@ -54151,7 +54151,7 @@
         <v>7201</v>
       </c>
       <c r="F844">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="G844" t="s">
         <v>7228</v>
@@ -54537,7 +54537,7 @@
         <v>7198</v>
       </c>
       <c r="F860">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G860" t="s">
         <v>7228</v>
@@ -54589,7 +54589,7 @@
         <v>7198</v>
       </c>
       <c r="F862">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G862" t="s">
         <v>7228</v>
@@ -54641,7 +54641,7 @@
         <v>7198</v>
       </c>
       <c r="F864">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G864" t="s">
         <v>7228</v>
@@ -54693,7 +54693,7 @@
         <v>7198</v>
       </c>
       <c r="F866">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G866" t="s">
         <v>7228</v>
@@ -56307,7 +56307,7 @@
         <v>7202</v>
       </c>
       <c r="F929">
-        <v>1209</v>
+        <v>1177</v>
       </c>
       <c r="G929" t="s">
         <v>7228</v>
@@ -57191,7 +57191,7 @@
         <v>7191</v>
       </c>
       <c r="F963">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="G963" t="s">
         <v>7228</v>
@@ -57243,7 +57243,7 @@
         <v>7191</v>
       </c>
       <c r="F965">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G965" t="s">
         <v>7228</v>
@@ -57295,7 +57295,7 @@
         <v>7191</v>
       </c>
       <c r="F967">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G967" t="s">
         <v>7228</v>
@@ -57419,7 +57419,7 @@
         <v>7219</v>
       </c>
       <c r="F972">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="G972" t="s">
         <v>7228</v>
@@ -57445,7 +57445,7 @@
         <v>7191</v>
       </c>
       <c r="F973">
-        <v>3426</v>
+        <v>3408</v>
       </c>
       <c r="G973" t="s">
         <v>7228</v>
@@ -57471,7 +57471,7 @@
         <v>7191</v>
       </c>
       <c r="F974">
-        <v>1363</v>
+        <v>1339</v>
       </c>
       <c r="G974" t="s">
         <v>7228</v>
@@ -57497,7 +57497,7 @@
         <v>7191</v>
       </c>
       <c r="F975">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="G975" t="s">
         <v>7228</v>
@@ -57647,7 +57647,7 @@
         <v>7191</v>
       </c>
       <c r="F981">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G981" t="s">
         <v>7228</v>
@@ -59319,7 +59319,7 @@
         <v>7204</v>
       </c>
       <c r="F1046">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G1046" t="s">
         <v>7229</v>
@@ -59489,7 +59489,7 @@
         <v>7209</v>
       </c>
       <c r="F1053">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G1053" t="s">
         <v>7228</v>
@@ -59749,7 +59749,7 @@
         <v>7204</v>
       </c>
       <c r="F1063">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G1063" t="s">
         <v>7228</v>
@@ -59795,7 +59795,7 @@
         <v>7204</v>
       </c>
       <c r="F1065">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G1065" t="s">
         <v>7228</v>
@@ -60161,7 +60161,7 @@
         <v>7204</v>
       </c>
       <c r="F1083">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G1083" t="s">
         <v>7229</v>
@@ -60181,7 +60181,7 @@
         <v>7204</v>
       </c>
       <c r="F1084">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G1084" t="s">
         <v>7228</v>
@@ -60207,7 +60207,7 @@
         <v>7204</v>
       </c>
       <c r="F1085">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G1085" t="s">
         <v>7228</v>
@@ -60259,7 +60259,7 @@
         <v>7222</v>
       </c>
       <c r="F1087">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="G1087" t="s">
         <v>7228</v>
@@ -60389,7 +60389,7 @@
         <v>7222</v>
       </c>
       <c r="F1092">
-        <v>593</v>
+        <v>563</v>
       </c>
       <c r="G1092" t="s">
         <v>7229</v>
@@ -60409,7 +60409,7 @@
         <v>7222</v>
       </c>
       <c r="F1093">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="G1093" t="s">
         <v>7229</v>
@@ -60429,7 +60429,7 @@
         <v>7222</v>
       </c>
       <c r="F1094">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="G1094" t="s">
         <v>7229</v>
@@ -60449,7 +60449,7 @@
         <v>7222</v>
       </c>
       <c r="F1095">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="G1095" t="s">
         <v>7229</v>
@@ -60469,7 +60469,7 @@
         <v>7222</v>
       </c>
       <c r="F1096">
-        <v>1415</v>
+        <v>1406</v>
       </c>
       <c r="G1096" t="s">
         <v>7229</v>
@@ -60489,7 +60489,7 @@
         <v>7222</v>
       </c>
       <c r="F1097">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="G1097" t="s">
         <v>7229</v>
@@ -60509,7 +60509,7 @@
         <v>7222</v>
       </c>
       <c r="F1098">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="G1098" t="s">
         <v>7229</v>
@@ -60529,7 +60529,7 @@
         <v>7222</v>
       </c>
       <c r="F1099">
-        <v>1402</v>
+        <v>1393</v>
       </c>
       <c r="G1099" t="s">
         <v>7229</v>
@@ -60549,7 +60549,7 @@
         <v>7222</v>
       </c>
       <c r="F1100">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="G1100" t="s">
         <v>7229</v>
@@ -60569,7 +60569,7 @@
         <v>7222</v>
       </c>
       <c r="F1101">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="G1101" t="s">
         <v>7229</v>
@@ -60589,7 +60589,7 @@
         <v>7222</v>
       </c>
       <c r="F1102">
-        <v>1342</v>
+        <v>1333</v>
       </c>
       <c r="G1102" t="s">
         <v>7229</v>
@@ -60661,7 +60661,7 @@
         <v>7222</v>
       </c>
       <c r="F1105">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="G1105" t="s">
         <v>7229</v>
@@ -61079,7 +61079,7 @@
         <v>7222</v>
       </c>
       <c r="F1122">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="G1122" t="s">
         <v>7229</v>
@@ -61099,7 +61099,7 @@
         <v>7222</v>
       </c>
       <c r="F1123">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="G1123" t="s">
         <v>7229</v>
@@ -61119,7 +61119,7 @@
         <v>7204</v>
       </c>
       <c r="F1124">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1124" t="s">
         <v>7228</v>
@@ -61321,7 +61321,7 @@
         <v>7222</v>
       </c>
       <c r="F1132">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="G1132" t="s">
         <v>7228</v>
@@ -61511,7 +61511,7 @@
         <v>7204</v>
       </c>
       <c r="F1140">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G1140" t="s">
         <v>7228</v>
@@ -61563,7 +61563,7 @@
         <v>7222</v>
       </c>
       <c r="F1142">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="G1142" t="s">
         <v>7229</v>
@@ -61583,7 +61583,7 @@
         <v>7222</v>
       </c>
       <c r="F1143">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="G1143" t="s">
         <v>7229</v>
@@ -61603,7 +61603,7 @@
         <v>7222</v>
       </c>
       <c r="F1144">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G1144" t="s">
         <v>7229</v>
@@ -61623,7 +61623,7 @@
         <v>7222</v>
       </c>
       <c r="F1145">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="G1145" t="s">
         <v>7229</v>
@@ -61663,7 +61663,7 @@
         <v>7222</v>
       </c>
       <c r="F1147">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="G1147" t="s">
         <v>7229</v>
@@ -61683,7 +61683,7 @@
         <v>7222</v>
       </c>
       <c r="F1148">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="G1148" t="s">
         <v>7229</v>
@@ -61723,7 +61723,7 @@
         <v>7222</v>
       </c>
       <c r="F1150">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="G1150" t="s">
         <v>7229</v>
@@ -61743,7 +61743,7 @@
         <v>7222</v>
       </c>
       <c r="F1151">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="G1151" t="s">
         <v>7229</v>
@@ -62057,7 +62057,7 @@
         <v>7186</v>
       </c>
       <c r="F1164">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1164" t="s">
         <v>7228</v>
@@ -62083,7 +62083,7 @@
         <v>7186</v>
       </c>
       <c r="F1165">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G1165" t="s">
         <v>7228</v>
@@ -62291,7 +62291,7 @@
         <v>7186</v>
       </c>
       <c r="F1173">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G1173" t="s">
         <v>7228</v>
@@ -63085,7 +63085,7 @@
         <v>7191</v>
       </c>
       <c r="F1210">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G1210" t="s">
         <v>7229</v>
@@ -63131,7 +63131,7 @@
         <v>7191</v>
       </c>
       <c r="F1212">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="G1212" t="s">
         <v>7228</v>
@@ -63385,7 +63385,7 @@
         <v>7186</v>
       </c>
       <c r="F1222">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G1222" t="s">
         <v>7228</v>
@@ -63411,7 +63411,7 @@
         <v>7186</v>
       </c>
       <c r="F1223">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G1223" t="s">
         <v>7228</v>
@@ -63437,7 +63437,7 @@
         <v>7186</v>
       </c>
       <c r="F1224">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G1224" t="s">
         <v>7228</v>
@@ -63567,7 +63567,7 @@
         <v>7186</v>
       </c>
       <c r="F1229">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="G1229" t="s">
         <v>7228</v>
@@ -63593,7 +63593,7 @@
         <v>7186</v>
       </c>
       <c r="F1230">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G1230" t="s">
         <v>7228</v>
@@ -63616,7 +63616,7 @@
         <v>7186</v>
       </c>
       <c r="F1231">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G1231" t="s">
         <v>7229</v>
@@ -63636,7 +63636,7 @@
         <v>7186</v>
       </c>
       <c r="F1232">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G1232" t="s">
         <v>7228</v>
@@ -63748,7 +63748,7 @@
         <v>7186</v>
       </c>
       <c r="F1237">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G1237" t="s">
         <v>7228</v>
@@ -63912,7 +63912,7 @@
         <v>7201</v>
       </c>
       <c r="F1244">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G1244" t="s">
         <v>7228</v>
@@ -63938,7 +63938,7 @@
         <v>7186</v>
       </c>
       <c r="F1245">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G1245" t="s">
         <v>7228</v>
@@ -64016,7 +64016,7 @@
         <v>7184</v>
       </c>
       <c r="F1248">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="G1248" t="s">
         <v>7228</v>
@@ -64094,7 +64094,7 @@
         <v>7199</v>
       </c>
       <c r="F1251">
-        <v>7249</v>
+        <v>7242</v>
       </c>
       <c r="G1251" t="s">
         <v>7228</v>
@@ -64238,7 +64238,7 @@
         <v>7186</v>
       </c>
       <c r="F1257">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1257" t="s">
         <v>7228</v>
@@ -64264,7 +64264,7 @@
         <v>7186</v>
       </c>
       <c r="F1258">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="G1258" t="s">
         <v>7228</v>
@@ -64290,7 +64290,7 @@
         <v>7186</v>
       </c>
       <c r="F1259">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G1259" t="s">
         <v>7228</v>
@@ -64856,7 +64856,7 @@
         <v>7201</v>
       </c>
       <c r="F1284">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1284" t="s">
         <v>7228</v>
@@ -65312,7 +65312,7 @@
         <v>7191</v>
       </c>
       <c r="F1302">
-        <v>2205</v>
+        <v>2201</v>
       </c>
       <c r="G1302" t="s">
         <v>7228</v>
@@ -65390,7 +65390,7 @@
         <v>7191</v>
       </c>
       <c r="F1305">
-        <v>1929</v>
+        <v>1921</v>
       </c>
       <c r="G1305" t="s">
         <v>7228</v>
@@ -65416,7 +65416,7 @@
         <v>7191</v>
       </c>
       <c r="F1306">
-        <v>2633</v>
+        <v>2617</v>
       </c>
       <c r="G1306" t="s">
         <v>7228</v>
@@ -65850,7 +65850,7 @@
         <v>7186</v>
       </c>
       <c r="F1325">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G1325" t="s">
         <v>7228</v>
@@ -65876,7 +65876,7 @@
         <v>7186</v>
       </c>
       <c r="F1326">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G1326" t="s">
         <v>7228</v>
@@ -65902,7 +65902,7 @@
         <v>7186</v>
       </c>
       <c r="F1327">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G1327" t="s">
         <v>7228</v>
@@ -65928,7 +65928,7 @@
         <v>7186</v>
       </c>
       <c r="F1328">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G1328" t="s">
         <v>7228</v>
@@ -65980,7 +65980,7 @@
         <v>7186</v>
       </c>
       <c r="F1330">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G1330" t="s">
         <v>7228</v>
@@ -67018,7 +67018,7 @@
         <v>7186</v>
       </c>
       <c r="F1372">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G1372" t="s">
         <v>7228</v>
@@ -67044,7 +67044,7 @@
         <v>7186</v>
       </c>
       <c r="F1373">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1373" t="s">
         <v>7228</v>
@@ -67168,7 +67168,7 @@
         <v>7198</v>
       </c>
       <c r="F1378">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G1378" t="s">
         <v>7228</v>
@@ -67220,7 +67220,7 @@
         <v>7198</v>
       </c>
       <c r="F1380">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="G1380" t="s">
         <v>7228</v>
@@ -67298,7 +67298,7 @@
         <v>7198</v>
       </c>
       <c r="F1383">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G1383" t="s">
         <v>7228</v>
@@ -67324,7 +67324,7 @@
         <v>7198</v>
       </c>
       <c r="F1384">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G1384" t="s">
         <v>7228</v>
@@ -67350,7 +67350,7 @@
         <v>7198</v>
       </c>
       <c r="F1385">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="G1385" t="s">
         <v>7228</v>
@@ -67376,7 +67376,7 @@
         <v>7198</v>
       </c>
       <c r="F1386">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1386" t="s">
         <v>7228</v>
@@ -67454,7 +67454,7 @@
         <v>7186</v>
       </c>
       <c r="F1389">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G1389" t="s">
         <v>7228</v>
@@ -67480,7 +67480,7 @@
         <v>7198</v>
       </c>
       <c r="F1390">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="G1390" t="s">
         <v>7228</v>
@@ -67844,7 +67844,7 @@
         <v>7198</v>
       </c>
       <c r="F1404">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G1404" t="s">
         <v>7228</v>
@@ -68260,7 +68260,7 @@
         <v>7198</v>
       </c>
       <c r="F1420">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G1420" t="s">
         <v>7228</v>
@@ -68286,7 +68286,7 @@
         <v>7185</v>
       </c>
       <c r="F1421">
-        <v>6119</v>
+        <v>6011</v>
       </c>
       <c r="G1421" t="s">
         <v>7228</v>
@@ -68338,7 +68338,7 @@
         <v>7198</v>
       </c>
       <c r="F1423">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="G1423" t="s">
         <v>7228</v>
@@ -68364,7 +68364,7 @@
         <v>7198</v>
       </c>
       <c r="F1424">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="G1424" t="s">
         <v>7228</v>
@@ -68390,7 +68390,7 @@
         <v>7198</v>
       </c>
       <c r="F1425">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G1425" t="s">
         <v>7228</v>
@@ -68416,7 +68416,7 @@
         <v>7198</v>
       </c>
       <c r="F1426">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G1426" t="s">
         <v>7228</v>
@@ -68442,7 +68442,7 @@
         <v>7198</v>
       </c>
       <c r="F1427">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G1427" t="s">
         <v>7228</v>
@@ -68468,7 +68468,7 @@
         <v>7198</v>
       </c>
       <c r="F1428">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="G1428" t="s">
         <v>7228</v>
@@ -68546,7 +68546,7 @@
         <v>7198</v>
       </c>
       <c r="F1431">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G1431" t="s">
         <v>7228</v>
@@ -68572,7 +68572,7 @@
         <v>7198</v>
       </c>
       <c r="F1432">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="G1432" t="s">
         <v>7228</v>
@@ -68624,7 +68624,7 @@
         <v>7198</v>
       </c>
       <c r="F1434">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G1434" t="s">
         <v>7228</v>
@@ -69528,7 +69528,7 @@
         <v>7209</v>
       </c>
       <c r="F1478">
-        <v>688</v>
+        <v>658</v>
       </c>
       <c r="G1478" t="s">
         <v>7228</v>
@@ -69554,7 +69554,7 @@
         <v>7209</v>
       </c>
       <c r="F1479">
-        <v>577</v>
+        <v>541</v>
       </c>
       <c r="G1479" t="s">
         <v>7228</v>
@@ -69740,7 +69740,7 @@
         <v>7209</v>
       </c>
       <c r="F1488">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="G1488" t="s">
         <v>7228</v>
@@ -69806,7 +69806,7 @@
         <v>7209</v>
       </c>
       <c r="F1491">
-        <v>851</v>
+        <v>827</v>
       </c>
       <c r="G1491" t="s">
         <v>7228</v>
@@ -69832,7 +69832,7 @@
         <v>7209</v>
       </c>
       <c r="F1492">
-        <v>1569</v>
+        <v>1557</v>
       </c>
       <c r="G1492" t="s">
         <v>7228</v>
@@ -69884,7 +69884,7 @@
         <v>7209</v>
       </c>
       <c r="F1494">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="G1494" t="s">
         <v>7228</v>
@@ -70660,7 +70660,7 @@
         <v>7189</v>
       </c>
       <c r="F1525">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G1525" t="s">
         <v>7228</v>
@@ -70686,7 +70686,7 @@
         <v>7189</v>
       </c>
       <c r="F1526">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G1526" t="s">
         <v>7228</v>
@@ -70712,7 +70712,7 @@
         <v>7189</v>
       </c>
       <c r="F1527">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G1527" t="s">
         <v>7228</v>
@@ -70738,7 +70738,7 @@
         <v>7186</v>
       </c>
       <c r="F1528">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G1528" t="s">
         <v>7228</v>
@@ -70790,7 +70790,7 @@
         <v>7186</v>
       </c>
       <c r="F1530">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G1530" t="s">
         <v>7228</v>
@@ -70816,7 +70816,7 @@
         <v>7186</v>
       </c>
       <c r="F1531">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G1531" t="s">
         <v>7228</v>
@@ -70842,7 +70842,7 @@
         <v>7186</v>
       </c>
       <c r="F1532">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G1532" t="s">
         <v>7228</v>
@@ -70868,7 +70868,7 @@
         <v>7189</v>
       </c>
       <c r="F1533">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G1533" t="s">
         <v>7228</v>
@@ -72066,7 +72066,7 @@
         <v>7224</v>
       </c>
       <c r="F1586">
-        <v>1552</v>
+        <v>1534</v>
       </c>
       <c r="G1586" t="s">
         <v>7228</v>
@@ -72092,7 +72092,7 @@
         <v>7224</v>
       </c>
       <c r="F1587">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="G1587" t="s">
         <v>7228</v>
@@ -72144,7 +72144,7 @@
         <v>7224</v>
       </c>
       <c r="F1589">
-        <v>2660</v>
+        <v>2498</v>
       </c>
       <c r="G1589" t="s">
         <v>7228</v>
@@ -72170,7 +72170,7 @@
         <v>7224</v>
       </c>
       <c r="F1590">
-        <v>1792</v>
+        <v>1774</v>
       </c>
       <c r="G1590" t="s">
         <v>7228</v>
@@ -72196,7 +72196,7 @@
         <v>7224</v>
       </c>
       <c r="F1591">
-        <v>3475</v>
+        <v>3385</v>
       </c>
       <c r="G1591" t="s">
         <v>7228</v>
@@ -72378,7 +72378,7 @@
         <v>7223</v>
       </c>
       <c r="F1598">
-        <v>1560</v>
+        <v>1480</v>
       </c>
       <c r="G1598" t="s">
         <v>7228</v>
@@ -72404,7 +72404,7 @@
         <v>7223</v>
       </c>
       <c r="F1599">
-        <v>3362</v>
+        <v>3338</v>
       </c>
       <c r="G1599" t="s">
         <v>7228</v>
@@ -72430,7 +72430,7 @@
         <v>7223</v>
       </c>
       <c r="F1600">
-        <v>3344</v>
+        <v>3328</v>
       </c>
       <c r="G1600" t="s">
         <v>7228</v>
@@ -72456,7 +72456,7 @@
         <v>7223</v>
       </c>
       <c r="F1601">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="G1601" t="s">
         <v>7228</v>
@@ -72482,7 +72482,7 @@
         <v>7223</v>
       </c>
       <c r="F1602">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G1602" t="s">
         <v>7228</v>
@@ -72508,7 +72508,7 @@
         <v>7223</v>
       </c>
       <c r="F1603">
-        <v>1837</v>
+        <v>1789</v>
       </c>
       <c r="G1603" t="s">
         <v>7228</v>
@@ -72560,7 +72560,7 @@
         <v>7223</v>
       </c>
       <c r="F1605">
-        <v>3905</v>
+        <v>3875</v>
       </c>
       <c r="G1605" t="s">
         <v>7228</v>
@@ -72586,7 +72586,7 @@
         <v>7223</v>
       </c>
       <c r="F1606">
-        <v>2437</v>
+        <v>2422</v>
       </c>
       <c r="G1606" t="s">
         <v>7228</v>
@@ -72716,7 +72716,7 @@
         <v>7223</v>
       </c>
       <c r="F1611">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G1611" t="s">
         <v>7228</v>
@@ -72768,7 +72768,7 @@
         <v>7223</v>
       </c>
       <c r="F1613">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="G1613" t="s">
         <v>7228</v>
@@ -72820,7 +72820,7 @@
         <v>7223</v>
       </c>
       <c r="F1615">
-        <v>1837</v>
+        <v>1813</v>
       </c>
       <c r="G1615" t="s">
         <v>7228</v>
@@ -72846,7 +72846,7 @@
         <v>7223</v>
       </c>
       <c r="F1616">
-        <v>1588</v>
+        <v>1572</v>
       </c>
       <c r="G1616" t="s">
         <v>7228</v>
@@ -72872,7 +72872,7 @@
         <v>7223</v>
       </c>
       <c r="F1617">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="G1617" t="s">
         <v>7228</v>
@@ -72898,7 +72898,7 @@
         <v>7223</v>
       </c>
       <c r="F1618">
-        <v>1772</v>
+        <v>1739</v>
       </c>
       <c r="G1618" t="s">
         <v>7228</v>
@@ -73400,7 +73400,7 @@
         <v>7209</v>
       </c>
       <c r="F1638">
-        <v>2229</v>
+        <v>2199</v>
       </c>
       <c r="G1638" t="s">
         <v>7228</v>
@@ -73426,7 +73426,7 @@
         <v>7209</v>
       </c>
       <c r="F1639">
-        <v>4334</v>
+        <v>4304</v>
       </c>
       <c r="G1639" t="s">
         <v>7228</v>
@@ -73452,7 +73452,7 @@
         <v>7209</v>
       </c>
       <c r="F1640">
-        <v>2198</v>
+        <v>2158</v>
       </c>
       <c r="G1640" t="s">
         <v>7228</v>
@@ -73816,7 +73816,7 @@
         <v>7209</v>
       </c>
       <c r="F1654">
-        <v>2278</v>
+        <v>2248</v>
       </c>
       <c r="G1654" t="s">
         <v>7228</v>
@@ -73842,7 +73842,7 @@
         <v>7209</v>
       </c>
       <c r="F1655">
-        <v>2745</v>
+        <v>2705</v>
       </c>
       <c r="G1655" t="s">
         <v>7228</v>
@@ -74284,7 +74284,7 @@
         <v>7203</v>
       </c>
       <c r="F1672">
-        <v>5413</v>
+        <v>5401</v>
       </c>
       <c r="G1672" t="s">
         <v>7228</v>
@@ -74622,7 +74622,7 @@
         <v>7203</v>
       </c>
       <c r="F1685">
-        <v>715</v>
+        <v>691</v>
       </c>
       <c r="G1685" t="s">
         <v>7228</v>
@@ -74778,7 +74778,7 @@
         <v>7203</v>
       </c>
       <c r="F1691">
-        <v>3571</v>
+        <v>3547</v>
       </c>
       <c r="G1691" t="s">
         <v>7228</v>
@@ -74830,7 +74830,7 @@
         <v>7203</v>
       </c>
       <c r="F1693">
-        <v>1942</v>
+        <v>1918</v>
       </c>
       <c r="G1693" t="s">
         <v>7228</v>
@@ -75038,7 +75038,7 @@
         <v>7203</v>
       </c>
       <c r="F1701">
-        <v>8328</v>
+        <v>8316</v>
       </c>
       <c r="G1701" t="s">
         <v>7228</v>
@@ -75396,7 +75396,7 @@
         <v>7203</v>
       </c>
       <c r="F1715">
-        <v>1439</v>
+        <v>1427</v>
       </c>
       <c r="G1715" t="s">
         <v>7228</v>
@@ -75942,7 +75942,7 @@
         <v>7195</v>
       </c>
       <c r="F1736">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G1736" t="s">
         <v>7228</v>
@@ -76176,7 +76176,7 @@
         <v>7199</v>
       </c>
       <c r="F1745">
-        <v>8365</v>
+        <v>8353</v>
       </c>
       <c r="G1745" t="s">
         <v>7228</v>
@@ -76202,7 +76202,7 @@
         <v>7184</v>
       </c>
       <c r="F1746">
-        <v>888</v>
+        <v>808</v>
       </c>
       <c r="G1746" t="s">
         <v>7228</v>
@@ -76228,7 +76228,7 @@
         <v>7184</v>
       </c>
       <c r="F1747">
-        <v>1433</v>
+        <v>1409</v>
       </c>
       <c r="G1747" t="s">
         <v>7228</v>
@@ -76280,7 +76280,7 @@
         <v>7184</v>
       </c>
       <c r="F1749">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="G1749" t="s">
         <v>7228</v>
@@ -76306,7 +76306,7 @@
         <v>7184</v>
       </c>
       <c r="F1750">
-        <v>15930</v>
+        <v>15846</v>
       </c>
       <c r="G1750" t="s">
         <v>7228</v>
@@ -76332,7 +76332,7 @@
         <v>7184</v>
       </c>
       <c r="F1751">
-        <v>1651</v>
+        <v>1585</v>
       </c>
       <c r="G1751" t="s">
         <v>7228</v>
@@ -76358,7 +76358,7 @@
         <v>7184</v>
       </c>
       <c r="F1752">
-        <v>1257</v>
+        <v>1227</v>
       </c>
       <c r="G1752" t="s">
         <v>7228</v>
@@ -76384,7 +76384,7 @@
         <v>7204</v>
       </c>
       <c r="F1753">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G1753" t="s">
         <v>7228</v>
@@ -76410,7 +76410,7 @@
         <v>7204</v>
       </c>
       <c r="F1754">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G1754" t="s">
         <v>7228</v>
@@ -76508,7 +76508,7 @@
         <v>7193</v>
       </c>
       <c r="F1758">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G1758" t="s">
         <v>7228</v>
@@ -76854,7 +76854,7 @@
         <v>7195</v>
       </c>
       <c r="F1772">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="G1772" t="s">
         <v>7228</v>
@@ -76880,7 +76880,7 @@
         <v>7195</v>
       </c>
       <c r="F1773">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="G1773" t="s">
         <v>7228</v>
@@ -76906,7 +76906,7 @@
         <v>7195</v>
       </c>
       <c r="F1774">
-        <v>8903</v>
+        <v>8879</v>
       </c>
       <c r="G1774" t="s">
         <v>7228</v>
@@ -76932,7 +76932,7 @@
         <v>7195</v>
       </c>
       <c r="F1775">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G1775" t="s">
         <v>7228</v>
@@ -76958,7 +76958,7 @@
         <v>7195</v>
       </c>
       <c r="F1776">
-        <v>983</v>
+        <v>959</v>
       </c>
       <c r="G1776" t="s">
         <v>7228</v>
@@ -77088,7 +77088,7 @@
         <v>7195</v>
       </c>
       <c r="F1781">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="G1781" t="s">
         <v>7228</v>
@@ -77192,7 +77192,7 @@
         <v>7193</v>
       </c>
       <c r="F1785">
-        <v>4320</v>
+        <v>4308</v>
       </c>
       <c r="G1785" t="s">
         <v>7228</v>
@@ -77584,7 +77584,7 @@
         <v>7225</v>
       </c>
       <c r="F1801">
-        <v>2277</v>
+        <v>2265</v>
       </c>
       <c r="G1801" t="s">
         <v>7228</v>
@@ -77610,7 +77610,7 @@
         <v>7225</v>
       </c>
       <c r="F1802">
-        <v>1497</v>
+        <v>1485</v>
       </c>
       <c r="G1802" t="s">
         <v>7228</v>
@@ -77870,7 +77870,7 @@
         <v>7185</v>
       </c>
       <c r="F1812">
-        <v>2045</v>
+        <v>2005</v>
       </c>
       <c r="G1812" t="s">
         <v>7228</v>
@@ -77896,7 +77896,7 @@
         <v>7185</v>
       </c>
       <c r="F1813">
-        <v>1284</v>
+        <v>1254</v>
       </c>
       <c r="G1813" t="s">
         <v>7228</v>
@@ -77948,7 +77948,7 @@
         <v>7185</v>
       </c>
       <c r="F1815">
-        <v>2274</v>
+        <v>2256</v>
       </c>
       <c r="G1815" t="s">
         <v>7228</v>
@@ -77974,7 +77974,7 @@
         <v>7185</v>
       </c>
       <c r="F1816">
-        <v>5235</v>
+        <v>5037</v>
       </c>
       <c r="G1816" t="s">
         <v>7228</v>
@@ -78156,7 +78156,7 @@
         <v>7185</v>
       </c>
       <c r="F1823">
-        <v>1185</v>
+        <v>1105</v>
       </c>
       <c r="G1823" t="s">
         <v>7228</v>
@@ -78364,7 +78364,7 @@
         <v>7221</v>
       </c>
       <c r="F1831">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="G1831" t="s">
         <v>7228</v>
@@ -78520,7 +78520,7 @@
         <v>7222</v>
       </c>
       <c r="F1837">
-        <v>1104</v>
+        <v>1068</v>
       </c>
       <c r="G1837" t="s">
         <v>7228</v>
@@ -78572,7 +78572,7 @@
         <v>7222</v>
       </c>
       <c r="F1839">
-        <v>2607</v>
+        <v>2595</v>
       </c>
       <c r="G1839" t="s">
         <v>7228</v>
@@ -78702,7 +78702,7 @@
         <v>7222</v>
       </c>
       <c r="F1844">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="G1844" t="s">
         <v>7228</v>
@@ -78904,7 +78904,7 @@
         <v>7222</v>
       </c>
       <c r="F1852">
-        <v>1636</v>
+        <v>1612</v>
       </c>
       <c r="G1852" t="s">
         <v>7228</v>
@@ -78930,7 +78930,7 @@
         <v>7222</v>
       </c>
       <c r="F1853">
-        <v>3085</v>
+        <v>3073</v>
       </c>
       <c r="G1853" t="s">
         <v>7228</v>
@@ -79112,7 +79112,7 @@
         <v>7222</v>
       </c>
       <c r="F1860">
-        <v>2517</v>
+        <v>2505</v>
       </c>
       <c r="G1860" t="s">
         <v>7228</v>
@@ -79444,7 +79444,7 @@
         <v>7222</v>
       </c>
       <c r="F1873">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="G1873" t="s">
         <v>7228</v>
@@ -79496,7 +79496,7 @@
         <v>7222</v>
       </c>
       <c r="F1875">
-        <v>2288</v>
+        <v>2276</v>
       </c>
       <c r="G1875" t="s">
         <v>7228</v>
@@ -79548,7 +79548,7 @@
         <v>7191</v>
       </c>
       <c r="F1877">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="G1877" t="s">
         <v>7228</v>
@@ -79600,7 +79600,7 @@
         <v>7191</v>
       </c>
       <c r="F1879">
-        <v>1961</v>
+        <v>1955</v>
       </c>
       <c r="G1879" t="s">
         <v>7228</v>
@@ -79678,7 +79678,7 @@
         <v>7191</v>
       </c>
       <c r="F1882">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="G1882" t="s">
         <v>7228</v>
@@ -79782,7 +79782,7 @@
         <v>7191</v>
       </c>
       <c r="F1886">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="G1886" t="s">
         <v>7228</v>
@@ -79886,7 +79886,7 @@
         <v>7191</v>
       </c>
       <c r="F1890">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="G1890" t="s">
         <v>7228</v>
@@ -79964,7 +79964,7 @@
         <v>7191</v>
       </c>
       <c r="F1893">
-        <v>2783</v>
+        <v>2777</v>
       </c>
       <c r="G1893" t="s">
         <v>7228</v>
@@ -80088,7 +80088,7 @@
         <v>7222</v>
       </c>
       <c r="F1898">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="G1898" t="s">
         <v>7228</v>
@@ -80114,7 +80114,7 @@
         <v>7222</v>
       </c>
       <c r="F1899">
-        <v>638</v>
+        <v>602</v>
       </c>
       <c r="G1899" t="s">
         <v>7228</v>
@@ -80166,7 +80166,7 @@
         <v>7222</v>
       </c>
       <c r="F1901">
-        <v>1100</v>
+        <v>1064</v>
       </c>
       <c r="G1901" t="s">
         <v>7228</v>
@@ -81436,7 +81436,7 @@
         <v>7206</v>
       </c>
       <c r="F1951">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="G1951" t="s">
         <v>7228</v>
@@ -83008,7 +83008,7 @@
         <v>7186</v>
       </c>
       <c r="F2014">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G2014" t="s">
         <v>7228</v>
@@ -83384,7 +83384,7 @@
         <v>7186</v>
       </c>
       <c r="F2031">
-        <v>1029</v>
+        <v>1008</v>
       </c>
       <c r="G2031" t="s">
         <v>7228</v>
@@ -83462,7 +83462,7 @@
         <v>7186</v>
       </c>
       <c r="F2034">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G2034" t="s">
         <v>7228</v>
@@ -83488,7 +83488,7 @@
         <v>7186</v>
       </c>
       <c r="F2035">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="G2035" t="s">
         <v>7228</v>
@@ -83540,7 +83540,7 @@
         <v>7186</v>
       </c>
       <c r="F2037">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G2037" t="s">
         <v>7228</v>
@@ -83644,7 +83644,7 @@
         <v>7186</v>
       </c>
       <c r="F2041">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="G2041" t="s">
         <v>7228</v>
@@ -83670,7 +83670,7 @@
         <v>7186</v>
       </c>
       <c r="F2042">
-        <v>1051</v>
+        <v>1030</v>
       </c>
       <c r="G2042" t="s">
         <v>7228</v>
@@ -84074,7 +84074,7 @@
         <v>7186</v>
       </c>
       <c r="F2058">
-        <v>1456</v>
+        <v>1450</v>
       </c>
       <c r="G2058" t="s">
         <v>7228</v>
@@ -84100,7 +84100,7 @@
         <v>7186</v>
       </c>
       <c r="F2059">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G2059" t="s">
         <v>7228</v>
@@ -84256,7 +84256,7 @@
         <v>7189</v>
       </c>
       <c r="F2065">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G2065" t="s">
         <v>7228</v>
@@ -84282,7 +84282,7 @@
         <v>7189</v>
       </c>
       <c r="F2066">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G2066" t="s">
         <v>7228</v>
@@ -84308,7 +84308,7 @@
         <v>7189</v>
       </c>
       <c r="F2067">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G2067" t="s">
         <v>7228</v>
@@ -84334,7 +84334,7 @@
         <v>7189</v>
       </c>
       <c r="F2068">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G2068" t="s">
         <v>7228</v>
@@ -84922,7 +84922,7 @@
         <v>7186</v>
       </c>
       <c r="F2092">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2092" t="s">
         <v>7228</v>
@@ -85576,7 +85576,7 @@
         <v>7210</v>
       </c>
       <c r="F2119">
-        <v>589</v>
+        <v>547</v>
       </c>
       <c r="G2119" t="s">
         <v>7228</v>
@@ -85732,7 +85732,7 @@
         <v>7189</v>
       </c>
       <c r="F2125">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2125" t="s">
         <v>7228</v>
@@ -86086,7 +86086,7 @@
         <v>7210</v>
       </c>
       <c r="F2140">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="G2140" t="s">
         <v>7228</v>
@@ -86678,7 +86678,7 @@
         <v>7210</v>
       </c>
       <c r="F2163">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="G2163" t="s">
         <v>7228</v>
@@ -87436,7 +87436,7 @@
         <v>7210</v>
       </c>
       <c r="F2194">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G2194" t="s">
         <v>7228</v>
@@ -87626,7 +87626,7 @@
         <v>7194</v>
       </c>
       <c r="F2202">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G2202" t="s">
         <v>7229</v>
@@ -87646,7 +87646,7 @@
         <v>7194</v>
       </c>
       <c r="F2203">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G2203" t="s">
         <v>7229</v>
@@ -87830,7 +87830,7 @@
         <v>7194</v>
       </c>
       <c r="F2211">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G2211" t="s">
         <v>7228</v>
@@ -87916,7 +87916,7 @@
         <v>7194</v>
       </c>
       <c r="F2215">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G2215" t="s">
         <v>7228</v>
@@ -87942,7 +87942,7 @@
         <v>7194</v>
       </c>
       <c r="F2216">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G2216" t="s">
         <v>7228</v>
@@ -88158,7 +88158,7 @@
         <v>7194</v>
       </c>
       <c r="F2225">
-        <v>1047</v>
+        <v>1027</v>
       </c>
       <c r="G2225" t="s">
         <v>7228</v>
@@ -88184,7 +88184,7 @@
         <v>7194</v>
       </c>
       <c r="F2226">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="G2226" t="s">
         <v>7228</v>
@@ -88262,7 +88262,7 @@
         <v>7194</v>
       </c>
       <c r="F2229">
-        <v>32331</v>
+        <v>31941</v>
       </c>
       <c r="G2229" t="s">
         <v>7228</v>
@@ -88288,7 +88288,7 @@
         <v>7194</v>
       </c>
       <c r="F2230">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="G2230" t="s">
         <v>7228</v>
@@ -88314,7 +88314,7 @@
         <v>7194</v>
       </c>
       <c r="F2231">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="G2231" t="s">
         <v>7228</v>
@@ -88412,7 +88412,7 @@
         <v>7194</v>
       </c>
       <c r="F2235">
-        <v>6746</v>
+        <v>6706</v>
       </c>
       <c r="G2235" t="s">
         <v>7228</v>
@@ -88438,7 +88438,7 @@
         <v>7194</v>
       </c>
       <c r="F2236">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="G2236" t="s">
         <v>7228</v>
@@ -88542,7 +88542,7 @@
         <v>7194</v>
       </c>
       <c r="F2240">
-        <v>1809</v>
+        <v>1779</v>
       </c>
       <c r="G2240" t="s">
         <v>7228</v>
@@ -88726,7 +88726,7 @@
         <v>7194</v>
       </c>
       <c r="F2248">
-        <v>5610</v>
+        <v>5602</v>
       </c>
       <c r="G2248" t="s">
         <v>7228</v>
@@ -88856,7 +88856,7 @@
         <v>7194</v>
       </c>
       <c r="F2253">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G2253" t="s">
         <v>7228</v>
@@ -88942,7 +88942,7 @@
         <v>7194</v>
       </c>
       <c r="F2257">
-        <v>2984</v>
+        <v>2979</v>
       </c>
       <c r="G2257" t="s">
         <v>7228</v>
@@ -89112,7 +89112,7 @@
         <v>7189</v>
       </c>
       <c r="F2264">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G2264" t="s">
         <v>7228</v>
@@ -89138,7 +89138,7 @@
         <v>7189</v>
       </c>
       <c r="F2265">
-        <v>679</v>
+        <v>659</v>
       </c>
       <c r="G2265" t="s">
         <v>7228</v>
@@ -89164,7 +89164,7 @@
         <v>7189</v>
       </c>
       <c r="F2266">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G2266" t="s">
         <v>7228</v>
@@ -89604,7 +89604,7 @@
         <v>7189</v>
       </c>
       <c r="F2285">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G2285" t="s">
         <v>7228</v>
@@ -89630,7 +89630,7 @@
         <v>7189</v>
       </c>
       <c r="F2286">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="G2286" t="s">
         <v>7228</v>
@@ -89708,7 +89708,7 @@
         <v>7189</v>
       </c>
       <c r="F2289">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="G2289" t="s">
         <v>7228</v>
@@ -89734,7 +89734,7 @@
         <v>7189</v>
       </c>
       <c r="F2290">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="G2290" t="s">
         <v>7228</v>
@@ -89760,7 +89760,7 @@
         <v>7189</v>
       </c>
       <c r="F2291">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G2291" t="s">
         <v>7228</v>
@@ -89812,7 +89812,7 @@
         <v>7189</v>
       </c>
       <c r="F2293">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G2293" t="s">
         <v>7228</v>
@@ -90176,7 +90176,7 @@
         <v>7205</v>
       </c>
       <c r="F2310">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G2310" t="s">
         <v>7228</v>
@@ -90228,7 +90228,7 @@
         <v>7210</v>
       </c>
       <c r="F2312">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="G2312" t="s">
         <v>7228</v>
@@ -90332,7 +90332,7 @@
         <v>7205</v>
       </c>
       <c r="F2316">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G2316" t="s">
         <v>7228</v>
@@ -90358,7 +90358,7 @@
         <v>7205</v>
       </c>
       <c r="F2317">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G2317" t="s">
         <v>7228</v>
@@ -90384,7 +90384,7 @@
         <v>7205</v>
       </c>
       <c r="F2318">
-        <v>1658</v>
+        <v>1628</v>
       </c>
       <c r="G2318" t="s">
         <v>7228</v>
@@ -90410,7 +90410,7 @@
         <v>7205</v>
       </c>
       <c r="F2319">
-        <v>1157</v>
+        <v>1125</v>
       </c>
       <c r="G2319" t="s">
         <v>7228</v>
@@ -90436,7 +90436,7 @@
         <v>7205</v>
       </c>
       <c r="F2320">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="G2320" t="s">
         <v>7228</v>
@@ -90462,7 +90462,7 @@
         <v>7205</v>
       </c>
       <c r="F2321">
-        <v>1931</v>
+        <v>1925</v>
       </c>
       <c r="G2321" t="s">
         <v>7228</v>
@@ -90514,7 +90514,7 @@
         <v>7205</v>
       </c>
       <c r="F2323">
-        <v>1137</v>
+        <v>1101</v>
       </c>
       <c r="G2323" t="s">
         <v>7228</v>
@@ -90540,7 +90540,7 @@
         <v>7205</v>
       </c>
       <c r="F2324">
-        <v>1141</v>
+        <v>1123</v>
       </c>
       <c r="G2324" t="s">
         <v>7228</v>
@@ -90652,7 +90652,7 @@
         <v>7186</v>
       </c>
       <c r="F2329">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="G2329" t="s">
         <v>7228</v>
@@ -90678,7 +90678,7 @@
         <v>7186</v>
       </c>
       <c r="F2330">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G2330" t="s">
         <v>7228</v>
@@ -90704,7 +90704,7 @@
         <v>7186</v>
       </c>
       <c r="F2331">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G2331" t="s">
         <v>7228</v>
@@ -90730,7 +90730,7 @@
         <v>7186</v>
       </c>
       <c r="F2332">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G2332" t="s">
         <v>7228</v>
@@ -90756,7 +90756,7 @@
         <v>7186</v>
       </c>
       <c r="F2333">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G2333" t="s">
         <v>7228</v>
@@ -90782,7 +90782,7 @@
         <v>7186</v>
       </c>
       <c r="F2334">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G2334" t="s">
         <v>7229</v>
@@ -90802,7 +90802,7 @@
         <v>7189</v>
       </c>
       <c r="F2335">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G2335" t="s">
         <v>7228</v>
@@ -90828,7 +90828,7 @@
         <v>7189</v>
       </c>
       <c r="F2336">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G2336" t="s">
         <v>7228</v>
@@ -90854,7 +90854,7 @@
         <v>7189</v>
       </c>
       <c r="F2337">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G2337" t="s">
         <v>7228</v>
@@ -91392,7 +91392,7 @@
         <v>7210</v>
       </c>
       <c r="F2360">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="G2360" t="s">
         <v>7229</v>
@@ -91438,7 +91438,7 @@
         <v>7210</v>
       </c>
       <c r="F2362">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="G2362" t="s">
         <v>7228</v>
@@ -91464,7 +91464,7 @@
         <v>7210</v>
       </c>
       <c r="F2363">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2363" t="s">
         <v>7228</v>
@@ -91784,7 +91784,7 @@
         <v>7186</v>
       </c>
       <c r="F2376">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="G2376" t="s">
         <v>7229</v>
@@ -91944,7 +91944,7 @@
         <v>7186</v>
       </c>
       <c r="F2384">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G2384" t="s">
         <v>7228</v>
@@ -91970,7 +91970,7 @@
         <v>7186</v>
       </c>
       <c r="F2385">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G2385" t="s">
         <v>7228</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -34032,7 +34032,7 @@
         <v>7172</v>
       </c>
       <c r="F35">
-        <v>18830</v>
+        <v>18800</v>
       </c>
       <c r="G35" t="s">
         <v>7213</v>
@@ -34058,7 +34058,7 @@
         <v>7171</v>
       </c>
       <c r="F36">
-        <v>48209</v>
+        <v>48184</v>
       </c>
       <c r="G36" t="s">
         <v>7213</v>
@@ -34442,7 +34442,7 @@
         <v>7174</v>
       </c>
       <c r="F54">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="G54" t="s">
         <v>7214</v>
@@ -34618,7 +34618,7 @@
         <v>7174</v>
       </c>
       <c r="F61">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="G61" t="s">
         <v>7213</v>
@@ -35744,7 +35744,7 @@
         <v>7174</v>
       </c>
       <c r="F105">
-        <v>2404</v>
+        <v>2398</v>
       </c>
       <c r="G105" t="s">
         <v>7213</v>
@@ -35790,7 +35790,7 @@
         <v>7174</v>
       </c>
       <c r="F107">
-        <v>3123</v>
+        <v>3117</v>
       </c>
       <c r="G107" t="s">
         <v>7213</v>
@@ -36458,7 +36458,7 @@
         <v>7173</v>
       </c>
       <c r="F135">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G135" t="s">
         <v>7213</v>
@@ -38090,7 +38090,7 @@
         <v>7173</v>
       </c>
       <c r="F201">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G201" t="s">
         <v>7213</v>
@@ -38894,7 +38894,7 @@
         <v>7172</v>
       </c>
       <c r="F234">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="G234" t="s">
         <v>7213</v>
@@ -39578,7 +39578,7 @@
         <v>7186</v>
       </c>
       <c r="F261">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="G261" t="s">
         <v>7213</v>
@@ -40618,7 +40618,7 @@
         <v>7190</v>
       </c>
       <c r="F301">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="G301" t="s">
         <v>7213</v>
@@ -41770,7 +41770,7 @@
         <v>7173</v>
       </c>
       <c r="F346">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G346" t="s">
         <v>7214</v>
@@ -41790,7 +41790,7 @@
         <v>7173</v>
       </c>
       <c r="F347">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G347" t="s">
         <v>7213</v>
@@ -41816,7 +41816,7 @@
         <v>7173</v>
       </c>
       <c r="F348">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G348" t="s">
         <v>7213</v>
@@ -41920,7 +41920,7 @@
         <v>7173</v>
       </c>
       <c r="F352">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G352" t="s">
         <v>7214</v>
@@ -41966,7 +41966,7 @@
         <v>7173</v>
       </c>
       <c r="F354">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="G354" t="s">
         <v>7214</v>
@@ -41986,7 +41986,7 @@
         <v>7173</v>
       </c>
       <c r="F355">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G355" t="s">
         <v>7214</v>
@@ -42032,7 +42032,7 @@
         <v>7173</v>
       </c>
       <c r="F357">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="G357" t="s">
         <v>7214</v>
@@ -42104,7 +42104,7 @@
         <v>7173</v>
       </c>
       <c r="F360">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G360" t="s">
         <v>7214</v>
@@ -42124,7 +42124,7 @@
         <v>7173</v>
       </c>
       <c r="F361">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G361" t="s">
         <v>7213</v>
@@ -42150,7 +42150,7 @@
         <v>7173</v>
       </c>
       <c r="F362">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G362" t="s">
         <v>7214</v>
@@ -42378,7 +42378,7 @@
         <v>7181</v>
       </c>
       <c r="F371">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="G371" t="s">
         <v>7213</v>
@@ -42534,7 +42534,7 @@
         <v>7181</v>
       </c>
       <c r="F377">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G377" t="s">
         <v>7213</v>
@@ -42880,7 +42880,7 @@
         <v>7170</v>
       </c>
       <c r="F391">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G391" t="s">
         <v>7213</v>
@@ -43804,7 +43804,7 @@
         <v>7173</v>
       </c>
       <c r="F427">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G427" t="s">
         <v>7213</v>
@@ -43856,7 +43856,7 @@
         <v>7173</v>
       </c>
       <c r="F429">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="G429" t="s">
         <v>7213</v>
@@ -43882,7 +43882,7 @@
         <v>7173</v>
       </c>
       <c r="F430">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="G430" t="s">
         <v>7213</v>
@@ -43934,7 +43934,7 @@
         <v>7173</v>
       </c>
       <c r="F432">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G432" t="s">
         <v>7213</v>
@@ -43960,7 +43960,7 @@
         <v>7173</v>
       </c>
       <c r="F433">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G433" t="s">
         <v>7213</v>
@@ -43986,7 +43986,7 @@
         <v>7173</v>
       </c>
       <c r="F434">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="G434" t="s">
         <v>7213</v>
@@ -44038,7 +44038,7 @@
         <v>7173</v>
       </c>
       <c r="F436">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G436" t="s">
         <v>7213</v>
@@ -44288,7 +44288,7 @@
         <v>7188</v>
       </c>
       <c r="F447">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G447" t="s">
         <v>7213</v>
@@ -44526,7 +44526,7 @@
         <v>7176</v>
       </c>
       <c r="F458">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G458" t="s">
         <v>7214</v>
@@ -44956,7 +44956,7 @@
         <v>7170</v>
       </c>
       <c r="F475">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G475" t="s">
         <v>7213</v>
@@ -45086,7 +45086,7 @@
         <v>7169</v>
       </c>
       <c r="F480">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="G480" t="s">
         <v>7213</v>
@@ -45190,7 +45190,7 @@
         <v>7181</v>
       </c>
       <c r="F484">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G484" t="s">
         <v>7213</v>
@@ -45216,7 +45216,7 @@
         <v>7181</v>
       </c>
       <c r="F485">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G485" t="s">
         <v>7213</v>
@@ -45242,7 +45242,7 @@
         <v>7181</v>
       </c>
       <c r="F486">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G486" t="s">
         <v>7213</v>
@@ -45268,7 +45268,7 @@
         <v>7176</v>
       </c>
       <c r="F487">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="G487" t="s">
         <v>7213</v>
@@ -45294,7 +45294,7 @@
         <v>7176</v>
       </c>
       <c r="F488">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G488" t="s">
         <v>7213</v>
@@ -45320,7 +45320,7 @@
         <v>7176</v>
       </c>
       <c r="F489">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G489" t="s">
         <v>7213</v>
@@ -45346,7 +45346,7 @@
         <v>7176</v>
       </c>
       <c r="F490">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G490" t="s">
         <v>7213</v>
@@ -45398,7 +45398,7 @@
         <v>7176</v>
       </c>
       <c r="F492">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="G492" t="s">
         <v>7213</v>
@@ -45640,7 +45640,7 @@
         <v>7181</v>
       </c>
       <c r="F502">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="G502" t="s">
         <v>7213</v>
@@ -45822,7 +45822,7 @@
         <v>7181</v>
       </c>
       <c r="F509">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G509" t="s">
         <v>7213</v>
@@ -46134,7 +46134,7 @@
         <v>7181</v>
       </c>
       <c r="F521">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G521" t="s">
         <v>7213</v>
@@ -46160,7 +46160,7 @@
         <v>7174</v>
       </c>
       <c r="F522">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G522" t="s">
         <v>7213</v>
@@ -46728,7 +46728,7 @@
         <v>7176</v>
       </c>
       <c r="F545">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="G545" t="s">
         <v>7213</v>
@@ -46754,7 +46754,7 @@
         <v>7176</v>
       </c>
       <c r="F546">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G546" t="s">
         <v>7213</v>
@@ -46832,7 +46832,7 @@
         <v>7176</v>
       </c>
       <c r="F549">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="G549" t="s">
         <v>7213</v>
@@ -46858,7 +46858,7 @@
         <v>7176</v>
       </c>
       <c r="F550">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G550" t="s">
         <v>7213</v>
@@ -46884,7 +46884,7 @@
         <v>7176</v>
       </c>
       <c r="F551">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G551" t="s">
         <v>7213</v>
@@ -47380,7 +47380,7 @@
         <v>7173</v>
       </c>
       <c r="F571">
-        <v>609</v>
+        <v>579</v>
       </c>
       <c r="G571" t="s">
         <v>7214</v>
@@ -47570,7 +47570,7 @@
         <v>7173</v>
       </c>
       <c r="F579">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G579" t="s">
         <v>7213</v>
@@ -47596,7 +47596,7 @@
         <v>7173</v>
       </c>
       <c r="F580">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G580" t="s">
         <v>7213</v>
@@ -48266,7 +48266,7 @@
         <v>7173</v>
       </c>
       <c r="F606">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G606" t="s">
         <v>7213</v>
@@ -48344,7 +48344,7 @@
         <v>7173</v>
       </c>
       <c r="F609">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="G609" t="s">
         <v>7213</v>
@@ -48370,7 +48370,7 @@
         <v>7173</v>
       </c>
       <c r="F610">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G610" t="s">
         <v>7213</v>
@@ -49564,7 +49564,7 @@
         <v>7184</v>
       </c>
       <c r="F658">
-        <v>3755</v>
+        <v>3753</v>
       </c>
       <c r="G658" t="s">
         <v>7213</v>
@@ -49616,7 +49616,7 @@
         <v>7200</v>
       </c>
       <c r="F660">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="G660" t="s">
         <v>7213</v>
@@ -49642,7 +49642,7 @@
         <v>7184</v>
       </c>
       <c r="F661">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="G661" t="s">
         <v>7213</v>
@@ -60126,7 +60126,7 @@
         <v>7191</v>
       </c>
       <c r="F1079">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G1079" t="s">
         <v>7213</v>
@@ -60758,7 +60758,7 @@
         <v>7191</v>
       </c>
       <c r="F1107">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G1107" t="s">
         <v>7213</v>
@@ -60804,7 +60804,7 @@
         <v>7175</v>
       </c>
       <c r="F1109">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G1109" t="s">
         <v>7214</v>
@@ -62418,7 +62418,7 @@
         <v>7207</v>
       </c>
       <c r="F1178">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G1178" t="s">
         <v>7213</v>
@@ -64517,7 +64517,7 @@
         <v>7173</v>
       </c>
       <c r="F1269">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G1269" t="s">
         <v>7213</v>
@@ -64751,7 +64751,7 @@
         <v>7186</v>
       </c>
       <c r="F1278">
-        <v>7218</v>
+        <v>7214</v>
       </c>
       <c r="G1278" t="s">
         <v>7213</v>
@@ -66565,7 +66565,7 @@
         <v>7173</v>
       </c>
       <c r="F1354">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G1354" t="s">
         <v>7213</v>
@@ -68799,7 +68799,7 @@
         <v>7171</v>
       </c>
       <c r="F1442">
-        <v>5759</v>
+        <v>5747</v>
       </c>
       <c r="G1442" t="s">
         <v>7213</v>
@@ -71135,7 +71135,7 @@
         <v>7173</v>
       </c>
       <c r="F1545">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G1545" t="s">
         <v>7213</v>
@@ -72697,7 +72697,7 @@
         <v>7209</v>
       </c>
       <c r="F1612">
-        <v>1702</v>
+        <v>1666</v>
       </c>
       <c r="G1612" t="s">
         <v>7213</v>
@@ -73399,7 +73399,7 @@
         <v>7209</v>
       </c>
       <c r="F1639">
-        <v>2300</v>
+        <v>2282</v>
       </c>
       <c r="G1639" t="s">
         <v>7213</v>
@@ -73979,7 +73979,7 @@
         <v>7209</v>
       </c>
       <c r="F1662">
-        <v>1426</v>
+        <v>1390</v>
       </c>
       <c r="G1662" t="s">
         <v>7213</v>
@@ -74005,7 +74005,7 @@
         <v>7209</v>
       </c>
       <c r="F1663">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="G1663" t="s">
         <v>7213</v>
@@ -76567,7 +76567,7 @@
         <v>7186</v>
       </c>
       <c r="F1762">
-        <v>8245</v>
+        <v>8227</v>
       </c>
       <c r="G1762" t="s">
         <v>7213</v>
@@ -76827,7 +76827,7 @@
         <v>7172</v>
       </c>
       <c r="F1772">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="G1772" t="s">
         <v>7213</v>
@@ -76957,7 +76957,7 @@
         <v>7182</v>
       </c>
       <c r="F1777">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G1777" t="s">
         <v>7213</v>
@@ -78625,7 +78625,7 @@
         <v>7171</v>
       </c>
       <c r="F1843">
-        <v>4563</v>
+        <v>4551</v>
       </c>
       <c r="G1843" t="s">
         <v>7213</v>
@@ -79295,7 +79295,7 @@
         <v>7207</v>
       </c>
       <c r="F1869">
-        <v>3061</v>
+        <v>3049</v>
       </c>
       <c r="G1869" t="s">
         <v>7213</v>
@@ -79321,7 +79321,7 @@
         <v>7207</v>
       </c>
       <c r="F1870">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="G1870" t="s">
         <v>7213</v>
@@ -79373,7 +79373,7 @@
         <v>7207</v>
       </c>
       <c r="F1872">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G1872" t="s">
         <v>7213</v>
@@ -79425,7 +79425,7 @@
         <v>7207</v>
       </c>
       <c r="F1874">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G1874" t="s">
         <v>7213</v>
@@ -79503,7 +79503,7 @@
         <v>7207</v>
       </c>
       <c r="F1877">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="G1877" t="s">
         <v>7213</v>
@@ -80467,7 +80467,7 @@
         <v>7180</v>
       </c>
       <c r="F1915">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="G1915" t="s">
         <v>7213</v>
@@ -84393,7 +84393,7 @@
         <v>7173</v>
       </c>
       <c r="F2072">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G2072" t="s">
         <v>7213</v>
@@ -86469,7 +86469,7 @@
         <v>7173</v>
       </c>
       <c r="F2156">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G2156" t="s">
         <v>7213</v>
@@ -86521,7 +86521,7 @@
         <v>7176</v>
       </c>
       <c r="F2158">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G2158" t="s">
         <v>7213</v>
@@ -88113,7 +88113,7 @@
         <v>7178</v>
       </c>
       <c r="F2225">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G2225" t="s">
         <v>7213</v>
@@ -88297,7 +88297,7 @@
         <v>7178</v>
       </c>
       <c r="F2233">
-        <v>30209</v>
+        <v>30179</v>
       </c>
       <c r="G2233" t="s">
         <v>7213</v>
@@ -88963,7 +88963,7 @@
         <v>7169</v>
       </c>
       <c r="F2260">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G2260" t="s">
         <v>7213</v>
@@ -89145,7 +89145,7 @@
         <v>7170</v>
       </c>
       <c r="F2267">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G2267" t="s">
         <v>7213</v>
@@ -89249,7 +89249,7 @@
         <v>7176</v>
       </c>
       <c r="F2271">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G2271" t="s">
         <v>7213</v>
@@ -89361,7 +89361,7 @@
         <v>7176</v>
       </c>
       <c r="F2276">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G2276" t="s">
         <v>7213</v>
@@ -89849,7 +89849,7 @@
         <v>7173</v>
       </c>
       <c r="F2295">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="G2295" t="s">
         <v>7213</v>
@@ -90025,7 +90025,7 @@
         <v>7176</v>
       </c>
       <c r="F2302">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G2302" t="s">
         <v>7213</v>
@@ -92035,7 +92035,7 @@
         <v>7169</v>
       </c>
       <c r="F2389">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G2389" t="s">
         <v>7214</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -43762,7 +43762,7 @@
         <v>7161</v>
       </c>
       <c r="F427">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G427" t="s">
         <v>7201</v>
@@ -43788,7 +43788,7 @@
         <v>7161</v>
       </c>
       <c r="F428">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G428" t="s">
         <v>7201</v>
@@ -84273,7 +84273,7 @@
         <v>7161</v>
       </c>
       <c r="F2069">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G2069" t="s">
         <v>7201</v>

--- a/products_images_report.xlsx
+++ b/products_images_report.xlsx
@@ -48255,7 +48255,7 @@
         <v>7153</v>
       </c>
       <c r="F608">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G608" t="s">
         <v>7192</v>
